--- a/BehaviourChangeTechniques/bcto.xlsx
+++ b/BehaviourChangeTechniques/bcto.xlsx
@@ -4412,7 +4412,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>A &lt;directly restructure the physical environment BCT&gt; that creates a more positive sensory experience while engaging in the behaviour.</t>
+          <t>A &lt;directly restructure the physical environment BCT&gt; that creates a more negative sensory experience while engaging in the behaviour.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>A &lt;directly restructure the physical environment BCT&gt; that creates a more negative sensory experience while engaging in the behaviour.</t>
+          <t>A &lt;directly restructure the physical environment BCT&gt; that creates a more positive sensory experience while engaging in the behaviour.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">

--- a/BehaviourChangeTechniques/bcto.xlsx
+++ b/BehaviourChangeTechniques/bcto.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T303"/>
+  <dimension ref="A1:T304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,7 +577,7 @@
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -619,7 +619,7 @@
           <t>behaviour change technique</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="n"/>
       <c r="M3" s="3" t="n"/>
       <c r="N3" s="3" t="inlineStr">
         <is>
@@ -6578,66 +6578,66 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050987</t>
+          <t>BCIO:051007</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>increase exposure to people doing the behaviour BCT</t>
+          <t>increase awareness of others disapproval BCT</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>A &lt;restructure the social environment BCT&gt; that involves increasing exposure of the person to other people doing the behaviour.</t>
+          <t>An &lt;awareness of other people's thoughts, feelings and actions BCT&gt; that increases awareness of whether others will dislike or disapprove of the behaviour.</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>restructure the social environment BCT</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="n"/>
-      <c r="F107" s="2" t="n"/>
-      <c r="G107" s="2" t="n"/>
-      <c r="H107" s="2" t="n"/>
-      <c r="I107" s="2" t="n"/>
-      <c r="J107" s="2" t="n"/>
-      <c r="K107" s="2" t="n"/>
-      <c r="L107" s="2" t="n"/>
-      <c r="M107" s="2" t="n"/>
+          <t>awareness of other peoples thoughts, feelings and actions BCT</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr"/>
       <c r="N107" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="O107" s="2" t="n"/>
-      <c r="P107" s="2" t="n"/>
-      <c r="Q107" s="2" t="n"/>
-      <c r="R107" s="2" t="n"/>
+      <c r="O107" s="2" t="inlineStr"/>
+      <c r="P107" s="2" t="inlineStr"/>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
       <c r="S107" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T107" s="2" t="n"/>
+      <c r="T107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050988</t>
+          <t>BCIO:050987</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>increase financial affordability BCT</t>
+          <t>increase exposure to people doing the behaviour BCT</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>A &lt;restructure the physical environment BCT&gt; that reduces the financial cost of the behaviour relative to the person’s access to financial resources.</t>
+          <t>A &lt;restructure the social environment BCT&gt; that involves increasing exposure of the person to other people doing the behaviour.</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>restructure the physical environment BCT</t>
+          <t>restructure the social environment BCT</t>
         </is>
       </c>
       <c r="E108" s="2" t="n"/>
@@ -6664,106 +6664,84 @@
       <c r="T108" s="2" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="inlineStr">
-        <is>
-          <t>BCIO:007175</t>
-        </is>
-      </c>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>increase salience of behaviour BCT</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="inlineStr">
-        <is>
-          <t>An &lt;increase awareness of behaviour BCT&gt; that makes the possibility of performing the behaviour more distinctive or prominent.</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>increase awareness of behaviour BCT</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="n"/>
-      <c r="F109" s="3" t="n"/>
-      <c r="G109" s="3" t="n"/>
-      <c r="H109" s="3" t="inlineStr">
-        <is>
-          <t>salience of behaviour</t>
-        </is>
-      </c>
-      <c r="I109" s="3" t="inlineStr">
-        <is>
-          <t>Mask use at the start of the Covid pandemic through symbols/signs of masks in public spaces</t>
-        </is>
-      </c>
-      <c r="J109" s="3" t="n"/>
-      <c r="K109" s="3" t="inlineStr">
-        <is>
-          <t>behaviour change technique</t>
-        </is>
-      </c>
-      <c r="L109" s="3" t="n"/>
-      <c r="M109" s="3" t="n"/>
-      <c r="N109" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="O109" s="3" t="n"/>
-      <c r="P109" s="3" t="n"/>
-      <c r="Q109" s="3" t="n"/>
-      <c r="R109" s="3" t="inlineStr">
-        <is>
-          <t>lz; LZ</t>
-        </is>
-      </c>
-      <c r="S109" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T109" s="3" t="n"/>
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:050988</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>increase financial affordability BCT</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>A &lt;restructure the physical environment BCT&gt; that reduces the financial cost of the behaviour relative to the person’s access to financial resources.</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>restructure the physical environment BCT</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="n"/>
+      <c r="F109" s="2" t="n"/>
+      <c r="G109" s="2" t="n"/>
+      <c r="H109" s="2" t="n"/>
+      <c r="I109" s="2" t="n"/>
+      <c r="J109" s="2" t="n"/>
+      <c r="K109" s="2" t="n"/>
+      <c r="L109" s="2" t="n"/>
+      <c r="M109" s="2" t="n"/>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="n"/>
+      <c r="P109" s="2" t="n"/>
+      <c r="Q109" s="2" t="n"/>
+      <c r="R109" s="2" t="n"/>
+      <c r="S109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" s="2" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007068</t>
+          <t>BCIO:007175</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">increase salience of consequences BCT </t>
+          <t>increase salience of behaviour BCT</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">An &lt;awareness of consequences BCT&gt; that changes behaviour by the source emphasising the consequences of performing a behaviour to the person in a way that makes them memorable. </t>
+          <t>An &lt;increase awareness of behaviour BCT&gt; that makes the possibility of performing the behaviour more distinctive or prominent.</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>increase awareness of consequences BCT</t>
+          <t>increase awareness of behaviour BCT</t>
         </is>
       </c>
       <c r="E110" s="3" t="n"/>
       <c r="F110" s="3" t="n"/>
-      <c r="G110" s="3" t="inlineStr">
-        <is>
-          <t>BCT5.2 Salience of consequences</t>
-        </is>
-      </c>
+      <c r="G110" s="3" t="n"/>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>significance of outcomes, importance of consequences, relevance of results</t>
-        </is>
-      </c>
-      <c r="I110" s="3" t="n"/>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>Consider also coding one of "inform about health consequences", "inform about emotional consequences",  "inform about social consequences", or their child classes</t>
-        </is>
-      </c>
+          <t>salience of behaviour</t>
+        </is>
+      </c>
+      <c r="I110" s="3" t="inlineStr">
+        <is>
+          <t>Mask use at the start of the Covid pandemic through symbols/signs of masks in public spaces</t>
+        </is>
+      </c>
+      <c r="J110" s="3" t="n"/>
       <c r="K110" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -6792,134 +6770,146 @@
       <c r="T110" s="3" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:007068</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">increase salience of consequences BCT </t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An &lt;awareness of consequences BCT&gt; that changes behaviour by the source emphasising the consequences of performing a behaviour to the person in a way that makes them memorable. </t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>increase awareness of consequences BCT</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="n"/>
+      <c r="F111" s="3" t="n"/>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>BCT5.2 Salience of consequences</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>significance of outcomes, importance of consequences, relevance of results</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="n"/>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>Consider also coding one of "inform about health consequences", "inform about emotional consequences",  "inform about social consequences", or their child classes</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="n"/>
+      <c r="M111" s="3" t="n"/>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O111" s="3" t="n"/>
+      <c r="P111" s="3" t="n"/>
+      <c r="Q111" s="3" t="n"/>
+      <c r="R111" s="3" t="inlineStr">
+        <is>
+          <t>lz; LZ</t>
+        </is>
+      </c>
+      <c r="S111" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T111" s="3" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>BCIO:050989</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>increase salience of social rule BCT</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>An &lt;awareness of other peoples thoughts, feelings and actions BCT&gt; that involves increasing the salience of a social rule concerning the behaviour.</t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>awareness of other peoples thoughts, feelings and actions BCT</t>
         </is>
       </c>
-      <c r="E111" s="2" t="n"/>
-      <c r="F111" s="2" t="n"/>
-      <c r="G111" s="2" t="n"/>
-      <c r="H111" s="2" t="n"/>
-      <c r="I111" s="2" t="n"/>
-      <c r="J111" s="2" t="n"/>
-      <c r="K111" s="2" t="n"/>
-      <c r="L111" s="2" t="n"/>
-      <c r="M111" s="2" t="n"/>
-      <c r="N111" s="2" t="inlineStr">
+      <c r="E112" s="2" t="n"/>
+      <c r="F112" s="2" t="n"/>
+      <c r="G112" s="2" t="n"/>
+      <c r="H112" s="2" t="n"/>
+      <c r="I112" s="2" t="n"/>
+      <c r="J112" s="2" t="n"/>
+      <c r="K112" s="2" t="n"/>
+      <c r="L112" s="2" t="n"/>
+      <c r="M112" s="2" t="n"/>
+      <c r="N112" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="O111" s="2" t="n"/>
-      <c r="P111" s="2" t="n"/>
-      <c r="Q111" s="2" t="n"/>
-      <c r="R111" s="2" t="n"/>
-      <c r="S111" s="2" t="n">
+      <c r="O112" s="2" t="n"/>
+      <c r="P112" s="2" t="n"/>
+      <c r="Q112" s="2" t="n"/>
+      <c r="R112" s="2" t="n"/>
+      <c r="S112" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T111" s="2" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="3" t="inlineStr">
-        <is>
-          <t>BCIO:007152</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">indirectly restructure the physical environment BCT </t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="inlineStr">
-        <is>
-          <t>A &lt;restructure the physical environment BCT&gt; that changes the person's environment at a time or location other than when and where the behaviour is performed.</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>restructure the physical environment BCT</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="n"/>
-      <c r="F112" s="3" t="n"/>
-      <c r="G112" s="3" t="n"/>
-      <c r="H112" s="3" t="n"/>
-      <c r="I112" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Example 1: Putting cigarette packs out of sight in shops in order to promote smoking cessation or reduce smoking uptake
-Example 2: Introducing safe cycle routes in residential neighbourhood to increase frequency of initiating journeys from home by bicycle. </t>
-        </is>
-      </c>
-      <c r="J112" s="3" t="n"/>
-      <c r="K112" s="3" t="inlineStr">
-        <is>
-          <t>behaviour change technique</t>
-        </is>
-      </c>
-      <c r="L112" s="3" t="n"/>
-      <c r="M112" s="3" t="n"/>
-      <c r="N112" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="O112" s="3" t="n"/>
-      <c r="P112" s="3" t="n"/>
-      <c r="Q112" s="3" t="n"/>
-      <c r="R112" s="3" t="inlineStr">
-        <is>
-          <t>LZ</t>
-        </is>
-      </c>
-      <c r="S112" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T112" s="3" t="n"/>
+      <c r="T112" s="2" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>BCIO:050347</t>
+          <t>BCIO:007152</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">indirectly restructure the social environment BCT </t>
+          <t xml:space="preserve">indirectly restructure the physical environment BCT </t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A &lt;restructure the social environment BCT&gt; that changes the person's environment at a time or location other than when and where the behaviour is performed. </t>
+          <t>A &lt;restructure the physical environment BCT&gt; that changes the person's environment at a time or location other than when and where the behaviour is performed.</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>restructure the social environment BCT</t>
+          <t>restructure the physical environment BCT</t>
         </is>
       </c>
       <c r="E113" s="3" t="n"/>
       <c r="F113" s="3" t="n"/>
       <c r="G113" s="3" t="n"/>
       <c r="H113" s="3" t="n"/>
-      <c r="I113" s="3" t="n"/>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Example 1: Putting cigarette packs out of sight in shops in order to promote smoking cessation or reduce smoking uptake
+Example 2: Introducing safe cycle routes in residential neighbourhood to increase frequency of initiating journeys from home by bicycle. </t>
+        </is>
+      </c>
       <c r="J113" s="3" t="n"/>
       <c r="K113" s="3" t="inlineStr">
         <is>
@@ -6951,38 +6941,30 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007067</t>
+          <t>BCIO:050347</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">induce anticipated regret BCT </t>
+          <t xml:space="preserve">indirectly restructure the social environment BCT </t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>An &lt;inform about emotional consequences BCT&gt; that focuses on expectations of remorse after performing or not performing the behaviour.</t>
+          <t xml:space="preserve">A &lt;restructure the social environment BCT&gt; that changes the person's environment at a time or location other than when and where the behaviour is performed. </t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about emotional consequences BCT </t>
+          <t>restructure the social environment BCT</t>
         </is>
       </c>
       <c r="E114" s="3" t="n"/>
       <c r="F114" s="3" t="n"/>
-      <c r="G114" s="3" t="inlineStr">
-        <is>
-          <t>BCT5.5 Anticipated regret</t>
-        </is>
-      </c>
+      <c r="G114" s="3" t="n"/>
       <c r="H114" s="3" t="n"/>
       <c r="I114" s="3" t="n"/>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>If suggests adoption of a perspective or new perspective in order to change cognitions also code 'suggest different perspective on behaviour BCT' or one of its child classes</t>
-        </is>
-      </c>
+      <c r="J114" s="3" t="n"/>
       <c r="K114" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -7000,7 +6982,7 @@
       <c r="Q114" s="3" t="n"/>
       <c r="R114" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S114" s="3" t="inlineStr">
@@ -7013,38 +6995,38 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007052</t>
+          <t>BCIO:007067</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about antecedents BCT </t>
+          <t xml:space="preserve">induce anticipated regret BCT </t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>A &lt;suggest different perspective on behaviour BCT&gt; that involves providing factual information to the person regarding triggers or influences that precede the initiation of the behaviour.</t>
+          <t>An &lt;inform about emotional consequences BCT&gt; that focuses on expectations of remorse after performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>suggest different perspective on behaviour BCT</t>
+          <t xml:space="preserve">inform about emotional consequences BCT </t>
         </is>
       </c>
       <c r="E115" s="3" t="n"/>
       <c r="F115" s="3" t="n"/>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>BCT4.2 Information about antecedents</t>
-        </is>
-      </c>
-      <c r="H115" s="3" t="inlineStr">
-        <is>
-          <t>trigger recognition, understanding of antecedents</t>
-        </is>
-      </c>
+          <t>BCT5.5 Anticipated regret</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="n"/>
       <c r="I115" s="3" t="n"/>
-      <c r="J115" s="3" t="n"/>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>If suggests adoption of a perspective or new perspective in order to change cognitions also code 'suggest different perspective on behaviour BCT' or one of its child classes</t>
+        </is>
+      </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -7075,42 +7057,38 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007065</t>
+          <t>BCIO:007052</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about emotional consequences BCT </t>
+          <t xml:space="preserve">inform about antecedents BCT </t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>An &lt;increase awareness of consequences BCT&gt; that provides information about the emotional consequences of performing or not performing the behaviour.</t>
+          <t>A &lt;suggest different perspective on behaviour BCT&gt; that involves providing factual information to the person regarding triggers or influences that precede the initiation of the behaviour.</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>increase awareness of consequences BCT</t>
+          <t>suggest different perspective on behaviour BCT</t>
         </is>
       </c>
       <c r="E116" s="3" t="n"/>
       <c r="F116" s="3" t="n"/>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BCT5.6 Information about emotional consequences</t>
+          <t>BCT4.2 Information about antecedents</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>affective outcomes, emotional effects, consequences on emotions</t>
+          <t>trigger recognition, understanding of antecedents</t>
         </is>
       </c>
       <c r="I116" s="3" t="n"/>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>Consequences can be for any target, not just the recipient(s) of the intervention; emphasising importance of consequences is not sufficient. Consequences can be related to emotional health disorders (e.g. depression, anxiety) and/or states of mind (e.g. low mood, stress).</t>
-        </is>
-      </c>
+      <c r="J116" s="3" t="n"/>
       <c r="K116" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -7141,17 +7119,17 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007176</t>
+          <t>BCIO:007065</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>inform about environmental consequences BCT</t>
+          <t xml:space="preserve">inform about emotional consequences BCT </t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>An &lt;increase awareness of consequences BCT&gt; that provides information about the environmental consequences of performing or not performing the behaviour.</t>
+          <t>An &lt;increase awareness of consequences BCT&gt; that provides information about the emotional consequences of performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
@@ -7163,18 +7141,18 @@
       <c r="F117" s="3" t="n"/>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>BCT5.3 Information about social and environmental consequences</t>
+          <t xml:space="preserve"> BCT5.6 Information about emotional consequences</t>
         </is>
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
-          <t>environmental effects, ecological impacts</t>
+          <t>affective outcomes, emotional effects, consequences on emotions</t>
         </is>
       </c>
       <c r="I117" s="3" t="n"/>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>Consequences can be for any target, not just the recipient(s) of the intervention; emphasising importance of consequences is not sufficient.</t>
+          <t>Consequences can be for any target, not just the recipient(s) of the intervention; emphasising importance of consequences is not sufficient. Consequences can be related to emotional health disorders (e.g. depression, anxiety) and/or states of mind (e.g. low mood, stress).</t>
         </is>
       </c>
       <c r="K117" s="3" t="inlineStr">
@@ -7207,17 +7185,17 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007063</t>
+          <t>BCIO:007176</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about health consequences BCT </t>
+          <t>inform about environmental consequences BCT</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>An &lt;increase awareness of consequences BCT&gt; that provides information about the physical or mental health consequences of performing or not performing the behaviour.</t>
+          <t>An &lt;increase awareness of consequences BCT&gt; that provides information about the environmental consequences of performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
@@ -7229,12 +7207,12 @@
       <c r="F118" s="3" t="n"/>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>BCT5.1 Information about health consequences</t>
+          <t>BCT5.3 Information about social and environmental consequences</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>consequences for well-being, health effects, wellness outcomes</t>
+          <t>environmental effects, ecological impacts</t>
         </is>
       </c>
       <c r="I118" s="3" t="n"/>
@@ -7273,17 +7251,17 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>BCIO:050559</t>
+          <t>BCIO:007063</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>inform about negative consequences BCT</t>
+          <t xml:space="preserve">inform about health consequences BCT </t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>An &lt;increase awareness of consequences BCT&gt; that provides information about the negative consequences of performing or not performing the behaviour.</t>
+          <t>An &lt;increase awareness of consequences BCT&gt; that provides information about the physical or mental health consequences of performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -7291,18 +7269,22 @@
           <t>increase awareness of consequences BCT</t>
         </is>
       </c>
-      <c r="E119" s="3" t="inlineStr">
-        <is>
-          <t>'inform about negative emotional consequences BCT' OR 'inform about negative environmental consequences BCT' OR 'inform about negative health consequences BCT' OR 'inform about negative social consequences BCT'</t>
-        </is>
-      </c>
+      <c r="E119" s="3" t="n"/>
       <c r="F119" s="3" t="n"/>
-      <c r="G119" s="3" t="n"/>
-      <c r="H119" s="3" t="n"/>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>BCT5.1 Information about health consequences</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>consequences for well-being, health effects, wellness outcomes</t>
+        </is>
+      </c>
       <c r="I119" s="3" t="n"/>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>Preferable to use the more specific child classes.</t>
+          <t>Consequences can be for any target, not just the recipient(s) of the intervention; emphasising importance of consequences is not sufficient.</t>
         </is>
       </c>
       <c r="K119" s="3" t="inlineStr">
@@ -7322,7 +7304,7 @@
       <c r="Q119" s="3" t="n"/>
       <c r="R119" s="3" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S119" s="3" t="inlineStr">
@@ -7335,30 +7317,38 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007177</t>
+          <t>BCIO:050559</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about negative emotional consequences BCT </t>
+          <t>inform about negative consequences BCT</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>An &lt;inform about emotional consequences BCT&gt; that provides information about the negative emotional consequences of performing or not performing the behaviour.</t>
+          <t>An &lt;increase awareness of consequences BCT&gt; that provides information about the negative consequences of performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about emotional consequences BCT </t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="n"/>
+          <t>increase awareness of consequences BCT</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>'inform about negative emotional consequences BCT' OR 'inform about negative environmental consequences BCT' OR 'inform about negative health consequences BCT' OR 'inform about negative social consequences BCT'</t>
+        </is>
+      </c>
       <c r="F120" s="3" t="n"/>
       <c r="G120" s="3" t="n"/>
       <c r="H120" s="3" t="n"/>
       <c r="I120" s="3" t="n"/>
-      <c r="J120" s="3" t="n"/>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>Preferable to use the more specific child classes.</t>
+        </is>
+      </c>
       <c r="K120" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -7376,7 +7366,7 @@
       <c r="Q120" s="3" t="n"/>
       <c r="R120" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>PS</t>
         </is>
       </c>
       <c r="S120" s="3" t="inlineStr">
@@ -7389,22 +7379,22 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007178</t>
+          <t>BCIO:007177</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>inform about negative environmental consequences BCT</t>
+          <t xml:space="preserve">inform about negative emotional consequences BCT </t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>An &lt;inform about environmental consequences BCT&gt; that provides information about the negative environmental consequences of performing or not performing the behaviour.</t>
+          <t>An &lt;inform about emotional consequences BCT&gt; that provides information about the negative emotional consequences of performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>inform about environmental consequences BCT</t>
+          <t xml:space="preserve">inform about emotional consequences BCT </t>
         </is>
       </c>
       <c r="E121" s="3" t="n"/>
@@ -7430,7 +7420,7 @@
       <c r="Q121" s="3" t="n"/>
       <c r="R121" s="3" t="inlineStr">
         <is>
-          <t>lz; RW; LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S121" s="3" t="inlineStr">
@@ -7443,22 +7433,22 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007179</t>
+          <t>BCIO:007178</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>inform about negative health consequences BCT</t>
+          <t>inform about negative environmental consequences BCT</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>An &lt;inform about health consequences BCT&gt; that provides information about the negative physical or mental health consequences of performing or not performing the behaviour.</t>
+          <t>An &lt;inform about environmental consequences BCT&gt; that provides information about the negative environmental consequences of performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about health consequences BCT </t>
+          <t>inform about environmental consequences BCT</t>
         </is>
       </c>
       <c r="E122" s="3" t="n"/>
@@ -7497,22 +7487,22 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007180</t>
+          <t>BCIO:007179</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>inform about negative social consequences BCT</t>
+          <t>inform about negative health consequences BCT</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>An &lt;inform about social consequences BCT&gt; that provides information about the negative social consequences of performing or not performing the behaviour.</t>
+          <t>An &lt;inform about health consequences BCT&gt; that provides information about the negative physical or mental health consequences of performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about social consequences BCT </t>
+          <t xml:space="preserve">inform about health consequences BCT </t>
         </is>
       </c>
       <c r="E123" s="3" t="n"/>
@@ -7551,22 +7541,22 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007181</t>
+          <t>BCIO:007180</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about positive emotional consequences BCT </t>
+          <t>inform about negative social consequences BCT</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>An &lt;inform about emotional consequences BCT&gt; that provides information about the positive emotional consequences of performing or not performing the behaviour.</t>
+          <t>An &lt;inform about social consequences BCT&gt; that provides information about the negative social consequences of performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about emotional consequences BCT </t>
+          <t xml:space="preserve">inform about social consequences BCT </t>
         </is>
       </c>
       <c r="E124" s="3" t="n"/>
@@ -7592,7 +7582,7 @@
       <c r="Q124" s="3" t="n"/>
       <c r="R124" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>lz; RW; LZ</t>
         </is>
       </c>
       <c r="S124" s="3" t="inlineStr">
@@ -7605,22 +7595,22 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007182</t>
+          <t>BCIO:007181</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about positive environmental consequences BCT </t>
+          <t xml:space="preserve">inform about positive emotional consequences BCT </t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>An &lt;inform about environmental consequences BCT&gt; that provides information about the positive environmental consequences of performing or not performing the behaviour.</t>
+          <t>An &lt;inform about emotional consequences BCT&gt; that provides information about the positive emotional consequences of performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>inform about environmental consequences BCT</t>
+          <t xml:space="preserve">inform about emotional consequences BCT </t>
         </is>
       </c>
       <c r="E125" s="3" t="n"/>
@@ -7659,22 +7649,22 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007183</t>
+          <t>BCIO:007182</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about positive health consequences BCT </t>
+          <t xml:space="preserve">inform about positive environmental consequences BCT </t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>An &lt;inform about health consequences BCT&gt; that provides information about the positive physical or mental health consequences of performing or not performing the behaviour.</t>
+          <t>An &lt;inform about environmental consequences BCT&gt; that provides information about the positive environmental consequences of performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about health consequences BCT </t>
+          <t>inform about environmental consequences BCT</t>
         </is>
       </c>
       <c r="E126" s="3" t="n"/>
@@ -7713,22 +7703,22 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007184</t>
+          <t>BCIO:007183</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about positive social consequences BCT </t>
+          <t xml:space="preserve">inform about positive health consequences BCT </t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>An &lt;inform about social consequences BCT&gt; that provides information about the positive social consequences of performing or not performing the behaviour.</t>
+          <t>An &lt;inform about health consequences BCT&gt; that provides information about the positive physical or mental health consequences of performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about social consequences BCT </t>
+          <t xml:space="preserve">inform about health consequences BCT </t>
         </is>
       </c>
       <c r="E127" s="3" t="n"/>
@@ -7767,42 +7757,30 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007064</t>
+          <t>BCIO:007184</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">inform about positive social consequences BCT </t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>An &lt;inform about social consequences BCT&gt; that provides information about the positive social consequences of performing or not performing the behaviour.</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">inform about social consequences BCT </t>
-        </is>
-      </c>
-      <c r="C128" s="3" t="inlineStr">
-        <is>
-          <t>An &lt;increase awareness of consequences BCT&gt; that provides information about the social consequences of performing or not performing the behaviour.</t>
-        </is>
-      </c>
-      <c r="D128" s="3" t="inlineStr">
-        <is>
-          <t>increase awareness of consequences BCT</t>
         </is>
       </c>
       <c r="E128" s="3" t="n"/>
       <c r="F128" s="3" t="n"/>
-      <c r="G128" s="3" t="inlineStr">
-        <is>
-          <t>BCT5.3 Information about social and environmental consequences</t>
-        </is>
-      </c>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>social effects, community repercussions</t>
-        </is>
-      </c>
+      <c r="G128" s="3" t="n"/>
+      <c r="H128" s="3" t="n"/>
       <c r="I128" s="3" t="n"/>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>Consequences can be for any target, not just the recipient(s) of the intervention; emphasising importance of consequences is not sufficient.</t>
-        </is>
-      </c>
+      <c r="J128" s="3" t="n"/>
       <c r="K128" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -7831,144 +7809,152 @@
       <c r="T128" s="3" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:007064</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inform about social consequences BCT </t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>An &lt;increase awareness of consequences BCT&gt; that provides information about the social consequences of performing or not performing the behaviour.</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>increase awareness of consequences BCT</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="n"/>
+      <c r="F129" s="3" t="n"/>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>BCT5.3 Information about social and environmental consequences</t>
+        </is>
+      </c>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>social effects, community repercussions</t>
+        </is>
+      </c>
+      <c r="I129" s="3" t="n"/>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>Consequences can be for any target, not just the recipient(s) of the intervention; emphasising importance of consequences is not sufficient.</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="L129" s="3" t="n"/>
+      <c r="M129" s="3" t="n"/>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O129" s="3" t="n"/>
+      <c r="P129" s="3" t="n"/>
+      <c r="Q129" s="3" t="n"/>
+      <c r="R129" s="3" t="inlineStr">
+        <is>
+          <t>lz; LZ</t>
+        </is>
+      </c>
+      <c r="S129" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T129" s="3" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>BCIO:050990</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>inform about social rule BCT</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
         <is>
           <t>An &lt;awareness of other peoples thoughts, feelings and actions BCT&gt; that involves informing the person about a social rule regarding the behaviour.</t>
         </is>
       </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>awareness of other peoples thoughts, feelings and actions BCT</t>
         </is>
       </c>
-      <c r="E129" s="2" t="n"/>
-      <c r="F129" s="2" t="n"/>
-      <c r="G129" s="2" t="n"/>
-      <c r="H129" s="2" t="n"/>
-      <c r="I129" s="2" t="n"/>
-      <c r="J129" s="2" t="n"/>
-      <c r="K129" s="2" t="n"/>
-      <c r="L129" s="2" t="n"/>
-      <c r="M129" s="2" t="n"/>
-      <c r="N129" s="2" t="inlineStr">
+      <c r="E130" s="2" t="n"/>
+      <c r="F130" s="2" t="n"/>
+      <c r="G130" s="2" t="n"/>
+      <c r="H130" s="2" t="n"/>
+      <c r="I130" s="2" t="n"/>
+      <c r="J130" s="2" t="n"/>
+      <c r="K130" s="2" t="n"/>
+      <c r="L130" s="2" t="n"/>
+      <c r="M130" s="2" t="n"/>
+      <c r="N130" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="O129" s="2" t="n"/>
-      <c r="P129" s="2" t="n"/>
-      <c r="Q129" s="2" t="n"/>
-      <c r="R129" s="2" t="n"/>
-      <c r="S129" s="2" t="n">
+      <c r="O130" s="2" t="n"/>
+      <c r="P130" s="2" t="n"/>
+      <c r="Q130" s="2" t="n"/>
+      <c r="R130" s="2" t="n"/>
+      <c r="S130" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T129" s="2" t="n"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="3" t="inlineStr">
-        <is>
-          <t>BCIO:007058</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>instruct how to perform a behaviour BCT</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="inlineStr">
-        <is>
-          <t>A &lt;guide how to perform behaviour BCT&gt; that involves telling the person how to perform the behaviour.</t>
-        </is>
-      </c>
-      <c r="D130" s="3" t="inlineStr">
-        <is>
-          <t>guide how to perform behaviour BCT</t>
-        </is>
-      </c>
-      <c r="E130" s="3" t="n"/>
-      <c r="F130" s="3" t="n"/>
-      <c r="G130" s="3" t="inlineStr">
-        <is>
-          <t>BCT4.1 Instruction on how to perform a behaviour</t>
-        </is>
-      </c>
-      <c r="H130" s="3" t="inlineStr">
-        <is>
-          <t>skills training, instruction</t>
-        </is>
-      </c>
-      <c r="I130" s="3" t="n"/>
-      <c r="J130" s="3" t="inlineStr">
-        <is>
-          <t>When the person attends classes such as exercise or cookery, code 'instruct how to perform behaviour BCT', 'practise behaviour BCT', and 'demonstrate the behaviour BCT'.</t>
-        </is>
-      </c>
-      <c r="K130" s="3" t="inlineStr">
-        <is>
-          <t>behaviour change technique</t>
-        </is>
-      </c>
-      <c r="L130" s="3" t="n"/>
-      <c r="M130" s="3" t="n"/>
-      <c r="N130" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="O130" s="3" t="n"/>
-      <c r="P130" s="3" t="n"/>
-      <c r="Q130" s="3" t="n"/>
-      <c r="R130" s="3" t="inlineStr">
-        <is>
-          <t>lz; LZ</t>
-        </is>
-      </c>
-      <c r="S130" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T130" s="3" t="n"/>
+      <c r="T130" s="2" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007122</t>
+          <t>BCIO:007058</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>make a goal public BCT</t>
+          <t>instruct how to perform a behaviour BCT</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>A &lt;goal directed BCT&gt; that involves the person communicating their intention to achieve a goal.</t>
+          <t>A &lt;guide how to perform behaviour BCT&gt; that involves telling the person how to perform the behaviour.</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>goal directed BCT</t>
+          <t>guide how to perform behaviour BCT</t>
         </is>
       </c>
       <c r="E131" s="3" t="n"/>
       <c r="F131" s="3" t="n"/>
-      <c r="G131" s="3" t="n"/>
-      <c r="H131" s="3" t="n"/>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>BCT4.1 Instruction on how to perform a behaviour</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>skills training, instruction</t>
+        </is>
+      </c>
       <c r="I131" s="3" t="n"/>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>The goal being made public can be in terms of behaviour (e.g. to walk for 30 minutes a day) or an outcome of behaviour (e.g. to lose 5kg of body weight)</t>
+          <t>When the person attends classes such as exercise or cookery, code 'instruct how to perform behaviour BCT', 'practise behaviour BCT', and 'demonstrate the behaviour BCT'.</t>
         </is>
       </c>
       <c r="K131" s="3" t="inlineStr">
@@ -8001,22 +7987,22 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007185</t>
+          <t>BCIO:007122</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>manage mental processes BCT</t>
+          <t>make a goal public BCT</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A &lt;behaviour change technique&gt; that advises how to manage mental processes to facilitate the behaviour. </t>
+          <t>A &lt;goal directed BCT&gt; that involves the person communicating their intention to achieve a goal.</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>behaviour change technique</t>
+          <t>goal directed BCT</t>
         </is>
       </c>
       <c r="E132" s="3" t="n"/>
@@ -8026,7 +8012,7 @@
       <c r="I132" s="3" t="n"/>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>A mental process is something that occurs in the brain, and that can of itself be conscious, or can give rise to a process that can of itself be conscious or can give rise to behaviour.</t>
+          <t>The goal being made public can be in terms of behaviour (e.g. to walk for 30 minutes a day) or an outcome of behaviour (e.g. to lose 5kg of body weight)</t>
         </is>
       </c>
       <c r="K132" s="3" t="inlineStr">
@@ -8057,131 +8043,135 @@
       <c r="T132" s="3" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:007185</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>manage mental processes BCT</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A &lt;behaviour change technique&gt; that advises how to manage mental processes to facilitate the behaviour. </t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="n"/>
+      <c r="F133" s="3" t="n"/>
+      <c r="G133" s="3" t="n"/>
+      <c r="H133" s="3" t="n"/>
+      <c r="I133" s="3" t="n"/>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>A mental process is something that occurs in the brain, and that can of itself be conscious, or can give rise to a process that can of itself be conscious or can give rise to behaviour.</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="L133" s="3" t="n"/>
+      <c r="M133" s="3" t="n"/>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O133" s="3" t="n"/>
+      <c r="P133" s="3" t="n"/>
+      <c r="Q133" s="3" t="n"/>
+      <c r="R133" s="3" t="inlineStr">
+        <is>
+          <t>lz; LZ</t>
+        </is>
+      </c>
+      <c r="S133" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T133" s="3" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>BCIO:050991</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>modify objects in the environment BCT</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
         <is>
           <t>A &lt;restructure the physical environment BCT&gt; that modifies objects in the person’s physical surroundings.</t>
         </is>
       </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>restructure the physical environment BCT</t>
         </is>
       </c>
-      <c r="E133" s="2" t="n"/>
-      <c r="F133" s="2" t="n"/>
-      <c r="G133" s="2" t="n"/>
-      <c r="H133" s="2" t="n"/>
-      <c r="I133" s="2" t="n"/>
-      <c r="J133" s="2" t="n"/>
-      <c r="K133" s="2" t="n"/>
-      <c r="L133" s="2" t="n"/>
-      <c r="M133" s="2" t="n"/>
-      <c r="N133" s="2" t="inlineStr">
+      <c r="E134" s="2" t="n"/>
+      <c r="F134" s="2" t="n"/>
+      <c r="G134" s="2" t="n"/>
+      <c r="H134" s="2" t="n"/>
+      <c r="I134" s="2" t="n"/>
+      <c r="J134" s="2" t="n"/>
+      <c r="K134" s="2" t="n"/>
+      <c r="L134" s="2" t="n"/>
+      <c r="M134" s="2" t="n"/>
+      <c r="N134" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="O133" s="2" t="n"/>
-      <c r="P133" s="2" t="n"/>
-      <c r="Q133" s="2" t="n"/>
-      <c r="R133" s="2" t="n"/>
-      <c r="S133" s="2" t="n">
+      <c r="O134" s="2" t="n"/>
+      <c r="P134" s="2" t="n"/>
+      <c r="Q134" s="2" t="n"/>
+      <c r="R134" s="2" t="n"/>
+      <c r="S134" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T133" s="2" t="n"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="3" t="inlineStr">
-        <is>
-          <t>BCIO:007066</t>
-        </is>
-      </c>
-      <c r="B134" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">monitor emotional consequences BCT </t>
-        </is>
-      </c>
-      <c r="C134" s="3" t="inlineStr">
-        <is>
-          <t>A &lt;monitoring BCT&gt; that involves the person assessing their emotions after performing the behaviour.</t>
-        </is>
-      </c>
-      <c r="D134" s="3" t="inlineStr">
-        <is>
-          <t>monitoring BCT</t>
-        </is>
-      </c>
-      <c r="E134" s="3" t="n"/>
-      <c r="F134" s="3" t="n"/>
-      <c r="G134" s="3" t="inlineStr">
-        <is>
-          <t>BCT5.4 Monitoring of emotional consequences</t>
-        </is>
-      </c>
-      <c r="H134" s="3" t="n"/>
-      <c r="I134" s="3" t="n"/>
-      <c r="J134" s="3" t="n"/>
-      <c r="K134" s="3" t="inlineStr">
-        <is>
-          <t>behaviour change technique</t>
-        </is>
-      </c>
-      <c r="L134" s="3" t="n"/>
-      <c r="M134" s="3" t="n"/>
-      <c r="N134" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="O134" s="3" t="n"/>
-      <c r="P134" s="3" t="n"/>
-      <c r="Q134" s="3" t="n"/>
-      <c r="R134" s="3" t="inlineStr">
-        <is>
-          <t>LZ</t>
-        </is>
-      </c>
-      <c r="S134" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T134" s="3" t="n"/>
+      <c r="T134" s="2" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007017</t>
+          <t>BCIO:007066</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">monitor emotional consequences BCT </t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>A &lt;monitoring BCT&gt; that involves the person assessing their emotions after performing the behaviour.</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
           <t>monitoring BCT</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A &lt;behaviour change technique&gt; that involves gathering or using information about performance. </t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>behaviour change technique</t>
         </is>
       </c>
       <c r="E135" s="3" t="n"/>
       <c r="F135" s="3" t="n"/>
-      <c r="G135" s="3" t="n"/>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>BCT5.4 Monitoring of emotional consequences</t>
+        </is>
+      </c>
       <c r="H135" s="3" t="n"/>
       <c r="I135" s="3" t="n"/>
       <c r="J135" s="3" t="n"/>
@@ -8215,42 +8205,30 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007018</t>
+          <t>BCIO:007017</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">observe behaviour without feedback BCT </t>
+          <t>monitoring BCT</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>A &lt;monitoring BCT&gt; that observes current performance of the behaviour with the person’s knowledge but without providing feedback about their behaviour.</t>
+          <t xml:space="preserve">A &lt;behaviour change technique&gt; that involves gathering or using information about performance. </t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>monitoring BCT</t>
+          <t>behaviour change technique</t>
         </is>
       </c>
       <c r="E136" s="3" t="n"/>
       <c r="F136" s="3" t="n"/>
-      <c r="G136" s="3" t="inlineStr">
-        <is>
-          <t>BCT2.1 Monitoring of behaviour by others without feedback</t>
-        </is>
-      </c>
-      <c r="H136" s="3" t="inlineStr">
-        <is>
-          <t>observation, performance monitoring</t>
-        </is>
-      </c>
+      <c r="G136" s="3" t="n"/>
+      <c r="H136" s="3" t="n"/>
       <c r="I136" s="3" t="n"/>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>The monitoring agent can be a human or a technical device. If observation is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if feedback given, code only 'provide feedback on behaviour BCT' and not this class; if observing outcomes code 'observe outcome of behaviour without feedback BCT'.</t>
-        </is>
-      </c>
+      <c r="J136" s="3" t="n"/>
       <c r="K136" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -8268,7 +8246,7 @@
       <c r="Q136" s="3" t="n"/>
       <c r="R136" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S136" s="3" t="inlineStr">
@@ -8281,17 +8259,17 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007020</t>
+          <t>BCIO:007018</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">observe outcome of behaviour without feedback BCT </t>
+          <t xml:space="preserve">observe behaviour without feedback BCT </t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>A &lt;monitoring BCT&gt; that observes an outcome of performing the behaviour with the person’s knowledge but without providing feedback about the outcome.</t>
+          <t>A &lt;monitoring BCT&gt; that observes current performance of the behaviour with the person’s knowledge but without providing feedback about their behaviour.</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
@@ -8303,14 +8281,18 @@
       <c r="F137" s="3" t="n"/>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>BCT2.5 Monitoring outcome(s) of behaviour by others without feedback</t>
-        </is>
-      </c>
-      <c r="H137" s="3" t="n"/>
+          <t>BCT2.1 Monitoring of behaviour by others without feedback</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>observation, performance monitoring</t>
+        </is>
+      </c>
       <c r="I137" s="3" t="n"/>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>The monitoring agent can be a human or a technical device. If recording is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if feedback given, code only 'provide feedback on outcome of behaviour BCT' and not this class; if observing behaviour code 'observe behaviour without feedback BCT'.</t>
+          <t>The monitoring agent can be a human or a technical device. If observation is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if feedback given, code only 'provide feedback on behaviour BCT' and not this class; if observing outcomes code 'observe outcome of behaviour without feedback BCT'.</t>
         </is>
       </c>
       <c r="K137" s="3" t="inlineStr">
@@ -8343,30 +8325,38 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007186</t>
+          <t>BCIO:007020</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>outcome consequence BCT</t>
+          <t xml:space="preserve">observe outcome of behaviour without feedback BCT </t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>A &lt;behaviour change technique&gt; that alters the consequences or promised consequences for an outcome that results from performing or not performing the behaviour.</t>
+          <t>A &lt;monitoring BCT&gt; that observes an outcome of performing the behaviour with the person’s knowledge but without providing feedback about the outcome.</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>behaviour change technique</t>
+          <t>monitoring BCT</t>
         </is>
       </c>
       <c r="E138" s="3" t="n"/>
       <c r="F138" s="3" t="n"/>
-      <c r="G138" s="3" t="n"/>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>BCT2.5 Monitoring outcome(s) of behaviour by others without feedback</t>
+        </is>
+      </c>
       <c r="H138" s="3" t="n"/>
       <c r="I138" s="3" t="n"/>
-      <c r="J138" s="3" t="n"/>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>The monitoring agent can be a human or a technical device. If recording is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if feedback given, code only 'provide feedback on outcome of behaviour BCT' and not this class; if observing behaviour code 'observe behaviour without feedback BCT'.</t>
+        </is>
+      </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -8384,7 +8374,7 @@
       <c r="Q138" s="3" t="n"/>
       <c r="R138" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S138" s="3" t="inlineStr">
@@ -8397,36 +8387,28 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007098</t>
+          <t>BCIO:007186</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">overcorrect unwanted behaviour BCT </t>
+          <t>outcome consequence BCT</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>An &lt;advise specific behaviour BCT&gt; that advises the person to repeat a wanted behaviour in an exaggerated way following performance of an unwanted behaviour.</t>
+          <t>A &lt;behaviour change technique&gt; that alters the consequences or promised consequences for an outcome that results from performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>advise specific behaviour BCT</t>
+          <t>behaviour change technique</t>
         </is>
       </c>
       <c r="E139" s="3" t="n"/>
       <c r="F139" s="3" t="n"/>
-      <c r="G139" s="3" t="inlineStr">
-        <is>
-          <t>BCT8.5 Overcorrection</t>
-        </is>
-      </c>
-      <c r="H139" s="3" t="inlineStr">
-        <is>
-          <t>overcorrection, remedial overcompensation</t>
-        </is>
-      </c>
+      <c r="G139" s="3" t="n"/>
+      <c r="H139" s="3" t="n"/>
       <c r="I139" s="3" t="n"/>
       <c r="J139" s="3" t="n"/>
       <c r="K139" s="3" t="inlineStr">
@@ -8446,7 +8428,7 @@
       <c r="Q139" s="3" t="n"/>
       <c r="R139" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S139" s="3" t="inlineStr">
@@ -8459,37 +8441,37 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007137</t>
+          <t>BCIO:007098</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>persuade about personal capability BCT</t>
+          <t xml:space="preserve">overcorrect unwanted behaviour BCT </t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A &lt;prompt thinking related to successful performance BCT&gt; that persuades the person that they can successfully perform the behaviour. </t>
+          <t>An &lt;advise specific behaviour BCT&gt; that advises the person to repeat a wanted behaviour in an exaggerated way following performance of an unwanted behaviour.</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>prompt thinking related to successful performance BCT</t>
+          <t>advise specific behaviour BCT</t>
         </is>
       </c>
       <c r="E140" s="3" t="n"/>
       <c r="F140" s="3" t="n"/>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>BCT15.1 Verbal persuasion about capability</t>
-        </is>
-      </c>
-      <c r="H140" s="3" t="n"/>
-      <c r="I140" s="3" t="inlineStr">
-        <is>
-          <t>Arguing against self-doubts; asserting that the person can and will succeed.</t>
-        </is>
-      </c>
+          <t>BCT8.5 Overcorrection</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>overcorrection, remedial overcompensation</t>
+        </is>
+      </c>
+      <c r="I140" s="3" t="n"/>
       <c r="J140" s="3" t="n"/>
       <c r="K140" s="3" t="inlineStr">
         <is>
@@ -8508,7 +8490,7 @@
       <c r="Q140" s="3" t="n"/>
       <c r="R140" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S140" s="3" t="inlineStr">
@@ -8521,29 +8503,37 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007061</t>
+          <t>BCIO:007137</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">plan inclusion of enjoyment BCT </t>
+          <t>persuade about personal capability BCT</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>A &lt;goal directed BCT&gt; that advises the person to plan a way of performing the behaviour that is pleasurable or satisfying.</t>
+          <t xml:space="preserve">A &lt;prompt thinking related to successful performance BCT&gt; that persuades the person that they can successfully perform the behaviour. </t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>goal directed BCT</t>
+          <t>prompt thinking related to successful performance BCT</t>
         </is>
       </c>
       <c r="E141" s="3" t="n"/>
       <c r="F141" s="3" t="n"/>
-      <c r="G141" s="3" t="n"/>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>BCT15.1 Verbal persuasion about capability</t>
+        </is>
+      </c>
       <c r="H141" s="3" t="n"/>
-      <c r="I141" s="3" t="n"/>
+      <c r="I141" s="3" t="inlineStr">
+        <is>
+          <t>Arguing against self-doubts; asserting that the person can and will succeed.</t>
+        </is>
+      </c>
       <c r="J141" s="3" t="n"/>
       <c r="K141" s="3" t="inlineStr">
         <is>
@@ -8575,42 +8565,30 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007094</t>
+          <t>BCIO:007061</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">practise behaviour BCT </t>
+          <t xml:space="preserve">plan inclusion of enjoyment BCT </t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>An &lt;advise specific behaviour BCT&gt; that advises repetition of the behaviour in a way that has the function of increasing the skill in performing the behaviour.</t>
+          <t>A &lt;goal directed BCT&gt; that advises the person to plan a way of performing the behaviour that is pleasurable or satisfying.</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>advise specific behaviour BCT</t>
+          <t>goal directed BCT</t>
         </is>
       </c>
       <c r="E142" s="3" t="n"/>
       <c r="F142" s="3" t="n"/>
-      <c r="G142" s="3" t="inlineStr">
-        <is>
-          <t>BCT8.1 Behavioural practice/rehearsal</t>
-        </is>
-      </c>
-      <c r="H142" s="3" t="inlineStr">
-        <is>
-          <t>skill practise, rehearsal</t>
-        </is>
-      </c>
+      <c r="G142" s="3" t="n"/>
+      <c r="H142" s="3" t="n"/>
       <c r="I142" s="3" t="n"/>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>If aiming to associate performance with the context, also code 'context-specific repetition of behaviour BCT'</t>
-        </is>
-      </c>
+      <c r="J142" s="3" t="n"/>
       <c r="K142" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -8628,7 +8606,7 @@
       <c r="Q142" s="3" t="n"/>
       <c r="R142" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S142" s="3" t="inlineStr">
@@ -8641,36 +8619,40 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007075</t>
+          <t>BCIO:007094</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>present information from credible influence BCT</t>
+          <t xml:space="preserve">practise behaviour BCT </t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>An &lt;awareness of other people's thoughts, feelings and actions BCT&gt; that presents information from a credible person or organisation to influence the behaviour.</t>
+          <t>An &lt;advise specific behaviour BCT&gt; that advises repetition of the behaviour in a way that has the function of increasing the skill in performing the behaviour.</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>awareness of other peoples thoughts, feelings and actions BCT</t>
+          <t>advise specific behaviour BCT</t>
         </is>
       </c>
       <c r="E143" s="3" t="n"/>
       <c r="F143" s="3" t="n"/>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>BCT9.1 Credible source</t>
-        </is>
-      </c>
-      <c r="H143" s="3" t="n"/>
+          <t>BCT8.1 Behavioural practice/rehearsal</t>
+        </is>
+      </c>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>skill practise, rehearsal</t>
+        </is>
+      </c>
       <c r="I143" s="3" t="n"/>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>Code this BCT if influence generally agreed on as credible e.g., health professionals, celebrities or words used to indicate expertise or leader in field and if the communication has the aim of persuading</t>
+          <t>If aiming to associate performance with the context, also code 'context-specific repetition of behaviour BCT'</t>
         </is>
       </c>
       <c r="K143" s="3" t="inlineStr">
@@ -8703,40 +8685,36 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007189</t>
+          <t>BCIO:007075</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for behaviour BCT</t>
+          <t>present information from credible influence BCT</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise consequence for behaviour BCT&gt; where the consequence is aversive.</t>
+          <t>An &lt;awareness of other people's thoughts, feelings and actions BCT&gt; that presents information from a credible person or organisation to influence the behaviour.</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>promise consequence for behaviour BCT</t>
+          <t>awareness of other peoples thoughts, feelings and actions BCT</t>
         </is>
       </c>
       <c r="E144" s="3" t="n"/>
       <c r="F144" s="3" t="n"/>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>BCT10.11 Future punishment</t>
-        </is>
-      </c>
-      <c r="H144" s="3" t="inlineStr">
-        <is>
-          <t>threat, warning, disincentive</t>
-        </is>
-      </c>
+          <t>BCT9.1 Credible source</t>
+        </is>
+      </c>
+      <c r="H144" s="3" t="n"/>
       <c r="I144" s="3" t="n"/>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>To qualify as aversive, the consequence should be aversively valued by the person receiving it.</t>
+          <t>Code this BCT if influence generally agreed on as credible e.g., health professionals, celebrities or words used to indicate expertise or leader in field and if the communication has the aim of persuading</t>
         </is>
       </c>
       <c r="K144" s="3" t="inlineStr">
@@ -8769,34 +8747,42 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007195</t>
+          <t>BCIO:007189</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for outcome of behaviour BCT</t>
+          <t>promise aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise consequence for outcome of behaviour BCT&gt; where the consequence is aversive.</t>
+          <t>A &lt;promise consequence for behaviour BCT&gt; where the consequence is aversive.</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>promise consequence for outcome of behaviour BCT</t>
+          <t>promise consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E145" s="3" t="n"/>
       <c r="F145" s="3" t="n"/>
-      <c r="G145" s="3" t="n"/>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>BCT10.11 Future punishment</t>
+        </is>
+      </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
           <t>threat, warning, disincentive</t>
         </is>
       </c>
       <c r="I145" s="3" t="n"/>
-      <c r="J145" s="3" t="n"/>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>To qualify as aversive, the consequence should be aversively valued by the person receiving it.</t>
+        </is>
+      </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -8827,22 +8813,22 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007191</t>
+          <t>BCIO:007195</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for situation specific behaviour BCT</t>
+          <t>promise aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise aversive consequence for behaviour BCT&gt; that promises the consequence will be provided for the behaviour in one situation but not in another.</t>
+          <t>A &lt;promise consequence for outcome of behaviour BCT&gt; where the consequence is aversive.</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for behaviour BCT</t>
+          <t>promise consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E146" s="3" t="n"/>
@@ -8850,7 +8836,7 @@
       <c r="G146" s="3" t="n"/>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>threat for situation specific behaviour</t>
+          <t>threat, warning, disincentive</t>
         </is>
       </c>
       <c r="I146" s="3" t="n"/>
@@ -8885,17 +8871,17 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007192</t>
+          <t>BCIO:007191</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>promise aversive material consequence for behaviour BCT</t>
+          <t>promise aversive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise aversive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise aversive consequence for behaviour BCT&gt; that promises the consequence will be provided for the behaviour in one situation but not in another.</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
@@ -8908,7 +8894,7 @@
       <c r="G147" s="3" t="n"/>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>material threat</t>
+          <t>threat for situation specific behaviour</t>
         </is>
       </c>
       <c r="I147" s="3" t="n"/>
@@ -8943,28 +8929,32 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007194</t>
+          <t>BCIO:007192</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>promise aversive material consequence for outcome of behaviour</t>
+          <t>promise aversive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise aversive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise aversive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for outcome of behaviour BCT</t>
+          <t>promise aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E148" s="3" t="n"/>
       <c r="F148" s="3" t="n"/>
       <c r="G148" s="3" t="n"/>
-      <c r="H148" s="3" t="n"/>
+      <c r="H148" s="3" t="inlineStr">
+        <is>
+          <t>material threat</t>
+        </is>
+      </c>
       <c r="I148" s="3" t="n"/>
       <c r="J148" s="3" t="n"/>
       <c r="K148" s="3" t="inlineStr">
@@ -8997,32 +8987,28 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007193</t>
+          <t>BCIO:007194</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>promise aversive material consequence for situation specific behaviour BCT</t>
+          <t>promise aversive material consequence for outcome of behaviour</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise aversive consequence for situation specific behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise aversive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for situation specific behaviour BCT</t>
+          <t>promise aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E149" s="3" t="n"/>
       <c r="F149" s="3" t="n"/>
       <c r="G149" s="3" t="n"/>
-      <c r="H149" s="3" t="inlineStr">
-        <is>
-          <t>material threat for situation specific behaviour</t>
-        </is>
-      </c>
+      <c r="H149" s="3" t="n"/>
       <c r="I149" s="3" t="n"/>
       <c r="J149" s="3" t="n"/>
       <c r="K149" s="3" t="inlineStr">
@@ -9055,22 +9041,22 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007197</t>
+          <t>BCIO:007193</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>promise aversive social consequence for behaviour BCT</t>
+          <t>promise aversive material consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise aversive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise aversive consequence for situation specific behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for behaviour BCT</t>
+          <t>promise aversive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="E150" s="3" t="n"/>
@@ -9078,15 +9064,11 @@
       <c r="G150" s="3" t="n"/>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>social threat</t>
+          <t>material threat for situation specific behaviour</t>
         </is>
       </c>
       <c r="I150" s="3" t="n"/>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="J150" s="3" t="n"/>
       <c r="K150" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -9117,28 +9099,32 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007199</t>
+          <t>BCIO:007197</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>promise aversive social consequence for outcome of behaviour BCT</t>
+          <t>promise aversive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A &lt;promise aversive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process. </t>
+          <t>A &lt;promise aversive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for outcome of behaviour BCT</t>
+          <t>promise aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E151" s="3" t="n"/>
       <c r="F151" s="3" t="n"/>
       <c r="G151" s="3" t="n"/>
-      <c r="H151" s="3" t="n"/>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>social threat</t>
+        </is>
+      </c>
       <c r="I151" s="3" t="n"/>
       <c r="J151" s="3" t="inlineStr">
         <is>
@@ -9175,32 +9161,28 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007198</t>
+          <t>BCIO:007199</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>promise aversive social consequence for situation specific behaviour BCT</t>
+          <t>promise aversive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise aversive consequence for situation specific behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t xml:space="preserve">A &lt;promise aversive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process. </t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for situation specific behaviour BCT</t>
+          <t>promise aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E152" s="3" t="n"/>
       <c r="F152" s="3" t="n"/>
       <c r="G152" s="3" t="n"/>
-      <c r="H152" s="3" t="inlineStr">
-        <is>
-          <t>social threat for situation specific behaviour</t>
-        </is>
-      </c>
+      <c r="H152" s="3" t="n"/>
       <c r="I152" s="3" t="n"/>
       <c r="J152" s="3" t="inlineStr">
         <is>
@@ -9237,32 +9219,36 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007187</t>
+          <t>BCIO:007198</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>promise consequence for behaviour BCT</t>
+          <t>promise aversive social consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>A &lt;behavioural consequence BCT&gt; that promises a future consequence contingent on performing or not performing the behaviour.</t>
+          <t>A &lt;promise aversive consequence for situation specific behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>behavioural consequence BCT</t>
+          <t>promise aversive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="E153" s="3" t="n"/>
       <c r="F153" s="3" t="n"/>
       <c r="G153" s="3" t="n"/>
-      <c r="H153" s="3" t="n"/>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>social threat for situation specific behaviour</t>
+        </is>
+      </c>
       <c r="I153" s="3" t="n"/>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">"promises" here means assuring someone that one will do something or that something will happen.  </t>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
         </is>
       </c>
       <c r="K153" s="3" t="inlineStr">
@@ -9282,7 +9268,7 @@
       <c r="Q153" s="3" t="n"/>
       <c r="R153" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S153" s="3" t="inlineStr">
@@ -9295,22 +9281,22 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007200</t>
+          <t>BCIO:007187</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>promise consequence for outcome of behaviour BCT</t>
+          <t>promise consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">An &lt;outcome consequence BCT&gt; that promises a future consequence contingent on an outcome of performing or not performing the behaviour. </t>
+          <t>A &lt;behavioural consequence BCT&gt; that promises a future consequence contingent on performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>outcome consequence BCT</t>
+          <t>behavioural consequence BCT</t>
         </is>
       </c>
       <c r="E154" s="3" t="n"/>
@@ -9353,34 +9339,34 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007204</t>
+          <t>BCIO:007200</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for alternative behaviour BCT</t>
+          <t>promise consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for behaviour BCT&gt; that promises the consequence will be provided for the behaviour that is different from the unwanted behaviour.</t>
+          <t xml:space="preserve">An &lt;outcome consequence BCT&gt; that promises a future consequence contingent on an outcome of performing or not performing the behaviour. </t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for behaviour BCT</t>
+          <t>outcome consequence BCT</t>
         </is>
       </c>
       <c r="E155" s="3" t="n"/>
       <c r="F155" s="3" t="n"/>
       <c r="G155" s="3" t="n"/>
-      <c r="H155" s="3" t="inlineStr">
-        <is>
-          <t>incentive for alternative behaviour</t>
-        </is>
-      </c>
+      <c r="H155" s="3" t="n"/>
       <c r="I155" s="3" t="n"/>
-      <c r="J155" s="3" t="n"/>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"promises" here means assuring someone that one will do something or that something will happen.  </t>
+        </is>
+      </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -9398,7 +9384,7 @@
       <c r="Q155" s="3" t="n"/>
       <c r="R155" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S155" s="3" t="inlineStr">
@@ -9411,17 +9397,17 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007205</t>
+          <t>BCIO:007204</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for approximating behaviour BCT</t>
+          <t>promise positive consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for behaviour BCT&gt; where the consequence is provided as the performance gradually gets closer to the behaviour.</t>
+          <t>A &lt;promise positive consequence for behaviour BCT&gt; that promises the consequence will be provided for the behaviour that is different from the unwanted behaviour.</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
@@ -9434,7 +9420,7 @@
       <c r="G156" s="3" t="n"/>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>incentive for approximating behaviour</t>
+          <t>incentive for alternative behaviour</t>
         </is>
       </c>
       <c r="I156" s="3" t="n"/>
@@ -9469,42 +9455,34 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007202</t>
+          <t>BCIO:007205</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
+          <t>promise positive consequence for approximating behaviour BCT</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>A &lt;promise positive consequence for behaviour BCT&gt; where the consequence is provided as the performance gradually gets closer to the behaviour.</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
           <t>promise positive consequence for behaviour BCT</t>
-        </is>
-      </c>
-      <c r="C157" s="3" t="inlineStr">
-        <is>
-          <t>A &lt;promise consequence for behaviour BCT&gt; where the consequence is positive.</t>
-        </is>
-      </c>
-      <c r="D157" s="3" t="inlineStr">
-        <is>
-          <t>promise consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E157" s="3" t="n"/>
       <c r="F157" s="3" t="n"/>
-      <c r="G157" s="3" t="inlineStr">
-        <is>
-          <t>BCT10.6 Non-specific incentive; BCT10.7 Self-incentive</t>
-        </is>
-      </c>
+      <c r="G157" s="3" t="n"/>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>incentive</t>
+          <t>incentive for approximating behaviour</t>
         </is>
       </c>
       <c r="I157" s="3" t="n"/>
-      <c r="J157" s="3" t="inlineStr">
-        <is>
-          <t>To qualify as positive, the consequence should be positively valued by the person receiving it. If consequence is delivered, also code 'provide positive consequence for behaviour BCT' or one of its child classes.</t>
-        </is>
-      </c>
+      <c r="J157" s="3" t="n"/>
       <c r="K157" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -9535,34 +9513,42 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007206</t>
+          <t>BCIO:007202</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for completion of behavioural sequence BCT</t>
+          <t>promise positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for behaviour BCT&gt; in which the consequence will be provided for performing the final behaviour in a sequence of behaviours, followed by adding behaviours that occur earlier in the sequence.</t>
+          <t>A &lt;promise consequence for behaviour BCT&gt; where the consequence is positive.</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for behaviour BCT</t>
+          <t>promise consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E158" s="3" t="n"/>
       <c r="F158" s="3" t="n"/>
-      <c r="G158" s="3" t="n"/>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>BCT10.6 Non-specific incentive; BCT10.7 Self-incentive</t>
+        </is>
+      </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>incentive for completion of behavioural sequence</t>
+          <t>incentive</t>
         </is>
       </c>
       <c r="I158" s="3" t="n"/>
-      <c r="J158" s="3" t="n"/>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>To qualify as positive, the consequence should be positively valued by the person receiving it. If consequence is delivered, also code 'provide positive consequence for behaviour BCT' or one of its child classes.</t>
+        </is>
+      </c>
       <c r="K158" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -9593,17 +9579,17 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007207</t>
+          <t>BCIO:007206</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for incompatible behaviour BCT</t>
+          <t>promise positive consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for behaviour BCT&gt; that promises the consequence will be provided for the behaviour that is incompatible with the unwanted behaviour.</t>
+          <t>A &lt;promise positive consequence for behaviour BCT&gt; in which the consequence will be provided for performing the final behaviour in a sequence of behaviours, followed by adding behaviours that occur earlier in the sequence.</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
@@ -9616,7 +9602,7 @@
       <c r="G159" s="3" t="n"/>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>incentive for incompatible behaviour</t>
+          <t>incentive for completion of behavioural sequence</t>
         </is>
       </c>
       <c r="I159" s="3" t="n"/>
@@ -9638,7 +9624,7 @@
       <c r="Q159" s="3" t="n"/>
       <c r="R159" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S159" s="3" t="inlineStr">
@@ -9651,34 +9637,30 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007216</t>
+          <t>BCIO:007207</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for outcome of behaviour BCT</t>
+          <t>promise positive consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise consequence for outcome of behaviour BCT&gt; where the consequence is positive</t>
+          <t>A &lt;promise positive consequence for behaviour BCT&gt; that promises the consequence will be provided for the behaviour that is incompatible with the unwanted behaviour.</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>promise consequence for outcome of behaviour BCT</t>
+          <t>promise positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E160" s="3" t="n"/>
       <c r="F160" s="3" t="n"/>
-      <c r="G160" s="3" t="inlineStr">
-        <is>
-          <t>BCT10.8 Incentive (outcome)</t>
-        </is>
-      </c>
+      <c r="G160" s="3" t="n"/>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>incentive</t>
+          <t>incentive for incompatible behaviour</t>
         </is>
       </c>
       <c r="I160" s="3" t="n"/>
@@ -9700,7 +9682,7 @@
       <c r="Q160" s="3" t="n"/>
       <c r="R160" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S160" s="3" t="inlineStr">
@@ -9713,30 +9695,34 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007208</t>
+          <t>BCIO:007216</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for situation specific behaviour BCT</t>
+          <t>promise positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for behaviour BCT&gt; that promises the consequence will be provided for the behaviour in one situation but not in another.</t>
+          <t>A &lt;promise consequence for outcome of behaviour BCT&gt; where the consequence is positive</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for behaviour BCT</t>
+          <t>promise consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E161" s="3" t="n"/>
       <c r="F161" s="3" t="n"/>
-      <c r="G161" s="3" t="n"/>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>BCT10.8 Incentive (outcome)</t>
+        </is>
+      </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
-          <t>incentive for situation specific behaviour</t>
+          <t>incentive</t>
         </is>
       </c>
       <c r="I161" s="3" t="n"/>
@@ -9758,7 +9744,7 @@
       <c r="Q161" s="3" t="n"/>
       <c r="R161" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S161" s="3" t="inlineStr">
@@ -9771,22 +9757,22 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007210</t>
+          <t>BCIO:007208</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>promise positive material consequence for alternative behaviour BCT</t>
+          <t>promise positive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for alternative behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise positive consequence for behaviour BCT&gt; that promises the consequence will be provided for the behaviour in one situation but not in another.</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for alternative behaviour BCT</t>
+          <t>promise positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E162" s="3" t="n"/>
@@ -9794,7 +9780,7 @@
       <c r="G162" s="3" t="n"/>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>material incentive for alternative behaviour</t>
+          <t>incentive for situation specific behaviour</t>
         </is>
       </c>
       <c r="I162" s="3" t="n"/>
@@ -9829,22 +9815,22 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007211</t>
+          <t>BCIO:007210</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>promise positive material consequence for approximating behaviour BCT</t>
+          <t>promise positive material consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A &lt;promise positive consequence for approximating behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects. </t>
+          <t>A &lt;promise positive consequence for alternative behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for approximating behaviour BCT</t>
+          <t>promise positive consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="E163" s="3" t="n"/>
@@ -9852,7 +9838,7 @@
       <c r="G163" s="3" t="n"/>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>material incentive for approximating behaviour</t>
+          <t>material incentive for alternative behaviour</t>
         </is>
       </c>
       <c r="I163" s="3" t="n"/>
@@ -9887,34 +9873,30 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007209</t>
+          <t>BCIO:007211</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>promise positive material consequence for behaviour BCT</t>
+          <t>promise positive material consequence for approximating behaviour BCT</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t xml:space="preserve">A &lt;promise positive consequence for approximating behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects. </t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for behaviour BCT</t>
+          <t>promise positive consequence for approximating behaviour BCT</t>
         </is>
       </c>
       <c r="E164" s="3" t="n"/>
       <c r="F164" s="3" t="n"/>
-      <c r="G164" s="3" t="inlineStr">
-        <is>
-          <t>BCT10.1 Material incentive (behaviour)</t>
-        </is>
-      </c>
+      <c r="G164" s="3" t="n"/>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>material incentive</t>
+          <t>material incentive for approximating behaviour</t>
         </is>
       </c>
       <c r="I164" s="3" t="n"/>
@@ -9936,7 +9918,7 @@
       <c r="Q164" s="3" t="n"/>
       <c r="R164" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S164" s="3" t="inlineStr">
@@ -9949,30 +9931,34 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007212</t>
+          <t>BCIO:007209</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>promise positive material consequence for completion of behavioural sequence BCT</t>
+          <t>promise positive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for completion of behavioural sequence BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise positive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for completion of behavioural sequence BCT</t>
+          <t>promise positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E165" s="3" t="n"/>
       <c r="F165" s="3" t="n"/>
-      <c r="G165" s="3" t="n"/>
+      <c r="G165" s="3" t="inlineStr">
+        <is>
+          <t>BCT10.1 Material incentive (behaviour)</t>
+        </is>
+      </c>
       <c r="H165" s="3" t="inlineStr">
         <is>
-          <t>material incentive for completion of behavioural sequence</t>
+          <t>material incentive</t>
         </is>
       </c>
       <c r="I165" s="3" t="n"/>
@@ -9994,7 +9980,7 @@
       <c r="Q165" s="3" t="n"/>
       <c r="R165" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S165" s="3" t="inlineStr">
@@ -10007,22 +9993,22 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007213</t>
+          <t>BCIO:007212</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>promise positive material consequence for incompatible behaviour BCT</t>
+          <t>promise positive material consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for incompatible behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise positive consequence for completion of behavioural sequence BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for incompatible behaviour BCT</t>
+          <t>promise positive consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="E166" s="3" t="n"/>
@@ -10030,7 +10016,7 @@
       <c r="G166" s="3" t="n"/>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>material incentive for incompatible behaviour</t>
+          <t>material incentive for completion of behavioural sequence</t>
         </is>
       </c>
       <c r="I166" s="3" t="n"/>
@@ -10065,28 +10051,32 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007215</t>
+          <t>BCIO:007213</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>promise positive material consequence for outcome of behaviour BCT</t>
+          <t>promise positive material consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise positive consequence for incompatible behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for outcome of behaviour BCT</t>
+          <t>promise positive consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="E167" s="3" t="n"/>
       <c r="F167" s="3" t="n"/>
       <c r="G167" s="3" t="n"/>
-      <c r="H167" s="3" t="n"/>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>material incentive for incompatible behaviour</t>
+        </is>
+      </c>
       <c r="I167" s="3" t="n"/>
       <c r="J167" s="3" t="n"/>
       <c r="K167" s="3" t="inlineStr">
@@ -10119,32 +10109,28 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007214</t>
+          <t>BCIO:007215</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>promise positive material consequence for situation specific behaviour BCT</t>
+          <t>promise positive material consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for situation specific behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise positive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for situation specific behaviour BCT</t>
+          <t>promise positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E168" s="3" t="n"/>
       <c r="F168" s="3" t="n"/>
       <c r="G168" s="3" t="n"/>
-      <c r="H168" s="3" t="inlineStr">
-        <is>
-          <t>material incentive for situation specific behaviour</t>
-        </is>
-      </c>
+      <c r="H168" s="3" t="n"/>
       <c r="I168" s="3" t="n"/>
       <c r="J168" s="3" t="n"/>
       <c r="K168" s="3" t="inlineStr">
@@ -10177,22 +10163,22 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007219</t>
+          <t>BCIO:007214</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>promise positive social consequence for alternative behaviour BCT</t>
+          <t>promise positive material consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for alternative behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise positive consequence for situation specific behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for alternative behaviour BCT</t>
+          <t>promise positive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="E169" s="3" t="n"/>
@@ -10200,15 +10186,11 @@
       <c r="G169" s="3" t="n"/>
       <c r="H169" s="3" t="inlineStr">
         <is>
-          <t>social incentive for alternative behaviour</t>
+          <t>material incentive for situation specific behaviour</t>
         </is>
       </c>
       <c r="I169" s="3" t="n"/>
-      <c r="J169" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="J169" s="3" t="n"/>
       <c r="K169" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -10239,22 +10221,22 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007220</t>
+          <t>BCIO:007219</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>promise positive social consequence for approximating behaviour BCT</t>
+          <t>promise positive social consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for approximating behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise positive consequence for alternative behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for approximating behaviour BCT</t>
+          <t>promise positive consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="E170" s="3" t="n"/>
@@ -10262,7 +10244,7 @@
       <c r="G170" s="3" t="n"/>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>social incentive for approximating behaviour</t>
+          <t>social incentive for alternative behaviour</t>
         </is>
       </c>
       <c r="I170" s="3" t="n"/>
@@ -10301,34 +10283,30 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007218</t>
+          <t>BCIO:007220</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>promise positive social consequence for behaviour BCT</t>
+          <t>promise positive social consequence for approximating behaviour BCT</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise positive consequence for approximating behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for behaviour BCT</t>
+          <t>promise positive consequence for approximating behaviour BCT</t>
         </is>
       </c>
       <c r="E171" s="3" t="n"/>
       <c r="F171" s="3" t="n"/>
-      <c r="G171" s="3" t="inlineStr">
-        <is>
-          <t>BCT10.5 Social incentive</t>
-        </is>
-      </c>
+      <c r="G171" s="3" t="n"/>
       <c r="H171" s="3" t="inlineStr">
         <is>
-          <t>social incentive</t>
+          <t>social incentive for approximating behaviour</t>
         </is>
       </c>
       <c r="I171" s="3" t="n"/>
@@ -10354,7 +10332,7 @@
       <c r="Q171" s="3" t="n"/>
       <c r="R171" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S171" s="3" t="inlineStr">
@@ -10367,30 +10345,34 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007221</t>
+          <t>BCIO:007218</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>promise positive social consequence for completion of behavioural sequence BCT</t>
+          <t>promise positive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for completion of behavioural sequence BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise positive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for completion of behavioural sequence BCT</t>
+          <t>promise positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E172" s="3" t="n"/>
       <c r="F172" s="3" t="n"/>
-      <c r="G172" s="3" t="n"/>
+      <c r="G172" s="3" t="inlineStr">
+        <is>
+          <t>BCT10.5 Social incentive</t>
+        </is>
+      </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>social incentive for completion of behavioural sequence</t>
+          <t>social incentive</t>
         </is>
       </c>
       <c r="I172" s="3" t="n"/>
@@ -10416,7 +10398,7 @@
       <c r="Q172" s="3" t="n"/>
       <c r="R172" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S172" s="3" t="inlineStr">
@@ -10429,22 +10411,22 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007222</t>
+          <t>BCIO:007221</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>promise positive social consequence for incompatible behaviour BCT</t>
+          <t>promise positive social consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for incompatible behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise positive consequence for completion of behavioural sequence BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for incompatible behaviour BCT</t>
+          <t>promise positive consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="E173" s="3" t="n"/>
@@ -10452,7 +10434,7 @@
       <c r="G173" s="3" t="n"/>
       <c r="H173" s="3" t="inlineStr">
         <is>
-          <t>social incentive for incompatible behaviour</t>
+          <t>social incentive for completion of behavioural sequence</t>
         </is>
       </c>
       <c r="I173" s="3" t="n"/>
@@ -10491,28 +10473,32 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007224</t>
+          <t>BCIO:007222</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>promise positive social consequence for outcome of behaviour BCT</t>
+          <t>promise positive social consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A &lt;promise positive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process. </t>
+          <t>A &lt;promise positive consequence for incompatible behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for outcome of behaviour BCT</t>
+          <t>promise positive consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="E174" s="3" t="n"/>
       <c r="F174" s="3" t="n"/>
       <c r="G174" s="3" t="n"/>
-      <c r="H174" s="3" t="n"/>
+      <c r="H174" s="3" t="inlineStr">
+        <is>
+          <t>social incentive for incompatible behaviour</t>
+        </is>
+      </c>
       <c r="I174" s="3" t="n"/>
       <c r="J174" s="3" t="inlineStr">
         <is>
@@ -10549,32 +10535,28 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007223</t>
+          <t>BCIO:007224</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>promise positive social consequence for situation specific behaviour BCT</t>
+          <t>promise positive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for situation specific behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t xml:space="preserve">A &lt;promise positive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process. </t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for situation specific behaviour BCT</t>
+          <t>promise positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E175" s="3" t="n"/>
       <c r="F175" s="3" t="n"/>
       <c r="G175" s="3" t="n"/>
-      <c r="H175" s="3" t="inlineStr">
-        <is>
-          <t>social incentive for situation specific behaviour</t>
-        </is>
-      </c>
+      <c r="H175" s="3" t="n"/>
       <c r="I175" s="3" t="n"/>
       <c r="J175" s="3" t="inlineStr">
         <is>
@@ -10611,22 +10593,22 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007225</t>
+          <t>BCIO:007223</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>promise reduced frequency of aversive consequence for behaviour BCT</t>
+          <t>promise positive social consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for behaviour BCT&gt; that promises to provide the consequence at increasingly less frequent intervals.</t>
+          <t>A &lt;promise positive consequence for situation specific behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for behaviour BCT</t>
+          <t>promise positive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="E176" s="3" t="n"/>
@@ -10634,11 +10616,15 @@
       <c r="G176" s="3" t="n"/>
       <c r="H176" s="3" t="inlineStr">
         <is>
-          <t>reduce threat frequency</t>
+          <t>social incentive for situation specific behaviour</t>
         </is>
       </c>
       <c r="I176" s="3" t="n"/>
-      <c r="J176" s="3" t="n"/>
+      <c r="J176" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="K176" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -10656,7 +10642,7 @@
       <c r="Q176" s="3" t="n"/>
       <c r="R176" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S176" s="3" t="inlineStr">
@@ -10669,22 +10655,22 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007226</t>
+          <t>BCIO:007225</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>promise reduced frequency of aversive material consequence for behaviour BCT</t>
+          <t>promise reduced frequency of aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise reduced frequency of aversive consequence for behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise positive consequence for behaviour BCT&gt; that promises to provide the consequence at increasingly less frequent intervals.</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>promise reduced frequency of aversive consequence for behaviour BCT</t>
+          <t>promise positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E177" s="3" t="n"/>
@@ -10692,7 +10678,7 @@
       <c r="G177" s="3" t="n"/>
       <c r="H177" s="3" t="inlineStr">
         <is>
-          <t>reduce material threat frequency</t>
+          <t>reduce threat frequency</t>
         </is>
       </c>
       <c r="I177" s="3" t="n"/>
@@ -10727,17 +10713,17 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007227</t>
+          <t>BCIO:007226</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>promise reduced frequency of aversive social consequence for behaviour BCT</t>
+          <t>promise reduced frequency of aversive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise reduced frequency of aversive consequence for behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise reduced frequency of aversive consequence for behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
@@ -10750,15 +10736,11 @@
       <c r="G178" s="3" t="n"/>
       <c r="H178" s="3" t="inlineStr">
         <is>
-          <t>reduce social threat frequency</t>
+          <t>reduce material threat frequency</t>
         </is>
       </c>
       <c r="I178" s="3" t="n"/>
-      <c r="J178" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="J178" s="3" t="n"/>
       <c r="K178" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -10789,22 +10771,22 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007228</t>
+          <t>BCIO:007227</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>promise reduced frequency of positive consequence for behaviour BCT</t>
+          <t>promise reduced frequency of aversive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise aversive consequence for behaviour BCT&gt; that promises to provide the consequence at increasingly less frequent intervals.</t>
+          <t>A &lt;promise reduced frequency of aversive consequence for behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for outcome of behaviour BCT</t>
+          <t>promise reduced frequency of aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E179" s="3" t="n"/>
@@ -10812,11 +10794,15 @@
       <c r="G179" s="3" t="n"/>
       <c r="H179" s="3" t="inlineStr">
         <is>
-          <t>reduce incentive frequency</t>
+          <t>reduce social threat frequency</t>
         </is>
       </c>
       <c r="I179" s="3" t="n"/>
-      <c r="J179" s="3" t="n"/>
+      <c r="J179" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -10834,7 +10820,7 @@
       <c r="Q179" s="3" t="n"/>
       <c r="R179" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S179" s="3" t="inlineStr">
@@ -10847,22 +10833,22 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007229</t>
+          <t>BCIO:007228</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>promise reduced frequency of positive material consequence for behaviour BCT</t>
+          <t>promise reduced frequency of positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise reduced frequency of positive consequence for behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise aversive consequence for behaviour BCT&gt; that promises to provide the consequence at increasingly less frequent intervals.</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>promise reduced frequency of positive consequence for behaviour BCT</t>
+          <t>promise aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E180" s="3" t="n"/>
@@ -10870,7 +10856,7 @@
       <c r="G180" s="3" t="n"/>
       <c r="H180" s="3" t="inlineStr">
         <is>
-          <t>reduce material incentive frequency</t>
+          <t>reduce incentive frequency</t>
         </is>
       </c>
       <c r="I180" s="3" t="n"/>
@@ -10905,17 +10891,17 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007230</t>
+          <t>BCIO:007229</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>promise reduced frequency of positive social consequence for behaviour BCT</t>
+          <t>promise reduced frequency of positive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise reduced frequency of positive consequence for behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise reduced frequency of positive consequence for behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
@@ -10928,15 +10914,11 @@
       <c r="G181" s="3" t="n"/>
       <c r="H181" s="3" t="inlineStr">
         <is>
-          <t>reduce social incentive frequency</t>
+          <t>reduce material incentive frequency</t>
         </is>
       </c>
       <c r="I181" s="3" t="n"/>
-      <c r="J181" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="J181" s="3" t="n"/>
       <c r="K181" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -10967,22 +10949,22 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007190</t>
+          <t>BCIO:007230</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive consequence for behaviour BCT</t>
+          <t>promise reduced frequency of positive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove consequence for behaviour BCT&gt; where the consequence is aversive.</t>
+          <t>A &lt;promise reduced frequency of positive consequence for behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>promise to remove consequence for behaviour BCT</t>
+          <t>promise reduced frequency of positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E182" s="3" t="n"/>
@@ -10990,11 +10972,15 @@
       <c r="G182" s="3" t="n"/>
       <c r="H182" s="3" t="inlineStr">
         <is>
-          <t>incentive to remove punishment</t>
+          <t>reduce social incentive frequency</t>
         </is>
       </c>
       <c r="I182" s="3" t="n"/>
-      <c r="J182" s="3" t="n"/>
+      <c r="J182" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="K182" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -11012,7 +10998,7 @@
       <c r="Q182" s="3" t="n"/>
       <c r="R182" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S182" s="3" t="inlineStr">
@@ -11025,22 +11011,22 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007196</t>
+          <t>BCIO:007190</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive consequence for outcome of behaviour BCT</t>
+          <t>promise to remove aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove consequence for outcome of behaviour BCT&gt; where the consequence is aversive.</t>
+          <t>A &lt;promise to remove consequence for behaviour BCT&gt; where the consequence is aversive.</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>promise to remove consequence for outcome of behaviour BCT</t>
+          <t>promise to remove consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E183" s="3" t="n"/>
@@ -11083,22 +11069,22 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007231</t>
+          <t>BCIO:007196</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive material consequence for behaviour BCT</t>
+          <t>promise to remove aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove aversive consequence for behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise to remove consequence for outcome of behaviour BCT&gt; where the consequence is aversive.</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive consequence for behaviour BCT</t>
+          <t>promise to remove consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E184" s="3" t="n"/>
@@ -11106,7 +11092,7 @@
       <c r="G184" s="3" t="n"/>
       <c r="H184" s="3" t="inlineStr">
         <is>
-          <t>incentive to remove material punishment</t>
+          <t>incentive to remove punishment</t>
         </is>
       </c>
       <c r="I184" s="3" t="n"/>
@@ -11141,22 +11127,22 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007232</t>
+          <t>BCIO:007231</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive material consequence for outcome of behaviour BCT</t>
+          <t>promise to remove aversive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove aversive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise to remove aversive consequence for behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive consequence for outcome of behaviour BCT</t>
+          <t>promise to remove aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E185" s="3" t="n"/>
@@ -11199,22 +11185,22 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007233</t>
+          <t>BCIO:007232</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive social consequence for behaviour BCT</t>
+          <t>promise to remove aversive material consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove aversive consequence for behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process</t>
+          <t>A &lt;promise to remove aversive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive consequence for behaviour BCT</t>
+          <t>promise to remove aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E186" s="3" t="n"/>
@@ -11222,15 +11208,11 @@
       <c r="G186" s="3" t="n"/>
       <c r="H186" s="3" t="inlineStr">
         <is>
-          <t>incentive to remove social punishment</t>
+          <t>incentive to remove material punishment</t>
         </is>
       </c>
       <c r="I186" s="3" t="n"/>
-      <c r="J186" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="J186" s="3" t="n"/>
       <c r="K186" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -11261,22 +11243,22 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007234</t>
+          <t>BCIO:007233</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive social consequence for outcome of behaviour BCT</t>
+          <t>promise to remove aversive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove aversive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise to remove aversive consequence for behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive consequence for outcome of behaviour BCT</t>
+          <t>promise to remove aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E187" s="3" t="n"/>
@@ -11323,30 +11305,38 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007188</t>
+          <t>BCIO:007234</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>promise to remove consequence for behaviour BCT</t>
+          <t>promise to remove aversive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>A &lt;behavioural consequence BCT&gt; that promises future removal of a consequence contingent on performing or not performing the behaviour.</t>
+          <t>A &lt;promise to remove aversive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>behavioural consequence BCT</t>
+          <t>promise to remove aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E188" s="3" t="n"/>
       <c r="F188" s="3" t="n"/>
       <c r="G188" s="3" t="n"/>
-      <c r="H188" s="3" t="n"/>
+      <c r="H188" s="3" t="inlineStr">
+        <is>
+          <t>incentive to remove social punishment</t>
+        </is>
+      </c>
       <c r="I188" s="3" t="n"/>
-      <c r="J188" s="3" t="n"/>
+      <c r="J188" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="K188" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -11364,7 +11354,7 @@
       <c r="Q188" s="3" t="n"/>
       <c r="R188" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S188" s="3" t="inlineStr">
@@ -11377,22 +11367,22 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007201</t>
+          <t>BCIO:007188</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>promise to remove consequence for outcome of behaviour BCT</t>
+          <t>promise to remove consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>An &lt;outcome consequence BCT&gt; that promises future removal of a consequence contingent on an outcome of performing or not performing the behaviour.</t>
+          <t>A &lt;behavioural consequence BCT&gt; that promises future removal of a consequence contingent on performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>outcome consequence BCT</t>
+          <t>behavioural consequence BCT</t>
         </is>
       </c>
       <c r="E189" s="3" t="n"/>
@@ -11431,36 +11421,28 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007203</t>
+          <t>BCIO:007201</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive consequence for behaviour BCT</t>
+          <t>promise to remove consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove consequence for behaviour BCT&gt; where the consequence is positive.</t>
+          <t>An &lt;outcome consequence BCT&gt; that promises future removal of a consequence contingent on an outcome of performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>promise to remove consequence for behaviour BCT</t>
+          <t>outcome consequence BCT</t>
         </is>
       </c>
       <c r="E190" s="3" t="n"/>
       <c r="F190" s="3" t="n"/>
-      <c r="G190" s="3" t="inlineStr">
-        <is>
-          <t>BCT10.11 Future punishment</t>
-        </is>
-      </c>
-      <c r="H190" s="3" t="inlineStr">
-        <is>
-          <t>threaten to remove reward</t>
-        </is>
-      </c>
+      <c r="G190" s="3" t="n"/>
+      <c r="H190" s="3" t="n"/>
       <c r="I190" s="3" t="n"/>
       <c r="J190" s="3" t="n"/>
       <c r="K190" s="3" t="inlineStr">
@@ -11493,27 +11475,31 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007217</t>
+          <t>BCIO:007203</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive consequence for outcome of behaviour BCT</t>
+          <t>promise to remove positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove consequence for outcome of behaviour BCT&gt; where the consequence is positive.</t>
+          <t>A &lt;promise to remove consequence for behaviour BCT&gt; where the consequence is positive.</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>promise to remove consequence for outcome of behaviour BCT</t>
+          <t>promise to remove consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E191" s="3" t="n"/>
       <c r="F191" s="3" t="n"/>
-      <c r="G191" s="3" t="n"/>
+      <c r="G191" s="3" t="inlineStr">
+        <is>
+          <t>BCT10.11 Future punishment</t>
+        </is>
+      </c>
       <c r="H191" s="3" t="inlineStr">
         <is>
           <t>threaten to remove reward</t>
@@ -11551,22 +11537,22 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007235</t>
+          <t>BCIO:007217</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive material consequence for behaviour BCT</t>
+          <t>promise to remove positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove positive consequence for behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise to remove consequence for outcome of behaviour BCT&gt; where the consequence is positive.</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive consequence for behaviour BCT</t>
+          <t>promise to remove consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E192" s="3" t="n"/>
@@ -11574,7 +11560,7 @@
       <c r="G192" s="3" t="n"/>
       <c r="H192" s="3" t="inlineStr">
         <is>
-          <t>threaten to remove material reward</t>
+          <t>threaten to remove reward</t>
         </is>
       </c>
       <c r="I192" s="3" t="n"/>
@@ -11609,22 +11595,22 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007236</t>
+          <t>BCIO:007235</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive material consequence for outcome of behaviour BCT</t>
+          <t>promise to remove positive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove positive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise to remove positive consequence for behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive consequence for outcome of behaviour BCT</t>
+          <t>promise to remove positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E193" s="3" t="n"/>
@@ -11667,22 +11653,22 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007237</t>
+          <t>BCIO:007236</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive social consequence for behaviour BCT</t>
+          <t>promise to remove positive material consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove positive consequence for behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process</t>
+          <t>A &lt;promise to remove positive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive consequence for behaviour BCT</t>
+          <t>promise to remove positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E194" s="3" t="n"/>
@@ -11690,15 +11676,11 @@
       <c r="G194" s="3" t="n"/>
       <c r="H194" s="3" t="inlineStr">
         <is>
-          <t>threaten to remove social reward</t>
+          <t>threaten to remove material reward</t>
         </is>
       </c>
       <c r="I194" s="3" t="n"/>
-      <c r="J194" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="J194" s="3" t="n"/>
       <c r="K194" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -11729,22 +11711,22 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007238</t>
+          <t>BCIO:007237</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive social consequence for outcome of behaviour BCT</t>
+          <t>promise to remove positive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove positive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise to remove positive consequence for behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive consequence for outcome of behaviour BCT</t>
+          <t>promise to remove positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E195" s="3" t="n"/>
@@ -11791,36 +11773,36 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007144</t>
+          <t>BCIO:007238</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>promote pharmacological support BCT</t>
+          <t>promise to remove positive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>A &lt;behaviour change technique&gt; promoting medicines or other drugs.</t>
+          <t>A &lt;promise to remove positive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>behaviour change technique</t>
+          <t>promise to remove positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E196" s="3" t="n"/>
       <c r="F196" s="3" t="n"/>
-      <c r="G196" s="3" t="inlineStr">
-        <is>
-          <t>BCT11.1 Pharmacological support</t>
-        </is>
-      </c>
-      <c r="H196" s="3" t="n"/>
+      <c r="G196" s="3" t="n"/>
+      <c r="H196" s="3" t="inlineStr">
+        <is>
+          <t>threaten to remove social reward</t>
+        </is>
+      </c>
       <c r="I196" s="3" t="n"/>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>If pharmacological support to reduce negative emotions (i.e. anxiety) then also code 'advise how to reduce negative emotions BCT'</t>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
         </is>
       </c>
       <c r="K196" s="3" t="inlineStr">
@@ -11840,7 +11822,7 @@
       <c r="Q196" s="3" t="n"/>
       <c r="R196" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S196" s="3" t="inlineStr">
@@ -11853,38 +11835,38 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007070</t>
+          <t>BCIO:007144</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>prompt comparative imagining of future outcomes BCT</t>
+          <t>promote pharmacological support BCT</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>An &lt;increase awareness of consequences BCT&gt; that guides the person to imagine and compare the consequences of performing and not performing the behaviour.</t>
+          <t>A &lt;behaviour change technique&gt; promoting medicines or other drugs.</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>increase awareness of consequences BCT</t>
+          <t>behaviour change technique</t>
         </is>
       </c>
       <c r="E197" s="3" t="n"/>
       <c r="F197" s="3" t="n"/>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>BCT9.3 Comparative imagining of future outcomes</t>
-        </is>
-      </c>
-      <c r="H197" s="3" t="inlineStr">
-        <is>
-          <t>imagining future results</t>
-        </is>
-      </c>
+          <t>BCT11.1 Pharmacological support</t>
+        </is>
+      </c>
+      <c r="H197" s="3" t="n"/>
       <c r="I197" s="3" t="n"/>
-      <c r="J197" s="3" t="n"/>
+      <c r="J197" s="3" t="inlineStr">
+        <is>
+          <t>If pharmacological support to reduce negative emotions (i.e. anxiety) then also code 'advise how to reduce negative emotions BCT'</t>
+        </is>
+      </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -11915,32 +11897,36 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007139</t>
+          <t>BCIO:007070</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>prompt focus on past success BCT</t>
+          <t>prompt comparative imagining of future outcomes BCT</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>A &lt;prompt thinking related to successful performance BCT&gt; that prompts the person to think about previous successful performance of the behaviour.</t>
+          <t>An &lt;increase awareness of consequences BCT&gt; that guides the person to imagine and compare the consequences of performing and not performing the behaviour.</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>prompt thinking related to successful performance BCT</t>
+          <t>increase awareness of consequences BCT</t>
         </is>
       </c>
       <c r="E198" s="3" t="n"/>
       <c r="F198" s="3" t="n"/>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>BCT15.3 Focus on past success</t>
-        </is>
-      </c>
-      <c r="H198" s="3" t="n"/>
+          <t>BCT9.3 Comparative imagining of future outcomes</t>
+        </is>
+      </c>
+      <c r="H198" s="3" t="inlineStr">
+        <is>
+          <t>imagining future results</t>
+        </is>
+      </c>
       <c r="I198" s="3" t="n"/>
       <c r="J198" s="3" t="n"/>
       <c r="K198" s="3" t="inlineStr">
@@ -11960,7 +11946,7 @@
       <c r="Q198" s="3" t="n"/>
       <c r="R198" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S198" s="3" t="inlineStr">
@@ -11973,32 +11959,32 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007157</t>
+          <t>BCIO:007139</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>prompt focus on self-identity BCT</t>
+          <t>prompt focus on past success BCT</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A &lt;behaviour change technique&gt; that prompts the person to focus on their mental representation of themself. </t>
+          <t>A &lt;prompt thinking related to successful performance BCT&gt; that prompts the person to think about previous successful performance of the behaviour.</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>behaviour change technique</t>
+          <t>prompt thinking related to successful performance BCT</t>
         </is>
       </c>
       <c r="E199" s="3" t="n"/>
       <c r="F199" s="3" t="n"/>
-      <c r="G199" s="3" t="n"/>
-      <c r="H199" s="3" t="inlineStr">
-        <is>
-          <t>self-perception</t>
-        </is>
-      </c>
+      <c r="G199" s="3" t="inlineStr">
+        <is>
+          <t>BCT15.3 Focus on past success</t>
+        </is>
+      </c>
+      <c r="H199" s="3" t="n"/>
       <c r="I199" s="3" t="n"/>
       <c r="J199" s="3" t="n"/>
       <c r="K199" s="3" t="inlineStr">
@@ -12018,157 +12004,157 @@
       <c r="Q199" s="3" t="n"/>
       <c r="R199" s="3" t="inlineStr">
         <is>
+          <t>LZ</t>
+        </is>
+      </c>
+      <c r="S199" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T199" s="3" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:007157</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>prompt focus on self-identity BCT</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A &lt;behaviour change technique&gt; that prompts the person to focus on their mental representation of themself. </t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="n"/>
+      <c r="F200" s="3" t="n"/>
+      <c r="G200" s="3" t="n"/>
+      <c r="H200" s="3" t="inlineStr">
+        <is>
+          <t>self-perception</t>
+        </is>
+      </c>
+      <c r="I200" s="3" t="n"/>
+      <c r="J200" s="3" t="n"/>
+      <c r="K200" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="L200" s="3" t="n"/>
+      <c r="M200" s="3" t="n"/>
+      <c r="N200" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O200" s="3" t="n"/>
+      <c r="P200" s="3" t="n"/>
+      <c r="Q200" s="3" t="n"/>
+      <c r="R200" s="3" t="inlineStr">
+        <is>
           <t>lz; LZ</t>
         </is>
       </c>
-      <c r="S199" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T199" s="3" t="n"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
+      <c r="S200" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T200" s="3" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>BCIO:050992</t>
         </is>
       </c>
-      <c r="B200" s="2" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
         <is>
           <t>prompt immediate action BCT</t>
         </is>
       </c>
-      <c r="C200" s="2" t="inlineStr">
+      <c r="C201" s="2" t="inlineStr">
         <is>
           <t>An &lt;increase awareness of behaviour BCT&gt; that advises, reminds or directs the person to do the behaviour without delay.</t>
         </is>
       </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>increase awareness of behaviour BCT</t>
         </is>
       </c>
-      <c r="E200" s="2" t="n"/>
-      <c r="F200" s="2" t="n"/>
-      <c r="G200" s="2" t="n"/>
-      <c r="H200" s="2" t="n"/>
-      <c r="I200" s="2" t="n"/>
-      <c r="J200" s="2" t="n"/>
-      <c r="K200" s="2" t="n"/>
-      <c r="L200" s="2" t="n"/>
-      <c r="M200" s="2" t="n"/>
-      <c r="N200" s="2" t="inlineStr">
+      <c r="E201" s="2" t="n"/>
+      <c r="F201" s="2" t="n"/>
+      <c r="G201" s="2" t="n"/>
+      <c r="H201" s="2" t="n"/>
+      <c r="I201" s="2" t="n"/>
+      <c r="J201" s="2" t="n"/>
+      <c r="K201" s="2" t="n"/>
+      <c r="L201" s="2" t="n"/>
+      <c r="M201" s="2" t="n"/>
+      <c r="N201" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="O200" s="2" t="n"/>
-      <c r="P200" s="2" t="n"/>
-      <c r="Q200" s="2" t="n"/>
-      <c r="R200" s="2" t="n"/>
-      <c r="S200" s="2" t="n">
+      <c r="O201" s="2" t="n"/>
+      <c r="P201" s="2" t="n"/>
+      <c r="Q201" s="2" t="n"/>
+      <c r="R201" s="2" t="n"/>
+      <c r="S201" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T200" s="2" t="n"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="3" t="inlineStr">
-        <is>
-          <t>BCIO:007080</t>
-        </is>
-      </c>
-      <c r="B201" s="3" t="inlineStr">
-        <is>
-          <t>prompt intended action BCT</t>
-        </is>
-      </c>
-      <c r="C201" s="3" t="inlineStr">
-        <is>
-          <t>An &lt;alter external stimulus BCT&gt; that involves introducing an external stimulus to facilitate the behaviour for which an intention has previously been formed.</t>
-        </is>
-      </c>
-      <c r="D201" s="3" t="inlineStr">
-        <is>
-          <t>alter external stimulus BCT</t>
-        </is>
-      </c>
-      <c r="E201" s="3" t="n"/>
-      <c r="F201" s="3" t="n"/>
-      <c r="G201" s="3" t="inlineStr">
-        <is>
-          <t>BCT7.1 Prompts/cues</t>
-        </is>
-      </c>
-      <c r="H201" s="3" t="inlineStr">
-        <is>
-          <t>prompts</t>
-        </is>
-      </c>
-      <c r="I201" s="3" t="n"/>
-      <c r="J201" s="3" t="inlineStr">
-        <is>
-          <t>When a stimulus is linked to a specific action in an if-then plan including one or more of frequency, duration or intensity also code 'action planning BCT'</t>
-        </is>
-      </c>
-      <c r="K201" s="3" t="inlineStr">
-        <is>
-          <t>behaviour change technique</t>
-        </is>
-      </c>
-      <c r="L201" s="3" t="n"/>
-      <c r="M201" s="3" t="n"/>
-      <c r="N201" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="O201" s="3" t="n"/>
-      <c r="P201" s="3" t="n"/>
-      <c r="Q201" s="3" t="n"/>
-      <c r="R201" s="3" t="inlineStr">
-        <is>
-          <t>lz; LZ</t>
-        </is>
-      </c>
-      <c r="S201" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T201" s="3" t="n"/>
+      <c r="T201" s="2" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007138</t>
+          <t>BCIO:007080</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>prompt mental rehearsal of successful performance BCT</t>
+          <t>prompt intended action BCT</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>A &lt;prompt thinking related to successful performance BCT&gt; that prompts the person to practise imagining performing the behaviour well in a relevant context.</t>
+          <t>An &lt;alter external stimulus BCT&gt; that involves introducing an external stimulus to facilitate the behaviour for which an intention has previously been formed.</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>prompt thinking related to successful performance BCT</t>
+          <t>alter external stimulus BCT</t>
         </is>
       </c>
       <c r="E202" s="3" t="n"/>
       <c r="F202" s="3" t="n"/>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>BCT15.2 Mental rehearsal of successful performance</t>
-        </is>
-      </c>
-      <c r="H202" s="3" t="n"/>
+          <t>BCT7.1 Prompts/cues</t>
+        </is>
+      </c>
+      <c r="H202" s="3" t="inlineStr">
+        <is>
+          <t>prompts</t>
+        </is>
+      </c>
       <c r="I202" s="3" t="n"/>
-      <c r="J202" s="3" t="n"/>
+      <c r="J202" s="3" t="inlineStr">
+        <is>
+          <t>When a stimulus is linked to a specific action in an if-then plan including one or more of frequency, duration or intensity also code 'action planning BCT'</t>
+        </is>
+      </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -12186,7 +12172,7 @@
       <c r="Q202" s="3" t="n"/>
       <c r="R202" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S202" s="3" t="inlineStr">
@@ -12199,17 +12185,17 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007140</t>
+          <t>BCIO:007138</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>prompt self-talk BCT</t>
+          <t>prompt mental rehearsal of successful performance BCT</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A &lt;prompt thinking related to successful performance BCT&gt; that promotes the use of positive self-talk before or during the behaviour. </t>
+          <t>A &lt;prompt thinking related to successful performance BCT&gt; that prompts the person to practise imagining performing the behaviour well in a relevant context.</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
@@ -12221,16 +12207,12 @@
       <c r="F203" s="3" t="n"/>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>BCT15.4 Self-talk</t>
+          <t>BCT15.2 Mental rehearsal of successful performance</t>
         </is>
       </c>
       <c r="H203" s="3" t="n"/>
       <c r="I203" s="3" t="n"/>
-      <c r="J203" s="3" t="inlineStr">
-        <is>
-          <t>Self-talk could be about the behaviour or the context of the behaviour. Self-talk does not need to be spoken aloud</t>
-        </is>
-      </c>
+      <c r="J203" s="3" t="n"/>
       <c r="K203" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -12261,40 +12243,36 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007073</t>
+          <t>BCIO:007140</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">prompt social comparison BCT </t>
+          <t>prompt self-talk BCT</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>An &lt;awareness of other people's thoughts, feelings and actions BCT&gt; that draws attention to other people's behaviour and compares it with the person's own behaviour.</t>
+          <t xml:space="preserve">A &lt;prompt thinking related to successful performance BCT&gt; that promotes the use of positive self-talk before or during the behaviour. </t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>awareness of other peoples thoughts, feelings and actions BCT</t>
+          <t>prompt thinking related to successful performance BCT</t>
         </is>
       </c>
       <c r="E204" s="3" t="n"/>
       <c r="F204" s="3" t="n"/>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>BCT6.2 Social comparison</t>
-        </is>
-      </c>
-      <c r="H204" s="3" t="inlineStr">
-        <is>
-          <t>social comparison</t>
-        </is>
-      </c>
+          <t>BCT15.4 Self-talk</t>
+        </is>
+      </c>
+      <c r="H204" s="3" t="n"/>
       <c r="I204" s="3" t="n"/>
       <c r="J204" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Being in a group setting does not necessarily mean that social comparison is actually taking place </t>
+          <t>Self-talk could be about the behaviour or the context of the behaviour. Self-talk does not need to be spoken aloud</t>
         </is>
       </c>
       <c r="K204" s="3" t="inlineStr">
@@ -12314,7 +12292,7 @@
       <c r="Q204" s="3" t="n"/>
       <c r="R204" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S204" s="3" t="inlineStr">
@@ -12327,30 +12305,42 @@
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007239</t>
+          <t>BCIO:007073</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>prompt thinking related to successful performance BCT</t>
+          <t xml:space="preserve">prompt social comparison BCT </t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>A &lt;behaviour change technique&gt; that prompts thinking relating to successful performance of the behaviour.</t>
+          <t>An &lt;awareness of other people's thoughts, feelings and actions BCT&gt; that draws attention to other people's behaviour and compares it with the person's own behaviour.</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>behaviour change technique</t>
+          <t>awareness of other peoples thoughts, feelings and actions BCT</t>
         </is>
       </c>
       <c r="E205" s="3" t="n"/>
       <c r="F205" s="3" t="n"/>
-      <c r="G205" s="3" t="n"/>
-      <c r="H205" s="3" t="n"/>
+      <c r="G205" s="3" t="inlineStr">
+        <is>
+          <t>BCT6.2 Social comparison</t>
+        </is>
+      </c>
+      <c r="H205" s="3" t="inlineStr">
+        <is>
+          <t>social comparison</t>
+        </is>
+      </c>
       <c r="I205" s="3" t="n"/>
-      <c r="J205" s="3" t="n"/>
+      <c r="J205" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Being in a group setting does not necessarily mean that social comparison is actually taking place </t>
+        </is>
+      </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -12368,150 +12358,142 @@
       <c r="Q205" s="3" t="n"/>
       <c r="R205" s="3" t="inlineStr">
         <is>
+          <t>lz; LZ</t>
+        </is>
+      </c>
+      <c r="S205" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T205" s="3" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:007239</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>prompt thinking related to successful performance BCT</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>A &lt;behaviour change technique&gt; that prompts thinking relating to successful performance of the behaviour.</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="n"/>
+      <c r="F206" s="3" t="n"/>
+      <c r="G206" s="3" t="n"/>
+      <c r="H206" s="3" t="n"/>
+      <c r="I206" s="3" t="n"/>
+      <c r="J206" s="3" t="n"/>
+      <c r="K206" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="L206" s="3" t="n"/>
+      <c r="M206" s="3" t="n"/>
+      <c r="N206" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O206" s="3" t="n"/>
+      <c r="P206" s="3" t="n"/>
+      <c r="Q206" s="3" t="n"/>
+      <c r="R206" s="3" t="inlineStr">
+        <is>
           <t>LZ</t>
         </is>
       </c>
-      <c r="S205" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T205" s="3" t="n"/>
-    </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
+      <c r="S206" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T206" s="3" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
         <is>
           <t>BCIO:050993</t>
         </is>
       </c>
-      <c r="B206" s="2" t="inlineStr">
+      <c r="B207" s="2" t="inlineStr">
         <is>
           <t>protect time to perform behaviour BCT</t>
         </is>
       </c>
-      <c r="C206" s="2" t="inlineStr">
+      <c r="C207" s="2" t="inlineStr">
         <is>
           <t>A &lt;restructure the physical environment BCT&gt; that allocates a period of time to do the behaviour without competing with other behaviours.</t>
         </is>
       </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="D207" s="2" t="inlineStr">
         <is>
           <t>restructure the physical environment BCT</t>
         </is>
       </c>
-      <c r="E206" s="2" t="n"/>
-      <c r="F206" s="2" t="n"/>
-      <c r="G206" s="2" t="n"/>
-      <c r="H206" s="2" t="n"/>
-      <c r="I206" s="2" t="n"/>
-      <c r="J206" s="2" t="n"/>
-      <c r="K206" s="2" t="n"/>
-      <c r="L206" s="2" t="n"/>
-      <c r="M206" s="2" t="n"/>
-      <c r="N206" s="2" t="inlineStr">
+      <c r="E207" s="2" t="n"/>
+      <c r="F207" s="2" t="n"/>
+      <c r="G207" s="2" t="n"/>
+      <c r="H207" s="2" t="n"/>
+      <c r="I207" s="2" t="n"/>
+      <c r="J207" s="2" t="n"/>
+      <c r="K207" s="2" t="n"/>
+      <c r="L207" s="2" t="n"/>
+      <c r="M207" s="2" t="n"/>
+      <c r="N207" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="O206" s="2" t="n"/>
-      <c r="P206" s="2" t="n"/>
-      <c r="Q206" s="2" t="n"/>
-      <c r="R206" s="2" t="n"/>
-      <c r="S206" s="2" t="n">
+      <c r="O207" s="2" t="n"/>
+      <c r="P207" s="2" t="n"/>
+      <c r="Q207" s="2" t="n"/>
+      <c r="R207" s="2" t="n"/>
+      <c r="S207" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T206" s="2" t="n"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="3" t="inlineStr">
-        <is>
-          <t>BCIO:007241</t>
-        </is>
-      </c>
-      <c r="B207" s="3" t="inlineStr">
-        <is>
-          <t>provide aversive consequence for behaviour BCT</t>
-        </is>
-      </c>
-      <c r="C207" s="3" t="inlineStr">
-        <is>
-          <t>A &lt;provide consequence for behaviour BCT&gt; where the consequence is aversive.</t>
-        </is>
-      </c>
-      <c r="D207" s="3" t="inlineStr">
-        <is>
-          <t>provide consequence for behaviour BCT</t>
-        </is>
-      </c>
-      <c r="E207" s="3" t="n"/>
-      <c r="F207" s="3" t="n"/>
-      <c r="G207" s="3" t="inlineStr">
-        <is>
-          <t>BCT14.2 Punishment</t>
-        </is>
-      </c>
-      <c r="H207" s="3" t="inlineStr">
-        <is>
-          <t>punishment</t>
-        </is>
-      </c>
-      <c r="I207" s="3" t="n"/>
-      <c r="J207" s="3" t="inlineStr">
-        <is>
-          <t>To qualify as aversive, the consequence should be aversively valued by the person receiving it.</t>
-        </is>
-      </c>
-      <c r="K207" s="3" t="inlineStr">
-        <is>
-          <t>behaviour change technique</t>
-        </is>
-      </c>
-      <c r="L207" s="3" t="n"/>
-      <c r="M207" s="3" t="n"/>
-      <c r="N207" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="O207" s="3" t="n"/>
-      <c r="P207" s="3" t="n"/>
-      <c r="Q207" s="3" t="n"/>
-      <c r="R207" s="3" t="inlineStr">
-        <is>
-          <t>lz; LZ</t>
-        </is>
-      </c>
-      <c r="S207" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T207" s="3" t="n"/>
+      <c r="T207" s="2" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007246</t>
+          <t>BCIO:007241</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for outcome of behaviour BCT</t>
+          <t>provide aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide consequence for outcome of behaviour BCT&gt; where the consequence is aversive.</t>
+          <t>A &lt;provide consequence for behaviour BCT&gt; where the consequence is aversive.</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>provide consequence for outcome of behaviour BCT</t>
+          <t>provide consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E208" s="3" t="n"/>
       <c r="F208" s="3" t="n"/>
-      <c r="G208" s="3" t="n"/>
+      <c r="G208" s="3" t="inlineStr">
+        <is>
+          <t>BCT14.2 Punishment</t>
+        </is>
+      </c>
       <c r="H208" s="3" t="inlineStr">
         <is>
           <t>punishment</t>
@@ -12553,22 +12535,22 @@
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007242</t>
+          <t>BCIO:007246</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for situation specific behaviour BCT</t>
+          <t>provide aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide aversive consequence for behaviour BCT&gt; that provides the consequence for the behaviour in one situation but not in another.</t>
+          <t>A &lt;provide consequence for outcome of behaviour BCT&gt; where the consequence is aversive.</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for behaviour BCT</t>
+          <t>provide consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E209" s="3" t="n"/>
@@ -12576,11 +12558,15 @@
       <c r="G209" s="3" t="n"/>
       <c r="H209" s="3" t="inlineStr">
         <is>
-          <t>punishment for situation specific behaviour</t>
+          <t>punishment</t>
         </is>
       </c>
       <c r="I209" s="3" t="n"/>
-      <c r="J209" s="3" t="n"/>
+      <c r="J209" s="3" t="inlineStr">
+        <is>
+          <t>To qualify as aversive, the consequence should be aversively valued by the person receiving it.</t>
+        </is>
+      </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -12611,17 +12597,17 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007243</t>
+          <t>BCIO:007242</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>provide aversive material consequence for behaviour BCT</t>
+          <t>provide aversive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide aversive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide aversive consequence for behaviour BCT&gt; that provides the consequence for the behaviour in one situation but not in another.</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
@@ -12634,7 +12620,7 @@
       <c r="G210" s="3" t="n"/>
       <c r="H210" s="3" t="inlineStr">
         <is>
-          <t>material punishment</t>
+          <t>punishment for situation specific behaviour</t>
         </is>
       </c>
       <c r="I210" s="3" t="n"/>
@@ -12669,22 +12655,22 @@
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007245</t>
+          <t>BCIO:007243</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>provide aversive material consequence for outcome of behaviour BCT</t>
+          <t>provide aversive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide aversive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide aversive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for outcome of behaviour BCT</t>
+          <t>provide aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E211" s="3" t="n"/>
@@ -12727,22 +12713,22 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007244</t>
+          <t>BCIO:007245</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>provide aversive material consequence for situation specific behaviour BCT</t>
+          <t>provide aversive material consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide aversive consequence for situation specific behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide aversive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for situation specific behaviour BCT</t>
+          <t>provide aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E212" s="3" t="n"/>
@@ -12750,7 +12736,7 @@
       <c r="G212" s="3" t="n"/>
       <c r="H212" s="3" t="inlineStr">
         <is>
-          <t>material punishment for situation specific behaviour</t>
+          <t>material punishment</t>
         </is>
       </c>
       <c r="I212" s="3" t="n"/>
@@ -12785,22 +12771,22 @@
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007247</t>
+          <t>BCIO:007244</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>provide aversive social consequence for behaviour BCT</t>
+          <t>provide aversive material consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide aversive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide aversive consequence for situation specific behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for behaviour BCT</t>
+          <t>provide aversive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="E213" s="3" t="n"/>
@@ -12808,15 +12794,11 @@
       <c r="G213" s="3" t="n"/>
       <c r="H213" s="3" t="inlineStr">
         <is>
-          <t>social punishment</t>
+          <t>material punishment for situation specific behaviour</t>
         </is>
       </c>
       <c r="I213" s="3" t="n"/>
-      <c r="J213" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="J213" s="3" t="n"/>
       <c r="K213" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -12847,22 +12829,22 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007249</t>
+          <t>BCIO:007247</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>provide aversive social consequence for outcome of behaviour BCT</t>
+          <t>provide aversive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide aversive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide aversive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for outcome of behaviour BCT</t>
+          <t>provide aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E214" s="3" t="n"/>
@@ -12909,22 +12891,22 @@
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007248</t>
+          <t>BCIO:007249</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>provide aversive social consequence for situation specific behaviour BCT</t>
+          <t>provide aversive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide aversive consequence for situation specific behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide aversive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for situation specific behaviour BCT</t>
+          <t>provide aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E215" s="3" t="n"/>
@@ -12932,7 +12914,7 @@
       <c r="G215" s="3" t="n"/>
       <c r="H215" s="3" t="inlineStr">
         <is>
-          <t>social punishment for situation specific behaviour</t>
+          <t>social punishment</t>
         </is>
       </c>
       <c r="I215" s="3" t="n"/>
@@ -12971,42 +12953,38 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007026</t>
+          <t>BCIO:007248</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">provide biofeedback BCT </t>
+          <t>provide aversive social consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide feedback BCT&gt; that provides information about the functioning or state of the person's body, based on information collected by an external monitoring device.</t>
+          <t>A &lt;provide aversive consequence for situation specific behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>provide feedback BCT</t>
+          <t>provide aversive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="E216" s="3" t="n"/>
       <c r="F216" s="3" t="n"/>
-      <c r="G216" s="3" t="inlineStr">
-        <is>
-          <t>BCT2.6 Biofeedback</t>
-        </is>
-      </c>
+      <c r="G216" s="3" t="n"/>
       <c r="H216" s="3" t="inlineStr">
         <is>
-          <t>biofeedback</t>
-        </is>
-      </c>
-      <c r="I216" s="3" t="inlineStr">
-        <is>
-          <t>Using a pedometer to keep track of number of steps taken in a day.</t>
-        </is>
-      </c>
-      <c r="J216" s="3" t="n"/>
+          <t>social punishment for situation specific behaviour</t>
+        </is>
+      </c>
+      <c r="I216" s="3" t="n"/>
+      <c r="J216" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="K216" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -13037,29 +13015,41 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007240</t>
+          <t>BCIO:007026</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>provide consequence for behaviour BCT</t>
+          <t xml:space="preserve">provide biofeedback BCT </t>
         </is>
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>A &lt;behavioural consequence BCT&gt; that provides a consequence for the behaviour.</t>
+          <t>A &lt;provide feedback BCT&gt; that provides information about the functioning or state of the person's body, based on information collected by an external monitoring device.</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>behavioural consequence BCT</t>
+          <t>provide feedback BCT</t>
         </is>
       </c>
       <c r="E217" s="3" t="n"/>
       <c r="F217" s="3" t="n"/>
-      <c r="G217" s="3" t="n"/>
-      <c r="H217" s="3" t="n"/>
-      <c r="I217" s="3" t="n"/>
+      <c r="G217" s="3" t="inlineStr">
+        <is>
+          <t>BCT2.6 Biofeedback</t>
+        </is>
+      </c>
+      <c r="H217" s="3" t="inlineStr">
+        <is>
+          <t>biofeedback</t>
+        </is>
+      </c>
+      <c r="I217" s="3" t="inlineStr">
+        <is>
+          <t>Using a pedometer to keep track of number of steps taken in a day.</t>
+        </is>
+      </c>
       <c r="J217" s="3" t="n"/>
       <c r="K217" s="3" t="inlineStr">
         <is>
@@ -13078,7 +13068,7 @@
       <c r="Q217" s="3" t="n"/>
       <c r="R217" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S217" s="3" t="inlineStr">
@@ -13091,22 +13081,22 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007250</t>
+          <t>BCIO:007240</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>provide consequence for outcome of behaviour BCT</t>
+          <t>provide consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>An &lt;outcome consequence BCT&gt; that provides a consequence for an outcome resulting from performing or not performing the behaviour.</t>
+          <t>A &lt;behavioural consequence BCT&gt; that provides a consequence for the behaviour.</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>outcome consequence BCT</t>
+          <t>behavioural consequence BCT</t>
         </is>
       </c>
       <c r="E218" s="3" t="n"/>
@@ -13145,36 +13135,28 @@
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007155</t>
+          <t>BCIO:007250</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">provide distraction BCT </t>
+          <t>provide consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>A &lt;restructure the physical environment BCT&gt; that organises an alternative focus for attention for the person to avoid internal or external states or events associated with an unwanted behaviour.</t>
+          <t>An &lt;outcome consequence BCT&gt; that provides a consequence for an outcome resulting from performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
-          <t>restructure the physical environment BCT</t>
+          <t>outcome consequence BCT</t>
         </is>
       </c>
       <c r="E219" s="3" t="n"/>
       <c r="F219" s="3" t="n"/>
-      <c r="G219" s="3" t="inlineStr">
-        <is>
-          <t>BCT12.4 Distraction</t>
-        </is>
-      </c>
-      <c r="H219" s="3" t="inlineStr">
-        <is>
-          <t>attention shift</t>
-        </is>
-      </c>
+      <c r="G219" s="3" t="n"/>
+      <c r="H219" s="3" t="n"/>
       <c r="I219" s="3" t="n"/>
       <c r="J219" s="3" t="n"/>
       <c r="K219" s="3" t="inlineStr">
@@ -13194,7 +13176,7 @@
       <c r="Q219" s="3" t="n"/>
       <c r="R219" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S219" s="3" t="inlineStr">
@@ -13207,38 +13189,38 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007022</t>
+          <t>BCIO:007155</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>provide feedback BCT</t>
+          <t xml:space="preserve">provide distraction BCT </t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>A &lt;monitoring BCT&gt; in which feedback about the behaviour is provided.</t>
+          <t>A &lt;restructure the physical environment BCT&gt; that organises an alternative focus for attention for the person to avoid internal or external states or events associated with an unwanted behaviour.</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>monitoring BCT</t>
+          <t>restructure the physical environment BCT</t>
         </is>
       </c>
       <c r="E220" s="3" t="n"/>
       <c r="F220" s="3" t="n"/>
-      <c r="G220" s="3" t="n"/>
+      <c r="G220" s="3" t="inlineStr">
+        <is>
+          <t>BCT12.4 Distraction</t>
+        </is>
+      </c>
       <c r="H220" s="3" t="inlineStr">
         <is>
-          <t>feedback, behavioural feedback</t>
+          <t>attention shift</t>
         </is>
       </c>
       <c r="I220" s="3" t="n"/>
-      <c r="J220" s="3" t="inlineStr">
-        <is>
-          <t>Feedback is provision of data about some aspect of behaviour without an evaluation (positive or negative). Where feedback includes reward or punishment, see behavioural consequence BCT, outcome consequence BCT and their child classes. If there is no clear evidence that feedback was given, code 'observe behaviour without feedback BCT' or 'record behaviour without feedback BCT'.</t>
-        </is>
-      </c>
+      <c r="J220" s="3" t="n"/>
       <c r="K220" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -13269,34 +13251,38 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007023</t>
+          <t>BCIO:007022</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">provide feedback on behaviour BCT </t>
+          <t>provide feedback BCT</t>
         </is>
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide feedback BCT&gt; that provides information about the person's previous performance of the behaviour.</t>
+          <t>A &lt;monitoring BCT&gt; in which feedback about the behaviour is provided.</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>provide feedback BCT</t>
+          <t>monitoring BCT</t>
         </is>
       </c>
       <c r="E221" s="3" t="n"/>
       <c r="F221" s="3" t="n"/>
-      <c r="G221" s="3" t="inlineStr">
-        <is>
-          <t>BCT2.2 Feedback on behaviour</t>
-        </is>
-      </c>
-      <c r="H221" s="3" t="n"/>
+      <c r="G221" s="3" t="n"/>
+      <c r="H221" s="3" t="inlineStr">
+        <is>
+          <t>feedback, behavioural feedback</t>
+        </is>
+      </c>
       <c r="I221" s="3" t="n"/>
-      <c r="J221" s="3" t="n"/>
+      <c r="J221" s="3" t="inlineStr">
+        <is>
+          <t>Feedback is provision of data about some aspect of behaviour without an evaluation (positive or negative). Where feedback includes reward or punishment, see behavioural consequence BCT, outcome consequence BCT and their child classes. If there is no clear evidence that feedback was given, code 'observe behaviour without feedback BCT' or 'record behaviour without feedback BCT'.</t>
+        </is>
+      </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -13314,7 +13300,7 @@
       <c r="Q221" s="3" t="n"/>
       <c r="R221" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S221" s="3" t="inlineStr">
@@ -13327,17 +13313,17 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007027</t>
+          <t>BCIO:007023</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">provide feedback on outcome of behaviour BCT </t>
+          <t xml:space="preserve">provide feedback on behaviour BCT </t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide feedback BCT&gt; that provides information about an outcome of the person's previous performance of the behaviour.</t>
+          <t>A &lt;provide feedback BCT&gt; that provides information about the person's previous performance of the behaviour.</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
@@ -13349,7 +13335,7 @@
       <c r="F222" s="3" t="n"/>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>BCT2.7 Feedback on outcome(s) of behaviour</t>
+          <t>BCT2.2 Feedback on behaviour</t>
         </is>
       </c>
       <c r="H222" s="3" t="n"/>
@@ -13385,29 +13371,29 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007145</t>
+          <t>BCIO:007027</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">provide pharmacological support BCT </t>
+          <t xml:space="preserve">provide feedback on outcome of behaviour BCT </t>
         </is>
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promote pharmacological support BCT&gt; that provides the person with medicines or other drugs.</t>
+          <t>A &lt;provide feedback BCT&gt; that provides information about an outcome of the person's previous performance of the behaviour.</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
         <is>
-          <t>promote pharmacological support BCT</t>
+          <t>provide feedback BCT</t>
         </is>
       </c>
       <c r="E223" s="3" t="n"/>
       <c r="F223" s="3" t="n"/>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>BCT11.1 Pharmacological support</t>
+          <t>BCT2.7 Feedback on outcome(s) of behaviour</t>
         </is>
       </c>
       <c r="H223" s="3" t="n"/>
@@ -13443,41 +13429,33 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007251</t>
+          <t>BCIO:007145</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for alternative behaviour BCT</t>
+          <t xml:space="preserve">provide pharmacological support BCT </t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A &lt;provide positive consequence for behaviour BCT&gt; that provides the consequence for a behaviour that is different from the unwanted behaviour. </t>
+          <t>A &lt;promote pharmacological support BCT&gt; that provides the person with medicines or other drugs.</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for behaviour BCT</t>
+          <t>promote pharmacological support BCT</t>
         </is>
       </c>
       <c r="E224" s="3" t="n"/>
       <c r="F224" s="3" t="n"/>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>BCT14.8 Reward alternative behaviour</t>
-        </is>
-      </c>
-      <c r="H224" s="3" t="inlineStr">
-        <is>
-          <t>differential reinforcement, reward for alternative behaviour</t>
-        </is>
-      </c>
-      <c r="I224" s="3" t="inlineStr">
-        <is>
-          <t>Provide a reward for consuming low sugar food instead of high sugar food</t>
-        </is>
-      </c>
+          <t>BCT11.1 Pharmacological support</t>
+        </is>
+      </c>
+      <c r="H224" s="3" t="n"/>
+      <c r="I224" s="3" t="n"/>
       <c r="J224" s="3" t="n"/>
       <c r="K224" s="3" t="inlineStr">
         <is>
@@ -13496,7 +13474,7 @@
       <c r="Q224" s="3" t="n"/>
       <c r="R224" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S224" s="3" t="inlineStr">
@@ -13509,17 +13487,17 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007253</t>
+          <t>BCIO:007251</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for approximating behaviour BCT</t>
+          <t>provide positive consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for behaviour BCT&gt; where the consequence is provided as the performance gradually gets closer to the behaviour.</t>
+          <t xml:space="preserve">A &lt;provide positive consequence for behaviour BCT&gt; that provides the consequence for a behaviour that is different from the unwanted behaviour. </t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
@@ -13531,17 +13509,17 @@
       <c r="F225" s="3" t="n"/>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>BCT14.4 Reward approximation</t>
+          <t>BCT14.8 Reward alternative behaviour</t>
         </is>
       </c>
       <c r="H225" s="3" t="inlineStr">
         <is>
-          <t>shaping, reward for approximating behaviour</t>
+          <t>differential reinforcement, reward for alternative behaviour</t>
         </is>
       </c>
       <c r="I225" s="3" t="inlineStr">
         <is>
-          <t>Reward a person who has recently had a stroke who is learning to use cutlery again</t>
+          <t>Provide a reward for consuming low sugar food instead of high sugar food</t>
         </is>
       </c>
       <c r="J225" s="3" t="n"/>
@@ -13575,42 +13553,42 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007252</t>
+          <t>BCIO:007253</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
+          <t>provide positive consequence for approximating behaviour BCT</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>A &lt;provide positive consequence for behaviour BCT&gt; where the consequence is provided as the performance gradually gets closer to the behaviour.</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
           <t>provide positive consequence for behaviour BCT</t>
-        </is>
-      </c>
-      <c r="C226" s="3" t="inlineStr">
-        <is>
-          <t>A &lt;provide consequence for behaviour BCT&gt; where the consequence is positive.</t>
-        </is>
-      </c>
-      <c r="D226" s="3" t="inlineStr">
-        <is>
-          <t>provide consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E226" s="3" t="n"/>
       <c r="F226" s="3" t="n"/>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>BCT10.3 Non-specific reward; BCT10.9 Self-reward</t>
+          <t>BCT14.4 Reward approximation</t>
         </is>
       </c>
       <c r="H226" s="3" t="inlineStr">
         <is>
-          <t>positive reinforcement, reward</t>
-        </is>
-      </c>
-      <c r="I226" s="3" t="n"/>
-      <c r="J226" s="3" t="inlineStr">
-        <is>
-          <t>To qualify as positive, the consequence should be positively valued by the person receiving it. If informed of consequence in advance of rewarded behaviour, also code 'promise positive consequence for behaviour BCT' or one of its child classses.</t>
-        </is>
-      </c>
+          <t>shaping, reward for approximating behaviour</t>
+        </is>
+      </c>
+      <c r="I226" s="3" t="inlineStr">
+        <is>
+          <t>Reward a person who has recently had a stroke who is learning to use cutlery again</t>
+        </is>
+      </c>
+      <c r="J226" s="3" t="n"/>
       <c r="K226" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -13641,38 +13619,42 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007254</t>
+          <t>BCIO:007252</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for completion of behavioural sequence BCT</t>
+          <t>provide positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for behaviour BCT&gt; where the consequence is provided for performing the final behaviour in a sequence of behaviours, followed by adding behaviours that occur earlier in the sequence.</t>
+          <t>A &lt;provide consequence for behaviour BCT&gt; where the consequence is positive.</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for behaviour BCT</t>
+          <t>provide consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E227" s="3" t="n"/>
       <c r="F227" s="3" t="n"/>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>BCT14.5 Rewarding completion</t>
+          <t>BCT10.3 Non-specific reward; BCT10.9 Self-reward</t>
         </is>
       </c>
       <c r="H227" s="3" t="inlineStr">
         <is>
-          <t>backward chaining, reward for completion of behavoural sequence</t>
+          <t>positive reinforcement, reward</t>
         </is>
       </c>
       <c r="I227" s="3" t="n"/>
-      <c r="J227" s="3" t="n"/>
+      <c r="J227" s="3" t="inlineStr">
+        <is>
+          <t>To qualify as positive, the consequence should be positively valued by the person receiving it. If informed of consequence in advance of rewarded behaviour, also code 'promise positive consequence for behaviour BCT' or one of its child classses.</t>
+        </is>
+      </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -13703,17 +13685,17 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007255</t>
+          <t>BCIO:007254</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for incompatible behaviour BCT</t>
+          <t>provide positive consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for behaviour BCT&gt; that provides the consequence for a behaviour that is incompatible with the unwanted behaviour.</t>
+          <t>A &lt;provide positive consequence for behaviour BCT&gt; where the consequence is provided for performing the final behaviour in a sequence of behaviours, followed by adding behaviours that occur earlier in the sequence.</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
@@ -13725,19 +13707,15 @@
       <c r="F228" s="3" t="n"/>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>BCT14.7 Reward incompatible behaviour</t>
+          <t>BCT14.5 Rewarding completion</t>
         </is>
       </c>
       <c r="H228" s="3" t="inlineStr">
         <is>
-          <t>counter-conditioning, reward for incompatible behaviour</t>
-        </is>
-      </c>
-      <c r="I228" s="3" t="inlineStr">
-        <is>
-          <t>Provide a reward when a person folds their arms or sits on their hands instead of touching their face.</t>
-        </is>
-      </c>
+          <t>backward chaining, reward for completion of behavoural sequence</t>
+        </is>
+      </c>
+      <c r="I228" s="3" t="n"/>
       <c r="J228" s="3" t="n"/>
       <c r="K228" s="3" t="inlineStr">
         <is>
@@ -13769,42 +13747,42 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007264</t>
+          <t>BCIO:007255</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for outcome of behaviour BCT</t>
+          <t>provide positive consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide consequence for outcome of behaviour BCT&gt; where the consequence is positive.</t>
+          <t>A &lt;provide positive consequence for behaviour BCT&gt; that provides the consequence for a behaviour that is incompatible with the unwanted behaviour.</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
-          <t>provide consequence for outcome of behaviour BCT</t>
+          <t>provide positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E229" s="3" t="n"/>
       <c r="F229" s="3" t="n"/>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>BCT10.10 Reward (outcome)</t>
+          <t>BCT14.7 Reward incompatible behaviour</t>
         </is>
       </c>
       <c r="H229" s="3" t="inlineStr">
         <is>
-          <t>positive reinforcement, reward</t>
-        </is>
-      </c>
-      <c r="I229" s="3" t="n"/>
-      <c r="J229" s="3" t="inlineStr">
-        <is>
-          <t>To qualify as positive, the consequence should be positively valued by the person receiving it.</t>
-        </is>
-      </c>
+          <t>counter-conditioning, reward for incompatible behaviour</t>
+        </is>
+      </c>
+      <c r="I229" s="3" t="inlineStr">
+        <is>
+          <t>Provide a reward when a person folds their arms or sits on their hands instead of touching their face.</t>
+        </is>
+      </c>
+      <c r="J229" s="3" t="n"/>
       <c r="K229" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -13822,7 +13800,7 @@
       <c r="Q229" s="3" t="n"/>
       <c r="R229" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S229" s="3" t="inlineStr">
@@ -13835,38 +13813,42 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007256</t>
+          <t>BCIO:007264</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for situation specific behaviour BCT</t>
+          <t>provide positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for behaviour BCT&gt; that provides the consequence for the behaviour in one situation but not in another.</t>
+          <t>A &lt;provide consequence for outcome of behaviour BCT&gt; where the consequence is positive.</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for behaviour BCT</t>
+          <t>provide consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E230" s="3" t="n"/>
       <c r="F230" s="3" t="n"/>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>BCT14.6 Situation-specific reward</t>
+          <t>BCT10.10 Reward (outcome)</t>
         </is>
       </c>
       <c r="H230" s="3" t="inlineStr">
         <is>
-          <t>discrimination training, reward for situation specific behaviour</t>
+          <t>positive reinforcement, reward</t>
         </is>
       </c>
       <c r="I230" s="3" t="n"/>
-      <c r="J230" s="3" t="n"/>
+      <c r="J230" s="3" t="inlineStr">
+        <is>
+          <t>To qualify as positive, the consequence should be positively valued by the person receiving it.</t>
+        </is>
+      </c>
       <c r="K230" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -13897,30 +13879,34 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007258</t>
+          <t>BCIO:007256</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>provide positive material consequence for alternative behaviour BCT</t>
+          <t>provide positive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for alternative behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide positive consequence for behaviour BCT&gt; that provides the consequence for the behaviour in one situation but not in another.</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for alternative behaviour BCT</t>
+          <t>provide positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E231" s="3" t="n"/>
       <c r="F231" s="3" t="n"/>
-      <c r="G231" s="3" t="n"/>
+      <c r="G231" s="3" t="inlineStr">
+        <is>
+          <t>BCT14.6 Situation-specific reward</t>
+        </is>
+      </c>
       <c r="H231" s="3" t="inlineStr">
         <is>
-          <t>material reward for alternative behaviour</t>
+          <t>discrimination training, reward for situation specific behaviour</t>
         </is>
       </c>
       <c r="I231" s="3" t="n"/>
@@ -13955,22 +13941,22 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007259</t>
+          <t>BCIO:007258</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>provide positive material consequence for approximating behaviour BCT</t>
+          <t>provide positive material consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for approximating behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide positive consequence for alternative behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for approximating behaviour BCT</t>
+          <t>provide positive consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="E232" s="3" t="n"/>
@@ -13978,7 +13964,7 @@
       <c r="G232" s="3" t="n"/>
       <c r="H232" s="3" t="inlineStr">
         <is>
-          <t>material reward for approximating behaviour</t>
+          <t>material reward for alternative behaviour</t>
         </is>
       </c>
       <c r="I232" s="3" t="n"/>
@@ -14013,34 +13999,30 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007257</t>
+          <t>BCIO:007259</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>provide positive material consequence for behaviour BCT</t>
+          <t>provide positive material consequence for approximating behaviour BCT</t>
         </is>
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide positive consequence for approximating behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for behaviour BCT</t>
+          <t>provide positive consequence for approximating behaviour BCT</t>
         </is>
       </c>
       <c r="E233" s="3" t="n"/>
       <c r="F233" s="3" t="n"/>
-      <c r="G233" s="3" t="inlineStr">
-        <is>
-          <t>BCT10.2 Material reward (behaviour)</t>
-        </is>
-      </c>
+      <c r="G233" s="3" t="n"/>
       <c r="H233" s="3" t="inlineStr">
         <is>
-          <t>material reward, tangible reinforcement</t>
+          <t>material reward for approximating behaviour</t>
         </is>
       </c>
       <c r="I233" s="3" t="n"/>
@@ -14062,7 +14044,7 @@
       <c r="Q233" s="3" t="n"/>
       <c r="R233" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S233" s="3" t="inlineStr">
@@ -14075,30 +14057,34 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007260</t>
+          <t>BCIO:007257</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>provide positive material consequence for completion of behavioural sequence BCT</t>
+          <t>provide positive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for completion of behavioural sequence BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide positive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for completion of behavioural sequence BCT</t>
+          <t>provide positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E234" s="3" t="n"/>
       <c r="F234" s="3" t="n"/>
-      <c r="G234" s="3" t="n"/>
+      <c r="G234" s="3" t="inlineStr">
+        <is>
+          <t>BCT10.2 Material reward (behaviour)</t>
+        </is>
+      </c>
       <c r="H234" s="3" t="inlineStr">
         <is>
-          <t>material reward for completion of behavoural sequence</t>
+          <t>material reward, tangible reinforcement</t>
         </is>
       </c>
       <c r="I234" s="3" t="n"/>
@@ -14120,7 +14106,7 @@
       <c r="Q234" s="3" t="n"/>
       <c r="R234" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S234" s="3" t="inlineStr">
@@ -14133,22 +14119,22 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007261</t>
+          <t>BCIO:007260</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>provide positive material consequence for incompatible behaviour BCT</t>
+          <t>provide positive material consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for incompatible behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide positive consequence for completion of behavioural sequence BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for incompatible behaviour BCT</t>
+          <t>provide positive consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="E235" s="3" t="n"/>
@@ -14156,7 +14142,7 @@
       <c r="G235" s="3" t="n"/>
       <c r="H235" s="3" t="inlineStr">
         <is>
-          <t>material reward for incompatible behaviour</t>
+          <t>material reward for completion of behavoural sequence</t>
         </is>
       </c>
       <c r="I235" s="3" t="n"/>
@@ -14191,22 +14177,22 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007263</t>
+          <t>BCIO:007261</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>provide positive material consequence for outcome of behaviour BCT</t>
+          <t>provide positive material consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide positive consequence for incompatible behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for outcome of behaviour BCT</t>
+          <t>provide positive consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="E236" s="3" t="n"/>
@@ -14214,7 +14200,7 @@
       <c r="G236" s="3" t="n"/>
       <c r="H236" s="3" t="inlineStr">
         <is>
-          <t>material reward, tangible reinforcement</t>
+          <t>material reward for incompatible behaviour</t>
         </is>
       </c>
       <c r="I236" s="3" t="n"/>
@@ -14236,7 +14222,7 @@
       <c r="Q236" s="3" t="n"/>
       <c r="R236" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S236" s="3" t="inlineStr">
@@ -14249,22 +14235,22 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007262</t>
+          <t>BCIO:007263</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>provide positive material consequence for situation specific behaviour BCT</t>
+          <t>provide positive material consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for situation specific behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide positive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for situation specific behaviour BCT</t>
+          <t>provide positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E237" s="3" t="n"/>
@@ -14272,7 +14258,7 @@
       <c r="G237" s="3" t="n"/>
       <c r="H237" s="3" t="inlineStr">
         <is>
-          <t>material reward for situation specific behaviour</t>
+          <t>material reward, tangible reinforcement</t>
         </is>
       </c>
       <c r="I237" s="3" t="n"/>
@@ -14294,7 +14280,7 @@
       <c r="Q237" s="3" t="n"/>
       <c r="R237" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S237" s="3" t="inlineStr">
@@ -14307,22 +14293,22 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007266</t>
+          <t>BCIO:007262</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>provide positive social consequence for alternative behaviour BCT</t>
+          <t>provide positive material consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for alternative behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide positive consequence for situation specific behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for alternative behaviour BCT</t>
+          <t>provide positive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="E238" s="3" t="n"/>
@@ -14330,15 +14316,11 @@
       <c r="G238" s="3" t="n"/>
       <c r="H238" s="3" t="inlineStr">
         <is>
-          <t>social reward for alternative behaviour</t>
+          <t>material reward for situation specific behaviour</t>
         </is>
       </c>
       <c r="I238" s="3" t="n"/>
-      <c r="J238" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="J238" s="3" t="n"/>
       <c r="K238" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -14369,22 +14351,22 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007267</t>
+          <t>BCIO:007266</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>provide positive social consequence for approximating behaviour BCT</t>
+          <t>provide positive social consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for approximating behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide positive consequence for alternative behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for approximating behaviour BCT</t>
+          <t>provide positive consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="E239" s="3" t="n"/>
@@ -14392,7 +14374,7 @@
       <c r="G239" s="3" t="n"/>
       <c r="H239" s="3" t="inlineStr">
         <is>
-          <t>social reward for approximating behaviour</t>
+          <t>social reward for alternative behaviour</t>
         </is>
       </c>
       <c r="I239" s="3" t="n"/>
@@ -14431,34 +14413,30 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007265</t>
+          <t>BCIO:007267</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>provide positive social consequence for behaviour BCT</t>
+          <t>provide positive social consequence for approximating behaviour BCT</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide positive consequence for approximating behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for behaviour BCT</t>
+          <t>provide positive consequence for approximating behaviour BCT</t>
         </is>
       </c>
       <c r="E240" s="3" t="n"/>
       <c r="F240" s="3" t="n"/>
-      <c r="G240" s="3" t="inlineStr">
-        <is>
-          <t>BCT10.4 Social reward</t>
-        </is>
-      </c>
+      <c r="G240" s="3" t="n"/>
       <c r="H240" s="3" t="inlineStr">
         <is>
-          <t>social reward</t>
+          <t>social reward for approximating behaviour</t>
         </is>
       </c>
       <c r="I240" s="3" t="n"/>
@@ -14484,7 +14462,7 @@
       <c r="Q240" s="3" t="n"/>
       <c r="R240" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S240" s="3" t="inlineStr">
@@ -14497,30 +14475,34 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007268</t>
+          <t>BCIO:007265</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>provide positive social consequence for completion of behavioural sequence BCT</t>
+          <t>provide positive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for completion of behavioural sequence BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide positive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for completion of behavioural sequence BCT</t>
+          <t>provide positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E241" s="3" t="n"/>
       <c r="F241" s="3" t="n"/>
-      <c r="G241" s="3" t="n"/>
+      <c r="G241" s="3" t="inlineStr">
+        <is>
+          <t>BCT10.4 Social reward</t>
+        </is>
+      </c>
       <c r="H241" s="3" t="inlineStr">
         <is>
-          <t>social reward for completion of behavoural sequence</t>
+          <t>social reward</t>
         </is>
       </c>
       <c r="I241" s="3" t="n"/>
@@ -14546,7 +14528,7 @@
       <c r="Q241" s="3" t="n"/>
       <c r="R241" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S241" s="3" t="inlineStr">
@@ -14559,22 +14541,22 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007269</t>
+          <t>BCIO:007268</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>provide positive social consequence for incompatible behaviour BCT</t>
+          <t>provide positive social consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for incompatible behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide positive consequence for completion of behavioural sequence BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for incompatible behaviour BCT</t>
+          <t>provide positive consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="E242" s="3" t="n"/>
@@ -14582,7 +14564,7 @@
       <c r="G242" s="3" t="n"/>
       <c r="H242" s="3" t="inlineStr">
         <is>
-          <t>social reward for incompatible behaviour</t>
+          <t>social reward for completion of behavoural sequence</t>
         </is>
       </c>
       <c r="I242" s="3" t="n"/>
@@ -14621,22 +14603,22 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007271</t>
+          <t>BCIO:007269</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>provide positive social consequence for outcome of behaviour BCT</t>
+          <t>provide positive social consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide positive consequence for incompatible behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for outcome of behaviour BCT</t>
+          <t>provide positive consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="E243" s="3" t="n"/>
@@ -14644,7 +14626,7 @@
       <c r="G243" s="3" t="n"/>
       <c r="H243" s="3" t="inlineStr">
         <is>
-          <t>social reward</t>
+          <t>social reward for incompatible behaviour</t>
         </is>
       </c>
       <c r="I243" s="3" t="n"/>
@@ -14683,22 +14665,22 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007270</t>
+          <t>BCIO:007271</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>provide positive social consequence for situation specific behaviour BCT</t>
+          <t>provide positive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for  situation specific behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide positive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for situation specific behaviour BCT</t>
+          <t>provide positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E244" s="3" t="n"/>
@@ -14706,7 +14688,7 @@
       <c r="G244" s="3" t="n"/>
       <c r="H244" s="3" t="inlineStr">
         <is>
-          <t>social reward for situation specific behaviour</t>
+          <t>social reward</t>
         </is>
       </c>
       <c r="I244" s="3" t="n"/>
@@ -14745,22 +14727,22 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007273</t>
+          <t>BCIO:007270</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive consequence for behaviour BCT</t>
+          <t>provide positive social consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide aversive consequence for behaviour BCT&gt; that provides the consequence at increasingly less frequent intervals.</t>
+          <t>A &lt;provide positive consequence for  situation specific behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for behaviour BCT</t>
+          <t>provide positive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="E245" s="3" t="n"/>
@@ -14768,11 +14750,15 @@
       <c r="G245" s="3" t="n"/>
       <c r="H245" s="3" t="inlineStr">
         <is>
-          <t>reduce punishment frequency</t>
+          <t>social reward for situation specific behaviour</t>
         </is>
       </c>
       <c r="I245" s="3" t="n"/>
-      <c r="J245" s="3" t="n"/>
+      <c r="J245" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -14790,7 +14776,7 @@
       <c r="Q245" s="3" t="n"/>
       <c r="R245" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S245" s="3" t="inlineStr">
@@ -14803,22 +14789,22 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007276</t>
+          <t>BCIO:007273</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide aversive consequence for outcome of behaviour BCT&gt; that provides the consequence at increasingly less frequent intervals.</t>
+          <t>A &lt;provide aversive consequence for behaviour BCT&gt; that provides the consequence at increasingly less frequent intervals.</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for outcome of behaviour BCT</t>
+          <t>provide aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E246" s="3" t="n"/>
@@ -14861,22 +14847,22 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007274</t>
+          <t>BCIO:007276</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive material consequence for behaviour BCT</t>
+          <t>provide reduced frequency of aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide reduced frequency of aversive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide aversive consequence for outcome of behaviour BCT&gt; that provides the consequence at increasingly less frequent intervals.</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive consequence for behaviour BCT</t>
+          <t>provide aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E247" s="3" t="n"/>
@@ -14884,7 +14870,7 @@
       <c r="G247" s="3" t="n"/>
       <c r="H247" s="3" t="inlineStr">
         <is>
-          <t>reduce material punishment frequency</t>
+          <t>reduce punishment frequency</t>
         </is>
       </c>
       <c r="I247" s="3" t="n"/>
@@ -14919,22 +14905,22 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007275</t>
+          <t>BCIO:007274</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive material consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of aversive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide reduced frequency of aversive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide reduced frequency of aversive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E248" s="3" t="n"/>
@@ -14977,22 +14963,22 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007277</t>
+          <t>BCIO:007275</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive social consequence for behaviour BCT</t>
+          <t>provide reduced frequency of aversive material consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide reduced frequency of aversive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide reduced frequency of aversive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive consequence for behaviour BCT</t>
+          <t>provide reduced frequency of aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E249" s="3" t="n"/>
@@ -15000,15 +14986,11 @@
       <c r="G249" s="3" t="n"/>
       <c r="H249" s="3" t="inlineStr">
         <is>
-          <t>reduce social punishment frequency</t>
+          <t>reduce material punishment frequency</t>
         </is>
       </c>
       <c r="I249" s="3" t="n"/>
-      <c r="J249" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="J249" s="3" t="n"/>
       <c r="K249" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -15039,22 +15021,22 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007278</t>
+          <t>BCIO:007277</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive social consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of aversive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide reduced frequency of aversive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide reduced frequency of aversive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E250" s="3" t="n"/>
@@ -15101,38 +15083,38 @@
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007279</t>
+          <t>BCIO:007278</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive consequence for behaviour BCT</t>
+          <t>provide reduced frequency of aversive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for behaviour BCT&gt; that provides the consequence at increasingly less frequent intervals.</t>
+          <t>A &lt;provide reduced frequency of aversive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for behaviour BCT</t>
+          <t>provide reduced frequency of aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E251" s="3" t="n"/>
       <c r="F251" s="3" t="n"/>
-      <c r="G251" s="3" t="inlineStr">
-        <is>
-          <t>BCT14.9 Reduce reward frequency</t>
-        </is>
-      </c>
+      <c r="G251" s="3" t="n"/>
       <c r="H251" s="3" t="inlineStr">
         <is>
-          <t>thinning, reduce reward frequency</t>
+          <t>reduce social punishment frequency</t>
         </is>
       </c>
       <c r="I251" s="3" t="n"/>
-      <c r="J251" s="3" t="n"/>
+      <c r="J251" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -15150,7 +15132,7 @@
       <c r="Q251" s="3" t="n"/>
       <c r="R251" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S251" s="3" t="inlineStr">
@@ -15163,27 +15145,31 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007281</t>
+          <t>BCIO:007279</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for outcome of behaviour BCT&gt; that provides the consequence at increasingly less frequent intervals.</t>
+          <t>A &lt;provide positive consequence for behaviour BCT&gt; that provides the consequence at increasingly less frequent intervals.</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for outcome of behaviour BCT</t>
+          <t>provide positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E252" s="3" t="n"/>
       <c r="F252" s="3" t="n"/>
-      <c r="G252" s="3" t="n"/>
+      <c r="G252" s="3" t="inlineStr">
+        <is>
+          <t>BCT14.9 Reduce reward frequency</t>
+        </is>
+      </c>
       <c r="H252" s="3" t="inlineStr">
         <is>
           <t>thinning, reduce reward frequency</t>
@@ -15221,22 +15207,22 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007280</t>
+          <t>BCIO:007281</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive material consequence for behaviour BCT</t>
+          <t>provide reduced frequency of positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide reduced frequency of positive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide positive consequence for outcome of behaviour BCT&gt; that provides the consequence at increasingly less frequent intervals.</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive consequence for behaviour BCT</t>
+          <t>provide positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E253" s="3" t="n"/>
@@ -15244,7 +15230,7 @@
       <c r="G253" s="3" t="n"/>
       <c r="H253" s="3" t="inlineStr">
         <is>
-          <t>reduce material reward frequency</t>
+          <t>thinning, reduce reward frequency</t>
         </is>
       </c>
       <c r="I253" s="3" t="n"/>
@@ -15279,22 +15265,22 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007272</t>
+          <t>BCIO:007280</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive material consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of positive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide reduced frequency of positive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide reduced frequency of positive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E254" s="3" t="n"/>
@@ -15337,22 +15323,22 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007282</t>
+          <t>BCIO:007272</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive social consequence for behaviour BCT</t>
+          <t>provide reduced frequency of positive material consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide reduced frequency of positive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide reduced frequency of positive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive consequence for behaviour BCT</t>
+          <t>provide reduced frequency of positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E255" s="3" t="n"/>
@@ -15360,15 +15346,11 @@
       <c r="G255" s="3" t="n"/>
       <c r="H255" s="3" t="inlineStr">
         <is>
-          <t>reduce social reward frequency</t>
+          <t>reduce material reward frequency</t>
         </is>
       </c>
       <c r="I255" s="3" t="n"/>
-      <c r="J255" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="J255" s="3" t="n"/>
       <c r="K255" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -15399,22 +15381,22 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007283</t>
+          <t>BCIO:007282</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive social consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of positive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide reduced frequency of positive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide reduced frequency of positive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E256" s="3" t="n"/>
@@ -15461,38 +15443,38 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007053</t>
+          <t>BCIO:007283</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">re-attribute cause BCT </t>
+          <t>provide reduced frequency of positive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>A &lt;suggest different perspective on behaviour BCT&gt; that involves eliciting the person's beliefs about, and suggesting alternative beliefs about, the causes of the behaviour.</t>
+          <t>A &lt;provide reduced frequency of positive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
         <is>
-          <t>suggest different perspective on behaviour BCT</t>
+          <t>provide reduced frequency of positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E257" s="3" t="n"/>
       <c r="F257" s="3" t="n"/>
-      <c r="G257" s="3" t="inlineStr">
-        <is>
-          <t>BCT4.3 Re-attribution</t>
-        </is>
-      </c>
+      <c r="G257" s="3" t="n"/>
       <c r="H257" s="3" t="inlineStr">
         <is>
-          <t>re-attribution</t>
+          <t>reduce social reward frequency</t>
         </is>
       </c>
       <c r="I257" s="3" t="n"/>
-      <c r="J257" s="3" t="n"/>
+      <c r="J257" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -15510,7 +15492,7 @@
       <c r="Q257" s="3" t="n"/>
       <c r="R257" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S257" s="3" t="inlineStr">
@@ -15523,42 +15505,38 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007019</t>
+          <t>BCIO:007053</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">record behaviour without feedback BCT </t>
+          <t xml:space="preserve">re-attribute cause BCT </t>
         </is>
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>A &lt;monitoring BCT&gt; that records current performance of the behaviour with the person’s knowledge but without providing feedback about their behaviour.</t>
+          <t>A &lt;suggest different perspective on behaviour BCT&gt; that involves eliciting the person's beliefs about, and suggesting alternative beliefs about, the causes of the behaviour.</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>monitoring BCT</t>
+          <t>suggest different perspective on behaviour BCT</t>
         </is>
       </c>
       <c r="E258" s="3" t="n"/>
       <c r="F258" s="3" t="n"/>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>BCT2.1 Monitoring of behaviour by others without feedback</t>
+          <t>BCT4.3 Re-attribution</t>
         </is>
       </c>
       <c r="H258" s="3" t="inlineStr">
         <is>
-          <t>monitoring</t>
+          <t>re-attribution</t>
         </is>
       </c>
       <c r="I258" s="3" t="n"/>
-      <c r="J258" s="3" t="inlineStr">
-        <is>
-          <t>The monitoring agent can be a human or a technical device. If recording is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if feedback given, code only 'provide feedback on behaviour BCT' and not this class; if recording outcomes code 'record outcome of behaviour without feedback BCT'.</t>
-        </is>
-      </c>
+      <c r="J258" s="3" t="n"/>
       <c r="K258" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -15589,17 +15567,17 @@
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007021</t>
+          <t>BCIO:007019</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">record outcome of behaviour without feedback BCT </t>
+          <t xml:space="preserve">record behaviour without feedback BCT </t>
         </is>
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>A &lt;monitoring BCT&gt; that records an outcome of performing the behaviour with the person's knowledge but without providing feedback about the outcome.</t>
+          <t>A &lt;monitoring BCT&gt; that records current performance of the behaviour with the person’s knowledge but without providing feedback about their behaviour.</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
@@ -15611,14 +15589,18 @@
       <c r="F259" s="3" t="n"/>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>BCT2.5 Monitoring outcome(s) of behaviour by others without feedback</t>
-        </is>
-      </c>
-      <c r="H259" s="3" t="n"/>
+          <t>BCT2.1 Monitoring of behaviour by others without feedback</t>
+        </is>
+      </c>
+      <c r="H259" s="3" t="inlineStr">
+        <is>
+          <t>monitoring</t>
+        </is>
+      </c>
       <c r="I259" s="3" t="n"/>
       <c r="J259" s="3" t="inlineStr">
         <is>
-          <t>The monitoring agent can be a human or a technical device. If recording is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if feedback given, code only 'provide feedback on outcome of behaviour BCT' and not this class; if recording behaviour code 'record behaviour without feedback BCT'.</t>
+          <t>The monitoring agent can be a human or a technical device. If recording is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if feedback given, code only 'provide feedback on behaviour BCT' and not this class; if recording outcomes code 'record outcome of behaviour without feedback BCT'.</t>
         </is>
       </c>
       <c r="K259" s="3" t="inlineStr">
@@ -15651,40 +15633,36 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007084</t>
+          <t>BCIO:007021</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>reduce cue frequency BCTs</t>
+          <t xml:space="preserve">record outcome of behaviour without feedback BCT </t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>An &lt;alter external stimulus BCT&gt; in which cues for the behaviour are presented less frequently.</t>
+          <t>A &lt;monitoring BCT&gt; that records an outcome of performing the behaviour with the person's knowledge but without providing feedback about the outcome.</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>alter external stimulus BCT</t>
+          <t>monitoring BCT</t>
         </is>
       </c>
       <c r="E260" s="3" t="n"/>
       <c r="F260" s="3" t="n"/>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>BCT7.3 Reduce prompts/cues</t>
-        </is>
-      </c>
-      <c r="H260" s="3" t="inlineStr">
-        <is>
-          <t>fading</t>
-        </is>
-      </c>
+          <t>BCT2.5 Monitoring outcome(s) of behaviour by others without feedback</t>
+        </is>
+      </c>
+      <c r="H260" s="3" t="n"/>
       <c r="I260" s="3" t="n"/>
       <c r="J260" s="3" t="inlineStr">
         <is>
-          <t>The reduction in frequency of cue presentation can be gradual or rapid. This BCT is concerned with reducing the frequency of cue presentation. In contrast, in "reduce exposure to cues for the behaviour BCT", the cue frequency may remain unchanged but the person's exposure to the presentation of the cue is reduced.</t>
+          <t>The monitoring agent can be a human or a technical device. If recording is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if feedback given, code only 'provide feedback on outcome of behaviour BCT' and not this class; if recording behaviour code 'record behaviour without feedback BCT'.</t>
         </is>
       </c>
       <c r="K260" s="3" t="inlineStr">
@@ -15704,7 +15682,7 @@
       <c r="Q260" s="3" t="n"/>
       <c r="R260" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S260" s="3" t="inlineStr">
@@ -15717,32 +15695,40 @@
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007284</t>
+          <t>BCIO:007084</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>reduce distraction BCT</t>
+          <t>reduce cue frequency BCTs</t>
         </is>
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>A &lt;restructure the physical environment BCT&gt; that reduces an alternative focus for attention for the person to concentrate on internal or external states or events associated with the behaviour.</t>
+          <t>An &lt;alter external stimulus BCT&gt; in which cues for the behaviour are presented less frequently.</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
-          <t>restructure the physical environment BCT</t>
+          <t>alter external stimulus BCT</t>
         </is>
       </c>
       <c r="E261" s="3" t="n"/>
       <c r="F261" s="3" t="n"/>
-      <c r="G261" s="3" t="n"/>
-      <c r="H261" s="3" t="n"/>
+      <c r="G261" s="3" t="inlineStr">
+        <is>
+          <t>BCT7.3 Reduce prompts/cues</t>
+        </is>
+      </c>
+      <c r="H261" s="3" t="inlineStr">
+        <is>
+          <t>fading</t>
+        </is>
+      </c>
       <c r="I261" s="3" t="n"/>
       <c r="J261" s="3" t="inlineStr">
         <is>
-          <t>Reducing a distraction to zero is equivalent to removing a distraction</t>
+          <t>The reduction in frequency of cue presentation can be gradual or rapid. This BCT is concerned with reducing the frequency of cue presentation. In contrast, in "reduce exposure to cues for the behaviour BCT", the cue frequency may remain unchanged but the person's exposure to the presentation of the cue is reduced.</t>
         </is>
       </c>
       <c r="K261" s="3" t="inlineStr">
@@ -15775,36 +15761,32 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007153</t>
+          <t>BCIO:007284</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">reduce exposure to cues for the behaviour BCT </t>
+          <t>reduce distraction BCT</t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">An &lt;alter external stimulus BCT&gt; that reduces an external stimulus that signals the behaviour. </t>
+          <t>A &lt;restructure the physical environment BCT&gt; that reduces an alternative focus for attention for the person to concentrate on internal or external states or events associated with the behaviour.</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>alter external stimulus BCT</t>
+          <t>restructure the physical environment BCT</t>
         </is>
       </c>
       <c r="E262" s="3" t="n"/>
       <c r="F262" s="3" t="n"/>
-      <c r="G262" s="3" t="inlineStr">
-        <is>
-          <t>BCT12.3 Avoidance/reducing exposure to cues for the behaviour</t>
-        </is>
-      </c>
+      <c r="G262" s="3" t="n"/>
       <c r="H262" s="3" t="n"/>
       <c r="I262" s="3" t="n"/>
       <c r="J262" s="3" t="inlineStr">
         <is>
-          <t>The reduction in exposure can be gradual, as in the technique of "fading" or not so gradual. This BCT is concerned with reducing the person's exposure to the cue, while the cue frequency may remain unchanged. In contrast, "reduce cue frequency BCT" is concerned with a reduction in the number of times with which the cue is presented. This BCT may also involve 'restructure the physical environment BCT' and/or 'restructure the social environment BCT'.</t>
+          <t>Reducing a distraction to zero is equivalent to removing a distraction</t>
         </is>
       </c>
       <c r="K262" s="3" t="inlineStr">
@@ -15824,147 +15806,155 @@
       <c r="Q262" s="3" t="n"/>
       <c r="R262" s="3" t="inlineStr">
         <is>
+          <t>LZ</t>
+        </is>
+      </c>
+      <c r="S262" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T262" s="3" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:007153</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reduce exposure to cues for the behaviour BCT </t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An &lt;alter external stimulus BCT&gt; that reduces an external stimulus that signals the behaviour. </t>
+        </is>
+      </c>
+      <c r="D263" s="3" t="inlineStr">
+        <is>
+          <t>alter external stimulus BCT</t>
+        </is>
+      </c>
+      <c r="E263" s="3" t="n"/>
+      <c r="F263" s="3" t="n"/>
+      <c r="G263" s="3" t="inlineStr">
+        <is>
+          <t>BCT12.3 Avoidance/reducing exposure to cues for the behaviour</t>
+        </is>
+      </c>
+      <c r="H263" s="3" t="n"/>
+      <c r="I263" s="3" t="n"/>
+      <c r="J263" s="3" t="inlineStr">
+        <is>
+          <t>The reduction in exposure can be gradual, as in the technique of "fading" or not so gradual. This BCT is concerned with reducing the person's exposure to the cue, while the cue frequency may remain unchanged. In contrast, "reduce cue frequency BCT" is concerned with a reduction in the number of times with which the cue is presented. This BCT may also involve 'restructure the physical environment BCT' and/or 'restructure the social environment BCT'.</t>
+        </is>
+      </c>
+      <c r="K263" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="L263" s="3" t="n"/>
+      <c r="M263" s="3" t="n"/>
+      <c r="N263" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O263" s="3" t="n"/>
+      <c r="P263" s="3" t="n"/>
+      <c r="Q263" s="3" t="n"/>
+      <c r="R263" s="3" t="inlineStr">
+        <is>
           <t>lz; LZ</t>
         </is>
       </c>
-      <c r="S262" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T262" s="3" t="n"/>
-    </row>
-    <row r="263">
-      <c r="A263" s="2" t="inlineStr">
+      <c r="S263" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T263" s="3" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
         <is>
           <t>BCIO:050994</t>
         </is>
       </c>
-      <c r="B263" s="2" t="inlineStr">
+      <c r="B264" s="2" t="inlineStr">
         <is>
           <t>reduce time needed to perform behaviour BCT</t>
         </is>
       </c>
-      <c r="C263" s="2" t="inlineStr">
+      <c r="C264" s="2" t="inlineStr">
         <is>
           <t>A &lt;restructure the physical environment BCT&gt; that reduces the amount of time required for the behaviour to be undertaken.</t>
         </is>
       </c>
-      <c r="D263" s="2" t="inlineStr">
+      <c r="D264" s="2" t="inlineStr">
         <is>
           <t>restructure the physical environment BCT</t>
         </is>
       </c>
-      <c r="E263" s="2" t="n"/>
-      <c r="F263" s="2" t="n"/>
-      <c r="G263" s="2" t="n"/>
-      <c r="H263" s="2" t="n"/>
-      <c r="I263" s="2" t="n"/>
-      <c r="J263" s="2" t="n"/>
-      <c r="K263" s="2" t="n"/>
-      <c r="L263" s="2" t="n"/>
-      <c r="M263" s="2" t="n"/>
-      <c r="N263" s="2" t="inlineStr">
+      <c r="E264" s="2" t="n"/>
+      <c r="F264" s="2" t="n"/>
+      <c r="G264" s="2" t="n"/>
+      <c r="H264" s="2" t="n"/>
+      <c r="I264" s="2" t="n"/>
+      <c r="J264" s="2" t="n"/>
+      <c r="K264" s="2" t="n"/>
+      <c r="L264" s="2" t="n"/>
+      <c r="M264" s="2" t="n"/>
+      <c r="N264" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="O263" s="2" t="n"/>
-      <c r="P263" s="2" t="n"/>
-      <c r="Q263" s="2" t="n"/>
-      <c r="R263" s="2" t="n"/>
-      <c r="S263" s="2" t="n">
+      <c r="O264" s="2" t="n"/>
+      <c r="P264" s="2" t="n"/>
+      <c r="Q264" s="2" t="n"/>
+      <c r="R264" s="2" t="n"/>
+      <c r="S264" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T263" s="2" t="n"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="3" t="inlineStr">
-        <is>
-          <t>BCIO:007056</t>
-        </is>
-      </c>
-      <c r="B264" s="3" t="inlineStr">
-        <is>
-          <t>reframe past behaviour BCT</t>
-        </is>
-      </c>
-      <c r="C264" s="3" t="inlineStr">
-        <is>
-          <t>A &lt;suggest different perspective on behaviour BCT&gt; that involves reattributing a person's successes to internal, stable or global factors or failures to external, unstable or specific factors.</t>
-        </is>
-      </c>
-      <c r="D264" s="3" t="inlineStr">
-        <is>
-          <t>suggest different perspective on behaviour BCT</t>
-        </is>
-      </c>
-      <c r="E264" s="3" t="n"/>
-      <c r="F264" s="3" t="n"/>
-      <c r="G264" s="3" t="inlineStr">
-        <is>
-          <t>BCT13.2 Framing/reframing</t>
-        </is>
-      </c>
-      <c r="H264" s="3" t="inlineStr">
-        <is>
-          <t>cognitive re-structuring, re-attribution</t>
-        </is>
-      </c>
-      <c r="I264" s="3" t="n"/>
-      <c r="J264" s="3" t="n"/>
-      <c r="K264" s="3" t="inlineStr">
-        <is>
-          <t>behaviour change technique</t>
-        </is>
-      </c>
-      <c r="L264" s="3" t="n"/>
-      <c r="M264" s="3" t="n"/>
-      <c r="N264" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="O264" s="3" t="n"/>
-      <c r="P264" s="3" t="n"/>
-      <c r="Q264" s="3" t="n"/>
-      <c r="R264" s="3" t="inlineStr">
-        <is>
-          <t>lz; LZ</t>
-        </is>
-      </c>
-      <c r="S264" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T264" s="3" t="n"/>
+      <c r="T264" s="2" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007060</t>
+          <t>BCIO:007056</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>remind about personal capability BCT</t>
+          <t>reframe past behaviour BCT</t>
         </is>
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>A &lt;prompt thinking related to successful performance BCT&gt; that reminds the person of their skills and abilities that are relevant to the performance of the behaviour.</t>
+          <t>A &lt;suggest different perspective on behaviour BCT&gt; that involves reattributing a person's successes to internal, stable or global factors or failures to external, unstable or specific factors.</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
         <is>
-          <t>prompt thinking related to successful performance BCT</t>
+          <t>suggest different perspective on behaviour BCT</t>
         </is>
       </c>
       <c r="E265" s="3" t="n"/>
       <c r="F265" s="3" t="n"/>
-      <c r="G265" s="3" t="n"/>
-      <c r="H265" s="3" t="n"/>
+      <c r="G265" s="3" t="inlineStr">
+        <is>
+          <t>BCT13.2 Framing/reframing</t>
+        </is>
+      </c>
+      <c r="H265" s="3" t="inlineStr">
+        <is>
+          <t>cognitive re-structuring, re-attribution</t>
+        </is>
+      </c>
       <c r="I265" s="3" t="n"/>
       <c r="J265" s="3" t="n"/>
       <c r="K265" s="3" t="inlineStr">
@@ -15984,7 +15974,7 @@
       <c r="Q265" s="3" t="n"/>
       <c r="R265" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S265" s="3" t="inlineStr">
@@ -15997,42 +15987,30 @@
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007286</t>
+          <t>BCIO:007060</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>remove aversive consequence for behaviour BCT</t>
+          <t>remind about personal capability BCT</t>
         </is>
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove consequence for behaviour BCT&gt; where the consequence is aversive.</t>
+          <t>A &lt;prompt thinking related to successful performance BCT&gt; that reminds the person of their skills and abilities that are relevant to the performance of the behaviour.</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>remove consequence for behaviour BCT</t>
+          <t>prompt thinking related to successful performance BCT</t>
         </is>
       </c>
       <c r="E266" s="3" t="n"/>
       <c r="F266" s="3" t="n"/>
-      <c r="G266" s="3" t="inlineStr">
-        <is>
-          <t>BCT14.10 Remove punishment</t>
-        </is>
-      </c>
-      <c r="H266" s="3" t="inlineStr">
-        <is>
-          <t>negative reinforcement, remove punishment</t>
-        </is>
-      </c>
+      <c r="G266" s="3" t="n"/>
+      <c r="H266" s="3" t="n"/>
       <c r="I266" s="3" t="n"/>
-      <c r="J266" s="3" t="inlineStr">
-        <is>
-          <t>To qualify as aversive, the consequence should have been aversively valued by the person receiving it.</t>
-        </is>
-      </c>
+      <c r="J266" s="3" t="n"/>
       <c r="K266" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -16050,7 +16028,7 @@
       <c r="Q266" s="3" t="n"/>
       <c r="R266" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S266" s="3" t="inlineStr">
@@ -16063,27 +16041,31 @@
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007289</t>
+          <t>BCIO:007286</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>remove aversive consequence for outcome of behaviour BCT</t>
+          <t>remove aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove consequence for outcome of behaviour BCT&gt; in which the consequence is aversive.</t>
+          <t>A &lt;remove consequence for behaviour BCT&gt; where the consequence is aversive.</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
         <is>
-          <t>remove consequence for outcome of behaviour BCT</t>
+          <t>remove consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E267" s="3" t="n"/>
       <c r="F267" s="3" t="n"/>
-      <c r="G267" s="3" t="n"/>
+      <c r="G267" s="3" t="inlineStr">
+        <is>
+          <t>BCT14.10 Remove punishment</t>
+        </is>
+      </c>
       <c r="H267" s="3" t="inlineStr">
         <is>
           <t>negative reinforcement, remove punishment</t>
@@ -16125,22 +16107,22 @@
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007287</t>
+          <t>BCIO:007289</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>remove aversive material consequence for behaviour BCT</t>
+          <t>remove aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove aversive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;remove consequence for outcome of behaviour BCT&gt; in which the consequence is aversive.</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>remove aversive consequence for behaviour BCT</t>
+          <t>remove consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E268" s="3" t="n"/>
@@ -16148,11 +16130,15 @@
       <c r="G268" s="3" t="n"/>
       <c r="H268" s="3" t="inlineStr">
         <is>
-          <t>remove material punishment</t>
+          <t>negative reinforcement, remove punishment</t>
         </is>
       </c>
       <c r="I268" s="3" t="n"/>
-      <c r="J268" s="3" t="n"/>
+      <c r="J268" s="3" t="inlineStr">
+        <is>
+          <t>To qualify as aversive, the consequence should have been aversively valued by the person receiving it.</t>
+        </is>
+      </c>
       <c r="K268" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -16183,22 +16169,22 @@
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007288</t>
+          <t>BCIO:007287</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>remove aversive material consequence for outcome of behaviour BCT</t>
+          <t>remove aversive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove aversive consequence for outcome of behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;remove aversive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
         <is>
-          <t>remove aversive consequence for outcome of behaviour BCT</t>
+          <t>remove aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E269" s="3" t="n"/>
@@ -16241,22 +16227,22 @@
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007290</t>
+          <t>BCIO:007288</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>remove aversive social consequence for behaviour BCT</t>
+          <t>remove aversive material consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove aversive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;remove aversive consequence for outcome of behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
-          <t>remove aversive consequence for behaviour BCT</t>
+          <t>remove aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E270" s="3" t="n"/>
@@ -16264,15 +16250,11 @@
       <c r="G270" s="3" t="n"/>
       <c r="H270" s="3" t="inlineStr">
         <is>
-          <t>remove social punishment</t>
+          <t>remove material punishment</t>
         </is>
       </c>
       <c r="I270" s="3" t="n"/>
-      <c r="J270" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="J270" s="3" t="n"/>
       <c r="K270" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -16303,22 +16285,22 @@
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007291</t>
+          <t>BCIO:007290</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>remove aversive social consequence for outcome of behaviour BCT</t>
+          <t>remove aversive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove aversive consequence for outcome of behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;remove aversive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
         <is>
-          <t>remove aversive consequence for outcome of behaviour BCT</t>
+          <t>remove aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E271" s="3" t="n"/>
@@ -16365,38 +16347,38 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>BCIO:050331</t>
+          <t>BCIO:007291</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>remove aversive stimulus BCT</t>
+          <t>remove aversive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>An &lt;alter external stimulus BCT&gt; that involves removing an aversive stimulus to bring about behaviour change.</t>
+          <t>A &lt;remove aversive consequence for outcome of behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>alter external stimulus BCT</t>
+          <t>remove aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E272" s="3" t="n"/>
       <c r="F272" s="3" t="n"/>
-      <c r="G272" s="3" t="inlineStr">
-        <is>
-          <t>BCT7.5 Remove aversive stimulus</t>
-        </is>
-      </c>
+      <c r="G272" s="3" t="n"/>
       <c r="H272" s="3" t="inlineStr">
         <is>
-          <t>escape learning</t>
+          <t>remove social punishment</t>
         </is>
       </c>
       <c r="I272" s="3" t="n"/>
-      <c r="J272" s="3" t="n"/>
+      <c r="J272" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="K272" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -16414,7 +16396,7 @@
       <c r="Q272" s="3" t="n"/>
       <c r="R272" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S272" s="3" t="inlineStr">
@@ -16427,28 +16409,36 @@
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007285</t>
+          <t>BCIO:050331</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>remove consequence for behaviour BCT</t>
+          <t>remove aversive stimulus BCT</t>
         </is>
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>A &lt;behavioural consequence BCT&gt; that removes a previously provided consequence for performing the behaviour.</t>
+          <t>An &lt;alter external stimulus BCT&gt; that involves removing an aversive stimulus to bring about behaviour change.</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
         <is>
-          <t>behavioural consequence BCT</t>
+          <t>alter external stimulus BCT</t>
         </is>
       </c>
       <c r="E273" s="3" t="n"/>
       <c r="F273" s="3" t="n"/>
-      <c r="G273" s="3" t="n"/>
-      <c r="H273" s="3" t="n"/>
+      <c r="G273" s="3" t="inlineStr">
+        <is>
+          <t>BCT7.5 Remove aversive stimulus</t>
+        </is>
+      </c>
+      <c r="H273" s="3" t="inlineStr">
+        <is>
+          <t>escape learning</t>
+        </is>
+      </c>
       <c r="I273" s="3" t="n"/>
       <c r="J273" s="3" t="n"/>
       <c r="K273" s="3" t="inlineStr">
@@ -16481,22 +16471,22 @@
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007292</t>
+          <t>BCIO:007285</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>remove consequence for outcome of behaviour BCT</t>
+          <t>remove consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>An &lt;outcome consequence BCT&gt; that removes a previously provided consequence for an outcome resulting from performing or not performing the behaviour.</t>
+          <t>A &lt;behavioural consequence BCT&gt; that removes a previously provided consequence for performing the behaviour.</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>outcome consequence BCT</t>
+          <t>behavioural consequence BCT</t>
         </is>
       </c>
       <c r="E274" s="3" t="n"/>
@@ -16533,142 +16523,134 @@
       <c r="T274" s="3" t="n"/>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="inlineStr">
+      <c r="A275" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:007292</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="inlineStr">
+        <is>
+          <t>remove consequence for outcome of behaviour BCT</t>
+        </is>
+      </c>
+      <c r="C275" s="3" t="inlineStr">
+        <is>
+          <t>An &lt;outcome consequence BCT&gt; that removes a previously provided consequence for an outcome resulting from performing or not performing the behaviour.</t>
+        </is>
+      </c>
+      <c r="D275" s="3" t="inlineStr">
+        <is>
+          <t>outcome consequence BCT</t>
+        </is>
+      </c>
+      <c r="E275" s="3" t="n"/>
+      <c r="F275" s="3" t="n"/>
+      <c r="G275" s="3" t="n"/>
+      <c r="H275" s="3" t="n"/>
+      <c r="I275" s="3" t="n"/>
+      <c r="J275" s="3" t="n"/>
+      <c r="K275" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="L275" s="3" t="n"/>
+      <c r="M275" s="3" t="n"/>
+      <c r="N275" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O275" s="3" t="n"/>
+      <c r="P275" s="3" t="n"/>
+      <c r="Q275" s="3" t="n"/>
+      <c r="R275" s="3" t="inlineStr">
+        <is>
+          <t>LZ</t>
+        </is>
+      </c>
+      <c r="S275" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T275" s="3" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
         <is>
           <t>BCIO:050995</t>
         </is>
       </c>
-      <c r="B275" s="2" t="inlineStr">
+      <c r="B276" s="2" t="inlineStr">
         <is>
           <t>remove objects from the environment BCT</t>
         </is>
       </c>
-      <c r="C275" s="2" t="inlineStr">
+      <c r="C276" s="2" t="inlineStr">
         <is>
           <t>A &lt;restructure the physical environment BCT&gt; that removes objects from the person’s physical surroundings.</t>
         </is>
       </c>
-      <c r="D275" s="2" t="inlineStr">
+      <c r="D276" s="2" t="inlineStr">
         <is>
           <t>restructure the physical environment BCT</t>
         </is>
       </c>
-      <c r="E275" s="2" t="n"/>
-      <c r="F275" s="2" t="n"/>
-      <c r="G275" s="2" t="n"/>
-      <c r="H275" s="2" t="n"/>
-      <c r="I275" s="2" t="n"/>
-      <c r="J275" s="2" t="n"/>
-      <c r="K275" s="2" t="n"/>
-      <c r="L275" s="2" t="n"/>
-      <c r="M275" s="2" t="n"/>
-      <c r="N275" s="2" t="inlineStr">
+      <c r="E276" s="2" t="n"/>
+      <c r="F276" s="2" t="n"/>
+      <c r="G276" s="2" t="n"/>
+      <c r="H276" s="2" t="n"/>
+      <c r="I276" s="2" t="n"/>
+      <c r="J276" s="2" t="n"/>
+      <c r="K276" s="2" t="n"/>
+      <c r="L276" s="2" t="n"/>
+      <c r="M276" s="2" t="n"/>
+      <c r="N276" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="O275" s="2" t="n"/>
-      <c r="P275" s="2" t="n"/>
-      <c r="Q275" s="2" t="n"/>
-      <c r="R275" s="2" t="n"/>
-      <c r="S275" s="2" t="n">
+      <c r="O276" s="2" t="n"/>
+      <c r="P276" s="2" t="n"/>
+      <c r="Q276" s="2" t="n"/>
+      <c r="R276" s="2" t="n"/>
+      <c r="S276" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T275" s="2" t="n"/>
-    </row>
-    <row r="276">
-      <c r="A276" s="3" t="inlineStr">
-        <is>
-          <t>BCIO:007293</t>
-        </is>
-      </c>
-      <c r="B276" s="3" t="inlineStr">
-        <is>
-          <t>remove positive consequence for behaviour BCT</t>
-        </is>
-      </c>
-      <c r="C276" s="3" t="inlineStr">
-        <is>
-          <t>A &lt;remove consequence for behaviour BCT&gt; where the consequence is positive.</t>
-        </is>
-      </c>
-      <c r="D276" s="3" t="inlineStr">
-        <is>
-          <t>remove consequence for behaviour BCT</t>
-        </is>
-      </c>
-      <c r="E276" s="3" t="n"/>
-      <c r="F276" s="3" t="n"/>
-      <c r="G276" s="3" t="inlineStr">
-        <is>
-          <t>BCT7.4 Remove access to the reward; BCT14.1 Behaviour cost; BCT14.3 Remove reward</t>
-        </is>
-      </c>
-      <c r="H276" s="3" t="inlineStr">
-        <is>
-          <t>time out, response cost, extinction, remove reward</t>
-        </is>
-      </c>
-      <c r="I276" s="3" t="n"/>
-      <c r="J276" s="3" t="inlineStr">
-        <is>
-          <t>To qualify as positive, the consequence should have been positively valued by the person receiving it.</t>
-        </is>
-      </c>
-      <c r="K276" s="3" t="inlineStr">
-        <is>
-          <t>behaviour change technique</t>
-        </is>
-      </c>
-      <c r="L276" s="3" t="n"/>
-      <c r="M276" s="3" t="n"/>
-      <c r="N276" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="O276" s="3" t="n"/>
-      <c r="P276" s="3" t="n"/>
-      <c r="Q276" s="3" t="n"/>
-      <c r="R276" s="3" t="inlineStr">
-        <is>
-          <t>LZ</t>
-        </is>
-      </c>
-      <c r="S276" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T276" s="3" t="n"/>
+      <c r="T276" s="2" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007296</t>
+          <t>BCIO:007293</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>remove positive consequence for outcome of behaviour BCT</t>
+          <t>remove positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove consequence for outcome of behaviour BCT&gt; in which the consequence is positive.</t>
+          <t>A &lt;remove consequence for behaviour BCT&gt; where the consequence is positive.</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
         <is>
-          <t>remove consequence for outcome of behaviour BCT</t>
+          <t>remove consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E277" s="3" t="n"/>
       <c r="F277" s="3" t="n"/>
-      <c r="G277" s="3" t="n"/>
+      <c r="G277" s="3" t="inlineStr">
+        <is>
+          <t>BCT7.4 Remove access to the reward; BCT14.1 Behaviour cost; BCT14.3 Remove reward</t>
+        </is>
+      </c>
       <c r="H277" s="3" t="inlineStr">
         <is>
-          <t>remove reward</t>
+          <t>time out, response cost, extinction, remove reward</t>
         </is>
       </c>
       <c r="I277" s="3" t="n"/>
@@ -16707,22 +16689,22 @@
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007294</t>
+          <t>BCIO:007296</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>remove positive material consequence for behaviour BCT</t>
+          <t>remove positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove positive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;remove consequence for outcome of behaviour BCT&gt; in which the consequence is positive.</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>remove positive consequence for behaviour BCT</t>
+          <t>remove consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E278" s="3" t="n"/>
@@ -16730,11 +16712,15 @@
       <c r="G278" s="3" t="n"/>
       <c r="H278" s="3" t="inlineStr">
         <is>
-          <t>remove material reward</t>
+          <t>remove reward</t>
         </is>
       </c>
       <c r="I278" s="3" t="n"/>
-      <c r="J278" s="3" t="n"/>
+      <c r="J278" s="3" t="inlineStr">
+        <is>
+          <t>To qualify as positive, the consequence should have been positively valued by the person receiving it.</t>
+        </is>
+      </c>
       <c r="K278" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -16765,22 +16751,22 @@
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007295</t>
+          <t>BCIO:007294</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>remove positive material consequence for outcome of behaviour BCT</t>
+          <t>remove positive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove positive consequence for outcome of behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;remove positive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
         <is>
-          <t>remove positive consequence for outcome of behaviour BCT</t>
+          <t>remove positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E279" s="3" t="n"/>
@@ -16823,22 +16809,22 @@
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007297</t>
+          <t>BCIO:007295</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>remove positive social consequence for behaviour BCT</t>
+          <t>remove positive material consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove positive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;remove positive consequence for outcome of behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>remove positive consequence for behaviour BCT</t>
+          <t>remove positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E280" s="3" t="n"/>
@@ -16846,15 +16832,11 @@
       <c r="G280" s="3" t="n"/>
       <c r="H280" s="3" t="inlineStr">
         <is>
-          <t>remove social reward</t>
+          <t>remove material reward</t>
         </is>
       </c>
       <c r="I280" s="3" t="n"/>
-      <c r="J280" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="J280" s="3" t="n"/>
       <c r="K280" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -16885,22 +16867,22 @@
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007298</t>
+          <t>BCIO:007297</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>remove positive social consequence for outcome of behaviour BCT</t>
+          <t>remove positive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove positive consequence for outcome of behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;remove positive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
         <is>
-          <t>remove positive consequence for outcome of behaviour BCT</t>
+          <t>remove positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E281" s="3" t="n"/>
@@ -16947,30 +16929,38 @@
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007150</t>
+          <t>BCIO:007298</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>restructure the environment BCT</t>
+          <t>remove positive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>A &lt;behaviour change technique&gt; that alters the environment in which the behaviour is, or would have been, performed in a way that facilitates or impedes the behaviour.</t>
+          <t>A &lt;remove positive consequence for outcome of behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
         <is>
-          <t>behaviour change technique</t>
+          <t>remove positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E282" s="3" t="n"/>
       <c r="F282" s="3" t="n"/>
       <c r="G282" s="3" t="n"/>
-      <c r="H282" s="3" t="n"/>
+      <c r="H282" s="3" t="inlineStr">
+        <is>
+          <t>remove social reward</t>
+        </is>
+      </c>
       <c r="I282" s="3" t="n"/>
-      <c r="J282" s="3" t="n"/>
+      <c r="J282" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="K282" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -17001,42 +16991,30 @@
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>BCIO:050348</t>
+          <t>BCIO:007150</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>restructure the physical environment BCT</t>
+          <t>restructure the environment BCT</t>
         </is>
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>A &lt;restructure the environment BCT&gt; that alters the physical environment in which the behaviour is, or would have been, performed in a way that facilitates or impedes the behaviour.</t>
+          <t>A &lt;behaviour change technique&gt; that alters the environment in which the behaviour is, or would have been, performed in a way that facilitates or impedes the behaviour.</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr">
         <is>
-          <t>restructure the environment BCT</t>
+          <t>behaviour change technique</t>
         </is>
       </c>
       <c r="E283" s="3" t="n"/>
       <c r="F283" s="3" t="n"/>
-      <c r="G283" s="3" t="inlineStr">
-        <is>
-          <t>BCT12.1 Restructuring the physical environment</t>
-        </is>
-      </c>
-      <c r="H283" s="3" t="inlineStr">
-        <is>
-          <t>physical space reorganisation, environmental modification</t>
-        </is>
-      </c>
+      <c r="G283" s="3" t="n"/>
+      <c r="H283" s="3" t="n"/>
       <c r="I283" s="3" t="n"/>
-      <c r="J283" s="3" t="inlineStr">
-        <is>
-          <t>This may also involve 'reduce exposure to cues for the behaviour BCT'</t>
-        </is>
-      </c>
+      <c r="J283" s="3" t="n"/>
       <c r="K283" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -17054,7 +17032,7 @@
       <c r="Q283" s="3" t="n"/>
       <c r="R283" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S283" s="3" t="inlineStr">
@@ -17067,17 +17045,17 @@
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>BCIO:050349</t>
+          <t>BCIO:050348</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>restructure the social environment BCT</t>
+          <t>restructure the physical environment BCT</t>
         </is>
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>A &lt;restructure the environment BCT&gt; that alters the social environment in which the behaviour is, or would have been, performed in a way that facilitates or impedes the behaviour.</t>
+          <t>A &lt;restructure the environment BCT&gt; that alters the physical environment in which the behaviour is, or would have been, performed in a way that facilitates or impedes the behaviour.</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
@@ -17089,19 +17067,15 @@
       <c r="F284" s="3" t="n"/>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>BCT12.2 Restructuring the social environment</t>
+          <t>BCT12.1 Restructuring the physical environment</t>
         </is>
       </c>
       <c r="H284" s="3" t="inlineStr">
         <is>
-          <t>interpersonal environment restructuring, social context modification</t>
-        </is>
-      </c>
-      <c r="I284" s="3" t="inlineStr">
-        <is>
-          <t>Instructing people in a smoking cessation group to sit in a circle rather than in rows; Instructing schoolchildren to form a single file queue rather than mingle in a crowd.</t>
-        </is>
-      </c>
+          <t>physical space reorganisation, environmental modification</t>
+        </is>
+      </c>
+      <c r="I284" s="3" t="n"/>
       <c r="J284" s="3" t="inlineStr">
         <is>
           <t>This may also involve 'reduce exposure to cues for the behaviour BCT'</t>
@@ -17137,36 +17111,44 @@
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007011</t>
+          <t>BCIO:050349</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">review behaviour goal BCT </t>
+          <t>restructure the social environment BCT</t>
         </is>
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>A &lt;goal directed BCT&gt; that reviews a behavioural goal and considers modifying the goal in light of progress toward the goal.</t>
+          <t>A &lt;restructure the environment BCT&gt; that alters the social environment in which the behaviour is, or would have been, performed in a way that facilitates or impedes the behaviour.</t>
         </is>
       </c>
       <c r="D285" s="3" t="inlineStr">
         <is>
-          <t>goal directed BCT</t>
+          <t>restructure the environment BCT</t>
         </is>
       </c>
       <c r="E285" s="3" t="n"/>
       <c r="F285" s="3" t="n"/>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>BCT1.5 Review behaviour goal(s)</t>
-        </is>
-      </c>
-      <c r="H285" s="3" t="n"/>
-      <c r="I285" s="3" t="n"/>
+          <t>BCT12.2 Restructuring the social environment</t>
+        </is>
+      </c>
+      <c r="H285" s="3" t="inlineStr">
+        <is>
+          <t>interpersonal environment restructuring, social context modification</t>
+        </is>
+      </c>
+      <c r="I285" s="3" t="inlineStr">
+        <is>
+          <t>Instructing people in a smoking cessation group to sit in a circle rather than in rows; Instructing schoolchildren to form a single file queue rather than mingle in a crowd.</t>
+        </is>
+      </c>
       <c r="J285" s="3" t="inlineStr">
         <is>
-          <t>A goal is a cognitive representation of an end state towards which one is striving. If goal specified in terms of behaviour, code this class; if goal unspecified, code 'review outcome goal BCT'; if discrepancy created consider also 'attend to discrepancy between current behaviour and goal BCT'; if modifying the plan to achieve the goal consider also 'review behaviour goal plan BCT'.</t>
+          <t>This may also involve 'reduce exposure to cues for the behaviour BCT'</t>
         </is>
       </c>
       <c r="K285" s="3" t="inlineStr">
@@ -17199,17 +17181,17 @@
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007299</t>
+          <t>BCIO:007011</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">review behaviour goal plan BCT </t>
+          <t xml:space="preserve">review behaviour goal BCT </t>
         </is>
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>A &lt;goal directed BCT&gt; that reviews progress towards a behavioural goal and considers modifying the plan to achieve the goal.</t>
+          <t>A &lt;goal directed BCT&gt; that reviews a behavioural goal and considers modifying the goal in light of progress toward the goal.</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
@@ -17219,12 +17201,16 @@
       </c>
       <c r="E286" s="3" t="n"/>
       <c r="F286" s="3" t="n"/>
-      <c r="G286" s="3" t="n"/>
+      <c r="G286" s="3" t="inlineStr">
+        <is>
+          <t>BCT1.5 Review behaviour goal(s)</t>
+        </is>
+      </c>
       <c r="H286" s="3" t="n"/>
       <c r="I286" s="3" t="n"/>
       <c r="J286" s="3" t="inlineStr">
         <is>
-          <t>A goal is a cognitive representation of an end state towards which one is striving.</t>
+          <t>A goal is a cognitive representation of an end state towards which one is striving. If goal specified in terms of behaviour, code this class; if goal unspecified, code 'review outcome goal BCT'; if discrepancy created consider also 'attend to discrepancy between current behaviour and goal BCT'; if modifying the plan to achieve the goal consider also 'review behaviour goal plan BCT'.</t>
         </is>
       </c>
       <c r="K286" s="3" t="inlineStr">
@@ -17244,7 +17230,7 @@
       <c r="Q286" s="3" t="n"/>
       <c r="R286" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S286" s="3" t="inlineStr">
@@ -17257,17 +17243,17 @@
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007013</t>
+          <t>BCIO:007299</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">review outcome goal BCT </t>
+          <t xml:space="preserve">review behaviour goal plan BCT </t>
         </is>
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>A &lt;goal directed BCT&gt; that reviews an outcome goal and considers modifying the goal in light of achievement.</t>
+          <t>A &lt;goal directed BCT&gt; that reviews progress towards a behavioural goal and considers modifying the plan to achieve the goal.</t>
         </is>
       </c>
       <c r="D287" s="3" t="inlineStr">
@@ -17277,16 +17263,12 @@
       </c>
       <c r="E287" s="3" t="n"/>
       <c r="F287" s="3" t="n"/>
-      <c r="G287" s="3" t="inlineStr">
-        <is>
-          <t>BCT1.7 Review outcome goal(s)</t>
-        </is>
-      </c>
+      <c r="G287" s="3" t="n"/>
       <c r="H287" s="3" t="n"/>
       <c r="I287" s="3" t="n"/>
       <c r="J287" s="3" t="inlineStr">
         <is>
-          <t>A goal is a cognitive representation of an end state towards which one is striving. If goal specified in terms of behaviour, code 'review behaviour goal BCT'; if goal unspecified, code this class; if discrepancy created consider also 'attend to discrepancy between current behaviour and goal BCT'.</t>
+          <t>A goal is a cognitive representation of an end state towards which one is striving.</t>
         </is>
       </c>
       <c r="K287" s="3" t="inlineStr">
@@ -17306,7 +17288,7 @@
       <c r="Q287" s="3" t="n"/>
       <c r="R287" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S287" s="3" t="inlineStr">
@@ -17319,40 +17301,36 @@
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007024</t>
+          <t>BCIO:007013</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">self-monitor behaviour BCT </t>
+          <t xml:space="preserve">review outcome goal BCT </t>
         </is>
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>A &lt;monitoring BCT&gt; in which the person uses a method to monitor and record their behaviour.</t>
+          <t>A &lt;goal directed BCT&gt; that reviews an outcome goal and considers modifying the goal in light of achievement.</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
         <is>
-          <t>monitoring BCT</t>
+          <t>goal directed BCT</t>
         </is>
       </c>
       <c r="E288" s="3" t="n"/>
       <c r="F288" s="3" t="n"/>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>BCT2.3 Self-monitoring of behaviour</t>
-        </is>
-      </c>
-      <c r="H288" s="3" t="inlineStr">
-        <is>
-          <t>self-monitoring</t>
-        </is>
-      </c>
+          <t>BCT1.7 Review outcome goal(s)</t>
+        </is>
+      </c>
+      <c r="H288" s="3" t="n"/>
       <c r="I288" s="3" t="n"/>
       <c r="J288" s="3" t="inlineStr">
         <is>
-          <t>If monitoring is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if self-monitoring of outcome of behaviour, code 'self-monitor outcome of behaviour BCT'.</t>
+          <t>A goal is a cognitive representation of an end state towards which one is striving. If goal specified in terms of behaviour, code 'review behaviour goal BCT'; if goal unspecified, code this class; if discrepancy created consider also 'attend to discrepancy between current behaviour and goal BCT'.</t>
         </is>
       </c>
       <c r="K288" s="3" t="inlineStr">
@@ -17385,17 +17363,17 @@
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007025</t>
+          <t>BCIO:007024</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">self-monitor outcome of behaviour BCT </t>
+          <t xml:space="preserve">self-monitor behaviour BCT </t>
         </is>
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>A &lt;monitoring BCT&gt; in which the person uses a method to monitor and record an outcome of their behaviour.</t>
+          <t>A &lt;monitoring BCT&gt; in which the person uses a method to monitor and record their behaviour.</t>
         </is>
       </c>
       <c r="D289" s="3" t="inlineStr">
@@ -17407,14 +17385,18 @@
       <c r="F289" s="3" t="n"/>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>BCT2.4 Self-monitoring of outcome(s) of behaviour</t>
-        </is>
-      </c>
-      <c r="H289" s="3" t="n"/>
+          <t>BCT2.3 Self-monitoring of behaviour</t>
+        </is>
+      </c>
+      <c r="H289" s="3" t="inlineStr">
+        <is>
+          <t>self-monitoring</t>
+        </is>
+      </c>
       <c r="I289" s="3" t="n"/>
       <c r="J289" s="3" t="inlineStr">
         <is>
-          <t>If monitoring is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if self-monitoring behaviour, code 'self-monitor behaviour BCT'.</t>
+          <t>If monitoring is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if self-monitoring of outcome of behaviour, code 'self-monitor outcome of behaviour BCT'.</t>
         </is>
       </c>
       <c r="K289" s="3" t="inlineStr">
@@ -17447,36 +17429,36 @@
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007003</t>
+          <t>BCIO:007025</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">set behaviour goal BCT </t>
+          <t xml:space="preserve">self-monitor outcome of behaviour BCT </t>
         </is>
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>A &lt;goal setting BCT&gt; that sets a goal for the behaviour to be achieved.</t>
+          <t>A &lt;monitoring BCT&gt; in which the person uses a method to monitor and record an outcome of their behaviour.</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
         <is>
-          <t>goal setting BCT</t>
-        </is>
-      </c>
-      <c r="E290" s="3" t="inlineStr"/>
+          <t>monitoring BCT</t>
+        </is>
+      </c>
+      <c r="E290" s="3" t="n"/>
       <c r="F290" s="3" t="n"/>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>BCT1.1 Goal setting (behaviour)</t>
+          <t>BCT2.4 Self-monitoring of outcome(s) of behaviour</t>
         </is>
       </c>
       <c r="H290" s="3" t="n"/>
       <c r="I290" s="3" t="n"/>
       <c r="J290" s="3" t="inlineStr">
         <is>
-          <t>A goal is a cognitive representation of an end state towards which one is striving. The goal could be set for the self or another person. Only code if there is sufficient evidence that the goal is set as part of intervention; if goal is a behavioural outcome, code 'set outcome goal BCT'; if goal unspecified code 'goal setting BCT'; if the goal defines a specific context, frequency, duration or intensity for the behaviour, also code 'action planning BCT'.</t>
+          <t>If monitoring is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if self-monitoring behaviour, code 'self-monitor behaviour BCT'.</t>
         </is>
       </c>
       <c r="K290" s="3" t="inlineStr">
@@ -17484,7 +17466,7 @@
           <t>behaviour change technique</t>
         </is>
       </c>
-      <c r="L290" s="3" t="inlineStr"/>
+      <c r="L290" s="3" t="n"/>
       <c r="M290" s="3" t="n"/>
       <c r="N290" s="3" t="inlineStr">
         <is>
@@ -17509,38 +17491,38 @@
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007100</t>
+          <t>BCIO:007003</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>set graded tasks BCT</t>
+          <t xml:space="preserve">set behaviour goal BCT </t>
         </is>
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>A &lt;goal directed BCT&gt; that sets easy-to-perform tasks for the person, making them increasingly difficult, but achievable, until the behaviour is performed.</t>
+          <t>A &lt;goal setting BCT&gt; that sets a goal for the behaviour to be achieved.</t>
         </is>
       </c>
       <c r="D291" s="3" t="inlineStr">
         <is>
-          <t>goal directed BCT</t>
+          <t>goal setting BCT</t>
         </is>
       </c>
       <c r="E291" s="3" t="n"/>
       <c r="F291" s="3" t="n"/>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>BCT8.7 Graded tasks</t>
-        </is>
-      </c>
-      <c r="H291" s="3" t="inlineStr">
-        <is>
-          <t>graded tasks</t>
-        </is>
-      </c>
+          <t>BCT1.1 Goal setting (behaviour)</t>
+        </is>
+      </c>
+      <c r="H291" s="3" t="n"/>
       <c r="I291" s="3" t="n"/>
-      <c r="J291" s="3" t="n"/>
+      <c r="J291" s="3" t="inlineStr">
+        <is>
+          <t>A goal is a cognitive representation of an end state towards which one is striving. The goal could be set for the self or another person. Only code if there is sufficient evidence that the goal is set as part of intervention; if goal is a behavioural outcome, code 'set outcome goal BCT'; if goal unspecified code 'goal setting BCT'; if the goal defines a specific context, frequency, duration or intensity for the behaviour, also code 'action planning BCT'.</t>
+        </is>
+      </c>
       <c r="K291" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -17571,34 +17553,38 @@
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007300</t>
+          <t>BCIO:007100</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">set measurable behaviour goal BCT </t>
+          <t>set graded tasks BCT</t>
         </is>
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>A &lt;set behaviour goal BCT&gt; that describes the behaviour to be achieved in terms of a measurable target.</t>
+          <t>A &lt;goal directed BCT&gt; that sets easy-to-perform tasks for the person, making them increasingly difficult, but achievable, until the behaviour is performed.</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">set behaviour goal BCT </t>
+          <t>goal directed BCT</t>
         </is>
       </c>
       <c r="E292" s="3" t="n"/>
       <c r="F292" s="3" t="n"/>
-      <c r="G292" s="3" t="n"/>
-      <c r="H292" s="3" t="n"/>
+      <c r="G292" s="3" t="inlineStr">
+        <is>
+          <t>BCT8.7 Graded tasks</t>
+        </is>
+      </c>
+      <c r="H292" s="3" t="inlineStr">
+        <is>
+          <t>graded tasks</t>
+        </is>
+      </c>
       <c r="I292" s="3" t="n"/>
-      <c r="J292" s="3" t="inlineStr">
-        <is>
-          <t>A behaviour goal might be set in general terms e.g. "to do more physical activity" or in measurable terms e.g. "to do 30 minutes of physical activity five times a week" or "to walk 8000 steps a day." Use this class for measurable behaviour goals</t>
-        </is>
-      </c>
+      <c r="J292" s="3" t="n"/>
       <c r="K292" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -17616,7 +17602,7 @@
       <c r="Q292" s="3" t="n"/>
       <c r="R292" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S292" s="3" t="inlineStr">
@@ -17629,22 +17615,22 @@
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007301</t>
+          <t>BCIO:007300</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">set measurable outcome goal BCT </t>
+          <t xml:space="preserve">set measurable behaviour goal BCT </t>
         </is>
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>A &lt;set outcome goal BCT&gt; that describes the behavioural outcome to be achieved in terms of a measurable target.</t>
+          <t>A &lt;set behaviour goal BCT&gt; that describes the behaviour to be achieved in terms of a measurable target.</t>
         </is>
       </c>
       <c r="D293" s="3" t="inlineStr">
         <is>
-          <t>set outcome goal BCT</t>
+          <t xml:space="preserve">set behaviour goal BCT </t>
         </is>
       </c>
       <c r="E293" s="3" t="n"/>
@@ -17654,7 +17640,7 @@
       <c r="I293" s="3" t="n"/>
       <c r="J293" s="3" t="inlineStr">
         <is>
-          <t>An outcome goal might be set in general terms - e.g. "to lose weight" or in measurable terms - e.g. "to lose 5kg of weight" or "to lose 10% of my body weight". Use this class for measurable outcome goals</t>
+          <t>A behaviour goal might be set in general terms e.g. "to do more physical activity" or in measurable terms e.g. "to do 30 minutes of physical activity five times a week" or "to walk 8000 steps a day." Use this class for measurable behaviour goals</t>
         </is>
       </c>
       <c r="K293" s="3" t="inlineStr">
@@ -17687,36 +17673,32 @@
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007005</t>
+          <t>BCIO:007301</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">set measurable outcome goal BCT </t>
+        </is>
+      </c>
+      <c r="C294" s="3" t="inlineStr">
+        <is>
+          <t>A &lt;set outcome goal BCT&gt; that describes the behavioural outcome to be achieved in terms of a measurable target.</t>
+        </is>
+      </c>
+      <c r="D294" s="3" t="inlineStr">
+        <is>
           <t>set outcome goal BCT</t>
-        </is>
-      </c>
-      <c r="C294" s="3" t="inlineStr">
-        <is>
-          <t>A &lt;goal setting BCT&gt; in which the goal is a positive outcome of performing the behaviour.</t>
-        </is>
-      </c>
-      <c r="D294" s="3" t="inlineStr">
-        <is>
-          <t>goal setting BCT</t>
         </is>
       </c>
       <c r="E294" s="3" t="n"/>
       <c r="F294" s="3" t="n"/>
-      <c r="G294" s="3" t="inlineStr">
-        <is>
-          <t>BCT1.3 Goal setting (outcome)</t>
-        </is>
-      </c>
+      <c r="G294" s="3" t="n"/>
       <c r="H294" s="3" t="n"/>
       <c r="I294" s="3" t="n"/>
       <c r="J294" s="3" t="inlineStr">
         <is>
-          <t>A goal is a cognitive representation of an end state towards which one is striving. The goal could be set for the self or another person. Only code guidelines if set as a goal in an intervention context; if goal is a behaviour, code 'set behaviour goal BCT'; if goal unspecified code 'goal setting BCT'.</t>
+          <t>An outcome goal might be set in general terms - e.g. "to lose weight" or in measurable terms - e.g. "to lose 5kg of weight" or "to lose 10% of my body weight". Use this class for measurable outcome goals</t>
         </is>
       </c>
       <c r="K294" s="3" t="inlineStr">
@@ -17736,7 +17718,7 @@
       <c r="Q294" s="3" t="n"/>
       <c r="R294" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S294" s="3" t="inlineStr">
@@ -17749,36 +17731,36 @@
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007028</t>
+          <t>BCIO:007005</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>social support BCT</t>
+          <t>set outcome goal BCT</t>
         </is>
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>A &lt;behaviour change technique&gt; that involves taking steps to secure or deliver the support or aid of another person.</t>
+          <t>A &lt;goal setting BCT&gt; in which the goal is a positive outcome of performing the behaviour.</t>
         </is>
       </c>
       <c r="D295" s="3" t="inlineStr">
         <is>
-          <t>behaviour change technique</t>
+          <t>goal setting BCT</t>
         </is>
       </c>
       <c r="E295" s="3" t="n"/>
       <c r="F295" s="3" t="n"/>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>BCT3.1 Social support (unspecified)</t>
+          <t>BCT1.3 Goal setting (outcome)</t>
         </is>
       </c>
       <c r="H295" s="3" t="n"/>
       <c r="I295" s="3" t="n"/>
       <c r="J295" s="3" t="inlineStr">
         <is>
-          <t>Attending a group class and/or mention of ‘follow-up’ does not necessarily apply this BCT, support must be explicitly mentioned.</t>
+          <t>A goal is a cognitive representation of an end state towards which one is striving. The goal could be set for the self or another person. Only code guidelines if set as a goal in an intervention context; if goal is a behaviour, code 'set behaviour goal BCT'; if goal unspecified code 'goal setting BCT'.</t>
         </is>
       </c>
       <c r="K295" s="3" t="inlineStr">
@@ -17811,40 +17793,36 @@
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007095</t>
+          <t>BCIO:007028</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">substitute behaviour BCT </t>
+          <t>social support BCT</t>
         </is>
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>An &lt;advise specific behaviour BCT&gt; that advises the person to replace the unwanted behaviour with another behaviour.</t>
+          <t>A &lt;behaviour change technique&gt; that involves taking steps to secure or deliver the support or aid of another person.</t>
         </is>
       </c>
       <c r="D296" s="3" t="inlineStr">
         <is>
-          <t>advise specific behaviour BCT</t>
+          <t>behaviour change technique</t>
         </is>
       </c>
       <c r="E296" s="3" t="n"/>
       <c r="F296" s="3" t="n"/>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>BCT8.2 Behaviour substitution</t>
-        </is>
-      </c>
-      <c r="H296" s="3" t="inlineStr">
-        <is>
-          <t>behaviour replacement, alternative response</t>
-        </is>
-      </c>
+          <t>BCT3.1 Social support (unspecified)</t>
+        </is>
+      </c>
+      <c r="H296" s="3" t="n"/>
       <c r="I296" s="3" t="n"/>
       <c r="J296" s="3" t="inlineStr">
         <is>
-          <t>If this occurs regularly, also code 'context-specific repetition of alternative behaviour BCT'</t>
+          <t>Attending a group class and/or mention of ‘follow-up’ does not necessarily apply this BCT, support must be explicitly mentioned.</t>
         </is>
       </c>
       <c r="K296" s="3" t="inlineStr">
@@ -17877,34 +17855,42 @@
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007302</t>
+          <t>BCIO:007095</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>suggest different perspective on behaviour BCT</t>
+          <t xml:space="preserve">substitute behaviour BCT </t>
         </is>
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A &lt;behaviour change technique&gt; that suggests the deliberate adoption of a new perspective on the behaviour. </t>
+          <t>An &lt;advise specific behaviour BCT&gt; that advises the person to replace the unwanted behaviour with another behaviour.</t>
         </is>
       </c>
       <c r="D297" s="3" t="inlineStr">
         <is>
-          <t>behaviour change technique</t>
+          <t>advise specific behaviour BCT</t>
         </is>
       </c>
       <c r="E297" s="3" t="n"/>
       <c r="F297" s="3" t="n"/>
-      <c r="G297" s="3" t="n"/>
+      <c r="G297" s="3" t="inlineStr">
+        <is>
+          <t>BCT8.2 Behaviour substitution</t>
+        </is>
+      </c>
       <c r="H297" s="3" t="inlineStr">
         <is>
-          <t>cognitive reframing</t>
+          <t>behaviour replacement, alternative response</t>
         </is>
       </c>
       <c r="I297" s="3" t="n"/>
-      <c r="J297" s="3" t="n"/>
+      <c r="J297" s="3" t="inlineStr">
+        <is>
+          <t>If this occurs regularly, also code 'context-specific repetition of alternative behaviour BCT'</t>
+        </is>
+      </c>
       <c r="K297" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -17935,28 +17921,32 @@
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007303</t>
+          <t>BCIO:007302</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>suggest how to perform behaviour BCT</t>
+          <t>suggest different perspective on behaviour BCT</t>
         </is>
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>A &lt;guide how to perform behaviour BCT&gt; that provides a suggestion regarding how to perform the behaviour.</t>
+          <t xml:space="preserve">A &lt;behaviour change technique&gt; that suggests the deliberate adoption of a new perspective on the behaviour. </t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>guide how to perform behaviour BCT</t>
+          <t>behaviour change technique</t>
         </is>
       </c>
       <c r="E298" s="3" t="n"/>
       <c r="F298" s="3" t="n"/>
       <c r="G298" s="3" t="n"/>
-      <c r="H298" s="3" t="n"/>
+      <c r="H298" s="3" t="inlineStr">
+        <is>
+          <t>cognitive reframing</t>
+        </is>
+      </c>
       <c r="I298" s="3" t="n"/>
       <c r="J298" s="3" t="n"/>
       <c r="K298" s="3" t="inlineStr">
@@ -17976,7 +17966,7 @@
       <c r="Q298" s="3" t="n"/>
       <c r="R298" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S298" s="3" t="inlineStr">
@@ -17989,42 +17979,30 @@
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007076</t>
+          <t>BCIO:007303</t>
         </is>
       </c>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>suggest to change behaviour BCT</t>
+          <t>suggest how to perform behaviour BCT</t>
         </is>
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>An &lt;awareness of other people's thoughts, feelings and actions BCT&gt; that involves sharing a view about what behaviour the person should do.</t>
+          <t>A &lt;guide how to perform behaviour BCT&gt; that provides a suggestion regarding how to perform the behaviour.</t>
         </is>
       </c>
       <c r="D299" s="3" t="inlineStr">
         <is>
-          <t>awareness of other peoples thoughts, feelings and actions BCT</t>
+          <t>guide how to perform behaviour BCT</t>
         </is>
       </c>
       <c r="E299" s="3" t="n"/>
       <c r="F299" s="3" t="n"/>
-      <c r="G299" s="3" t="inlineStr">
-        <is>
-          <t>BCT4.5 Advise to change behaviour</t>
-        </is>
-      </c>
-      <c r="H299" s="3" t="inlineStr">
-        <is>
-          <t>encourage to change behaviour</t>
-        </is>
-      </c>
+      <c r="G299" s="3" t="n"/>
+      <c r="H299" s="3" t="n"/>
       <c r="I299" s="3" t="n"/>
-      <c r="J299" s="3" t="inlineStr">
-        <is>
-          <t>An example of the "suggest to change behaviour BCT" would be saying to someone: "I think you should do this behaviour" whereas an example of the "Tell to change behaviour BCT" is saying "Do this behaviour". This class includes "strongly encourage".</t>
-        </is>
-      </c>
+      <c r="J299" s="3" t="n"/>
       <c r="K299" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -18055,30 +18033,42 @@
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007089</t>
+          <t>BCIO:007076</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>systematically desensitise BCT</t>
+          <t>suggest to change behaviour BCT</t>
         </is>
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>An &lt;expose to stimulus BCT&gt; that gradually exposes the person to an aversive stimulus while also engaging them in a relaxation process to reduce the response to that stimulus.</t>
+          <t>An &lt;awareness of other people's thoughts, feelings and actions BCT&gt; that involves sharing a view about what behaviour the person should do.</t>
         </is>
       </c>
       <c r="D300" s="3" t="inlineStr">
         <is>
-          <t>expose to stimulus BCT</t>
+          <t>awareness of other peoples thoughts, feelings and actions BCT</t>
         </is>
       </c>
       <c r="E300" s="3" t="n"/>
       <c r="F300" s="3" t="n"/>
-      <c r="G300" s="3" t="n"/>
-      <c r="H300" s="3" t="n"/>
+      <c r="G300" s="3" t="inlineStr">
+        <is>
+          <t>BCT4.5 Advise to change behaviour</t>
+        </is>
+      </c>
+      <c r="H300" s="3" t="inlineStr">
+        <is>
+          <t>encourage to change behaviour</t>
+        </is>
+      </c>
       <c r="I300" s="3" t="n"/>
-      <c r="J300" s="3" t="n"/>
+      <c r="J300" s="3" t="inlineStr">
+        <is>
+          <t>An example of the "suggest to change behaviour BCT" would be saying to someone: "I think you should do this behaviour" whereas an example of the "Tell to change behaviour BCT" is saying "Do this behaviour". This class includes "strongly encourage".</t>
+        </is>
+      </c>
       <c r="K300" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -18109,42 +18099,30 @@
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007077</t>
+          <t>BCIO:007089</t>
         </is>
       </c>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>tell to change behaviour BCT</t>
+          <t>systematically desensitise BCT</t>
         </is>
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>An &lt;awareness of other people's thoughts, feelings and actions BCT&gt; that involves telling the person to perform the behaviour.</t>
+          <t>An &lt;expose to stimulus BCT&gt; that gradually exposes the person to an aversive stimulus while also engaging them in a relaxation process to reduce the response to that stimulus.</t>
         </is>
       </c>
       <c r="D301" s="3" t="inlineStr">
         <is>
-          <t>awareness of other peoples thoughts, feelings and actions BCT</t>
+          <t>expose to stimulus BCT</t>
         </is>
       </c>
       <c r="E301" s="3" t="n"/>
       <c r="F301" s="3" t="n"/>
-      <c r="G301" s="3" t="inlineStr">
-        <is>
-          <t>BCT4.5 Advise to change behaviour</t>
-        </is>
-      </c>
-      <c r="H301" s="3" t="inlineStr">
-        <is>
-          <t>instruct, command</t>
-        </is>
-      </c>
+      <c r="G301" s="3" t="n"/>
+      <c r="H301" s="3" t="n"/>
       <c r="I301" s="3" t="n"/>
-      <c r="J301" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">An example of the "Tell to change behaviour BCT" is saying "Do this behaviour" whereas an example of the "suggest to change behaviour BCT" would be saying to someone: "I think you should do this behaviour." </t>
-        </is>
-      </c>
+      <c r="J301" s="3" t="n"/>
       <c r="K301" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -18162,7 +18140,7 @@
       <c r="Q301" s="3" t="n"/>
       <c r="R301" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S301" s="3" t="inlineStr">
@@ -18175,34 +18153,42 @@
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007121</t>
+          <t>BCIO:007077</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>vicarious punishment BCT</t>
+          <t>tell to change behaviour BCT</t>
         </is>
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>An &lt;increase awareness of consequences BCT&gt; that prompts observation of another person being punished when they perform the behaviour.</t>
+          <t>An &lt;awareness of other people's thoughts, feelings and actions BCT&gt; that involves telling the person to perform the behaviour.</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr">
         <is>
-          <t>increase awareness of consequences BCT</t>
+          <t>awareness of other peoples thoughts, feelings and actions BCT</t>
         </is>
       </c>
       <c r="E302" s="3" t="n"/>
       <c r="F302" s="3" t="n"/>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>BCT16.3 Vicarious consequences</t>
-        </is>
-      </c>
-      <c r="H302" s="3" t="n"/>
+          <t>BCT4.5 Advise to change behaviour</t>
+        </is>
+      </c>
+      <c r="H302" s="3" t="inlineStr">
+        <is>
+          <t>instruct, command</t>
+        </is>
+      </c>
       <c r="I302" s="3" t="n"/>
-      <c r="J302" s="3" t="n"/>
+      <c r="J302" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An example of the "Tell to change behaviour BCT" is saying "Do this behaviour" whereas an example of the "suggest to change behaviour BCT" would be saying to someone: "I think you should do this behaviour." </t>
+        </is>
+      </c>
       <c r="K302" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -18220,7 +18206,7 @@
       <c r="Q302" s="3" t="n"/>
       <c r="R302" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S302" s="3" t="inlineStr">
@@ -18233,17 +18219,17 @@
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007120</t>
+          <t>BCIO:007121</t>
         </is>
       </c>
       <c r="B303" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">vicarious reward BCT </t>
+          <t>vicarious punishment BCT</t>
         </is>
       </c>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t>An &lt;increase awareness of consequences BCT&gt; that prompts observation of another person being rewarded when they perform the behaviour.</t>
+          <t>An &lt;increase awareness of consequences BCT&gt; that prompts observation of another person being punished when they perform the behaviour.</t>
         </is>
       </c>
       <c r="D303" s="3" t="inlineStr">
@@ -18258,11 +18244,7 @@
           <t>BCT16.3 Vicarious consequences</t>
         </is>
       </c>
-      <c r="H303" s="3" t="inlineStr">
-        <is>
-          <t>vicarious reinforcement</t>
-        </is>
-      </c>
+      <c r="H303" s="3" t="n"/>
       <c r="I303" s="3" t="n"/>
       <c r="J303" s="3" t="n"/>
       <c r="K303" s="3" t="inlineStr">
@@ -18282,15 +18264,77 @@
       <c r="Q303" s="3" t="n"/>
       <c r="R303" s="3" t="inlineStr">
         <is>
+          <t>LZ</t>
+        </is>
+      </c>
+      <c r="S303" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T303" s="3" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:007120</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vicarious reward BCT </t>
+        </is>
+      </c>
+      <c r="C304" s="3" t="inlineStr">
+        <is>
+          <t>An &lt;increase awareness of consequences BCT&gt; that prompts observation of another person being rewarded when they perform the behaviour.</t>
+        </is>
+      </c>
+      <c r="D304" s="3" t="inlineStr">
+        <is>
+          <t>increase awareness of consequences BCT</t>
+        </is>
+      </c>
+      <c r="E304" s="3" t="n"/>
+      <c r="F304" s="3" t="n"/>
+      <c r="G304" s="3" t="inlineStr">
+        <is>
+          <t>BCT16.3 Vicarious consequences</t>
+        </is>
+      </c>
+      <c r="H304" s="3" t="inlineStr">
+        <is>
+          <t>vicarious reinforcement</t>
+        </is>
+      </c>
+      <c r="I304" s="3" t="n"/>
+      <c r="J304" s="3" t="n"/>
+      <c r="K304" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="L304" s="3" t="n"/>
+      <c r="M304" s="3" t="n"/>
+      <c r="N304" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O304" s="3" t="n"/>
+      <c r="P304" s="3" t="n"/>
+      <c r="Q304" s="3" t="n"/>
+      <c r="R304" s="3" t="inlineStr">
+        <is>
           <t>lz; LZ</t>
         </is>
       </c>
-      <c r="S303" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T303" s="3" t="n"/>
+      <c r="S304" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T304" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BehaviourChangeTechniques/bcto.xlsx
+++ b/BehaviourChangeTechniques/bcto.xlsx
@@ -564,7 +564,7 @@
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
+      <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
@@ -6596,28 +6596,28 @@
           <t>awareness of other peoples thoughts, feelings and actions BCT</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr"/>
-      <c r="F107" s="2" t="inlineStr"/>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr"/>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-      <c r="K107" s="2" t="inlineStr"/>
-      <c r="L107" s="2" t="inlineStr"/>
-      <c r="M107" s="2" t="inlineStr"/>
+      <c r="E107" s="2" t="n"/>
+      <c r="F107" s="2" t="n"/>
+      <c r="G107" s="2" t="n"/>
+      <c r="H107" s="2" t="n"/>
+      <c r="I107" s="2" t="n"/>
+      <c r="J107" s="2" t="n"/>
+      <c r="K107" s="2" t="n"/>
+      <c r="L107" s="2" t="n"/>
+      <c r="M107" s="2" t="n"/>
       <c r="N107" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="O107" s="2" t="inlineStr"/>
-      <c r="P107" s="2" t="inlineStr"/>
-      <c r="Q107" s="2" t="inlineStr"/>
-      <c r="R107" s="2" t="inlineStr"/>
+      <c r="O107" s="2" t="n"/>
+      <c r="P107" s="2" t="n"/>
+      <c r="Q107" s="2" t="n"/>
+      <c r="R107" s="2" t="n"/>
       <c r="S107" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">

--- a/BehaviourChangeTechniques/bcto.xlsx
+++ b/BehaviourChangeTechniques/bcto.xlsx
@@ -564,7 +564,7 @@
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
@@ -727,7 +727,8 @@
       <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Provision of information (e.g. written, verbal, visual) in a booklet or leaflet is insufficient. If this is accompanied by social support, also code 'social support BCT' or one of its child classes. If the environment is changed beyond the addition of objects, also code 'directly restructure the physical environment BCT' and/or 'indirectly restructure the physical environment BCT'.</t>
+          <t>Provision of information (e.g. written, verbal, visual) in a booklet or leaflet is insufficient. If this is accompanied by social support, also code 'social support BCT' or one of its child classes. If the environment is changed beyond the addition of objects, also code 'directly restructure the physical environment BCT' and/or 'indirectly restructure the physical environment BCT'.
+Objects include fixed structures such as fences, as well as equipment, digital devices and interactive displays. This BCT includes removing 'virtual' buttons or other interactive elements on digital devices.</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -8126,7 +8127,11 @@
       <c r="G134" s="2" t="n"/>
       <c r="H134" s="2" t="n"/>
       <c r="I134" s="2" t="n"/>
-      <c r="J134" s="2" t="n"/>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>Objects include fixed structures such as fences, as well as equipment, digital devices and interactive displays. Modifying includes changing the position, size and accessibility of object, and includes modifying 'virtual' buttons or other interactive elements on digital devices.</t>
+        </is>
+      </c>
       <c r="K134" s="2" t="n"/>
       <c r="L134" s="2" t="n"/>
       <c r="M134" s="2" t="n"/>
@@ -16602,7 +16607,11 @@
       <c r="G276" s="2" t="n"/>
       <c r="H276" s="2" t="n"/>
       <c r="I276" s="2" t="n"/>
-      <c r="J276" s="2" t="n"/>
+      <c r="J276" s="2" t="inlineStr">
+        <is>
+          <t>Objects include fixed structures such as fences, as well as equipment, digital devices and interactive displays. This BCT includes removing 'virtual' buttons or other interactive elements on digital devices.</t>
+        </is>
+      </c>
       <c r="K276" s="2" t="n"/>
       <c r="L276" s="2" t="n"/>
       <c r="M276" s="2" t="n"/>

--- a/BehaviourChangeTechniques/bcto.xlsx
+++ b/BehaviourChangeTechniques/bcto.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T304"/>
+  <dimension ref="A1:T305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>increase awareness of others approval BCT</t>
+          <t>increase awareness of others appraisal of the behaviour BCT</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -6579,66 +6579,66 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>BCIO:051007</t>
+          <t>BCIO:051016</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>increase awareness of others disapproval BCT</t>
+          <t>increase awareness of others approval BCT</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>An &lt;awareness of other people's thoughts, feelings and actions BCT&gt; that increases awareness of whether others will dislike or disapprove of the behaviour.</t>
+          <t>An &lt;increase awareness of others appraisal of the behaviour BCT&gt; that increases awareness of whether others will like or approve of the behaviour.</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>awareness of other peoples thoughts, feelings and actions BCT</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="n"/>
-      <c r="F107" s="2" t="n"/>
-      <c r="G107" s="2" t="n"/>
-      <c r="H107" s="2" t="n"/>
-      <c r="I107" s="2" t="n"/>
-      <c r="J107" s="2" t="n"/>
-      <c r="K107" s="2" t="n"/>
-      <c r="L107" s="2" t="n"/>
-      <c r="M107" s="2" t="n"/>
+          <t>increase awareness of others appraisal of the behaviour BCT</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr"/>
       <c r="N107" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="O107" s="2" t="n"/>
-      <c r="P107" s="2" t="n"/>
-      <c r="Q107" s="2" t="n"/>
-      <c r="R107" s="2" t="n"/>
+      <c r="O107" s="2" t="inlineStr"/>
+      <c r="P107" s="2" t="inlineStr"/>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
       <c r="S107" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T107" s="2" t="n"/>
+      <c r="T107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050987</t>
+          <t>BCIO:051007</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>increase exposure to people doing the behaviour BCT</t>
+          <t>increase awareness of others disapproval BCT</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>A &lt;restructure the social environment BCT&gt; that involves increasing exposure of the person to other people doing the behaviour.</t>
+          <t>An &lt;increase awareness of others appraisal of the behaviour BCT&gt; that increases awareness of whether others will dislike or disapprove of the behaviour.</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>restructure the social environment BCT</t>
+          <t>increase awareness of others appraisal of the behaviour BCT</t>
         </is>
       </c>
       <c r="E108" s="2" t="n"/>
@@ -6667,22 +6667,22 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050988</t>
+          <t>BCIO:050987</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>increase financial affordability BCT</t>
+          <t>increase exposure to people doing the behaviour BCT</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>A &lt;restructure the physical environment BCT&gt; that reduces the financial cost of the behaviour relative to the person’s access to financial resources.</t>
+          <t>A &lt;restructure the social environment BCT&gt; that involves increasing exposure of the person to other people doing the behaviour.</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>restructure the physical environment BCT</t>
+          <t>restructure the social environment BCT</t>
         </is>
       </c>
       <c r="E109" s="2" t="n"/>
@@ -6709,106 +6709,84 @@
       <c r="T109" s="2" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="inlineStr">
-        <is>
-          <t>BCIO:007175</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>increase salience of behaviour BCT</t>
-        </is>
-      </c>
-      <c r="C110" s="3" t="inlineStr">
-        <is>
-          <t>An &lt;increase awareness of behaviour BCT&gt; that makes the possibility of performing the behaviour more distinctive or prominent.</t>
-        </is>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>increase awareness of behaviour BCT</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="n"/>
-      <c r="F110" s="3" t="n"/>
-      <c r="G110" s="3" t="n"/>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>salience of behaviour</t>
-        </is>
-      </c>
-      <c r="I110" s="3" t="inlineStr">
-        <is>
-          <t>Mask use at the start of the Covid pandemic through symbols/signs of masks in public spaces</t>
-        </is>
-      </c>
-      <c r="J110" s="3" t="n"/>
-      <c r="K110" s="3" t="inlineStr">
-        <is>
-          <t>behaviour change technique</t>
-        </is>
-      </c>
-      <c r="L110" s="3" t="n"/>
-      <c r="M110" s="3" t="n"/>
-      <c r="N110" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="O110" s="3" t="n"/>
-      <c r="P110" s="3" t="n"/>
-      <c r="Q110" s="3" t="n"/>
-      <c r="R110" s="3" t="inlineStr">
-        <is>
-          <t>lz; LZ</t>
-        </is>
-      </c>
-      <c r="S110" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T110" s="3" t="n"/>
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:050988</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>increase financial affordability BCT</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>A &lt;restructure the physical environment BCT&gt; that reduces the financial cost of the behaviour relative to the person’s access to financial resources.</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>restructure the physical environment BCT</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="n"/>
+      <c r="F110" s="2" t="n"/>
+      <c r="G110" s="2" t="n"/>
+      <c r="H110" s="2" t="n"/>
+      <c r="I110" s="2" t="n"/>
+      <c r="J110" s="2" t="n"/>
+      <c r="K110" s="2" t="n"/>
+      <c r="L110" s="2" t="n"/>
+      <c r="M110" s="2" t="n"/>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="n"/>
+      <c r="P110" s="2" t="n"/>
+      <c r="Q110" s="2" t="n"/>
+      <c r="R110" s="2" t="n"/>
+      <c r="S110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007068</t>
+          <t>BCIO:007175</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">increase salience of consequences BCT </t>
+          <t>increase salience of behaviour BCT</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">An &lt;awareness of consequences BCT&gt; that changes behaviour by the source emphasising the consequences of performing a behaviour to the person in a way that makes them memorable. </t>
+          <t>An &lt;increase awareness of behaviour BCT&gt; that makes the possibility of performing the behaviour more distinctive or prominent.</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>increase awareness of consequences BCT</t>
+          <t>increase awareness of behaviour BCT</t>
         </is>
       </c>
       <c r="E111" s="3" t="n"/>
       <c r="F111" s="3" t="n"/>
-      <c r="G111" s="3" t="inlineStr">
-        <is>
-          <t>BCT5.2 Salience of consequences</t>
-        </is>
-      </c>
+      <c r="G111" s="3" t="n"/>
       <c r="H111" s="3" t="inlineStr">
         <is>
-          <t>significance of outcomes, importance of consequences, relevance of results</t>
-        </is>
-      </c>
-      <c r="I111" s="3" t="n"/>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>Consider also coding one of "inform about health consequences", "inform about emotional consequences",  "inform about social consequences", or their child classes</t>
-        </is>
-      </c>
+          <t>salience of behaviour</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>Mask use at the start of the Covid pandemic through symbols/signs of masks in public spaces</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="n"/>
       <c r="K111" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -6837,134 +6815,146 @@
       <c r="T111" s="3" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:007068</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">increase salience of consequences BCT </t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An &lt;awareness of consequences BCT&gt; that changes behaviour by the source emphasising the consequences of performing a behaviour to the person in a way that makes them memorable. </t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>increase awareness of consequences BCT</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="n"/>
+      <c r="F112" s="3" t="n"/>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>BCT5.2 Salience of consequences</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>significance of outcomes, importance of consequences, relevance of results</t>
+        </is>
+      </c>
+      <c r="I112" s="3" t="n"/>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>Consider also coding one of "inform about health consequences", "inform about emotional consequences",  "inform about social consequences", or their child classes</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="L112" s="3" t="n"/>
+      <c r="M112" s="3" t="n"/>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O112" s="3" t="n"/>
+      <c r="P112" s="3" t="n"/>
+      <c r="Q112" s="3" t="n"/>
+      <c r="R112" s="3" t="inlineStr">
+        <is>
+          <t>lz; LZ</t>
+        </is>
+      </c>
+      <c r="S112" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T112" s="3" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>BCIO:050989</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>increase salience of social rule BCT</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
         <is>
           <t>An &lt;awareness of other peoples thoughts, feelings and actions BCT&gt; that involves increasing the salience of a social rule concerning the behaviour.</t>
         </is>
       </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>awareness of other peoples thoughts, feelings and actions BCT</t>
         </is>
       </c>
-      <c r="E112" s="2" t="n"/>
-      <c r="F112" s="2" t="n"/>
-      <c r="G112" s="2" t="n"/>
-      <c r="H112" s="2" t="n"/>
-      <c r="I112" s="2" t="n"/>
-      <c r="J112" s="2" t="n"/>
-      <c r="K112" s="2" t="n"/>
-      <c r="L112" s="2" t="n"/>
-      <c r="M112" s="2" t="n"/>
-      <c r="N112" s="2" t="inlineStr">
+      <c r="E113" s="2" t="n"/>
+      <c r="F113" s="2" t="n"/>
+      <c r="G113" s="2" t="n"/>
+      <c r="H113" s="2" t="n"/>
+      <c r="I113" s="2" t="n"/>
+      <c r="J113" s="2" t="n"/>
+      <c r="K113" s="2" t="n"/>
+      <c r="L113" s="2" t="n"/>
+      <c r="M113" s="2" t="n"/>
+      <c r="N113" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="O112" s="2" t="n"/>
-      <c r="P112" s="2" t="n"/>
-      <c r="Q112" s="2" t="n"/>
-      <c r="R112" s="2" t="n"/>
-      <c r="S112" s="2" t="n">
+      <c r="O113" s="2" t="n"/>
+      <c r="P113" s="2" t="n"/>
+      <c r="Q113" s="2" t="n"/>
+      <c r="R113" s="2" t="n"/>
+      <c r="S113" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T112" s="2" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t>BCIO:007152</t>
-        </is>
-      </c>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">indirectly restructure the physical environment BCT </t>
-        </is>
-      </c>
-      <c r="C113" s="3" t="inlineStr">
-        <is>
-          <t>A &lt;restructure the physical environment BCT&gt; that changes the person's environment at a time or location other than when and where the behaviour is performed.</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>restructure the physical environment BCT</t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="n"/>
-      <c r="F113" s="3" t="n"/>
-      <c r="G113" s="3" t="n"/>
-      <c r="H113" s="3" t="n"/>
-      <c r="I113" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Example 1: Putting cigarette packs out of sight in shops in order to promote smoking cessation or reduce smoking uptake
-Example 2: Introducing safe cycle routes in residential neighbourhood to increase frequency of initiating journeys from home by bicycle. </t>
-        </is>
-      </c>
-      <c r="J113" s="3" t="n"/>
-      <c r="K113" s="3" t="inlineStr">
-        <is>
-          <t>behaviour change technique</t>
-        </is>
-      </c>
-      <c r="L113" s="3" t="n"/>
-      <c r="M113" s="3" t="n"/>
-      <c r="N113" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="O113" s="3" t="n"/>
-      <c r="P113" s="3" t="n"/>
-      <c r="Q113" s="3" t="n"/>
-      <c r="R113" s="3" t="inlineStr">
-        <is>
-          <t>LZ</t>
-        </is>
-      </c>
-      <c r="S113" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T113" s="3" t="n"/>
+      <c r="T113" s="2" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>BCIO:050347</t>
+          <t>BCIO:007152</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">indirectly restructure the social environment BCT </t>
+          <t xml:space="preserve">indirectly restructure the physical environment BCT </t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A &lt;restructure the social environment BCT&gt; that changes the person's environment at a time or location other than when and where the behaviour is performed. </t>
+          <t>A &lt;restructure the physical environment BCT&gt; that changes the person's environment at a time or location other than when and where the behaviour is performed.</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>restructure the social environment BCT</t>
+          <t>restructure the physical environment BCT</t>
         </is>
       </c>
       <c r="E114" s="3" t="n"/>
       <c r="F114" s="3" t="n"/>
       <c r="G114" s="3" t="n"/>
       <c r="H114" s="3" t="n"/>
-      <c r="I114" s="3" t="n"/>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Example 1: Putting cigarette packs out of sight in shops in order to promote smoking cessation or reduce smoking uptake
+Example 2: Introducing safe cycle routes in residential neighbourhood to increase frequency of initiating journeys from home by bicycle. </t>
+        </is>
+      </c>
       <c r="J114" s="3" t="n"/>
       <c r="K114" s="3" t="inlineStr">
         <is>
@@ -6996,38 +6986,30 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007067</t>
+          <t>BCIO:050347</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">induce anticipated regret BCT </t>
+          <t xml:space="preserve">indirectly restructure the social environment BCT </t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>An &lt;inform about emotional consequences BCT&gt; that focuses on expectations of remorse after performing or not performing the behaviour.</t>
+          <t xml:space="preserve">A &lt;restructure the social environment BCT&gt; that changes the person's environment at a time or location other than when and where the behaviour is performed. </t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about emotional consequences BCT </t>
+          <t>restructure the social environment BCT</t>
         </is>
       </c>
       <c r="E115" s="3" t="n"/>
       <c r="F115" s="3" t="n"/>
-      <c r="G115" s="3" t="inlineStr">
-        <is>
-          <t>BCT5.5 Anticipated regret</t>
-        </is>
-      </c>
+      <c r="G115" s="3" t="n"/>
       <c r="H115" s="3" t="n"/>
       <c r="I115" s="3" t="n"/>
-      <c r="J115" s="3" t="inlineStr">
-        <is>
-          <t>If suggests adoption of a perspective or new perspective in order to change cognitions also code 'suggest different perspective on behaviour BCT' or one of its child classes</t>
-        </is>
-      </c>
+      <c r="J115" s="3" t="n"/>
       <c r="K115" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -7045,7 +7027,7 @@
       <c r="Q115" s="3" t="n"/>
       <c r="R115" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S115" s="3" t="inlineStr">
@@ -7058,38 +7040,38 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007052</t>
+          <t>BCIO:007067</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about antecedents BCT </t>
+          <t xml:space="preserve">induce anticipated regret BCT </t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>A &lt;suggest different perspective on behaviour BCT&gt; that involves providing factual information to the person regarding triggers or influences that precede the initiation of the behaviour.</t>
+          <t>An &lt;inform about emotional consequences BCT&gt; that focuses on expectations of remorse after performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>suggest different perspective on behaviour BCT</t>
+          <t xml:space="preserve">inform about emotional consequences BCT </t>
         </is>
       </c>
       <c r="E116" s="3" t="n"/>
       <c r="F116" s="3" t="n"/>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>BCT4.2 Information about antecedents</t>
-        </is>
-      </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>trigger recognition, understanding of antecedents</t>
-        </is>
-      </c>
+          <t>BCT5.5 Anticipated regret</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="n"/>
       <c r="I116" s="3" t="n"/>
-      <c r="J116" s="3" t="n"/>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>If suggests adoption of a perspective or new perspective in order to change cognitions also code 'suggest different perspective on behaviour BCT' or one of its child classes</t>
+        </is>
+      </c>
       <c r="K116" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -7120,42 +7102,38 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007065</t>
+          <t>BCIO:007052</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about emotional consequences BCT </t>
+          <t xml:space="preserve">inform about antecedents BCT </t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>An &lt;increase awareness of consequences BCT&gt; that provides information about the emotional consequences of performing or not performing the behaviour.</t>
+          <t>A &lt;suggest different perspective on behaviour BCT&gt; that involves providing factual information to the person regarding triggers or influences that precede the initiation of the behaviour.</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>increase awareness of consequences BCT</t>
+          <t>suggest different perspective on behaviour BCT</t>
         </is>
       </c>
       <c r="E117" s="3" t="n"/>
       <c r="F117" s="3" t="n"/>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BCT5.6 Information about emotional consequences</t>
+          <t>BCT4.2 Information about antecedents</t>
         </is>
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
-          <t>affective outcomes, emotional effects, consequences on emotions</t>
+          <t>trigger recognition, understanding of antecedents</t>
         </is>
       </c>
       <c r="I117" s="3" t="n"/>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>Consequences can be for any target, not just the recipient(s) of the intervention; emphasising importance of consequences is not sufficient. Consequences can be related to emotional health disorders (e.g. depression, anxiety) and/or states of mind (e.g. low mood, stress).</t>
-        </is>
-      </c>
+      <c r="J117" s="3" t="n"/>
       <c r="K117" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -7186,17 +7164,17 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007176</t>
+          <t>BCIO:007065</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>inform about environmental consequences BCT</t>
+          <t xml:space="preserve">inform about emotional consequences BCT </t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>An &lt;increase awareness of consequences BCT&gt; that provides information about the environmental consequences of performing or not performing the behaviour.</t>
+          <t>An &lt;increase awareness of consequences BCT&gt; that provides information about the emotional consequences of performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
@@ -7208,18 +7186,18 @@
       <c r="F118" s="3" t="n"/>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>BCT5.3 Information about social and environmental consequences</t>
+          <t xml:space="preserve"> BCT5.6 Information about emotional consequences</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>environmental effects, ecological impacts</t>
+          <t>affective outcomes, emotional effects, consequences on emotions</t>
         </is>
       </c>
       <c r="I118" s="3" t="n"/>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>Consequences can be for any target, not just the recipient(s) of the intervention; emphasising importance of consequences is not sufficient.</t>
+          <t>Consequences can be for any target, not just the recipient(s) of the intervention; emphasising importance of consequences is not sufficient. Consequences can be related to emotional health disorders (e.g. depression, anxiety) and/or states of mind (e.g. low mood, stress).</t>
         </is>
       </c>
       <c r="K118" s="3" t="inlineStr">
@@ -7252,17 +7230,17 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007063</t>
+          <t>BCIO:007176</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about health consequences BCT </t>
+          <t>inform about environmental consequences BCT</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>An &lt;increase awareness of consequences BCT&gt; that provides information about the physical or mental health consequences of performing or not performing the behaviour.</t>
+          <t>An &lt;increase awareness of consequences BCT&gt; that provides information about the environmental consequences of performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -7274,12 +7252,12 @@
       <c r="F119" s="3" t="n"/>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>BCT5.1 Information about health consequences</t>
+          <t>BCT5.3 Information about social and environmental consequences</t>
         </is>
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
-          <t>consequences for well-being, health effects, wellness outcomes</t>
+          <t>environmental effects, ecological impacts</t>
         </is>
       </c>
       <c r="I119" s="3" t="n"/>
@@ -7318,17 +7296,17 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>BCIO:050559</t>
+          <t>BCIO:007063</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>inform about negative consequences BCT</t>
+          <t xml:space="preserve">inform about health consequences BCT </t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>An &lt;increase awareness of consequences BCT&gt; that provides information about the negative consequences of performing or not performing the behaviour.</t>
+          <t>An &lt;increase awareness of consequences BCT&gt; that provides information about the physical or mental health consequences of performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
@@ -7336,18 +7314,22 @@
           <t>increase awareness of consequences BCT</t>
         </is>
       </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>'inform about negative emotional consequences BCT' OR 'inform about negative environmental consequences BCT' OR 'inform about negative health consequences BCT' OR 'inform about negative social consequences BCT'</t>
-        </is>
-      </c>
+      <c r="E120" s="3" t="n"/>
       <c r="F120" s="3" t="n"/>
-      <c r="G120" s="3" t="n"/>
-      <c r="H120" s="3" t="n"/>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>BCT5.1 Information about health consequences</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>consequences for well-being, health effects, wellness outcomes</t>
+        </is>
+      </c>
       <c r="I120" s="3" t="n"/>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>Preferable to use the more specific child classes.</t>
+          <t>Consequences can be for any target, not just the recipient(s) of the intervention; emphasising importance of consequences is not sufficient.</t>
         </is>
       </c>
       <c r="K120" s="3" t="inlineStr">
@@ -7367,7 +7349,7 @@
       <c r="Q120" s="3" t="n"/>
       <c r="R120" s="3" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S120" s="3" t="inlineStr">
@@ -7380,30 +7362,38 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007177</t>
+          <t>BCIO:050559</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about negative emotional consequences BCT </t>
+          <t>inform about negative consequences BCT</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>An &lt;inform about emotional consequences BCT&gt; that provides information about the negative emotional consequences of performing or not performing the behaviour.</t>
+          <t>An &lt;increase awareness of consequences BCT&gt; that provides information about the negative consequences of performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about emotional consequences BCT </t>
-        </is>
-      </c>
-      <c r="E121" s="3" t="n"/>
+          <t>increase awareness of consequences BCT</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>'inform about negative emotional consequences BCT' OR 'inform about negative environmental consequences BCT' OR 'inform about negative health consequences BCT' OR 'inform about negative social consequences BCT'</t>
+        </is>
+      </c>
       <c r="F121" s="3" t="n"/>
       <c r="G121" s="3" t="n"/>
       <c r="H121" s="3" t="n"/>
       <c r="I121" s="3" t="n"/>
-      <c r="J121" s="3" t="n"/>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>Preferable to use the more specific child classes.</t>
+        </is>
+      </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -7421,7 +7411,7 @@
       <c r="Q121" s="3" t="n"/>
       <c r="R121" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>PS</t>
         </is>
       </c>
       <c r="S121" s="3" t="inlineStr">
@@ -7434,22 +7424,22 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007178</t>
+          <t>BCIO:007177</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>inform about negative environmental consequences BCT</t>
+          <t xml:space="preserve">inform about negative emotional consequences BCT </t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>An &lt;inform about environmental consequences BCT&gt; that provides information about the negative environmental consequences of performing or not performing the behaviour.</t>
+          <t>An &lt;inform about emotional consequences BCT&gt; that provides information about the negative emotional consequences of performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>inform about environmental consequences BCT</t>
+          <t xml:space="preserve">inform about emotional consequences BCT </t>
         </is>
       </c>
       <c r="E122" s="3" t="n"/>
@@ -7475,7 +7465,7 @@
       <c r="Q122" s="3" t="n"/>
       <c r="R122" s="3" t="inlineStr">
         <is>
-          <t>lz; RW; LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S122" s="3" t="inlineStr">
@@ -7488,22 +7478,22 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007179</t>
+          <t>BCIO:007178</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>inform about negative health consequences BCT</t>
+          <t>inform about negative environmental consequences BCT</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>An &lt;inform about health consequences BCT&gt; that provides information about the negative physical or mental health consequences of performing or not performing the behaviour.</t>
+          <t>An &lt;inform about environmental consequences BCT&gt; that provides information about the negative environmental consequences of performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about health consequences BCT </t>
+          <t>inform about environmental consequences BCT</t>
         </is>
       </c>
       <c r="E123" s="3" t="n"/>
@@ -7542,22 +7532,22 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007180</t>
+          <t>BCIO:007179</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>inform about negative social consequences BCT</t>
+          <t>inform about negative health consequences BCT</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>An &lt;inform about social consequences BCT&gt; that provides information about the negative social consequences of performing or not performing the behaviour.</t>
+          <t>An &lt;inform about health consequences BCT&gt; that provides information about the negative physical or mental health consequences of performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about social consequences BCT </t>
+          <t xml:space="preserve">inform about health consequences BCT </t>
         </is>
       </c>
       <c r="E124" s="3" t="n"/>
@@ -7596,22 +7586,22 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007181</t>
+          <t>BCIO:007180</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about positive emotional consequences BCT </t>
+          <t>inform about negative social consequences BCT</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>An &lt;inform about emotional consequences BCT&gt; that provides information about the positive emotional consequences of performing or not performing the behaviour.</t>
+          <t>An &lt;inform about social consequences BCT&gt; that provides information about the negative social consequences of performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about emotional consequences BCT </t>
+          <t xml:space="preserve">inform about social consequences BCT </t>
         </is>
       </c>
       <c r="E125" s="3" t="n"/>
@@ -7637,7 +7627,7 @@
       <c r="Q125" s="3" t="n"/>
       <c r="R125" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>lz; RW; LZ</t>
         </is>
       </c>
       <c r="S125" s="3" t="inlineStr">
@@ -7650,22 +7640,22 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007182</t>
+          <t>BCIO:007181</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about positive environmental consequences BCT </t>
+          <t xml:space="preserve">inform about positive emotional consequences BCT </t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>An &lt;inform about environmental consequences BCT&gt; that provides information about the positive environmental consequences of performing or not performing the behaviour.</t>
+          <t>An &lt;inform about emotional consequences BCT&gt; that provides information about the positive emotional consequences of performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>inform about environmental consequences BCT</t>
+          <t xml:space="preserve">inform about emotional consequences BCT </t>
         </is>
       </c>
       <c r="E126" s="3" t="n"/>
@@ -7704,22 +7694,22 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007183</t>
+          <t>BCIO:007182</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about positive health consequences BCT </t>
+          <t xml:space="preserve">inform about positive environmental consequences BCT </t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>An &lt;inform about health consequences BCT&gt; that provides information about the positive physical or mental health consequences of performing or not performing the behaviour.</t>
+          <t>An &lt;inform about environmental consequences BCT&gt; that provides information about the positive environmental consequences of performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about health consequences BCT </t>
+          <t>inform about environmental consequences BCT</t>
         </is>
       </c>
       <c r="E127" s="3" t="n"/>
@@ -7758,22 +7748,22 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007184</t>
+          <t>BCIO:007183</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about positive social consequences BCT </t>
+          <t xml:space="preserve">inform about positive health consequences BCT </t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>An &lt;inform about social consequences BCT&gt; that provides information about the positive social consequences of performing or not performing the behaviour.</t>
+          <t>An &lt;inform about health consequences BCT&gt; that provides information about the positive physical or mental health consequences of performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inform about social consequences BCT </t>
+          <t xml:space="preserve">inform about health consequences BCT </t>
         </is>
       </c>
       <c r="E128" s="3" t="n"/>
@@ -7812,42 +7802,30 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007064</t>
+          <t>BCIO:007184</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">inform about positive social consequences BCT </t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>An &lt;inform about social consequences BCT&gt; that provides information about the positive social consequences of performing or not performing the behaviour.</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">inform about social consequences BCT </t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="inlineStr">
-        <is>
-          <t>An &lt;increase awareness of consequences BCT&gt; that provides information about the social consequences of performing or not performing the behaviour.</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t>increase awareness of consequences BCT</t>
         </is>
       </c>
       <c r="E129" s="3" t="n"/>
       <c r="F129" s="3" t="n"/>
-      <c r="G129" s="3" t="inlineStr">
-        <is>
-          <t>BCT5.3 Information about social and environmental consequences</t>
-        </is>
-      </c>
-      <c r="H129" s="3" t="inlineStr">
-        <is>
-          <t>social effects, community repercussions</t>
-        </is>
-      </c>
+      <c r="G129" s="3" t="n"/>
+      <c r="H129" s="3" t="n"/>
       <c r="I129" s="3" t="n"/>
-      <c r="J129" s="3" t="inlineStr">
-        <is>
-          <t>Consequences can be for any target, not just the recipient(s) of the intervention; emphasising importance of consequences is not sufficient.</t>
-        </is>
-      </c>
+      <c r="J129" s="3" t="n"/>
       <c r="K129" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -7876,144 +7854,152 @@
       <c r="T129" s="3" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:007064</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inform about social consequences BCT </t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>An &lt;increase awareness of consequences BCT&gt; that provides information about the social consequences of performing or not performing the behaviour.</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>increase awareness of consequences BCT</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="n"/>
+      <c r="F130" s="3" t="n"/>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>BCT5.3 Information about social and environmental consequences</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>social effects, community repercussions</t>
+        </is>
+      </c>
+      <c r="I130" s="3" t="n"/>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>Consequences can be for any target, not just the recipient(s) of the intervention; emphasising importance of consequences is not sufficient.</t>
+        </is>
+      </c>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="n"/>
+      <c r="M130" s="3" t="n"/>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O130" s="3" t="n"/>
+      <c r="P130" s="3" t="n"/>
+      <c r="Q130" s="3" t="n"/>
+      <c r="R130" s="3" t="inlineStr">
+        <is>
+          <t>lz; LZ</t>
+        </is>
+      </c>
+      <c r="S130" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T130" s="3" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>BCIO:050990</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>inform about social rule BCT</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
         <is>
           <t>An &lt;awareness of other peoples thoughts, feelings and actions BCT&gt; that involves informing the person about a social rule regarding the behaviour.</t>
         </is>
       </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>awareness of other peoples thoughts, feelings and actions BCT</t>
         </is>
       </c>
-      <c r="E130" s="2" t="n"/>
-      <c r="F130" s="2" t="n"/>
-      <c r="G130" s="2" t="n"/>
-      <c r="H130" s="2" t="n"/>
-      <c r="I130" s="2" t="n"/>
-      <c r="J130" s="2" t="n"/>
-      <c r="K130" s="2" t="n"/>
-      <c r="L130" s="2" t="n"/>
-      <c r="M130" s="2" t="n"/>
-      <c r="N130" s="2" t="inlineStr">
+      <c r="E131" s="2" t="n"/>
+      <c r="F131" s="2" t="n"/>
+      <c r="G131" s="2" t="n"/>
+      <c r="H131" s="2" t="n"/>
+      <c r="I131" s="2" t="n"/>
+      <c r="J131" s="2" t="n"/>
+      <c r="K131" s="2" t="n"/>
+      <c r="L131" s="2" t="n"/>
+      <c r="M131" s="2" t="n"/>
+      <c r="N131" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="O130" s="2" t="n"/>
-      <c r="P130" s="2" t="n"/>
-      <c r="Q130" s="2" t="n"/>
-      <c r="R130" s="2" t="n"/>
-      <c r="S130" s="2" t="n">
+      <c r="O131" s="2" t="n"/>
+      <c r="P131" s="2" t="n"/>
+      <c r="Q131" s="2" t="n"/>
+      <c r="R131" s="2" t="n"/>
+      <c r="S131" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T130" s="2" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="3" t="inlineStr">
-        <is>
-          <t>BCIO:007058</t>
-        </is>
-      </c>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>instruct how to perform a behaviour BCT</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t>A &lt;guide how to perform behaviour BCT&gt; that involves telling the person how to perform the behaviour.</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>guide how to perform behaviour BCT</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="n"/>
-      <c r="F131" s="3" t="n"/>
-      <c r="G131" s="3" t="inlineStr">
-        <is>
-          <t>BCT4.1 Instruction on how to perform a behaviour</t>
-        </is>
-      </c>
-      <c r="H131" s="3" t="inlineStr">
-        <is>
-          <t>skills training, instruction</t>
-        </is>
-      </c>
-      <c r="I131" s="3" t="n"/>
-      <c r="J131" s="3" t="inlineStr">
-        <is>
-          <t>When the person attends classes such as exercise or cookery, code 'instruct how to perform behaviour BCT', 'practise behaviour BCT', and 'demonstrate the behaviour BCT'.</t>
-        </is>
-      </c>
-      <c r="K131" s="3" t="inlineStr">
-        <is>
-          <t>behaviour change technique</t>
-        </is>
-      </c>
-      <c r="L131" s="3" t="n"/>
-      <c r="M131" s="3" t="n"/>
-      <c r="N131" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="O131" s="3" t="n"/>
-      <c r="P131" s="3" t="n"/>
-      <c r="Q131" s="3" t="n"/>
-      <c r="R131" s="3" t="inlineStr">
-        <is>
-          <t>lz; LZ</t>
-        </is>
-      </c>
-      <c r="S131" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T131" s="3" t="n"/>
+      <c r="T131" s="2" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007122</t>
+          <t>BCIO:007058</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>make a goal public BCT</t>
+          <t>instruct how to perform a behaviour BCT</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>A &lt;goal directed BCT&gt; that involves the person communicating their intention to achieve a goal.</t>
+          <t>A &lt;guide how to perform behaviour BCT&gt; that involves telling the person how to perform the behaviour.</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>goal directed BCT</t>
+          <t>guide how to perform behaviour BCT</t>
         </is>
       </c>
       <c r="E132" s="3" t="n"/>
       <c r="F132" s="3" t="n"/>
-      <c r="G132" s="3" t="n"/>
-      <c r="H132" s="3" t="n"/>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>BCT4.1 Instruction on how to perform a behaviour</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>skills training, instruction</t>
+        </is>
+      </c>
       <c r="I132" s="3" t="n"/>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>The goal being made public can be in terms of behaviour (e.g. to walk for 30 minutes a day) or an outcome of behaviour (e.g. to lose 5kg of body weight)</t>
+          <t>When the person attends classes such as exercise or cookery, code 'instruct how to perform behaviour BCT', 'practise behaviour BCT', and 'demonstrate the behaviour BCT'.</t>
         </is>
       </c>
       <c r="K132" s="3" t="inlineStr">
@@ -8046,22 +8032,22 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007185</t>
+          <t>BCIO:007122</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>manage mental processes BCT</t>
+          <t>make a goal public BCT</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A &lt;behaviour change technique&gt; that advises how to manage mental processes to facilitate the behaviour. </t>
+          <t>A &lt;goal directed BCT&gt; that involves the person communicating their intention to achieve a goal.</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>behaviour change technique</t>
+          <t>goal directed BCT</t>
         </is>
       </c>
       <c r="E133" s="3" t="n"/>
@@ -8071,7 +8057,7 @@
       <c r="I133" s="3" t="n"/>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>A mental process is something that occurs in the brain, and that can of itself be conscious, or can give rise to a process that can of itself be conscious or can give rise to behaviour.</t>
+          <t>The goal being made public can be in terms of behaviour (e.g. to walk for 30 minutes a day) or an outcome of behaviour (e.g. to lose 5kg of body weight)</t>
         </is>
       </c>
       <c r="K133" s="3" t="inlineStr">
@@ -8102,135 +8088,139 @@
       <c r="T133" s="3" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:007185</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>manage mental processes BCT</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A &lt;behaviour change technique&gt; that advises how to manage mental processes to facilitate the behaviour. </t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="n"/>
+      <c r="F134" s="3" t="n"/>
+      <c r="G134" s="3" t="n"/>
+      <c r="H134" s="3" t="n"/>
+      <c r="I134" s="3" t="n"/>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>A mental process is something that occurs in the brain, and that can of itself be conscious, or can give rise to a process that can of itself be conscious or can give rise to behaviour.</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="L134" s="3" t="n"/>
+      <c r="M134" s="3" t="n"/>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O134" s="3" t="n"/>
+      <c r="P134" s="3" t="n"/>
+      <c r="Q134" s="3" t="n"/>
+      <c r="R134" s="3" t="inlineStr">
+        <is>
+          <t>lz; LZ</t>
+        </is>
+      </c>
+      <c r="S134" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T134" s="3" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>BCIO:050991</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>modify objects in the environment BCT</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
         <is>
           <t>A &lt;restructure the physical environment BCT&gt; that modifies objects in the person’s physical surroundings.</t>
         </is>
       </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>restructure the physical environment BCT</t>
         </is>
       </c>
-      <c r="E134" s="2" t="n"/>
-      <c r="F134" s="2" t="n"/>
-      <c r="G134" s="2" t="n"/>
-      <c r="H134" s="2" t="n"/>
-      <c r="I134" s="2" t="n"/>
-      <c r="J134" s="2" t="inlineStr">
+      <c r="E135" s="2" t="n"/>
+      <c r="F135" s="2" t="n"/>
+      <c r="G135" s="2" t="n"/>
+      <c r="H135" s="2" t="n"/>
+      <c r="I135" s="2" t="n"/>
+      <c r="J135" s="2" t="inlineStr">
         <is>
           <t>Objects include fixed structures such as fences, as well as equipment, digital devices and interactive displays. Modifying includes changing the position, size and accessibility of object, and includes modifying 'virtual' buttons or other interactive elements on digital devices.</t>
         </is>
       </c>
-      <c r="K134" s="2" t="n"/>
-      <c r="L134" s="2" t="n"/>
-      <c r="M134" s="2" t="n"/>
-      <c r="N134" s="2" t="inlineStr">
+      <c r="K135" s="2" t="n"/>
+      <c r="L135" s="2" t="n"/>
+      <c r="M135" s="2" t="n"/>
+      <c r="N135" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="O134" s="2" t="n"/>
-      <c r="P134" s="2" t="n"/>
-      <c r="Q134" s="2" t="n"/>
-      <c r="R134" s="2" t="n"/>
-      <c r="S134" s="2" t="n">
+      <c r="O135" s="2" t="n"/>
+      <c r="P135" s="2" t="n"/>
+      <c r="Q135" s="2" t="n"/>
+      <c r="R135" s="2" t="n"/>
+      <c r="S135" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T134" s="2" t="n"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="3" t="inlineStr">
-        <is>
-          <t>BCIO:007066</t>
-        </is>
-      </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">monitor emotional consequences BCT </t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t>A &lt;monitoring BCT&gt; that involves the person assessing their emotions after performing the behaviour.</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>monitoring BCT</t>
-        </is>
-      </c>
-      <c r="E135" s="3" t="n"/>
-      <c r="F135" s="3" t="n"/>
-      <c r="G135" s="3" t="inlineStr">
-        <is>
-          <t>BCT5.4 Monitoring of emotional consequences</t>
-        </is>
-      </c>
-      <c r="H135" s="3" t="n"/>
-      <c r="I135" s="3" t="n"/>
-      <c r="J135" s="3" t="n"/>
-      <c r="K135" s="3" t="inlineStr">
-        <is>
-          <t>behaviour change technique</t>
-        </is>
-      </c>
-      <c r="L135" s="3" t="n"/>
-      <c r="M135" s="3" t="n"/>
-      <c r="N135" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="O135" s="3" t="n"/>
-      <c r="P135" s="3" t="n"/>
-      <c r="Q135" s="3" t="n"/>
-      <c r="R135" s="3" t="inlineStr">
-        <is>
-          <t>LZ</t>
-        </is>
-      </c>
-      <c r="S135" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T135" s="3" t="n"/>
+      <c r="T135" s="2" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007017</t>
+          <t>BCIO:007066</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">monitor emotional consequences BCT </t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>A &lt;monitoring BCT&gt; that involves the person assessing their emotions after performing the behaviour.</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
           <t>monitoring BCT</t>
-        </is>
-      </c>
-      <c r="C136" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A &lt;behaviour change technique&gt; that involves gathering or using information about performance. </t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="inlineStr">
-        <is>
-          <t>behaviour change technique</t>
         </is>
       </c>
       <c r="E136" s="3" t="n"/>
       <c r="F136" s="3" t="n"/>
-      <c r="G136" s="3" t="n"/>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>BCT5.4 Monitoring of emotional consequences</t>
+        </is>
+      </c>
       <c r="H136" s="3" t="n"/>
       <c r="I136" s="3" t="n"/>
       <c r="J136" s="3" t="n"/>
@@ -8264,42 +8254,30 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007018</t>
+          <t>BCIO:007017</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">observe behaviour without feedback BCT </t>
+          <t>monitoring BCT</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>A &lt;monitoring BCT&gt; that observes current performance of the behaviour with the person’s knowledge but without providing feedback about their behaviour.</t>
+          <t xml:space="preserve">A &lt;behaviour change technique&gt; that involves gathering or using information about performance. </t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>monitoring BCT</t>
+          <t>behaviour change technique</t>
         </is>
       </c>
       <c r="E137" s="3" t="n"/>
       <c r="F137" s="3" t="n"/>
-      <c r="G137" s="3" t="inlineStr">
-        <is>
-          <t>BCT2.1 Monitoring of behaviour by others without feedback</t>
-        </is>
-      </c>
-      <c r="H137" s="3" t="inlineStr">
-        <is>
-          <t>observation, performance monitoring</t>
-        </is>
-      </c>
+      <c r="G137" s="3" t="n"/>
+      <c r="H137" s="3" t="n"/>
       <c r="I137" s="3" t="n"/>
-      <c r="J137" s="3" t="inlineStr">
-        <is>
-          <t>The monitoring agent can be a human or a technical device. If observation is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if feedback given, code only 'provide feedback on behaviour BCT' and not this class; if observing outcomes code 'observe outcome of behaviour without feedback BCT'.</t>
-        </is>
-      </c>
+      <c r="J137" s="3" t="n"/>
       <c r="K137" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -8317,7 +8295,7 @@
       <c r="Q137" s="3" t="n"/>
       <c r="R137" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S137" s="3" t="inlineStr">
@@ -8330,17 +8308,17 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007020</t>
+          <t>BCIO:007018</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">observe outcome of behaviour without feedback BCT </t>
+          <t xml:space="preserve">observe behaviour without feedback BCT </t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>A &lt;monitoring BCT&gt; that observes an outcome of performing the behaviour with the person’s knowledge but without providing feedback about the outcome.</t>
+          <t>A &lt;monitoring BCT&gt; that observes current performance of the behaviour with the person’s knowledge but without providing feedback about their behaviour.</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
@@ -8352,14 +8330,18 @@
       <c r="F138" s="3" t="n"/>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>BCT2.5 Monitoring outcome(s) of behaviour by others without feedback</t>
-        </is>
-      </c>
-      <c r="H138" s="3" t="n"/>
+          <t>BCT2.1 Monitoring of behaviour by others without feedback</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>observation, performance monitoring</t>
+        </is>
+      </c>
       <c r="I138" s="3" t="n"/>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>The monitoring agent can be a human or a technical device. If recording is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if feedback given, code only 'provide feedback on outcome of behaviour BCT' and not this class; if observing behaviour code 'observe behaviour without feedback BCT'.</t>
+          <t>The monitoring agent can be a human or a technical device. If observation is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if feedback given, code only 'provide feedback on behaviour BCT' and not this class; if observing outcomes code 'observe outcome of behaviour without feedback BCT'.</t>
         </is>
       </c>
       <c r="K138" s="3" t="inlineStr">
@@ -8392,30 +8374,38 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007186</t>
+          <t>BCIO:007020</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>outcome consequence BCT</t>
+          <t xml:space="preserve">observe outcome of behaviour without feedback BCT </t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>A &lt;behaviour change technique&gt; that alters the consequences or promised consequences for an outcome that results from performing or not performing the behaviour.</t>
+          <t>A &lt;monitoring BCT&gt; that observes an outcome of performing the behaviour with the person’s knowledge but without providing feedback about the outcome.</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>behaviour change technique</t>
+          <t>monitoring BCT</t>
         </is>
       </c>
       <c r="E139" s="3" t="n"/>
       <c r="F139" s="3" t="n"/>
-      <c r="G139" s="3" t="n"/>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>BCT2.5 Monitoring outcome(s) of behaviour by others without feedback</t>
+        </is>
+      </c>
       <c r="H139" s="3" t="n"/>
       <c r="I139" s="3" t="n"/>
-      <c r="J139" s="3" t="n"/>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>The monitoring agent can be a human or a technical device. If recording is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if feedback given, code only 'provide feedback on outcome of behaviour BCT' and not this class; if observing behaviour code 'observe behaviour without feedback BCT'.</t>
+        </is>
+      </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -8433,7 +8423,7 @@
       <c r="Q139" s="3" t="n"/>
       <c r="R139" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S139" s="3" t="inlineStr">
@@ -8446,36 +8436,28 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007098</t>
+          <t>BCIO:007186</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">overcorrect unwanted behaviour BCT </t>
+          <t>outcome consequence BCT</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>An &lt;advise specific behaviour BCT&gt; that advises the person to repeat a wanted behaviour in an exaggerated way following performance of an unwanted behaviour.</t>
+          <t>A &lt;behaviour change technique&gt; that alters the consequences or promised consequences for an outcome that results from performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>advise specific behaviour BCT</t>
+          <t>behaviour change technique</t>
         </is>
       </c>
       <c r="E140" s="3" t="n"/>
       <c r="F140" s="3" t="n"/>
-      <c r="G140" s="3" t="inlineStr">
-        <is>
-          <t>BCT8.5 Overcorrection</t>
-        </is>
-      </c>
-      <c r="H140" s="3" t="inlineStr">
-        <is>
-          <t>overcorrection, remedial overcompensation</t>
-        </is>
-      </c>
+      <c r="G140" s="3" t="n"/>
+      <c r="H140" s="3" t="n"/>
       <c r="I140" s="3" t="n"/>
       <c r="J140" s="3" t="n"/>
       <c r="K140" s="3" t="inlineStr">
@@ -8495,7 +8477,7 @@
       <c r="Q140" s="3" t="n"/>
       <c r="R140" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S140" s="3" t="inlineStr">
@@ -8508,37 +8490,37 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007137</t>
+          <t>BCIO:007098</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>persuade about personal capability BCT</t>
+          <t xml:space="preserve">overcorrect unwanted behaviour BCT </t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A &lt;prompt thinking related to successful performance BCT&gt; that persuades the person that they can successfully perform the behaviour. </t>
+          <t>An &lt;advise specific behaviour BCT&gt; that advises the person to repeat a wanted behaviour in an exaggerated way following performance of an unwanted behaviour.</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>prompt thinking related to successful performance BCT</t>
+          <t>advise specific behaviour BCT</t>
         </is>
       </c>
       <c r="E141" s="3" t="n"/>
       <c r="F141" s="3" t="n"/>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>BCT15.1 Verbal persuasion about capability</t>
-        </is>
-      </c>
-      <c r="H141" s="3" t="n"/>
-      <c r="I141" s="3" t="inlineStr">
-        <is>
-          <t>Arguing against self-doubts; asserting that the person can and will succeed.</t>
-        </is>
-      </c>
+          <t>BCT8.5 Overcorrection</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>overcorrection, remedial overcompensation</t>
+        </is>
+      </c>
+      <c r="I141" s="3" t="n"/>
       <c r="J141" s="3" t="n"/>
       <c r="K141" s="3" t="inlineStr">
         <is>
@@ -8557,7 +8539,7 @@
       <c r="Q141" s="3" t="n"/>
       <c r="R141" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S141" s="3" t="inlineStr">
@@ -8570,29 +8552,37 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007061</t>
+          <t>BCIO:007137</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">plan inclusion of enjoyment BCT </t>
+          <t>persuade about personal capability BCT</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>A &lt;goal directed BCT&gt; that advises the person to plan a way of performing the behaviour that is pleasurable or satisfying.</t>
+          <t xml:space="preserve">A &lt;prompt thinking related to successful performance BCT&gt; that persuades the person that they can successfully perform the behaviour. </t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>goal directed BCT</t>
+          <t>prompt thinking related to successful performance BCT</t>
         </is>
       </c>
       <c r="E142" s="3" t="n"/>
       <c r="F142" s="3" t="n"/>
-      <c r="G142" s="3" t="n"/>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>BCT15.1 Verbal persuasion about capability</t>
+        </is>
+      </c>
       <c r="H142" s="3" t="n"/>
-      <c r="I142" s="3" t="n"/>
+      <c r="I142" s="3" t="inlineStr">
+        <is>
+          <t>Arguing against self-doubts; asserting that the person can and will succeed.</t>
+        </is>
+      </c>
       <c r="J142" s="3" t="n"/>
       <c r="K142" s="3" t="inlineStr">
         <is>
@@ -8624,42 +8614,30 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007094</t>
+          <t>BCIO:007061</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">practise behaviour BCT </t>
+          <t xml:space="preserve">plan inclusion of enjoyment BCT </t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>An &lt;advise specific behaviour BCT&gt; that advises repetition of the behaviour in a way that has the function of increasing the skill in performing the behaviour.</t>
+          <t>A &lt;goal directed BCT&gt; that advises the person to plan a way of performing the behaviour that is pleasurable or satisfying.</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>advise specific behaviour BCT</t>
+          <t>goal directed BCT</t>
         </is>
       </c>
       <c r="E143" s="3" t="n"/>
       <c r="F143" s="3" t="n"/>
-      <c r="G143" s="3" t="inlineStr">
-        <is>
-          <t>BCT8.1 Behavioural practice/rehearsal</t>
-        </is>
-      </c>
-      <c r="H143" s="3" t="inlineStr">
-        <is>
-          <t>skill practise, rehearsal</t>
-        </is>
-      </c>
+      <c r="G143" s="3" t="n"/>
+      <c r="H143" s="3" t="n"/>
       <c r="I143" s="3" t="n"/>
-      <c r="J143" s="3" t="inlineStr">
-        <is>
-          <t>If aiming to associate performance with the context, also code 'context-specific repetition of behaviour BCT'</t>
-        </is>
-      </c>
+      <c r="J143" s="3" t="n"/>
       <c r="K143" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -8677,7 +8655,7 @@
       <c r="Q143" s="3" t="n"/>
       <c r="R143" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S143" s="3" t="inlineStr">
@@ -8690,36 +8668,40 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007075</t>
+          <t>BCIO:007094</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>present information from credible influence BCT</t>
+          <t xml:space="preserve">practise behaviour BCT </t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>An &lt;awareness of other people's thoughts, feelings and actions BCT&gt; that presents information from a credible person or organisation to influence the behaviour.</t>
+          <t>An &lt;advise specific behaviour BCT&gt; that advises repetition of the behaviour in a way that has the function of increasing the skill in performing the behaviour.</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>awareness of other peoples thoughts, feelings and actions BCT</t>
+          <t>advise specific behaviour BCT</t>
         </is>
       </c>
       <c r="E144" s="3" t="n"/>
       <c r="F144" s="3" t="n"/>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>BCT9.1 Credible source</t>
-        </is>
-      </c>
-      <c r="H144" s="3" t="n"/>
+          <t>BCT8.1 Behavioural practice/rehearsal</t>
+        </is>
+      </c>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>skill practise, rehearsal</t>
+        </is>
+      </c>
       <c r="I144" s="3" t="n"/>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>Code this BCT if influence generally agreed on as credible e.g., health professionals, celebrities or words used to indicate expertise or leader in field and if the communication has the aim of persuading</t>
+          <t>If aiming to associate performance with the context, also code 'context-specific repetition of behaviour BCT'</t>
         </is>
       </c>
       <c r="K144" s="3" t="inlineStr">
@@ -8752,40 +8734,36 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007189</t>
+          <t>BCIO:007075</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for behaviour BCT</t>
+          <t>present information from credible influence BCT</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise consequence for behaviour BCT&gt; where the consequence is aversive.</t>
+          <t>An &lt;awareness of other people's thoughts, feelings and actions BCT&gt; that presents information from a credible person or organisation to influence the behaviour.</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>promise consequence for behaviour BCT</t>
+          <t>awareness of other peoples thoughts, feelings and actions BCT</t>
         </is>
       </c>
       <c r="E145" s="3" t="n"/>
       <c r="F145" s="3" t="n"/>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>BCT10.11 Future punishment</t>
-        </is>
-      </c>
-      <c r="H145" s="3" t="inlineStr">
-        <is>
-          <t>threat, warning, disincentive</t>
-        </is>
-      </c>
+          <t>BCT9.1 Credible source</t>
+        </is>
+      </c>
+      <c r="H145" s="3" t="n"/>
       <c r="I145" s="3" t="n"/>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>To qualify as aversive, the consequence should be aversively valued by the person receiving it.</t>
+          <t>Code this BCT if influence generally agreed on as credible e.g., health professionals, celebrities or words used to indicate expertise or leader in field and if the communication has the aim of persuading</t>
         </is>
       </c>
       <c r="K145" s="3" t="inlineStr">
@@ -8818,34 +8796,42 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007195</t>
+          <t>BCIO:007189</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for outcome of behaviour BCT</t>
+          <t>promise aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise consequence for outcome of behaviour BCT&gt; where the consequence is aversive.</t>
+          <t>A &lt;promise consequence for behaviour BCT&gt; where the consequence is aversive.</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>promise consequence for outcome of behaviour BCT</t>
+          <t>promise consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E146" s="3" t="n"/>
       <c r="F146" s="3" t="n"/>
-      <c r="G146" s="3" t="n"/>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t>BCT10.11 Future punishment</t>
+        </is>
+      </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
           <t>threat, warning, disincentive</t>
         </is>
       </c>
       <c r="I146" s="3" t="n"/>
-      <c r="J146" s="3" t="n"/>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>To qualify as aversive, the consequence should be aversively valued by the person receiving it.</t>
+        </is>
+      </c>
       <c r="K146" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -8876,22 +8862,22 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007191</t>
+          <t>BCIO:007195</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for situation specific behaviour BCT</t>
+          <t>promise aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise aversive consequence for behaviour BCT&gt; that promises the consequence will be provided for the behaviour in one situation but not in another.</t>
+          <t>A &lt;promise consequence for outcome of behaviour BCT&gt; where the consequence is aversive.</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for behaviour BCT</t>
+          <t>promise consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E147" s="3" t="n"/>
@@ -8899,7 +8885,7 @@
       <c r="G147" s="3" t="n"/>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>threat for situation specific behaviour</t>
+          <t>threat, warning, disincentive</t>
         </is>
       </c>
       <c r="I147" s="3" t="n"/>
@@ -8934,17 +8920,17 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007192</t>
+          <t>BCIO:007191</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>promise aversive material consequence for behaviour BCT</t>
+          <t>promise aversive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise aversive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise aversive consequence for behaviour BCT&gt; that promises the consequence will be provided for the behaviour in one situation but not in another.</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
@@ -8957,7 +8943,7 @@
       <c r="G148" s="3" t="n"/>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>material threat</t>
+          <t>threat for situation specific behaviour</t>
         </is>
       </c>
       <c r="I148" s="3" t="n"/>
@@ -8992,28 +8978,32 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007194</t>
+          <t>BCIO:007192</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>promise aversive material consequence for outcome of behaviour</t>
+          <t>promise aversive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise aversive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise aversive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for outcome of behaviour BCT</t>
+          <t>promise aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E149" s="3" t="n"/>
       <c r="F149" s="3" t="n"/>
       <c r="G149" s="3" t="n"/>
-      <c r="H149" s="3" t="n"/>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>material threat</t>
+        </is>
+      </c>
       <c r="I149" s="3" t="n"/>
       <c r="J149" s="3" t="n"/>
       <c r="K149" s="3" t="inlineStr">
@@ -9046,32 +9036,28 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007193</t>
+          <t>BCIO:007194</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>promise aversive material consequence for situation specific behaviour BCT</t>
+          <t>promise aversive material consequence for outcome of behaviour</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise aversive consequence for situation specific behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise aversive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for situation specific behaviour BCT</t>
+          <t>promise aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E150" s="3" t="n"/>
       <c r="F150" s="3" t="n"/>
       <c r="G150" s="3" t="n"/>
-      <c r="H150" s="3" t="inlineStr">
-        <is>
-          <t>material threat for situation specific behaviour</t>
-        </is>
-      </c>
+      <c r="H150" s="3" t="n"/>
       <c r="I150" s="3" t="n"/>
       <c r="J150" s="3" t="n"/>
       <c r="K150" s="3" t="inlineStr">
@@ -9104,22 +9090,22 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007197</t>
+          <t>BCIO:007193</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>promise aversive social consequence for behaviour BCT</t>
+          <t>promise aversive material consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise aversive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise aversive consequence for situation specific behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for behaviour BCT</t>
+          <t>promise aversive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="E151" s="3" t="n"/>
@@ -9127,15 +9113,11 @@
       <c r="G151" s="3" t="n"/>
       <c r="H151" s="3" t="inlineStr">
         <is>
-          <t>social threat</t>
+          <t>material threat for situation specific behaviour</t>
         </is>
       </c>
       <c r="I151" s="3" t="n"/>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="J151" s="3" t="n"/>
       <c r="K151" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -9166,28 +9148,32 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007199</t>
+          <t>BCIO:007197</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>promise aversive social consequence for outcome of behaviour BCT</t>
+          <t>promise aversive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A &lt;promise aversive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process. </t>
+          <t>A &lt;promise aversive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for outcome of behaviour BCT</t>
+          <t>promise aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E152" s="3" t="n"/>
       <c r="F152" s="3" t="n"/>
       <c r="G152" s="3" t="n"/>
-      <c r="H152" s="3" t="n"/>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>social threat</t>
+        </is>
+      </c>
       <c r="I152" s="3" t="n"/>
       <c r="J152" s="3" t="inlineStr">
         <is>
@@ -9224,32 +9210,28 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007198</t>
+          <t>BCIO:007199</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>promise aversive social consequence for situation specific behaviour BCT</t>
+          <t>promise aversive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise aversive consequence for situation specific behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t xml:space="preserve">A &lt;promise aversive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process. </t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for situation specific behaviour BCT</t>
+          <t>promise aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E153" s="3" t="n"/>
       <c r="F153" s="3" t="n"/>
       <c r="G153" s="3" t="n"/>
-      <c r="H153" s="3" t="inlineStr">
-        <is>
-          <t>social threat for situation specific behaviour</t>
-        </is>
-      </c>
+      <c r="H153" s="3" t="n"/>
       <c r="I153" s="3" t="n"/>
       <c r="J153" s="3" t="inlineStr">
         <is>
@@ -9286,32 +9268,36 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007187</t>
+          <t>BCIO:007198</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>promise consequence for behaviour BCT</t>
+          <t>promise aversive social consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>A &lt;behavioural consequence BCT&gt; that promises a future consequence contingent on performing or not performing the behaviour.</t>
+          <t>A &lt;promise aversive consequence for situation specific behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>behavioural consequence BCT</t>
+          <t>promise aversive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="E154" s="3" t="n"/>
       <c r="F154" s="3" t="n"/>
       <c r="G154" s="3" t="n"/>
-      <c r="H154" s="3" t="n"/>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>social threat for situation specific behaviour</t>
+        </is>
+      </c>
       <c r="I154" s="3" t="n"/>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">"promises" here means assuring someone that one will do something or that something will happen.  </t>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
         </is>
       </c>
       <c r="K154" s="3" t="inlineStr">
@@ -9331,7 +9317,7 @@
       <c r="Q154" s="3" t="n"/>
       <c r="R154" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S154" s="3" t="inlineStr">
@@ -9344,22 +9330,22 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007200</t>
+          <t>BCIO:007187</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>promise consequence for outcome of behaviour BCT</t>
+          <t>promise consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">An &lt;outcome consequence BCT&gt; that promises a future consequence contingent on an outcome of performing or not performing the behaviour. </t>
+          <t>A &lt;behavioural consequence BCT&gt; that promises a future consequence contingent on performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>outcome consequence BCT</t>
+          <t>behavioural consequence BCT</t>
         </is>
       </c>
       <c r="E155" s="3" t="n"/>
@@ -9402,34 +9388,34 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007204</t>
+          <t>BCIO:007200</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for alternative behaviour BCT</t>
+          <t>promise consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for behaviour BCT&gt; that promises the consequence will be provided for the behaviour that is different from the unwanted behaviour.</t>
+          <t xml:space="preserve">An &lt;outcome consequence BCT&gt; that promises a future consequence contingent on an outcome of performing or not performing the behaviour. </t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for behaviour BCT</t>
+          <t>outcome consequence BCT</t>
         </is>
       </c>
       <c r="E156" s="3" t="n"/>
       <c r="F156" s="3" t="n"/>
       <c r="G156" s="3" t="n"/>
-      <c r="H156" s="3" t="inlineStr">
-        <is>
-          <t>incentive for alternative behaviour</t>
-        </is>
-      </c>
+      <c r="H156" s="3" t="n"/>
       <c r="I156" s="3" t="n"/>
-      <c r="J156" s="3" t="n"/>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"promises" here means assuring someone that one will do something or that something will happen.  </t>
+        </is>
+      </c>
       <c r="K156" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -9447,7 +9433,7 @@
       <c r="Q156" s="3" t="n"/>
       <c r="R156" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S156" s="3" t="inlineStr">
@@ -9460,17 +9446,17 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007205</t>
+          <t>BCIO:007204</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for approximating behaviour BCT</t>
+          <t>promise positive consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for behaviour BCT&gt; where the consequence is provided as the performance gradually gets closer to the behaviour.</t>
+          <t>A &lt;promise positive consequence for behaviour BCT&gt; that promises the consequence will be provided for the behaviour that is different from the unwanted behaviour.</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
@@ -9483,7 +9469,7 @@
       <c r="G157" s="3" t="n"/>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>incentive for approximating behaviour</t>
+          <t>incentive for alternative behaviour</t>
         </is>
       </c>
       <c r="I157" s="3" t="n"/>
@@ -9518,42 +9504,34 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007202</t>
+          <t>BCIO:007205</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
+          <t>promise positive consequence for approximating behaviour BCT</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>A &lt;promise positive consequence for behaviour BCT&gt; where the consequence is provided as the performance gradually gets closer to the behaviour.</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
           <t>promise positive consequence for behaviour BCT</t>
-        </is>
-      </c>
-      <c r="C158" s="3" t="inlineStr">
-        <is>
-          <t>A &lt;promise consequence for behaviour BCT&gt; where the consequence is positive.</t>
-        </is>
-      </c>
-      <c r="D158" s="3" t="inlineStr">
-        <is>
-          <t>promise consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E158" s="3" t="n"/>
       <c r="F158" s="3" t="n"/>
-      <c r="G158" s="3" t="inlineStr">
-        <is>
-          <t>BCT10.6 Non-specific incentive; BCT10.7 Self-incentive</t>
-        </is>
-      </c>
+      <c r="G158" s="3" t="n"/>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>incentive</t>
+          <t>incentive for approximating behaviour</t>
         </is>
       </c>
       <c r="I158" s="3" t="n"/>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>To qualify as positive, the consequence should be positively valued by the person receiving it. If consequence is delivered, also code 'provide positive consequence for behaviour BCT' or one of its child classes.</t>
-        </is>
-      </c>
+      <c r="J158" s="3" t="n"/>
       <c r="K158" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -9584,34 +9562,42 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007206</t>
+          <t>BCIO:007202</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for completion of behavioural sequence BCT</t>
+          <t>promise positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for behaviour BCT&gt; in which the consequence will be provided for performing the final behaviour in a sequence of behaviours, followed by adding behaviours that occur earlier in the sequence.</t>
+          <t>A &lt;promise consequence for behaviour BCT&gt; where the consequence is positive.</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for behaviour BCT</t>
+          <t>promise consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E159" s="3" t="n"/>
       <c r="F159" s="3" t="n"/>
-      <c r="G159" s="3" t="n"/>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>BCT10.6 Non-specific incentive; BCT10.7 Self-incentive</t>
+        </is>
+      </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>incentive for completion of behavioural sequence</t>
+          <t>incentive</t>
         </is>
       </c>
       <c r="I159" s="3" t="n"/>
-      <c r="J159" s="3" t="n"/>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>To qualify as positive, the consequence should be positively valued by the person receiving it. If consequence is delivered, also code 'provide positive consequence for behaviour BCT' or one of its child classes.</t>
+        </is>
+      </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -9642,17 +9628,17 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007207</t>
+          <t>BCIO:007206</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for incompatible behaviour BCT</t>
+          <t>promise positive consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for behaviour BCT&gt; that promises the consequence will be provided for the behaviour that is incompatible with the unwanted behaviour.</t>
+          <t>A &lt;promise positive consequence for behaviour BCT&gt; in which the consequence will be provided for performing the final behaviour in a sequence of behaviours, followed by adding behaviours that occur earlier in the sequence.</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
@@ -9665,7 +9651,7 @@
       <c r="G160" s="3" t="n"/>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>incentive for incompatible behaviour</t>
+          <t>incentive for completion of behavioural sequence</t>
         </is>
       </c>
       <c r="I160" s="3" t="n"/>
@@ -9687,7 +9673,7 @@
       <c r="Q160" s="3" t="n"/>
       <c r="R160" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S160" s="3" t="inlineStr">
@@ -9700,34 +9686,30 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007216</t>
+          <t>BCIO:007207</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for outcome of behaviour BCT</t>
+          <t>promise positive consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise consequence for outcome of behaviour BCT&gt; where the consequence is positive</t>
+          <t>A &lt;promise positive consequence for behaviour BCT&gt; that promises the consequence will be provided for the behaviour that is incompatible with the unwanted behaviour.</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>promise consequence for outcome of behaviour BCT</t>
+          <t>promise positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E161" s="3" t="n"/>
       <c r="F161" s="3" t="n"/>
-      <c r="G161" s="3" t="inlineStr">
-        <is>
-          <t>BCT10.8 Incentive (outcome)</t>
-        </is>
-      </c>
+      <c r="G161" s="3" t="n"/>
       <c r="H161" s="3" t="inlineStr">
         <is>
-          <t>incentive</t>
+          <t>incentive for incompatible behaviour</t>
         </is>
       </c>
       <c r="I161" s="3" t="n"/>
@@ -9749,7 +9731,7 @@
       <c r="Q161" s="3" t="n"/>
       <c r="R161" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S161" s="3" t="inlineStr">
@@ -9762,30 +9744,34 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007208</t>
+          <t>BCIO:007216</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for situation specific behaviour BCT</t>
+          <t>promise positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for behaviour BCT&gt; that promises the consequence will be provided for the behaviour in one situation but not in another.</t>
+          <t>A &lt;promise consequence for outcome of behaviour BCT&gt; where the consequence is positive</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for behaviour BCT</t>
+          <t>promise consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E162" s="3" t="n"/>
       <c r="F162" s="3" t="n"/>
-      <c r="G162" s="3" t="n"/>
+      <c r="G162" s="3" t="inlineStr">
+        <is>
+          <t>BCT10.8 Incentive (outcome)</t>
+        </is>
+      </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>incentive for situation specific behaviour</t>
+          <t>incentive</t>
         </is>
       </c>
       <c r="I162" s="3" t="n"/>
@@ -9807,7 +9793,7 @@
       <c r="Q162" s="3" t="n"/>
       <c r="R162" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S162" s="3" t="inlineStr">
@@ -9820,22 +9806,22 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007210</t>
+          <t>BCIO:007208</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>promise positive material consequence for alternative behaviour BCT</t>
+          <t>promise positive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for alternative behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise positive consequence for behaviour BCT&gt; that promises the consequence will be provided for the behaviour in one situation but not in another.</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for alternative behaviour BCT</t>
+          <t>promise positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E163" s="3" t="n"/>
@@ -9843,7 +9829,7 @@
       <c r="G163" s="3" t="n"/>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>material incentive for alternative behaviour</t>
+          <t>incentive for situation specific behaviour</t>
         </is>
       </c>
       <c r="I163" s="3" t="n"/>
@@ -9878,22 +9864,22 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007211</t>
+          <t>BCIO:007210</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>promise positive material consequence for approximating behaviour BCT</t>
+          <t>promise positive material consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A &lt;promise positive consequence for approximating behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects. </t>
+          <t>A &lt;promise positive consequence for alternative behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for approximating behaviour BCT</t>
+          <t>promise positive consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="E164" s="3" t="n"/>
@@ -9901,7 +9887,7 @@
       <c r="G164" s="3" t="n"/>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>material incentive for approximating behaviour</t>
+          <t>material incentive for alternative behaviour</t>
         </is>
       </c>
       <c r="I164" s="3" t="n"/>
@@ -9936,34 +9922,30 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007209</t>
+          <t>BCIO:007211</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>promise positive material consequence for behaviour BCT</t>
+          <t>promise positive material consequence for approximating behaviour BCT</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t xml:space="preserve">A &lt;promise positive consequence for approximating behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects. </t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for behaviour BCT</t>
+          <t>promise positive consequence for approximating behaviour BCT</t>
         </is>
       </c>
       <c r="E165" s="3" t="n"/>
       <c r="F165" s="3" t="n"/>
-      <c r="G165" s="3" t="inlineStr">
-        <is>
-          <t>BCT10.1 Material incentive (behaviour)</t>
-        </is>
-      </c>
+      <c r="G165" s="3" t="n"/>
       <c r="H165" s="3" t="inlineStr">
         <is>
-          <t>material incentive</t>
+          <t>material incentive for approximating behaviour</t>
         </is>
       </c>
       <c r="I165" s="3" t="n"/>
@@ -9985,7 +9967,7 @@
       <c r="Q165" s="3" t="n"/>
       <c r="R165" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S165" s="3" t="inlineStr">
@@ -9998,30 +9980,34 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007212</t>
+          <t>BCIO:007209</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>promise positive material consequence for completion of behavioural sequence BCT</t>
+          <t>promise positive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for completion of behavioural sequence BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise positive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for completion of behavioural sequence BCT</t>
+          <t>promise positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E166" s="3" t="n"/>
       <c r="F166" s="3" t="n"/>
-      <c r="G166" s="3" t="n"/>
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t>BCT10.1 Material incentive (behaviour)</t>
+        </is>
+      </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>material incentive for completion of behavioural sequence</t>
+          <t>material incentive</t>
         </is>
       </c>
       <c r="I166" s="3" t="n"/>
@@ -10043,7 +10029,7 @@
       <c r="Q166" s="3" t="n"/>
       <c r="R166" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S166" s="3" t="inlineStr">
@@ -10056,22 +10042,22 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007213</t>
+          <t>BCIO:007212</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>promise positive material consequence for incompatible behaviour BCT</t>
+          <t>promise positive material consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for incompatible behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise positive consequence for completion of behavioural sequence BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for incompatible behaviour BCT</t>
+          <t>promise positive consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="E167" s="3" t="n"/>
@@ -10079,7 +10065,7 @@
       <c r="G167" s="3" t="n"/>
       <c r="H167" s="3" t="inlineStr">
         <is>
-          <t>material incentive for incompatible behaviour</t>
+          <t>material incentive for completion of behavioural sequence</t>
         </is>
       </c>
       <c r="I167" s="3" t="n"/>
@@ -10114,28 +10100,32 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007215</t>
+          <t>BCIO:007213</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>promise positive material consequence for outcome of behaviour BCT</t>
+          <t>promise positive material consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise positive consequence for incompatible behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for outcome of behaviour BCT</t>
+          <t>promise positive consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="E168" s="3" t="n"/>
       <c r="F168" s="3" t="n"/>
       <c r="G168" s="3" t="n"/>
-      <c r="H168" s="3" t="n"/>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>material incentive for incompatible behaviour</t>
+        </is>
+      </c>
       <c r="I168" s="3" t="n"/>
       <c r="J168" s="3" t="n"/>
       <c r="K168" s="3" t="inlineStr">
@@ -10168,32 +10158,28 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007214</t>
+          <t>BCIO:007215</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>promise positive material consequence for situation specific behaviour BCT</t>
+          <t>promise positive material consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for situation specific behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise positive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for situation specific behaviour BCT</t>
+          <t>promise positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E169" s="3" t="n"/>
       <c r="F169" s="3" t="n"/>
       <c r="G169" s="3" t="n"/>
-      <c r="H169" s="3" t="inlineStr">
-        <is>
-          <t>material incentive for situation specific behaviour</t>
-        </is>
-      </c>
+      <c r="H169" s="3" t="n"/>
       <c r="I169" s="3" t="n"/>
       <c r="J169" s="3" t="n"/>
       <c r="K169" s="3" t="inlineStr">
@@ -10226,22 +10212,22 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007219</t>
+          <t>BCIO:007214</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>promise positive social consequence for alternative behaviour BCT</t>
+          <t>promise positive material consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for alternative behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise positive consequence for situation specific behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for alternative behaviour BCT</t>
+          <t>promise positive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="E170" s="3" t="n"/>
@@ -10249,15 +10235,11 @@
       <c r="G170" s="3" t="n"/>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>social incentive for alternative behaviour</t>
+          <t>material incentive for situation specific behaviour</t>
         </is>
       </c>
       <c r="I170" s="3" t="n"/>
-      <c r="J170" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="J170" s="3" t="n"/>
       <c r="K170" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -10288,22 +10270,22 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007220</t>
+          <t>BCIO:007219</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>promise positive social consequence for approximating behaviour BCT</t>
+          <t>promise positive social consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for approximating behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise positive consequence for alternative behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for approximating behaviour BCT</t>
+          <t>promise positive consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="E171" s="3" t="n"/>
@@ -10311,7 +10293,7 @@
       <c r="G171" s="3" t="n"/>
       <c r="H171" s="3" t="inlineStr">
         <is>
-          <t>social incentive for approximating behaviour</t>
+          <t>social incentive for alternative behaviour</t>
         </is>
       </c>
       <c r="I171" s="3" t="n"/>
@@ -10350,34 +10332,30 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007218</t>
+          <t>BCIO:007220</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>promise positive social consequence for behaviour BCT</t>
+          <t>promise positive social consequence for approximating behaviour BCT</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise positive consequence for approximating behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for behaviour BCT</t>
+          <t>promise positive consequence for approximating behaviour BCT</t>
         </is>
       </c>
       <c r="E172" s="3" t="n"/>
       <c r="F172" s="3" t="n"/>
-      <c r="G172" s="3" t="inlineStr">
-        <is>
-          <t>BCT10.5 Social incentive</t>
-        </is>
-      </c>
+      <c r="G172" s="3" t="n"/>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>social incentive</t>
+          <t>social incentive for approximating behaviour</t>
         </is>
       </c>
       <c r="I172" s="3" t="n"/>
@@ -10403,7 +10381,7 @@
       <c r="Q172" s="3" t="n"/>
       <c r="R172" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S172" s="3" t="inlineStr">
@@ -10416,30 +10394,34 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007221</t>
+          <t>BCIO:007218</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>promise positive social consequence for completion of behavioural sequence BCT</t>
+          <t>promise positive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for completion of behavioural sequence BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise positive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for completion of behavioural sequence BCT</t>
+          <t>promise positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E173" s="3" t="n"/>
       <c r="F173" s="3" t="n"/>
-      <c r="G173" s="3" t="n"/>
+      <c r="G173" s="3" t="inlineStr">
+        <is>
+          <t>BCT10.5 Social incentive</t>
+        </is>
+      </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
-          <t>social incentive for completion of behavioural sequence</t>
+          <t>social incentive</t>
         </is>
       </c>
       <c r="I173" s="3" t="n"/>
@@ -10465,7 +10447,7 @@
       <c r="Q173" s="3" t="n"/>
       <c r="R173" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S173" s="3" t="inlineStr">
@@ -10478,22 +10460,22 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007222</t>
+          <t>BCIO:007221</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>promise positive social consequence for incompatible behaviour BCT</t>
+          <t>promise positive social consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for incompatible behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise positive consequence for completion of behavioural sequence BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for incompatible behaviour BCT</t>
+          <t>promise positive consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="E174" s="3" t="n"/>
@@ -10501,7 +10483,7 @@
       <c r="G174" s="3" t="n"/>
       <c r="H174" s="3" t="inlineStr">
         <is>
-          <t>social incentive for incompatible behaviour</t>
+          <t>social incentive for completion of behavioural sequence</t>
         </is>
       </c>
       <c r="I174" s="3" t="n"/>
@@ -10540,28 +10522,32 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007224</t>
+          <t>BCIO:007222</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>promise positive social consequence for outcome of behaviour BCT</t>
+          <t>promise positive social consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A &lt;promise positive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process. </t>
+          <t>A &lt;promise positive consequence for incompatible behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for outcome of behaviour BCT</t>
+          <t>promise positive consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="E175" s="3" t="n"/>
       <c r="F175" s="3" t="n"/>
       <c r="G175" s="3" t="n"/>
-      <c r="H175" s="3" t="n"/>
+      <c r="H175" s="3" t="inlineStr">
+        <is>
+          <t>social incentive for incompatible behaviour</t>
+        </is>
+      </c>
       <c r="I175" s="3" t="n"/>
       <c r="J175" s="3" t="inlineStr">
         <is>
@@ -10598,32 +10584,28 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007223</t>
+          <t>BCIO:007224</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>promise positive social consequence for situation specific behaviour BCT</t>
+          <t>promise positive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for situation specific behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t xml:space="preserve">A &lt;promise positive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process. </t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for situation specific behaviour BCT</t>
+          <t>promise positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E176" s="3" t="n"/>
       <c r="F176" s="3" t="n"/>
       <c r="G176" s="3" t="n"/>
-      <c r="H176" s="3" t="inlineStr">
-        <is>
-          <t>social incentive for situation specific behaviour</t>
-        </is>
-      </c>
+      <c r="H176" s="3" t="n"/>
       <c r="I176" s="3" t="n"/>
       <c r="J176" s="3" t="inlineStr">
         <is>
@@ -10660,22 +10642,22 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007225</t>
+          <t>BCIO:007223</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>promise reduced frequency of aversive consequence for behaviour BCT</t>
+          <t>promise positive social consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for behaviour BCT&gt; that promises to provide the consequence at increasingly less frequent intervals.</t>
+          <t>A &lt;promise positive consequence for situation specific behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for behaviour BCT</t>
+          <t>promise positive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="E177" s="3" t="n"/>
@@ -10683,11 +10665,15 @@
       <c r="G177" s="3" t="n"/>
       <c r="H177" s="3" t="inlineStr">
         <is>
-          <t>reduce threat frequency</t>
+          <t>social incentive for situation specific behaviour</t>
         </is>
       </c>
       <c r="I177" s="3" t="n"/>
-      <c r="J177" s="3" t="n"/>
+      <c r="J177" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -10705,7 +10691,7 @@
       <c r="Q177" s="3" t="n"/>
       <c r="R177" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S177" s="3" t="inlineStr">
@@ -10718,22 +10704,22 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007226</t>
+          <t>BCIO:007225</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>promise reduced frequency of aversive material consequence for behaviour BCT</t>
+          <t>promise reduced frequency of aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise reduced frequency of aversive consequence for behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise positive consequence for behaviour BCT&gt; that promises to provide the consequence at increasingly less frequent intervals.</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>promise reduced frequency of aversive consequence for behaviour BCT</t>
+          <t>promise positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E178" s="3" t="n"/>
@@ -10741,7 +10727,7 @@
       <c r="G178" s="3" t="n"/>
       <c r="H178" s="3" t="inlineStr">
         <is>
-          <t>reduce material threat frequency</t>
+          <t>reduce threat frequency</t>
         </is>
       </c>
       <c r="I178" s="3" t="n"/>
@@ -10776,17 +10762,17 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007227</t>
+          <t>BCIO:007226</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>promise reduced frequency of aversive social consequence for behaviour BCT</t>
+          <t>promise reduced frequency of aversive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise reduced frequency of aversive consequence for behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise reduced frequency of aversive consequence for behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
@@ -10799,15 +10785,11 @@
       <c r="G179" s="3" t="n"/>
       <c r="H179" s="3" t="inlineStr">
         <is>
-          <t>reduce social threat frequency</t>
+          <t>reduce material threat frequency</t>
         </is>
       </c>
       <c r="I179" s="3" t="n"/>
-      <c r="J179" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="J179" s="3" t="n"/>
       <c r="K179" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -10838,22 +10820,22 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007228</t>
+          <t>BCIO:007227</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>promise reduced frequency of positive consequence for behaviour BCT</t>
+          <t>promise reduced frequency of aversive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise aversive consequence for behaviour BCT&gt; that promises to provide the consequence at increasingly less frequent intervals.</t>
+          <t>A &lt;promise reduced frequency of aversive consequence for behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for outcome of behaviour BCT</t>
+          <t>promise reduced frequency of aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E180" s="3" t="n"/>
@@ -10861,11 +10843,15 @@
       <c r="G180" s="3" t="n"/>
       <c r="H180" s="3" t="inlineStr">
         <is>
-          <t>reduce incentive frequency</t>
+          <t>reduce social threat frequency</t>
         </is>
       </c>
       <c r="I180" s="3" t="n"/>
-      <c r="J180" s="3" t="n"/>
+      <c r="J180" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="K180" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -10883,7 +10869,7 @@
       <c r="Q180" s="3" t="n"/>
       <c r="R180" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S180" s="3" t="inlineStr">
@@ -10896,22 +10882,22 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007229</t>
+          <t>BCIO:007228</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>promise reduced frequency of positive material consequence for behaviour BCT</t>
+          <t>promise reduced frequency of positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise reduced frequency of positive consequence for behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise aversive consequence for behaviour BCT&gt; that promises to provide the consequence at increasingly less frequent intervals.</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>promise reduced frequency of positive consequence for behaviour BCT</t>
+          <t>promise aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E181" s="3" t="n"/>
@@ -10919,7 +10905,7 @@
       <c r="G181" s="3" t="n"/>
       <c r="H181" s="3" t="inlineStr">
         <is>
-          <t>reduce material incentive frequency</t>
+          <t>reduce incentive frequency</t>
         </is>
       </c>
       <c r="I181" s="3" t="n"/>
@@ -10954,17 +10940,17 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007230</t>
+          <t>BCIO:007229</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>promise reduced frequency of positive social consequence for behaviour BCT</t>
+          <t>promise reduced frequency of positive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise reduced frequency of positive consequence for behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise reduced frequency of positive consequence for behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
@@ -10977,15 +10963,11 @@
       <c r="G182" s="3" t="n"/>
       <c r="H182" s="3" t="inlineStr">
         <is>
-          <t>reduce social incentive frequency</t>
+          <t>reduce material incentive frequency</t>
         </is>
       </c>
       <c r="I182" s="3" t="n"/>
-      <c r="J182" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="J182" s="3" t="n"/>
       <c r="K182" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -11016,22 +10998,22 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007190</t>
+          <t>BCIO:007230</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive consequence for behaviour BCT</t>
+          <t>promise reduced frequency of positive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove consequence for behaviour BCT&gt; where the consequence is aversive.</t>
+          <t>A &lt;promise reduced frequency of positive consequence for behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>promise to remove consequence for behaviour BCT</t>
+          <t>promise reduced frequency of positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E183" s="3" t="n"/>
@@ -11039,11 +11021,15 @@
       <c r="G183" s="3" t="n"/>
       <c r="H183" s="3" t="inlineStr">
         <is>
-          <t>incentive to remove punishment</t>
+          <t>reduce social incentive frequency</t>
         </is>
       </c>
       <c r="I183" s="3" t="n"/>
-      <c r="J183" s="3" t="n"/>
+      <c r="J183" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -11061,7 +11047,7 @@
       <c r="Q183" s="3" t="n"/>
       <c r="R183" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S183" s="3" t="inlineStr">
@@ -11074,22 +11060,22 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007196</t>
+          <t>BCIO:007190</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive consequence for outcome of behaviour BCT</t>
+          <t>promise to remove aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove consequence for outcome of behaviour BCT&gt; where the consequence is aversive.</t>
+          <t>A &lt;promise to remove consequence for behaviour BCT&gt; where the consequence is aversive.</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>promise to remove consequence for outcome of behaviour BCT</t>
+          <t>promise to remove consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E184" s="3" t="n"/>
@@ -11132,22 +11118,22 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007231</t>
+          <t>BCIO:007196</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive material consequence for behaviour BCT</t>
+          <t>promise to remove aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove aversive consequence for behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise to remove consequence for outcome of behaviour BCT&gt; where the consequence is aversive.</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive consequence for behaviour BCT</t>
+          <t>promise to remove consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E185" s="3" t="n"/>
@@ -11155,7 +11141,7 @@
       <c r="G185" s="3" t="n"/>
       <c r="H185" s="3" t="inlineStr">
         <is>
-          <t>incentive to remove material punishment</t>
+          <t>incentive to remove punishment</t>
         </is>
       </c>
       <c r="I185" s="3" t="n"/>
@@ -11190,22 +11176,22 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007232</t>
+          <t>BCIO:007231</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive material consequence for outcome of behaviour BCT</t>
+          <t>promise to remove aversive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove aversive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise to remove aversive consequence for behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive consequence for outcome of behaviour BCT</t>
+          <t>promise to remove aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E186" s="3" t="n"/>
@@ -11248,22 +11234,22 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007233</t>
+          <t>BCIO:007232</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive social consequence for behaviour BCT</t>
+          <t>promise to remove aversive material consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove aversive consequence for behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process</t>
+          <t>A &lt;promise to remove aversive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive consequence for behaviour BCT</t>
+          <t>promise to remove aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E187" s="3" t="n"/>
@@ -11271,15 +11257,11 @@
       <c r="G187" s="3" t="n"/>
       <c r="H187" s="3" t="inlineStr">
         <is>
-          <t>incentive to remove social punishment</t>
+          <t>incentive to remove material punishment</t>
         </is>
       </c>
       <c r="I187" s="3" t="n"/>
-      <c r="J187" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="J187" s="3" t="n"/>
       <c r="K187" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -11310,22 +11292,22 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007234</t>
+          <t>BCIO:007233</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive social consequence for outcome of behaviour BCT</t>
+          <t>promise to remove aversive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove aversive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise to remove aversive consequence for behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive consequence for outcome of behaviour BCT</t>
+          <t>promise to remove aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E188" s="3" t="n"/>
@@ -11372,30 +11354,38 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007188</t>
+          <t>BCIO:007234</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>promise to remove consequence for behaviour BCT</t>
+          <t>promise to remove aversive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>A &lt;behavioural consequence BCT&gt; that promises future removal of a consequence contingent on performing or not performing the behaviour.</t>
+          <t>A &lt;promise to remove aversive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>behavioural consequence BCT</t>
+          <t>promise to remove aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E189" s="3" t="n"/>
       <c r="F189" s="3" t="n"/>
       <c r="G189" s="3" t="n"/>
-      <c r="H189" s="3" t="n"/>
+      <c r="H189" s="3" t="inlineStr">
+        <is>
+          <t>incentive to remove social punishment</t>
+        </is>
+      </c>
       <c r="I189" s="3" t="n"/>
-      <c r="J189" s="3" t="n"/>
+      <c r="J189" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -11413,7 +11403,7 @@
       <c r="Q189" s="3" t="n"/>
       <c r="R189" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S189" s="3" t="inlineStr">
@@ -11426,22 +11416,22 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007201</t>
+          <t>BCIO:007188</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>promise to remove consequence for outcome of behaviour BCT</t>
+          <t>promise to remove consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>An &lt;outcome consequence BCT&gt; that promises future removal of a consequence contingent on an outcome of performing or not performing the behaviour.</t>
+          <t>A &lt;behavioural consequence BCT&gt; that promises future removal of a consequence contingent on performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>outcome consequence BCT</t>
+          <t>behavioural consequence BCT</t>
         </is>
       </c>
       <c r="E190" s="3" t="n"/>
@@ -11480,36 +11470,28 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007203</t>
+          <t>BCIO:007201</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive consequence for behaviour BCT</t>
+          <t>promise to remove consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove consequence for behaviour BCT&gt; where the consequence is positive.</t>
+          <t>An &lt;outcome consequence BCT&gt; that promises future removal of a consequence contingent on an outcome of performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>promise to remove consequence for behaviour BCT</t>
+          <t>outcome consequence BCT</t>
         </is>
       </c>
       <c r="E191" s="3" t="n"/>
       <c r="F191" s="3" t="n"/>
-      <c r="G191" s="3" t="inlineStr">
-        <is>
-          <t>BCT10.11 Future punishment</t>
-        </is>
-      </c>
-      <c r="H191" s="3" t="inlineStr">
-        <is>
-          <t>threaten to remove reward</t>
-        </is>
-      </c>
+      <c r="G191" s="3" t="n"/>
+      <c r="H191" s="3" t="n"/>
       <c r="I191" s="3" t="n"/>
       <c r="J191" s="3" t="n"/>
       <c r="K191" s="3" t="inlineStr">
@@ -11542,27 +11524,31 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007217</t>
+          <t>BCIO:007203</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive consequence for outcome of behaviour BCT</t>
+          <t>promise to remove positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove consequence for outcome of behaviour BCT&gt; where the consequence is positive.</t>
+          <t>A &lt;promise to remove consequence for behaviour BCT&gt; where the consequence is positive.</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>promise to remove consequence for outcome of behaviour BCT</t>
+          <t>promise to remove consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E192" s="3" t="n"/>
       <c r="F192" s="3" t="n"/>
-      <c r="G192" s="3" t="n"/>
+      <c r="G192" s="3" t="inlineStr">
+        <is>
+          <t>BCT10.11 Future punishment</t>
+        </is>
+      </c>
       <c r="H192" s="3" t="inlineStr">
         <is>
           <t>threaten to remove reward</t>
@@ -11600,22 +11586,22 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007235</t>
+          <t>BCIO:007217</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive material consequence for behaviour BCT</t>
+          <t>promise to remove positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove positive consequence for behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise to remove consequence for outcome of behaviour BCT&gt; where the consequence is positive.</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive consequence for behaviour BCT</t>
+          <t>promise to remove consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E193" s="3" t="n"/>
@@ -11623,7 +11609,7 @@
       <c r="G193" s="3" t="n"/>
       <c r="H193" s="3" t="inlineStr">
         <is>
-          <t>threaten to remove material reward</t>
+          <t>threaten to remove reward</t>
         </is>
       </c>
       <c r="I193" s="3" t="n"/>
@@ -11658,22 +11644,22 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007236</t>
+          <t>BCIO:007235</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive material consequence for outcome of behaviour BCT</t>
+          <t>promise to remove positive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove positive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise to remove positive consequence for behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive consequence for outcome of behaviour BCT</t>
+          <t>promise to remove positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E194" s="3" t="n"/>
@@ -11716,22 +11702,22 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007237</t>
+          <t>BCIO:007236</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive social consequence for behaviour BCT</t>
+          <t>promise to remove positive material consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove positive consequence for behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process</t>
+          <t>A &lt;promise to remove positive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive consequence for behaviour BCT</t>
+          <t>promise to remove positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E195" s="3" t="n"/>
@@ -11739,15 +11725,11 @@
       <c r="G195" s="3" t="n"/>
       <c r="H195" s="3" t="inlineStr">
         <is>
-          <t>threaten to remove social reward</t>
+          <t>threaten to remove material reward</t>
         </is>
       </c>
       <c r="I195" s="3" t="n"/>
-      <c r="J195" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="J195" s="3" t="n"/>
       <c r="K195" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -11778,22 +11760,22 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007238</t>
+          <t>BCIO:007237</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive social consequence for outcome of behaviour BCT</t>
+          <t>promise to remove positive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove positive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise to remove positive consequence for behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive consequence for outcome of behaviour BCT</t>
+          <t>promise to remove positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E196" s="3" t="n"/>
@@ -11840,36 +11822,36 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007144</t>
+          <t>BCIO:007238</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>promote pharmacological support BCT</t>
+          <t>promise to remove positive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>A &lt;behaviour change technique&gt; promoting medicines or other drugs.</t>
+          <t>A &lt;promise to remove positive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>behaviour change technique</t>
+          <t>promise to remove positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E197" s="3" t="n"/>
       <c r="F197" s="3" t="n"/>
-      <c r="G197" s="3" t="inlineStr">
-        <is>
-          <t>BCT11.1 Pharmacological support</t>
-        </is>
-      </c>
-      <c r="H197" s="3" t="n"/>
+      <c r="G197" s="3" t="n"/>
+      <c r="H197" s="3" t="inlineStr">
+        <is>
+          <t>threaten to remove social reward</t>
+        </is>
+      </c>
       <c r="I197" s="3" t="n"/>
       <c r="J197" s="3" t="inlineStr">
         <is>
-          <t>If pharmacological support to reduce negative emotions (i.e. anxiety) then also code 'advise how to reduce negative emotions BCT'</t>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
         </is>
       </c>
       <c r="K197" s="3" t="inlineStr">
@@ -11889,7 +11871,7 @@
       <c r="Q197" s="3" t="n"/>
       <c r="R197" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S197" s="3" t="inlineStr">
@@ -11902,38 +11884,38 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007070</t>
+          <t>BCIO:007144</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>prompt comparative imagining of future outcomes BCT</t>
+          <t>promote pharmacological support BCT</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>An &lt;increase awareness of consequences BCT&gt; that guides the person to imagine and compare the consequences of performing and not performing the behaviour.</t>
+          <t>A &lt;behaviour change technique&gt; promoting medicines or other drugs.</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>increase awareness of consequences BCT</t>
+          <t>behaviour change technique</t>
         </is>
       </c>
       <c r="E198" s="3" t="n"/>
       <c r="F198" s="3" t="n"/>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>BCT9.3 Comparative imagining of future outcomes</t>
-        </is>
-      </c>
-      <c r="H198" s="3" t="inlineStr">
-        <is>
-          <t>imagining future results</t>
-        </is>
-      </c>
+          <t>BCT11.1 Pharmacological support</t>
+        </is>
+      </c>
+      <c r="H198" s="3" t="n"/>
       <c r="I198" s="3" t="n"/>
-      <c r="J198" s="3" t="n"/>
+      <c r="J198" s="3" t="inlineStr">
+        <is>
+          <t>If pharmacological support to reduce negative emotions (i.e. anxiety) then also code 'advise how to reduce negative emotions BCT'</t>
+        </is>
+      </c>
       <c r="K198" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -11964,32 +11946,36 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007139</t>
+          <t>BCIO:007070</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>prompt focus on past success BCT</t>
+          <t>prompt comparative imagining of future outcomes BCT</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>A &lt;prompt thinking related to successful performance BCT&gt; that prompts the person to think about previous successful performance of the behaviour.</t>
+          <t>An &lt;increase awareness of consequences BCT&gt; that guides the person to imagine and compare the consequences of performing and not performing the behaviour.</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>prompt thinking related to successful performance BCT</t>
+          <t>increase awareness of consequences BCT</t>
         </is>
       </c>
       <c r="E199" s="3" t="n"/>
       <c r="F199" s="3" t="n"/>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>BCT15.3 Focus on past success</t>
-        </is>
-      </c>
-      <c r="H199" s="3" t="n"/>
+          <t>BCT9.3 Comparative imagining of future outcomes</t>
+        </is>
+      </c>
+      <c r="H199" s="3" t="inlineStr">
+        <is>
+          <t>imagining future results</t>
+        </is>
+      </c>
       <c r="I199" s="3" t="n"/>
       <c r="J199" s="3" t="n"/>
       <c r="K199" s="3" t="inlineStr">
@@ -12009,7 +11995,7 @@
       <c r="Q199" s="3" t="n"/>
       <c r="R199" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S199" s="3" t="inlineStr">
@@ -12022,32 +12008,32 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007157</t>
+          <t>BCIO:007139</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>prompt focus on self-identity BCT</t>
+          <t>prompt focus on past success BCT</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A &lt;behaviour change technique&gt; that prompts the person to focus on their mental representation of themself. </t>
+          <t>A &lt;prompt thinking related to successful performance BCT&gt; that prompts the person to think about previous successful performance of the behaviour.</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>behaviour change technique</t>
+          <t>prompt thinking related to successful performance BCT</t>
         </is>
       </c>
       <c r="E200" s="3" t="n"/>
       <c r="F200" s="3" t="n"/>
-      <c r="G200" s="3" t="n"/>
-      <c r="H200" s="3" t="inlineStr">
-        <is>
-          <t>self-perception</t>
-        </is>
-      </c>
+      <c r="G200" s="3" t="inlineStr">
+        <is>
+          <t>BCT15.3 Focus on past success</t>
+        </is>
+      </c>
+      <c r="H200" s="3" t="n"/>
       <c r="I200" s="3" t="n"/>
       <c r="J200" s="3" t="n"/>
       <c r="K200" s="3" t="inlineStr">
@@ -12067,157 +12053,157 @@
       <c r="Q200" s="3" t="n"/>
       <c r="R200" s="3" t="inlineStr">
         <is>
+          <t>LZ</t>
+        </is>
+      </c>
+      <c r="S200" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T200" s="3" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:007157</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>prompt focus on self-identity BCT</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A &lt;behaviour change technique&gt; that prompts the person to focus on their mental representation of themself. </t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="n"/>
+      <c r="F201" s="3" t="n"/>
+      <c r="G201" s="3" t="n"/>
+      <c r="H201" s="3" t="inlineStr">
+        <is>
+          <t>self-perception</t>
+        </is>
+      </c>
+      <c r="I201" s="3" t="n"/>
+      <c r="J201" s="3" t="n"/>
+      <c r="K201" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="L201" s="3" t="n"/>
+      <c r="M201" s="3" t="n"/>
+      <c r="N201" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O201" s="3" t="n"/>
+      <c r="P201" s="3" t="n"/>
+      <c r="Q201" s="3" t="n"/>
+      <c r="R201" s="3" t="inlineStr">
+        <is>
           <t>lz; LZ</t>
         </is>
       </c>
-      <c r="S200" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T200" s="3" t="n"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
+      <c r="S201" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T201" s="3" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
         <is>
           <t>BCIO:050992</t>
         </is>
       </c>
-      <c r="B201" s="2" t="inlineStr">
+      <c r="B202" s="2" t="inlineStr">
         <is>
           <t>prompt immediate action BCT</t>
         </is>
       </c>
-      <c r="C201" s="2" t="inlineStr">
+      <c r="C202" s="2" t="inlineStr">
         <is>
           <t>An &lt;increase awareness of behaviour BCT&gt; that advises, reminds or directs the person to do the behaviour without delay.</t>
         </is>
       </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>increase awareness of behaviour BCT</t>
         </is>
       </c>
-      <c r="E201" s="2" t="n"/>
-      <c r="F201" s="2" t="n"/>
-      <c r="G201" s="2" t="n"/>
-      <c r="H201" s="2" t="n"/>
-      <c r="I201" s="2" t="n"/>
-      <c r="J201" s="2" t="n"/>
-      <c r="K201" s="2" t="n"/>
-      <c r="L201" s="2" t="n"/>
-      <c r="M201" s="2" t="n"/>
-      <c r="N201" s="2" t="inlineStr">
+      <c r="E202" s="2" t="n"/>
+      <c r="F202" s="2" t="n"/>
+      <c r="G202" s="2" t="n"/>
+      <c r="H202" s="2" t="n"/>
+      <c r="I202" s="2" t="n"/>
+      <c r="J202" s="2" t="n"/>
+      <c r="K202" s="2" t="n"/>
+      <c r="L202" s="2" t="n"/>
+      <c r="M202" s="2" t="n"/>
+      <c r="N202" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="O201" s="2" t="n"/>
-      <c r="P201" s="2" t="n"/>
-      <c r="Q201" s="2" t="n"/>
-      <c r="R201" s="2" t="n"/>
-      <c r="S201" s="2" t="n">
+      <c r="O202" s="2" t="n"/>
+      <c r="P202" s="2" t="n"/>
+      <c r="Q202" s="2" t="n"/>
+      <c r="R202" s="2" t="n"/>
+      <c r="S202" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T201" s="2" t="n"/>
-    </row>
-    <row r="202">
-      <c r="A202" s="3" t="inlineStr">
-        <is>
-          <t>BCIO:007080</t>
-        </is>
-      </c>
-      <c r="B202" s="3" t="inlineStr">
-        <is>
-          <t>prompt intended action BCT</t>
-        </is>
-      </c>
-      <c r="C202" s="3" t="inlineStr">
-        <is>
-          <t>An &lt;alter external stimulus BCT&gt; that involves introducing an external stimulus to facilitate the behaviour for which an intention has previously been formed.</t>
-        </is>
-      </c>
-      <c r="D202" s="3" t="inlineStr">
-        <is>
-          <t>alter external stimulus BCT</t>
-        </is>
-      </c>
-      <c r="E202" s="3" t="n"/>
-      <c r="F202" s="3" t="n"/>
-      <c r="G202" s="3" t="inlineStr">
-        <is>
-          <t>BCT7.1 Prompts/cues</t>
-        </is>
-      </c>
-      <c r="H202" s="3" t="inlineStr">
-        <is>
-          <t>prompts</t>
-        </is>
-      </c>
-      <c r="I202" s="3" t="n"/>
-      <c r="J202" s="3" t="inlineStr">
-        <is>
-          <t>When a stimulus is linked to a specific action in an if-then plan including one or more of frequency, duration or intensity also code 'action planning BCT'</t>
-        </is>
-      </c>
-      <c r="K202" s="3" t="inlineStr">
-        <is>
-          <t>behaviour change technique</t>
-        </is>
-      </c>
-      <c r="L202" s="3" t="n"/>
-      <c r="M202" s="3" t="n"/>
-      <c r="N202" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="O202" s="3" t="n"/>
-      <c r="P202" s="3" t="n"/>
-      <c r="Q202" s="3" t="n"/>
-      <c r="R202" s="3" t="inlineStr">
-        <is>
-          <t>lz; LZ</t>
-        </is>
-      </c>
-      <c r="S202" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T202" s="3" t="n"/>
+      <c r="T202" s="2" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007138</t>
+          <t>BCIO:007080</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>prompt mental rehearsal of successful performance BCT</t>
+          <t>prompt intended action BCT</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>A &lt;prompt thinking related to successful performance BCT&gt; that prompts the person to practise imagining performing the behaviour well in a relevant context.</t>
+          <t>An &lt;alter external stimulus BCT&gt; that involves introducing an external stimulus to facilitate the behaviour for which an intention has previously been formed.</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>prompt thinking related to successful performance BCT</t>
+          <t>alter external stimulus BCT</t>
         </is>
       </c>
       <c r="E203" s="3" t="n"/>
       <c r="F203" s="3" t="n"/>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>BCT15.2 Mental rehearsal of successful performance</t>
-        </is>
-      </c>
-      <c r="H203" s="3" t="n"/>
+          <t>BCT7.1 Prompts/cues</t>
+        </is>
+      </c>
+      <c r="H203" s="3" t="inlineStr">
+        <is>
+          <t>prompts</t>
+        </is>
+      </c>
       <c r="I203" s="3" t="n"/>
-      <c r="J203" s="3" t="n"/>
+      <c r="J203" s="3" t="inlineStr">
+        <is>
+          <t>When a stimulus is linked to a specific action in an if-then plan including one or more of frequency, duration or intensity also code 'action planning BCT'</t>
+        </is>
+      </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -12235,7 +12221,7 @@
       <c r="Q203" s="3" t="n"/>
       <c r="R203" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S203" s="3" t="inlineStr">
@@ -12248,17 +12234,17 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007140</t>
+          <t>BCIO:007138</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>prompt self-talk BCT</t>
+          <t>prompt mental rehearsal of successful performance BCT</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A &lt;prompt thinking related to successful performance BCT&gt; that promotes the use of positive self-talk before or during the behaviour. </t>
+          <t>A &lt;prompt thinking related to successful performance BCT&gt; that prompts the person to practise imagining performing the behaviour well in a relevant context.</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
@@ -12270,16 +12256,12 @@
       <c r="F204" s="3" t="n"/>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>BCT15.4 Self-talk</t>
+          <t>BCT15.2 Mental rehearsal of successful performance</t>
         </is>
       </c>
       <c r="H204" s="3" t="n"/>
       <c r="I204" s="3" t="n"/>
-      <c r="J204" s="3" t="inlineStr">
-        <is>
-          <t>Self-talk could be about the behaviour or the context of the behaviour. Self-talk does not need to be spoken aloud</t>
-        </is>
-      </c>
+      <c r="J204" s="3" t="n"/>
       <c r="K204" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -12310,40 +12292,36 @@
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007073</t>
+          <t>BCIO:007140</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">prompt social comparison BCT </t>
+          <t>prompt self-talk BCT</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>An &lt;awareness of other people's thoughts, feelings and actions BCT&gt; that draws attention to other people's behaviour and compares it with the person's own behaviour.</t>
+          <t xml:space="preserve">A &lt;prompt thinking related to successful performance BCT&gt; that promotes the use of positive self-talk before or during the behaviour. </t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>awareness of other peoples thoughts, feelings and actions BCT</t>
+          <t>prompt thinking related to successful performance BCT</t>
         </is>
       </c>
       <c r="E205" s="3" t="n"/>
       <c r="F205" s="3" t="n"/>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>BCT6.2 Social comparison</t>
-        </is>
-      </c>
-      <c r="H205" s="3" t="inlineStr">
-        <is>
-          <t>social comparison</t>
-        </is>
-      </c>
+          <t>BCT15.4 Self-talk</t>
+        </is>
+      </c>
+      <c r="H205" s="3" t="n"/>
       <c r="I205" s="3" t="n"/>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Being in a group setting does not necessarily mean that social comparison is actually taking place </t>
+          <t>Self-talk could be about the behaviour or the context of the behaviour. Self-talk does not need to be spoken aloud</t>
         </is>
       </c>
       <c r="K205" s="3" t="inlineStr">
@@ -12363,7 +12341,7 @@
       <c r="Q205" s="3" t="n"/>
       <c r="R205" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S205" s="3" t="inlineStr">
@@ -12376,30 +12354,42 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007239</t>
+          <t>BCIO:007073</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>prompt thinking related to successful performance BCT</t>
+          <t xml:space="preserve">prompt social comparison BCT </t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>A &lt;behaviour change technique&gt; that prompts thinking relating to successful performance of the behaviour.</t>
+          <t>An &lt;awareness of other people's thoughts, feelings and actions BCT&gt; that draws attention to other people's behaviour and compares it with the person's own behaviour.</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>behaviour change technique</t>
+          <t>awareness of other peoples thoughts, feelings and actions BCT</t>
         </is>
       </c>
       <c r="E206" s="3" t="n"/>
       <c r="F206" s="3" t="n"/>
-      <c r="G206" s="3" t="n"/>
-      <c r="H206" s="3" t="n"/>
+      <c r="G206" s="3" t="inlineStr">
+        <is>
+          <t>BCT6.2 Social comparison</t>
+        </is>
+      </c>
+      <c r="H206" s="3" t="inlineStr">
+        <is>
+          <t>social comparison</t>
+        </is>
+      </c>
       <c r="I206" s="3" t="n"/>
-      <c r="J206" s="3" t="n"/>
+      <c r="J206" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Being in a group setting does not necessarily mean that social comparison is actually taking place </t>
+        </is>
+      </c>
       <c r="K206" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -12417,150 +12407,142 @@
       <c r="Q206" s="3" t="n"/>
       <c r="R206" s="3" t="inlineStr">
         <is>
+          <t>lz; LZ</t>
+        </is>
+      </c>
+      <c r="S206" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T206" s="3" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:007239</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>prompt thinking related to successful performance BCT</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>A &lt;behaviour change technique&gt; that prompts thinking relating to successful performance of the behaviour.</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="n"/>
+      <c r="F207" s="3" t="n"/>
+      <c r="G207" s="3" t="n"/>
+      <c r="H207" s="3" t="n"/>
+      <c r="I207" s="3" t="n"/>
+      <c r="J207" s="3" t="n"/>
+      <c r="K207" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="L207" s="3" t="n"/>
+      <c r="M207" s="3" t="n"/>
+      <c r="N207" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O207" s="3" t="n"/>
+      <c r="P207" s="3" t="n"/>
+      <c r="Q207" s="3" t="n"/>
+      <c r="R207" s="3" t="inlineStr">
+        <is>
           <t>LZ</t>
         </is>
       </c>
-      <c r="S206" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T206" s="3" t="n"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
+      <c r="S207" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T207" s="3" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
         <is>
           <t>BCIO:050993</t>
         </is>
       </c>
-      <c r="B207" s="2" t="inlineStr">
+      <c r="B208" s="2" t="inlineStr">
         <is>
           <t>protect time to perform behaviour BCT</t>
         </is>
       </c>
-      <c r="C207" s="2" t="inlineStr">
+      <c r="C208" s="2" t="inlineStr">
         <is>
           <t>A &lt;restructure the physical environment BCT&gt; that allocates a period of time to do the behaviour without competing with other behaviours.</t>
         </is>
       </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="D208" s="2" t="inlineStr">
         <is>
           <t>restructure the physical environment BCT</t>
         </is>
       </c>
-      <c r="E207" s="2" t="n"/>
-      <c r="F207" s="2" t="n"/>
-      <c r="G207" s="2" t="n"/>
-      <c r="H207" s="2" t="n"/>
-      <c r="I207" s="2" t="n"/>
-      <c r="J207" s="2" t="n"/>
-      <c r="K207" s="2" t="n"/>
-      <c r="L207" s="2" t="n"/>
-      <c r="M207" s="2" t="n"/>
-      <c r="N207" s="2" t="inlineStr">
+      <c r="E208" s="2" t="n"/>
+      <c r="F208" s="2" t="n"/>
+      <c r="G208" s="2" t="n"/>
+      <c r="H208" s="2" t="n"/>
+      <c r="I208" s="2" t="n"/>
+      <c r="J208" s="2" t="n"/>
+      <c r="K208" s="2" t="n"/>
+      <c r="L208" s="2" t="n"/>
+      <c r="M208" s="2" t="n"/>
+      <c r="N208" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="O207" s="2" t="n"/>
-      <c r="P207" s="2" t="n"/>
-      <c r="Q207" s="2" t="n"/>
-      <c r="R207" s="2" t="n"/>
-      <c r="S207" s="2" t="n">
+      <c r="O208" s="2" t="n"/>
+      <c r="P208" s="2" t="n"/>
+      <c r="Q208" s="2" t="n"/>
+      <c r="R208" s="2" t="n"/>
+      <c r="S208" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T207" s="2" t="n"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="3" t="inlineStr">
-        <is>
-          <t>BCIO:007241</t>
-        </is>
-      </c>
-      <c r="B208" s="3" t="inlineStr">
-        <is>
-          <t>provide aversive consequence for behaviour BCT</t>
-        </is>
-      </c>
-      <c r="C208" s="3" t="inlineStr">
-        <is>
-          <t>A &lt;provide consequence for behaviour BCT&gt; where the consequence is aversive.</t>
-        </is>
-      </c>
-      <c r="D208" s="3" t="inlineStr">
-        <is>
-          <t>provide consequence for behaviour BCT</t>
-        </is>
-      </c>
-      <c r="E208" s="3" t="n"/>
-      <c r="F208" s="3" t="n"/>
-      <c r="G208" s="3" t="inlineStr">
-        <is>
-          <t>BCT14.2 Punishment</t>
-        </is>
-      </c>
-      <c r="H208" s="3" t="inlineStr">
-        <is>
-          <t>punishment</t>
-        </is>
-      </c>
-      <c r="I208" s="3" t="n"/>
-      <c r="J208" s="3" t="inlineStr">
-        <is>
-          <t>To qualify as aversive, the consequence should be aversively valued by the person receiving it.</t>
-        </is>
-      </c>
-      <c r="K208" s="3" t="inlineStr">
-        <is>
-          <t>behaviour change technique</t>
-        </is>
-      </c>
-      <c r="L208" s="3" t="n"/>
-      <c r="M208" s="3" t="n"/>
-      <c r="N208" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="O208" s="3" t="n"/>
-      <c r="P208" s="3" t="n"/>
-      <c r="Q208" s="3" t="n"/>
-      <c r="R208" s="3" t="inlineStr">
-        <is>
-          <t>lz; LZ</t>
-        </is>
-      </c>
-      <c r="S208" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T208" s="3" t="n"/>
+      <c r="T208" s="2" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007246</t>
+          <t>BCIO:007241</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for outcome of behaviour BCT</t>
+          <t>provide aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide consequence for outcome of behaviour BCT&gt; where the consequence is aversive.</t>
+          <t>A &lt;provide consequence for behaviour BCT&gt; where the consequence is aversive.</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>provide consequence for outcome of behaviour BCT</t>
+          <t>provide consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E209" s="3" t="n"/>
       <c r="F209" s="3" t="n"/>
-      <c r="G209" s="3" t="n"/>
+      <c r="G209" s="3" t="inlineStr">
+        <is>
+          <t>BCT14.2 Punishment</t>
+        </is>
+      </c>
       <c r="H209" s="3" t="inlineStr">
         <is>
           <t>punishment</t>
@@ -12602,22 +12584,22 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007242</t>
+          <t>BCIO:007246</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for situation specific behaviour BCT</t>
+          <t>provide aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide aversive consequence for behaviour BCT&gt; that provides the consequence for the behaviour in one situation but not in another.</t>
+          <t>A &lt;provide consequence for outcome of behaviour BCT&gt; where the consequence is aversive.</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for behaviour BCT</t>
+          <t>provide consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E210" s="3" t="n"/>
@@ -12625,11 +12607,15 @@
       <c r="G210" s="3" t="n"/>
       <c r="H210" s="3" t="inlineStr">
         <is>
-          <t>punishment for situation specific behaviour</t>
+          <t>punishment</t>
         </is>
       </c>
       <c r="I210" s="3" t="n"/>
-      <c r="J210" s="3" t="n"/>
+      <c r="J210" s="3" t="inlineStr">
+        <is>
+          <t>To qualify as aversive, the consequence should be aversively valued by the person receiving it.</t>
+        </is>
+      </c>
       <c r="K210" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -12660,17 +12646,17 @@
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007243</t>
+          <t>BCIO:007242</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>provide aversive material consequence for behaviour BCT</t>
+          <t>provide aversive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide aversive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide aversive consequence for behaviour BCT&gt; that provides the consequence for the behaviour in one situation but not in another.</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
@@ -12683,7 +12669,7 @@
       <c r="G211" s="3" t="n"/>
       <c r="H211" s="3" t="inlineStr">
         <is>
-          <t>material punishment</t>
+          <t>punishment for situation specific behaviour</t>
         </is>
       </c>
       <c r="I211" s="3" t="n"/>
@@ -12718,22 +12704,22 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007245</t>
+          <t>BCIO:007243</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>provide aversive material consequence for outcome of behaviour BCT</t>
+          <t>provide aversive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide aversive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide aversive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for outcome of behaviour BCT</t>
+          <t>provide aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E212" s="3" t="n"/>
@@ -12776,22 +12762,22 @@
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007244</t>
+          <t>BCIO:007245</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>provide aversive material consequence for situation specific behaviour BCT</t>
+          <t>provide aversive material consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide aversive consequence for situation specific behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide aversive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for situation specific behaviour BCT</t>
+          <t>provide aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E213" s="3" t="n"/>
@@ -12799,7 +12785,7 @@
       <c r="G213" s="3" t="n"/>
       <c r="H213" s="3" t="inlineStr">
         <is>
-          <t>material punishment for situation specific behaviour</t>
+          <t>material punishment</t>
         </is>
       </c>
       <c r="I213" s="3" t="n"/>
@@ -12834,22 +12820,22 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007247</t>
+          <t>BCIO:007244</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>provide aversive social consequence for behaviour BCT</t>
+          <t>provide aversive material consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide aversive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide aversive consequence for situation specific behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for behaviour BCT</t>
+          <t>provide aversive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="E214" s="3" t="n"/>
@@ -12857,15 +12843,11 @@
       <c r="G214" s="3" t="n"/>
       <c r="H214" s="3" t="inlineStr">
         <is>
-          <t>social punishment</t>
+          <t>material punishment for situation specific behaviour</t>
         </is>
       </c>
       <c r="I214" s="3" t="n"/>
-      <c r="J214" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="J214" s="3" t="n"/>
       <c r="K214" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -12896,22 +12878,22 @@
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007249</t>
+          <t>BCIO:007247</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>provide aversive social consequence for outcome of behaviour BCT</t>
+          <t>provide aversive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide aversive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide aversive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for outcome of behaviour BCT</t>
+          <t>provide aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E215" s="3" t="n"/>
@@ -12958,22 +12940,22 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007248</t>
+          <t>BCIO:007249</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>provide aversive social consequence for situation specific behaviour BCT</t>
+          <t>provide aversive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide aversive consequence for situation specific behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide aversive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for situation specific behaviour BCT</t>
+          <t>provide aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E216" s="3" t="n"/>
@@ -12981,7 +12963,7 @@
       <c r="G216" s="3" t="n"/>
       <c r="H216" s="3" t="inlineStr">
         <is>
-          <t>social punishment for situation specific behaviour</t>
+          <t>social punishment</t>
         </is>
       </c>
       <c r="I216" s="3" t="n"/>
@@ -13020,42 +13002,38 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007026</t>
+          <t>BCIO:007248</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">provide biofeedback BCT </t>
+          <t>provide aversive social consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide feedback BCT&gt; that provides information about the functioning or state of the person's body, based on information collected by an external monitoring device.</t>
+          <t>A &lt;provide aversive consequence for situation specific behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>provide feedback BCT</t>
+          <t>provide aversive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="E217" s="3" t="n"/>
       <c r="F217" s="3" t="n"/>
-      <c r="G217" s="3" t="inlineStr">
-        <is>
-          <t>BCT2.6 Biofeedback</t>
-        </is>
-      </c>
+      <c r="G217" s="3" t="n"/>
       <c r="H217" s="3" t="inlineStr">
         <is>
-          <t>biofeedback</t>
-        </is>
-      </c>
-      <c r="I217" s="3" t="inlineStr">
-        <is>
-          <t>Using a pedometer to keep track of number of steps taken in a day.</t>
-        </is>
-      </c>
-      <c r="J217" s="3" t="n"/>
+          <t>social punishment for situation specific behaviour</t>
+        </is>
+      </c>
+      <c r="I217" s="3" t="n"/>
+      <c r="J217" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -13086,29 +13064,41 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007240</t>
+          <t>BCIO:007026</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>provide consequence for behaviour BCT</t>
+          <t xml:space="preserve">provide biofeedback BCT </t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>A &lt;behavioural consequence BCT&gt; that provides a consequence for the behaviour.</t>
+          <t>A &lt;provide feedback BCT&gt; that provides information about the functioning or state of the person's body, based on information collected by an external monitoring device.</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>behavioural consequence BCT</t>
+          <t>provide feedback BCT</t>
         </is>
       </c>
       <c r="E218" s="3" t="n"/>
       <c r="F218" s="3" t="n"/>
-      <c r="G218" s="3" t="n"/>
-      <c r="H218" s="3" t="n"/>
-      <c r="I218" s="3" t="n"/>
+      <c r="G218" s="3" t="inlineStr">
+        <is>
+          <t>BCT2.6 Biofeedback</t>
+        </is>
+      </c>
+      <c r="H218" s="3" t="inlineStr">
+        <is>
+          <t>biofeedback</t>
+        </is>
+      </c>
+      <c r="I218" s="3" t="inlineStr">
+        <is>
+          <t>Using a pedometer to keep track of number of steps taken in a day.</t>
+        </is>
+      </c>
       <c r="J218" s="3" t="n"/>
       <c r="K218" s="3" t="inlineStr">
         <is>
@@ -13127,7 +13117,7 @@
       <c r="Q218" s="3" t="n"/>
       <c r="R218" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S218" s="3" t="inlineStr">
@@ -13140,22 +13130,22 @@
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007250</t>
+          <t>BCIO:007240</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>provide consequence for outcome of behaviour BCT</t>
+          <t>provide consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>An &lt;outcome consequence BCT&gt; that provides a consequence for an outcome resulting from performing or not performing the behaviour.</t>
+          <t>A &lt;behavioural consequence BCT&gt; that provides a consequence for the behaviour.</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
-          <t>outcome consequence BCT</t>
+          <t>behavioural consequence BCT</t>
         </is>
       </c>
       <c r="E219" s="3" t="n"/>
@@ -13194,36 +13184,28 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007155</t>
+          <t>BCIO:007250</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">provide distraction BCT </t>
+          <t>provide consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>A &lt;restructure the physical environment BCT&gt; that organises an alternative focus for attention for the person to avoid internal or external states or events associated with an unwanted behaviour.</t>
+          <t>An &lt;outcome consequence BCT&gt; that provides a consequence for an outcome resulting from performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>restructure the physical environment BCT</t>
+          <t>outcome consequence BCT</t>
         </is>
       </c>
       <c r="E220" s="3" t="n"/>
       <c r="F220" s="3" t="n"/>
-      <c r="G220" s="3" t="inlineStr">
-        <is>
-          <t>BCT12.4 Distraction</t>
-        </is>
-      </c>
-      <c r="H220" s="3" t="inlineStr">
-        <is>
-          <t>attention shift</t>
-        </is>
-      </c>
+      <c r="G220" s="3" t="n"/>
+      <c r="H220" s="3" t="n"/>
       <c r="I220" s="3" t="n"/>
       <c r="J220" s="3" t="n"/>
       <c r="K220" s="3" t="inlineStr">
@@ -13243,7 +13225,7 @@
       <c r="Q220" s="3" t="n"/>
       <c r="R220" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S220" s="3" t="inlineStr">
@@ -13256,38 +13238,38 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007022</t>
+          <t>BCIO:007155</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>provide feedback BCT</t>
+          <t xml:space="preserve">provide distraction BCT </t>
         </is>
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>A &lt;monitoring BCT&gt; in which feedback about the behaviour is provided.</t>
+          <t>A &lt;restructure the physical environment BCT&gt; that organises an alternative focus for attention for the person to avoid internal or external states or events associated with an unwanted behaviour.</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>monitoring BCT</t>
+          <t>restructure the physical environment BCT</t>
         </is>
       </c>
       <c r="E221" s="3" t="n"/>
       <c r="F221" s="3" t="n"/>
-      <c r="G221" s="3" t="n"/>
+      <c r="G221" s="3" t="inlineStr">
+        <is>
+          <t>BCT12.4 Distraction</t>
+        </is>
+      </c>
       <c r="H221" s="3" t="inlineStr">
         <is>
-          <t>feedback, behavioural feedback</t>
+          <t>attention shift</t>
         </is>
       </c>
       <c r="I221" s="3" t="n"/>
-      <c r="J221" s="3" t="inlineStr">
-        <is>
-          <t>Feedback is provision of data about some aspect of behaviour without an evaluation (positive or negative). Where feedback includes reward or punishment, see behavioural consequence BCT, outcome consequence BCT and their child classes. If there is no clear evidence that feedback was given, code 'observe behaviour without feedback BCT' or 'record behaviour without feedback BCT'.</t>
-        </is>
-      </c>
+      <c r="J221" s="3" t="n"/>
       <c r="K221" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -13318,34 +13300,38 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007023</t>
+          <t>BCIO:007022</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">provide feedback on behaviour BCT </t>
+          <t>provide feedback BCT</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide feedback BCT&gt; that provides information about the person's previous performance of the behaviour.</t>
+          <t>A &lt;monitoring BCT&gt; in which feedback about the behaviour is provided.</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>provide feedback BCT</t>
+          <t>monitoring BCT</t>
         </is>
       </c>
       <c r="E222" s="3" t="n"/>
       <c r="F222" s="3" t="n"/>
-      <c r="G222" s="3" t="inlineStr">
-        <is>
-          <t>BCT2.2 Feedback on behaviour</t>
-        </is>
-      </c>
-      <c r="H222" s="3" t="n"/>
+      <c r="G222" s="3" t="n"/>
+      <c r="H222" s="3" t="inlineStr">
+        <is>
+          <t>feedback, behavioural feedback</t>
+        </is>
+      </c>
       <c r="I222" s="3" t="n"/>
-      <c r="J222" s="3" t="n"/>
+      <c r="J222" s="3" t="inlineStr">
+        <is>
+          <t>Feedback is provision of data about some aspect of behaviour without an evaluation (positive or negative). Where feedback includes reward or punishment, see behavioural consequence BCT, outcome consequence BCT and their child classes. If there is no clear evidence that feedback was given, code 'observe behaviour without feedback BCT' or 'record behaviour without feedback BCT'.</t>
+        </is>
+      </c>
       <c r="K222" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -13363,7 +13349,7 @@
       <c r="Q222" s="3" t="n"/>
       <c r="R222" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S222" s="3" t="inlineStr">
@@ -13376,17 +13362,17 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007027</t>
+          <t>BCIO:007023</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">provide feedback on outcome of behaviour BCT </t>
+          <t xml:space="preserve">provide feedback on behaviour BCT </t>
         </is>
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide feedback BCT&gt; that provides information about an outcome of the person's previous performance of the behaviour.</t>
+          <t>A &lt;provide feedback BCT&gt; that provides information about the person's previous performance of the behaviour.</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
@@ -13398,7 +13384,7 @@
       <c r="F223" s="3" t="n"/>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>BCT2.7 Feedback on outcome(s) of behaviour</t>
+          <t>BCT2.2 Feedback on behaviour</t>
         </is>
       </c>
       <c r="H223" s="3" t="n"/>
@@ -13434,29 +13420,29 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007145</t>
+          <t>BCIO:007027</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">provide pharmacological support BCT </t>
+          <t xml:space="preserve">provide feedback on outcome of behaviour BCT </t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promote pharmacological support BCT&gt; that provides the person with medicines or other drugs.</t>
+          <t>A &lt;provide feedback BCT&gt; that provides information about an outcome of the person's previous performance of the behaviour.</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
-          <t>promote pharmacological support BCT</t>
+          <t>provide feedback BCT</t>
         </is>
       </c>
       <c r="E224" s="3" t="n"/>
       <c r="F224" s="3" t="n"/>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>BCT11.1 Pharmacological support</t>
+          <t>BCT2.7 Feedback on outcome(s) of behaviour</t>
         </is>
       </c>
       <c r="H224" s="3" t="n"/>
@@ -13492,41 +13478,33 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007251</t>
+          <t>BCIO:007145</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for alternative behaviour BCT</t>
+          <t xml:space="preserve">provide pharmacological support BCT </t>
         </is>
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A &lt;provide positive consequence for behaviour BCT&gt; that provides the consequence for a behaviour that is different from the unwanted behaviour. </t>
+          <t>A &lt;promote pharmacological support BCT&gt; that provides the person with medicines or other drugs.</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for behaviour BCT</t>
+          <t>promote pharmacological support BCT</t>
         </is>
       </c>
       <c r="E225" s="3" t="n"/>
       <c r="F225" s="3" t="n"/>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>BCT14.8 Reward alternative behaviour</t>
-        </is>
-      </c>
-      <c r="H225" s="3" t="inlineStr">
-        <is>
-          <t>differential reinforcement, reward for alternative behaviour</t>
-        </is>
-      </c>
-      <c r="I225" s="3" t="inlineStr">
-        <is>
-          <t>Provide a reward for consuming low sugar food instead of high sugar food</t>
-        </is>
-      </c>
+          <t>BCT11.1 Pharmacological support</t>
+        </is>
+      </c>
+      <c r="H225" s="3" t="n"/>
+      <c r="I225" s="3" t="n"/>
       <c r="J225" s="3" t="n"/>
       <c r="K225" s="3" t="inlineStr">
         <is>
@@ -13545,7 +13523,7 @@
       <c r="Q225" s="3" t="n"/>
       <c r="R225" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S225" s="3" t="inlineStr">
@@ -13558,17 +13536,17 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007253</t>
+          <t>BCIO:007251</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for approximating behaviour BCT</t>
+          <t>provide positive consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for behaviour BCT&gt; where the consequence is provided as the performance gradually gets closer to the behaviour.</t>
+          <t xml:space="preserve">A &lt;provide positive consequence for behaviour BCT&gt; that provides the consequence for a behaviour that is different from the unwanted behaviour. </t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
@@ -13580,17 +13558,17 @@
       <c r="F226" s="3" t="n"/>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>BCT14.4 Reward approximation</t>
+          <t>BCT14.8 Reward alternative behaviour</t>
         </is>
       </c>
       <c r="H226" s="3" t="inlineStr">
         <is>
-          <t>shaping, reward for approximating behaviour</t>
+          <t>differential reinforcement, reward for alternative behaviour</t>
         </is>
       </c>
       <c r="I226" s="3" t="inlineStr">
         <is>
-          <t>Reward a person who has recently had a stroke who is learning to use cutlery again</t>
+          <t>Provide a reward for consuming low sugar food instead of high sugar food</t>
         </is>
       </c>
       <c r="J226" s="3" t="n"/>
@@ -13624,42 +13602,42 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007252</t>
+          <t>BCIO:007253</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
+          <t>provide positive consequence for approximating behaviour BCT</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>A &lt;provide positive consequence for behaviour BCT&gt; where the consequence is provided as the performance gradually gets closer to the behaviour.</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
           <t>provide positive consequence for behaviour BCT</t>
-        </is>
-      </c>
-      <c r="C227" s="3" t="inlineStr">
-        <is>
-          <t>A &lt;provide consequence for behaviour BCT&gt; where the consequence is positive.</t>
-        </is>
-      </c>
-      <c r="D227" s="3" t="inlineStr">
-        <is>
-          <t>provide consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E227" s="3" t="n"/>
       <c r="F227" s="3" t="n"/>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>BCT10.3 Non-specific reward; BCT10.9 Self-reward</t>
+          <t>BCT14.4 Reward approximation</t>
         </is>
       </c>
       <c r="H227" s="3" t="inlineStr">
         <is>
-          <t>positive reinforcement, reward</t>
-        </is>
-      </c>
-      <c r="I227" s="3" t="n"/>
-      <c r="J227" s="3" t="inlineStr">
-        <is>
-          <t>To qualify as positive, the consequence should be positively valued by the person receiving it. If informed of consequence in advance of rewarded behaviour, also code 'promise positive consequence for behaviour BCT' or one of its child classses.</t>
-        </is>
-      </c>
+          <t>shaping, reward for approximating behaviour</t>
+        </is>
+      </c>
+      <c r="I227" s="3" t="inlineStr">
+        <is>
+          <t>Reward a person who has recently had a stroke who is learning to use cutlery again</t>
+        </is>
+      </c>
+      <c r="J227" s="3" t="n"/>
       <c r="K227" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -13690,38 +13668,42 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007254</t>
+          <t>BCIO:007252</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for completion of behavioural sequence BCT</t>
+          <t>provide positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for behaviour BCT&gt; where the consequence is provided for performing the final behaviour in a sequence of behaviours, followed by adding behaviours that occur earlier in the sequence.</t>
+          <t>A &lt;provide consequence for behaviour BCT&gt; where the consequence is positive.</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for behaviour BCT</t>
+          <t>provide consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E228" s="3" t="n"/>
       <c r="F228" s="3" t="n"/>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>BCT14.5 Rewarding completion</t>
+          <t>BCT10.3 Non-specific reward; BCT10.9 Self-reward</t>
         </is>
       </c>
       <c r="H228" s="3" t="inlineStr">
         <is>
-          <t>backward chaining, reward for completion of behavoural sequence</t>
+          <t>positive reinforcement, reward</t>
         </is>
       </c>
       <c r="I228" s="3" t="n"/>
-      <c r="J228" s="3" t="n"/>
+      <c r="J228" s="3" t="inlineStr">
+        <is>
+          <t>To qualify as positive, the consequence should be positively valued by the person receiving it. If informed of consequence in advance of rewarded behaviour, also code 'promise positive consequence for behaviour BCT' or one of its child classses.</t>
+        </is>
+      </c>
       <c r="K228" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -13752,17 +13734,17 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007255</t>
+          <t>BCIO:007254</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for incompatible behaviour BCT</t>
+          <t>provide positive consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for behaviour BCT&gt; that provides the consequence for a behaviour that is incompatible with the unwanted behaviour.</t>
+          <t>A &lt;provide positive consequence for behaviour BCT&gt; where the consequence is provided for performing the final behaviour in a sequence of behaviours, followed by adding behaviours that occur earlier in the sequence.</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
@@ -13774,19 +13756,15 @@
       <c r="F229" s="3" t="n"/>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>BCT14.7 Reward incompatible behaviour</t>
+          <t>BCT14.5 Rewarding completion</t>
         </is>
       </c>
       <c r="H229" s="3" t="inlineStr">
         <is>
-          <t>counter-conditioning, reward for incompatible behaviour</t>
-        </is>
-      </c>
-      <c r="I229" s="3" t="inlineStr">
-        <is>
-          <t>Provide a reward when a person folds their arms or sits on their hands instead of touching their face.</t>
-        </is>
-      </c>
+          <t>backward chaining, reward for completion of behavoural sequence</t>
+        </is>
+      </c>
+      <c r="I229" s="3" t="n"/>
       <c r="J229" s="3" t="n"/>
       <c r="K229" s="3" t="inlineStr">
         <is>
@@ -13818,42 +13796,42 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007264</t>
+          <t>BCIO:007255</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for outcome of behaviour BCT</t>
+          <t>provide positive consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide consequence for outcome of behaviour BCT&gt; where the consequence is positive.</t>
+          <t>A &lt;provide positive consequence for behaviour BCT&gt; that provides the consequence for a behaviour that is incompatible with the unwanted behaviour.</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>provide consequence for outcome of behaviour BCT</t>
+          <t>provide positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E230" s="3" t="n"/>
       <c r="F230" s="3" t="n"/>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>BCT10.10 Reward (outcome)</t>
+          <t>BCT14.7 Reward incompatible behaviour</t>
         </is>
       </c>
       <c r="H230" s="3" t="inlineStr">
         <is>
-          <t>positive reinforcement, reward</t>
-        </is>
-      </c>
-      <c r="I230" s="3" t="n"/>
-      <c r="J230" s="3" t="inlineStr">
-        <is>
-          <t>To qualify as positive, the consequence should be positively valued by the person receiving it.</t>
-        </is>
-      </c>
+          <t>counter-conditioning, reward for incompatible behaviour</t>
+        </is>
+      </c>
+      <c r="I230" s="3" t="inlineStr">
+        <is>
+          <t>Provide a reward when a person folds their arms or sits on their hands instead of touching their face.</t>
+        </is>
+      </c>
+      <c r="J230" s="3" t="n"/>
       <c r="K230" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -13871,7 +13849,7 @@
       <c r="Q230" s="3" t="n"/>
       <c r="R230" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S230" s="3" t="inlineStr">
@@ -13884,38 +13862,42 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007256</t>
+          <t>BCIO:007264</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for situation specific behaviour BCT</t>
+          <t>provide positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for behaviour BCT&gt; that provides the consequence for the behaviour in one situation but not in another.</t>
+          <t>A &lt;provide consequence for outcome of behaviour BCT&gt; where the consequence is positive.</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for behaviour BCT</t>
+          <t>provide consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E231" s="3" t="n"/>
       <c r="F231" s="3" t="n"/>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>BCT14.6 Situation-specific reward</t>
+          <t>BCT10.10 Reward (outcome)</t>
         </is>
       </c>
       <c r="H231" s="3" t="inlineStr">
         <is>
-          <t>discrimination training, reward for situation specific behaviour</t>
+          <t>positive reinforcement, reward</t>
         </is>
       </c>
       <c r="I231" s="3" t="n"/>
-      <c r="J231" s="3" t="n"/>
+      <c r="J231" s="3" t="inlineStr">
+        <is>
+          <t>To qualify as positive, the consequence should be positively valued by the person receiving it.</t>
+        </is>
+      </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -13946,30 +13928,34 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007258</t>
+          <t>BCIO:007256</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>provide positive material consequence for alternative behaviour BCT</t>
+          <t>provide positive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for alternative behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide positive consequence for behaviour BCT&gt; that provides the consequence for the behaviour in one situation but not in another.</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for alternative behaviour BCT</t>
+          <t>provide positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E232" s="3" t="n"/>
       <c r="F232" s="3" t="n"/>
-      <c r="G232" s="3" t="n"/>
+      <c r="G232" s="3" t="inlineStr">
+        <is>
+          <t>BCT14.6 Situation-specific reward</t>
+        </is>
+      </c>
       <c r="H232" s="3" t="inlineStr">
         <is>
-          <t>material reward for alternative behaviour</t>
+          <t>discrimination training, reward for situation specific behaviour</t>
         </is>
       </c>
       <c r="I232" s="3" t="n"/>
@@ -14004,22 +13990,22 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007259</t>
+          <t>BCIO:007258</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>provide positive material consequence for approximating behaviour BCT</t>
+          <t>provide positive material consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for approximating behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide positive consequence for alternative behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for approximating behaviour BCT</t>
+          <t>provide positive consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="E233" s="3" t="n"/>
@@ -14027,7 +14013,7 @@
       <c r="G233" s="3" t="n"/>
       <c r="H233" s="3" t="inlineStr">
         <is>
-          <t>material reward for approximating behaviour</t>
+          <t>material reward for alternative behaviour</t>
         </is>
       </c>
       <c r="I233" s="3" t="n"/>
@@ -14062,34 +14048,30 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007257</t>
+          <t>BCIO:007259</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>provide positive material consequence for behaviour BCT</t>
+          <t>provide positive material consequence for approximating behaviour BCT</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide positive consequence for approximating behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for behaviour BCT</t>
+          <t>provide positive consequence for approximating behaviour BCT</t>
         </is>
       </c>
       <c r="E234" s="3" t="n"/>
       <c r="F234" s="3" t="n"/>
-      <c r="G234" s="3" t="inlineStr">
-        <is>
-          <t>BCT10.2 Material reward (behaviour)</t>
-        </is>
-      </c>
+      <c r="G234" s="3" t="n"/>
       <c r="H234" s="3" t="inlineStr">
         <is>
-          <t>material reward, tangible reinforcement</t>
+          <t>material reward for approximating behaviour</t>
         </is>
       </c>
       <c r="I234" s="3" t="n"/>
@@ -14111,7 +14093,7 @@
       <c r="Q234" s="3" t="n"/>
       <c r="R234" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S234" s="3" t="inlineStr">
@@ -14124,30 +14106,34 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007260</t>
+          <t>BCIO:007257</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>provide positive material consequence for completion of behavioural sequence BCT</t>
+          <t>provide positive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for completion of behavioural sequence BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide positive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for completion of behavioural sequence BCT</t>
+          <t>provide positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E235" s="3" t="n"/>
       <c r="F235" s="3" t="n"/>
-      <c r="G235" s="3" t="n"/>
+      <c r="G235" s="3" t="inlineStr">
+        <is>
+          <t>BCT10.2 Material reward (behaviour)</t>
+        </is>
+      </c>
       <c r="H235" s="3" t="inlineStr">
         <is>
-          <t>material reward for completion of behavoural sequence</t>
+          <t>material reward, tangible reinforcement</t>
         </is>
       </c>
       <c r="I235" s="3" t="n"/>
@@ -14169,7 +14155,7 @@
       <c r="Q235" s="3" t="n"/>
       <c r="R235" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S235" s="3" t="inlineStr">
@@ -14182,22 +14168,22 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007261</t>
+          <t>BCIO:007260</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>provide positive material consequence for incompatible behaviour BCT</t>
+          <t>provide positive material consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for incompatible behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide positive consequence for completion of behavioural sequence BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for incompatible behaviour BCT</t>
+          <t>provide positive consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="E236" s="3" t="n"/>
@@ -14205,7 +14191,7 @@
       <c r="G236" s="3" t="n"/>
       <c r="H236" s="3" t="inlineStr">
         <is>
-          <t>material reward for incompatible behaviour</t>
+          <t>material reward for completion of behavoural sequence</t>
         </is>
       </c>
       <c r="I236" s="3" t="n"/>
@@ -14240,22 +14226,22 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007263</t>
+          <t>BCIO:007261</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>provide positive material consequence for outcome of behaviour BCT</t>
+          <t>provide positive material consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide positive consequence for incompatible behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for outcome of behaviour BCT</t>
+          <t>provide positive consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="E237" s="3" t="n"/>
@@ -14263,7 +14249,7 @@
       <c r="G237" s="3" t="n"/>
       <c r="H237" s="3" t="inlineStr">
         <is>
-          <t>material reward, tangible reinforcement</t>
+          <t>material reward for incompatible behaviour</t>
         </is>
       </c>
       <c r="I237" s="3" t="n"/>
@@ -14285,7 +14271,7 @@
       <c r="Q237" s="3" t="n"/>
       <c r="R237" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S237" s="3" t="inlineStr">
@@ -14298,22 +14284,22 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007262</t>
+          <t>BCIO:007263</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>provide positive material consequence for situation specific behaviour BCT</t>
+          <t>provide positive material consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for situation specific behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide positive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for situation specific behaviour BCT</t>
+          <t>provide positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E238" s="3" t="n"/>
@@ -14321,7 +14307,7 @@
       <c r="G238" s="3" t="n"/>
       <c r="H238" s="3" t="inlineStr">
         <is>
-          <t>material reward for situation specific behaviour</t>
+          <t>material reward, tangible reinforcement</t>
         </is>
       </c>
       <c r="I238" s="3" t="n"/>
@@ -14343,7 +14329,7 @@
       <c r="Q238" s="3" t="n"/>
       <c r="R238" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S238" s="3" t="inlineStr">
@@ -14356,22 +14342,22 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007266</t>
+          <t>BCIO:007262</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>provide positive social consequence for alternative behaviour BCT</t>
+          <t>provide positive material consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for alternative behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide positive consequence for situation specific behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for alternative behaviour BCT</t>
+          <t>provide positive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="E239" s="3" t="n"/>
@@ -14379,15 +14365,11 @@
       <c r="G239" s="3" t="n"/>
       <c r="H239" s="3" t="inlineStr">
         <is>
-          <t>social reward for alternative behaviour</t>
+          <t>material reward for situation specific behaviour</t>
         </is>
       </c>
       <c r="I239" s="3" t="n"/>
-      <c r="J239" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="J239" s="3" t="n"/>
       <c r="K239" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -14418,22 +14400,22 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007267</t>
+          <t>BCIO:007266</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>provide positive social consequence for approximating behaviour BCT</t>
+          <t>provide positive social consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for approximating behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide positive consequence for alternative behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for approximating behaviour BCT</t>
+          <t>provide positive consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="E240" s="3" t="n"/>
@@ -14441,7 +14423,7 @@
       <c r="G240" s="3" t="n"/>
       <c r="H240" s="3" t="inlineStr">
         <is>
-          <t>social reward for approximating behaviour</t>
+          <t>social reward for alternative behaviour</t>
         </is>
       </c>
       <c r="I240" s="3" t="n"/>
@@ -14480,34 +14462,30 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007265</t>
+          <t>BCIO:007267</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>provide positive social consequence for behaviour BCT</t>
+          <t>provide positive social consequence for approximating behaviour BCT</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide positive consequence for approximating behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for behaviour BCT</t>
+          <t>provide positive consequence for approximating behaviour BCT</t>
         </is>
       </c>
       <c r="E241" s="3" t="n"/>
       <c r="F241" s="3" t="n"/>
-      <c r="G241" s="3" t="inlineStr">
-        <is>
-          <t>BCT10.4 Social reward</t>
-        </is>
-      </c>
+      <c r="G241" s="3" t="n"/>
       <c r="H241" s="3" t="inlineStr">
         <is>
-          <t>social reward</t>
+          <t>social reward for approximating behaviour</t>
         </is>
       </c>
       <c r="I241" s="3" t="n"/>
@@ -14533,7 +14511,7 @@
       <c r="Q241" s="3" t="n"/>
       <c r="R241" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S241" s="3" t="inlineStr">
@@ -14546,30 +14524,34 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007268</t>
+          <t>BCIO:007265</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>provide positive social consequence for completion of behavioural sequence BCT</t>
+          <t>provide positive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for completion of behavioural sequence BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide positive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for completion of behavioural sequence BCT</t>
+          <t>provide positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E242" s="3" t="n"/>
       <c r="F242" s="3" t="n"/>
-      <c r="G242" s="3" t="n"/>
+      <c r="G242" s="3" t="inlineStr">
+        <is>
+          <t>BCT10.4 Social reward</t>
+        </is>
+      </c>
       <c r="H242" s="3" t="inlineStr">
         <is>
-          <t>social reward for completion of behavoural sequence</t>
+          <t>social reward</t>
         </is>
       </c>
       <c r="I242" s="3" t="n"/>
@@ -14595,7 +14577,7 @@
       <c r="Q242" s="3" t="n"/>
       <c r="R242" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S242" s="3" t="inlineStr">
@@ -14608,22 +14590,22 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007269</t>
+          <t>BCIO:007268</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>provide positive social consequence for incompatible behaviour BCT</t>
+          <t>provide positive social consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for incompatible behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide positive consequence for completion of behavioural sequence BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for incompatible behaviour BCT</t>
+          <t>provide positive consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="E243" s="3" t="n"/>
@@ -14631,7 +14613,7 @@
       <c r="G243" s="3" t="n"/>
       <c r="H243" s="3" t="inlineStr">
         <is>
-          <t>social reward for incompatible behaviour</t>
+          <t>social reward for completion of behavoural sequence</t>
         </is>
       </c>
       <c r="I243" s="3" t="n"/>
@@ -14670,22 +14652,22 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007271</t>
+          <t>BCIO:007269</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>provide positive social consequence for outcome of behaviour BCT</t>
+          <t>provide positive social consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide positive consequence for incompatible behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for outcome of behaviour BCT</t>
+          <t>provide positive consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="E244" s="3" t="n"/>
@@ -14693,7 +14675,7 @@
       <c r="G244" s="3" t="n"/>
       <c r="H244" s="3" t="inlineStr">
         <is>
-          <t>social reward</t>
+          <t>social reward for incompatible behaviour</t>
         </is>
       </c>
       <c r="I244" s="3" t="n"/>
@@ -14732,22 +14714,22 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007270</t>
+          <t>BCIO:007271</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>provide positive social consequence for situation specific behaviour BCT</t>
+          <t>provide positive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for  situation specific behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide positive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for situation specific behaviour BCT</t>
+          <t>provide positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E245" s="3" t="n"/>
@@ -14755,7 +14737,7 @@
       <c r="G245" s="3" t="n"/>
       <c r="H245" s="3" t="inlineStr">
         <is>
-          <t>social reward for situation specific behaviour</t>
+          <t>social reward</t>
         </is>
       </c>
       <c r="I245" s="3" t="n"/>
@@ -14794,22 +14776,22 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007273</t>
+          <t>BCIO:007270</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive consequence for behaviour BCT</t>
+          <t>provide positive social consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide aversive consequence for behaviour BCT&gt; that provides the consequence at increasingly less frequent intervals.</t>
+          <t>A &lt;provide positive consequence for  situation specific behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for behaviour BCT</t>
+          <t>provide positive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="E246" s="3" t="n"/>
@@ -14817,11 +14799,15 @@
       <c r="G246" s="3" t="n"/>
       <c r="H246" s="3" t="inlineStr">
         <is>
-          <t>reduce punishment frequency</t>
+          <t>social reward for situation specific behaviour</t>
         </is>
       </c>
       <c r="I246" s="3" t="n"/>
-      <c r="J246" s="3" t="n"/>
+      <c r="J246" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="K246" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -14839,7 +14825,7 @@
       <c r="Q246" s="3" t="n"/>
       <c r="R246" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S246" s="3" t="inlineStr">
@@ -14852,22 +14838,22 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007276</t>
+          <t>BCIO:007273</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide aversive consequence for outcome of behaviour BCT&gt; that provides the consequence at increasingly less frequent intervals.</t>
+          <t>A &lt;provide aversive consequence for behaviour BCT&gt; that provides the consequence at increasingly less frequent intervals.</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for outcome of behaviour BCT</t>
+          <t>provide aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E247" s="3" t="n"/>
@@ -14910,22 +14896,22 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007274</t>
+          <t>BCIO:007276</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive material consequence for behaviour BCT</t>
+          <t>provide reduced frequency of aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide reduced frequency of aversive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide aversive consequence for outcome of behaviour BCT&gt; that provides the consequence at increasingly less frequent intervals.</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive consequence for behaviour BCT</t>
+          <t>provide aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E248" s="3" t="n"/>
@@ -14933,7 +14919,7 @@
       <c r="G248" s="3" t="n"/>
       <c r="H248" s="3" t="inlineStr">
         <is>
-          <t>reduce material punishment frequency</t>
+          <t>reduce punishment frequency</t>
         </is>
       </c>
       <c r="I248" s="3" t="n"/>
@@ -14968,22 +14954,22 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007275</t>
+          <t>BCIO:007274</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive material consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of aversive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide reduced frequency of aversive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide reduced frequency of aversive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E249" s="3" t="n"/>
@@ -15026,22 +15012,22 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007277</t>
+          <t>BCIO:007275</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive social consequence for behaviour BCT</t>
+          <t>provide reduced frequency of aversive material consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide reduced frequency of aversive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide reduced frequency of aversive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive consequence for behaviour BCT</t>
+          <t>provide reduced frequency of aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E250" s="3" t="n"/>
@@ -15049,15 +15035,11 @@
       <c r="G250" s="3" t="n"/>
       <c r="H250" s="3" t="inlineStr">
         <is>
-          <t>reduce social punishment frequency</t>
+          <t>reduce material punishment frequency</t>
         </is>
       </c>
       <c r="I250" s="3" t="n"/>
-      <c r="J250" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="J250" s="3" t="n"/>
       <c r="K250" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -15088,22 +15070,22 @@
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007278</t>
+          <t>BCIO:007277</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive social consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of aversive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide reduced frequency of aversive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide reduced frequency of aversive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E251" s="3" t="n"/>
@@ -15150,38 +15132,38 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007279</t>
+          <t>BCIO:007278</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive consequence for behaviour BCT</t>
+          <t>provide reduced frequency of aversive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for behaviour BCT&gt; that provides the consequence at increasingly less frequent intervals.</t>
+          <t>A &lt;provide reduced frequency of aversive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for behaviour BCT</t>
+          <t>provide reduced frequency of aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E252" s="3" t="n"/>
       <c r="F252" s="3" t="n"/>
-      <c r="G252" s="3" t="inlineStr">
-        <is>
-          <t>BCT14.9 Reduce reward frequency</t>
-        </is>
-      </c>
+      <c r="G252" s="3" t="n"/>
       <c r="H252" s="3" t="inlineStr">
         <is>
-          <t>thinning, reduce reward frequency</t>
+          <t>reduce social punishment frequency</t>
         </is>
       </c>
       <c r="I252" s="3" t="n"/>
-      <c r="J252" s="3" t="n"/>
+      <c r="J252" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="K252" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -15199,7 +15181,7 @@
       <c r="Q252" s="3" t="n"/>
       <c r="R252" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S252" s="3" t="inlineStr">
@@ -15212,27 +15194,31 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007281</t>
+          <t>BCIO:007279</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for outcome of behaviour BCT&gt; that provides the consequence at increasingly less frequent intervals.</t>
+          <t>A &lt;provide positive consequence for behaviour BCT&gt; that provides the consequence at increasingly less frequent intervals.</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for outcome of behaviour BCT</t>
+          <t>provide positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E253" s="3" t="n"/>
       <c r="F253" s="3" t="n"/>
-      <c r="G253" s="3" t="n"/>
+      <c r="G253" s="3" t="inlineStr">
+        <is>
+          <t>BCT14.9 Reduce reward frequency</t>
+        </is>
+      </c>
       <c r="H253" s="3" t="inlineStr">
         <is>
           <t>thinning, reduce reward frequency</t>
@@ -15270,22 +15256,22 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007280</t>
+          <t>BCIO:007281</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive material consequence for behaviour BCT</t>
+          <t>provide reduced frequency of positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide reduced frequency of positive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide positive consequence for outcome of behaviour BCT&gt; that provides the consequence at increasingly less frequent intervals.</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive consequence for behaviour BCT</t>
+          <t>provide positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E254" s="3" t="n"/>
@@ -15293,7 +15279,7 @@
       <c r="G254" s="3" t="n"/>
       <c r="H254" s="3" t="inlineStr">
         <is>
-          <t>reduce material reward frequency</t>
+          <t>thinning, reduce reward frequency</t>
         </is>
       </c>
       <c r="I254" s="3" t="n"/>
@@ -15328,22 +15314,22 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007272</t>
+          <t>BCIO:007280</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive material consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of positive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide reduced frequency of positive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide reduced frequency of positive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E255" s="3" t="n"/>
@@ -15386,22 +15372,22 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007282</t>
+          <t>BCIO:007272</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive social consequence for behaviour BCT</t>
+          <t>provide reduced frequency of positive material consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide reduced frequency of positive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide reduced frequency of positive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive consequence for behaviour BCT</t>
+          <t>provide reduced frequency of positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E256" s="3" t="n"/>
@@ -15409,15 +15395,11 @@
       <c r="G256" s="3" t="n"/>
       <c r="H256" s="3" t="inlineStr">
         <is>
-          <t>reduce social reward frequency</t>
+          <t>reduce material reward frequency</t>
         </is>
       </c>
       <c r="I256" s="3" t="n"/>
-      <c r="J256" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="J256" s="3" t="n"/>
       <c r="K256" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -15448,22 +15430,22 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007283</t>
+          <t>BCIO:007282</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive social consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of positive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide reduced frequency of positive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide reduced frequency of positive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E257" s="3" t="n"/>
@@ -15510,38 +15492,38 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007053</t>
+          <t>BCIO:007283</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">re-attribute cause BCT </t>
+          <t>provide reduced frequency of positive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>A &lt;suggest different perspective on behaviour BCT&gt; that involves eliciting the person's beliefs about, and suggesting alternative beliefs about, the causes of the behaviour.</t>
+          <t>A &lt;provide reduced frequency of positive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>suggest different perspective on behaviour BCT</t>
+          <t>provide reduced frequency of positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E258" s="3" t="n"/>
       <c r="F258" s="3" t="n"/>
-      <c r="G258" s="3" t="inlineStr">
-        <is>
-          <t>BCT4.3 Re-attribution</t>
-        </is>
-      </c>
+      <c r="G258" s="3" t="n"/>
       <c r="H258" s="3" t="inlineStr">
         <is>
-          <t>re-attribution</t>
+          <t>reduce social reward frequency</t>
         </is>
       </c>
       <c r="I258" s="3" t="n"/>
-      <c r="J258" s="3" t="n"/>
+      <c r="J258" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="K258" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -15559,7 +15541,7 @@
       <c r="Q258" s="3" t="n"/>
       <c r="R258" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S258" s="3" t="inlineStr">
@@ -15572,42 +15554,38 @@
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007019</t>
+          <t>BCIO:007053</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">record behaviour without feedback BCT </t>
+          <t xml:space="preserve">re-attribute cause BCT </t>
         </is>
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>A &lt;monitoring BCT&gt; that records current performance of the behaviour with the person’s knowledge but without providing feedback about their behaviour.</t>
+          <t>A &lt;suggest different perspective on behaviour BCT&gt; that involves eliciting the person's beliefs about, and suggesting alternative beliefs about, the causes of the behaviour.</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
         <is>
-          <t>monitoring BCT</t>
+          <t>suggest different perspective on behaviour BCT</t>
         </is>
       </c>
       <c r="E259" s="3" t="n"/>
       <c r="F259" s="3" t="n"/>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>BCT2.1 Monitoring of behaviour by others without feedback</t>
+          <t>BCT4.3 Re-attribution</t>
         </is>
       </c>
       <c r="H259" s="3" t="inlineStr">
         <is>
-          <t>monitoring</t>
+          <t>re-attribution</t>
         </is>
       </c>
       <c r="I259" s="3" t="n"/>
-      <c r="J259" s="3" t="inlineStr">
-        <is>
-          <t>The monitoring agent can be a human or a technical device. If recording is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if feedback given, code only 'provide feedback on behaviour BCT' and not this class; if recording outcomes code 'record outcome of behaviour without feedback BCT'.</t>
-        </is>
-      </c>
+      <c r="J259" s="3" t="n"/>
       <c r="K259" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -15638,17 +15616,17 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007021</t>
+          <t>BCIO:007019</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">record outcome of behaviour without feedback BCT </t>
+          <t xml:space="preserve">record behaviour without feedback BCT </t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>A &lt;monitoring BCT&gt; that records an outcome of performing the behaviour with the person's knowledge but without providing feedback about the outcome.</t>
+          <t>A &lt;monitoring BCT&gt; that records current performance of the behaviour with the person’s knowledge but without providing feedback about their behaviour.</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
@@ -15660,14 +15638,18 @@
       <c r="F260" s="3" t="n"/>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>BCT2.5 Monitoring outcome(s) of behaviour by others without feedback</t>
-        </is>
-      </c>
-      <c r="H260" s="3" t="n"/>
+          <t>BCT2.1 Monitoring of behaviour by others without feedback</t>
+        </is>
+      </c>
+      <c r="H260" s="3" t="inlineStr">
+        <is>
+          <t>monitoring</t>
+        </is>
+      </c>
       <c r="I260" s="3" t="n"/>
       <c r="J260" s="3" t="inlineStr">
         <is>
-          <t>The monitoring agent can be a human or a technical device. If recording is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if feedback given, code only 'provide feedback on outcome of behaviour BCT' and not this class; if recording behaviour code 'record behaviour without feedback BCT'.</t>
+          <t>The monitoring agent can be a human or a technical device. If recording is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if feedback given, code only 'provide feedback on behaviour BCT' and not this class; if recording outcomes code 'record outcome of behaviour without feedback BCT'.</t>
         </is>
       </c>
       <c r="K260" s="3" t="inlineStr">
@@ -15700,40 +15682,36 @@
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007084</t>
+          <t>BCIO:007021</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>reduce cue frequency BCTs</t>
+          <t xml:space="preserve">record outcome of behaviour without feedback BCT </t>
         </is>
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>An &lt;alter external stimulus BCT&gt; in which cues for the behaviour are presented less frequently.</t>
+          <t>A &lt;monitoring BCT&gt; that records an outcome of performing the behaviour with the person's knowledge but without providing feedback about the outcome.</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
-          <t>alter external stimulus BCT</t>
+          <t>monitoring BCT</t>
         </is>
       </c>
       <c r="E261" s="3" t="n"/>
       <c r="F261" s="3" t="n"/>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>BCT7.3 Reduce prompts/cues</t>
-        </is>
-      </c>
-      <c r="H261" s="3" t="inlineStr">
-        <is>
-          <t>fading</t>
-        </is>
-      </c>
+          <t>BCT2.5 Monitoring outcome(s) of behaviour by others without feedback</t>
+        </is>
+      </c>
+      <c r="H261" s="3" t="n"/>
       <c r="I261" s="3" t="n"/>
       <c r="J261" s="3" t="inlineStr">
         <is>
-          <t>The reduction in frequency of cue presentation can be gradual or rapid. This BCT is concerned with reducing the frequency of cue presentation. In contrast, in "reduce exposure to cues for the behaviour BCT", the cue frequency may remain unchanged but the person's exposure to the presentation of the cue is reduced.</t>
+          <t>The monitoring agent can be a human or a technical device. If recording is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if feedback given, code only 'provide feedback on outcome of behaviour BCT' and not this class; if recording behaviour code 'record behaviour without feedback BCT'.</t>
         </is>
       </c>
       <c r="K261" s="3" t="inlineStr">
@@ -15753,7 +15731,7 @@
       <c r="Q261" s="3" t="n"/>
       <c r="R261" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S261" s="3" t="inlineStr">
@@ -15766,32 +15744,40 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007284</t>
+          <t>BCIO:007084</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>reduce distraction BCT</t>
+          <t>reduce cue frequency BCTs</t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>A &lt;restructure the physical environment BCT&gt; that reduces an alternative focus for attention for the person to concentrate on internal or external states or events associated with the behaviour.</t>
+          <t>An &lt;alter external stimulus BCT&gt; in which cues for the behaviour are presented less frequently.</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>restructure the physical environment BCT</t>
+          <t>alter external stimulus BCT</t>
         </is>
       </c>
       <c r="E262" s="3" t="n"/>
       <c r="F262" s="3" t="n"/>
-      <c r="G262" s="3" t="n"/>
-      <c r="H262" s="3" t="n"/>
+      <c r="G262" s="3" t="inlineStr">
+        <is>
+          <t>BCT7.3 Reduce prompts/cues</t>
+        </is>
+      </c>
+      <c r="H262" s="3" t="inlineStr">
+        <is>
+          <t>fading</t>
+        </is>
+      </c>
       <c r="I262" s="3" t="n"/>
       <c r="J262" s="3" t="inlineStr">
         <is>
-          <t>Reducing a distraction to zero is equivalent to removing a distraction</t>
+          <t>The reduction in frequency of cue presentation can be gradual or rapid. This BCT is concerned with reducing the frequency of cue presentation. In contrast, in "reduce exposure to cues for the behaviour BCT", the cue frequency may remain unchanged but the person's exposure to the presentation of the cue is reduced.</t>
         </is>
       </c>
       <c r="K262" s="3" t="inlineStr">
@@ -15824,36 +15810,32 @@
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007153</t>
+          <t>BCIO:007284</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">reduce exposure to cues for the behaviour BCT </t>
+          <t>reduce distraction BCT</t>
         </is>
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">An &lt;alter external stimulus BCT&gt; that reduces an external stimulus that signals the behaviour. </t>
+          <t>A &lt;restructure the physical environment BCT&gt; that reduces an alternative focus for attention for the person to concentrate on internal or external states or events associated with the behaviour.</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
         <is>
-          <t>alter external stimulus BCT</t>
+          <t>restructure the physical environment BCT</t>
         </is>
       </c>
       <c r="E263" s="3" t="n"/>
       <c r="F263" s="3" t="n"/>
-      <c r="G263" s="3" t="inlineStr">
-        <is>
-          <t>BCT12.3 Avoidance/reducing exposure to cues for the behaviour</t>
-        </is>
-      </c>
+      <c r="G263" s="3" t="n"/>
       <c r="H263" s="3" t="n"/>
       <c r="I263" s="3" t="n"/>
       <c r="J263" s="3" t="inlineStr">
         <is>
-          <t>The reduction in exposure can be gradual, as in the technique of "fading" or not so gradual. This BCT is concerned with reducing the person's exposure to the cue, while the cue frequency may remain unchanged. In contrast, "reduce cue frequency BCT" is concerned with a reduction in the number of times with which the cue is presented. This BCT may also involve 'restructure the physical environment BCT' and/or 'restructure the social environment BCT'.</t>
+          <t>Reducing a distraction to zero is equivalent to removing a distraction</t>
         </is>
       </c>
       <c r="K263" s="3" t="inlineStr">
@@ -15873,147 +15855,155 @@
       <c r="Q263" s="3" t="n"/>
       <c r="R263" s="3" t="inlineStr">
         <is>
+          <t>LZ</t>
+        </is>
+      </c>
+      <c r="S263" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T263" s="3" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:007153</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reduce exposure to cues for the behaviour BCT </t>
+        </is>
+      </c>
+      <c r="C264" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An &lt;alter external stimulus BCT&gt; that reduces an external stimulus that signals the behaviour. </t>
+        </is>
+      </c>
+      <c r="D264" s="3" t="inlineStr">
+        <is>
+          <t>alter external stimulus BCT</t>
+        </is>
+      </c>
+      <c r="E264" s="3" t="n"/>
+      <c r="F264" s="3" t="n"/>
+      <c r="G264" s="3" t="inlineStr">
+        <is>
+          <t>BCT12.3 Avoidance/reducing exposure to cues for the behaviour</t>
+        </is>
+      </c>
+      <c r="H264" s="3" t="n"/>
+      <c r="I264" s="3" t="n"/>
+      <c r="J264" s="3" t="inlineStr">
+        <is>
+          <t>The reduction in exposure can be gradual, as in the technique of "fading" or not so gradual. This BCT is concerned with reducing the person's exposure to the cue, while the cue frequency may remain unchanged. In contrast, "reduce cue frequency BCT" is concerned with a reduction in the number of times with which the cue is presented. This BCT may also involve 'restructure the physical environment BCT' and/or 'restructure the social environment BCT'.</t>
+        </is>
+      </c>
+      <c r="K264" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="L264" s="3" t="n"/>
+      <c r="M264" s="3" t="n"/>
+      <c r="N264" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O264" s="3" t="n"/>
+      <c r="P264" s="3" t="n"/>
+      <c r="Q264" s="3" t="n"/>
+      <c r="R264" s="3" t="inlineStr">
+        <is>
           <t>lz; LZ</t>
         </is>
       </c>
-      <c r="S263" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T263" s="3" t="n"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="2" t="inlineStr">
+      <c r="S264" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T264" s="3" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
         <is>
           <t>BCIO:050994</t>
         </is>
       </c>
-      <c r="B264" s="2" t="inlineStr">
+      <c r="B265" s="2" t="inlineStr">
         <is>
           <t>reduce time needed to perform behaviour BCT</t>
         </is>
       </c>
-      <c r="C264" s="2" t="inlineStr">
+      <c r="C265" s="2" t="inlineStr">
         <is>
           <t>A &lt;restructure the physical environment BCT&gt; that reduces the amount of time required for the behaviour to be undertaken.</t>
         </is>
       </c>
-      <c r="D264" s="2" t="inlineStr">
+      <c r="D265" s="2" t="inlineStr">
         <is>
           <t>restructure the physical environment BCT</t>
         </is>
       </c>
-      <c r="E264" s="2" t="n"/>
-      <c r="F264" s="2" t="n"/>
-      <c r="G264" s="2" t="n"/>
-      <c r="H264" s="2" t="n"/>
-      <c r="I264" s="2" t="n"/>
-      <c r="J264" s="2" t="n"/>
-      <c r="K264" s="2" t="n"/>
-      <c r="L264" s="2" t="n"/>
-      <c r="M264" s="2" t="n"/>
-      <c r="N264" s="2" t="inlineStr">
+      <c r="E265" s="2" t="n"/>
+      <c r="F265" s="2" t="n"/>
+      <c r="G265" s="2" t="n"/>
+      <c r="H265" s="2" t="n"/>
+      <c r="I265" s="2" t="n"/>
+      <c r="J265" s="2" t="n"/>
+      <c r="K265" s="2" t="n"/>
+      <c r="L265" s="2" t="n"/>
+      <c r="M265" s="2" t="n"/>
+      <c r="N265" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="O264" s="2" t="n"/>
-      <c r="P264" s="2" t="n"/>
-      <c r="Q264" s="2" t="n"/>
-      <c r="R264" s="2" t="n"/>
-      <c r="S264" s="2" t="n">
+      <c r="O265" s="2" t="n"/>
+      <c r="P265" s="2" t="n"/>
+      <c r="Q265" s="2" t="n"/>
+      <c r="R265" s="2" t="n"/>
+      <c r="S265" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T264" s="2" t="n"/>
-    </row>
-    <row r="265">
-      <c r="A265" s="3" t="inlineStr">
-        <is>
-          <t>BCIO:007056</t>
-        </is>
-      </c>
-      <c r="B265" s="3" t="inlineStr">
-        <is>
-          <t>reframe past behaviour BCT</t>
-        </is>
-      </c>
-      <c r="C265" s="3" t="inlineStr">
-        <is>
-          <t>A &lt;suggest different perspective on behaviour BCT&gt; that involves reattributing a person's successes to internal, stable or global factors or failures to external, unstable or specific factors.</t>
-        </is>
-      </c>
-      <c r="D265" s="3" t="inlineStr">
-        <is>
-          <t>suggest different perspective on behaviour BCT</t>
-        </is>
-      </c>
-      <c r="E265" s="3" t="n"/>
-      <c r="F265" s="3" t="n"/>
-      <c r="G265" s="3" t="inlineStr">
-        <is>
-          <t>BCT13.2 Framing/reframing</t>
-        </is>
-      </c>
-      <c r="H265" s="3" t="inlineStr">
-        <is>
-          <t>cognitive re-structuring, re-attribution</t>
-        </is>
-      </c>
-      <c r="I265" s="3" t="n"/>
-      <c r="J265" s="3" t="n"/>
-      <c r="K265" s="3" t="inlineStr">
-        <is>
-          <t>behaviour change technique</t>
-        </is>
-      </c>
-      <c r="L265" s="3" t="n"/>
-      <c r="M265" s="3" t="n"/>
-      <c r="N265" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="O265" s="3" t="n"/>
-      <c r="P265" s="3" t="n"/>
-      <c r="Q265" s="3" t="n"/>
-      <c r="R265" s="3" t="inlineStr">
-        <is>
-          <t>lz; LZ</t>
-        </is>
-      </c>
-      <c r="S265" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T265" s="3" t="n"/>
+      <c r="T265" s="2" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007060</t>
+          <t>BCIO:007056</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>remind about personal capability BCT</t>
+          <t>reframe past behaviour BCT</t>
         </is>
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>A &lt;prompt thinking related to successful performance BCT&gt; that reminds the person of their skills and abilities that are relevant to the performance of the behaviour.</t>
+          <t>A &lt;suggest different perspective on behaviour BCT&gt; that involves reattributing a person's successes to internal, stable or global factors or failures to external, unstable or specific factors.</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>prompt thinking related to successful performance BCT</t>
+          <t>suggest different perspective on behaviour BCT</t>
         </is>
       </c>
       <c r="E266" s="3" t="n"/>
       <c r="F266" s="3" t="n"/>
-      <c r="G266" s="3" t="n"/>
-      <c r="H266" s="3" t="n"/>
+      <c r="G266" s="3" t="inlineStr">
+        <is>
+          <t>BCT13.2 Framing/reframing</t>
+        </is>
+      </c>
+      <c r="H266" s="3" t="inlineStr">
+        <is>
+          <t>cognitive re-structuring, re-attribution</t>
+        </is>
+      </c>
       <c r="I266" s="3" t="n"/>
       <c r="J266" s="3" t="n"/>
       <c r="K266" s="3" t="inlineStr">
@@ -16033,7 +16023,7 @@
       <c r="Q266" s="3" t="n"/>
       <c r="R266" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S266" s="3" t="inlineStr">
@@ -16046,42 +16036,30 @@
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007286</t>
+          <t>BCIO:007060</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>remove aversive consequence for behaviour BCT</t>
+          <t>remind about personal capability BCT</t>
         </is>
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove consequence for behaviour BCT&gt; where the consequence is aversive.</t>
+          <t>A &lt;prompt thinking related to successful performance BCT&gt; that reminds the person of their skills and abilities that are relevant to the performance of the behaviour.</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
         <is>
-          <t>remove consequence for behaviour BCT</t>
+          <t>prompt thinking related to successful performance BCT</t>
         </is>
       </c>
       <c r="E267" s="3" t="n"/>
       <c r="F267" s="3" t="n"/>
-      <c r="G267" s="3" t="inlineStr">
-        <is>
-          <t>BCT14.10 Remove punishment</t>
-        </is>
-      </c>
-      <c r="H267" s="3" t="inlineStr">
-        <is>
-          <t>negative reinforcement, remove punishment</t>
-        </is>
-      </c>
+      <c r="G267" s="3" t="n"/>
+      <c r="H267" s="3" t="n"/>
       <c r="I267" s="3" t="n"/>
-      <c r="J267" s="3" t="inlineStr">
-        <is>
-          <t>To qualify as aversive, the consequence should have been aversively valued by the person receiving it.</t>
-        </is>
-      </c>
+      <c r="J267" s="3" t="n"/>
       <c r="K267" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -16099,7 +16077,7 @@
       <c r="Q267" s="3" t="n"/>
       <c r="R267" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S267" s="3" t="inlineStr">
@@ -16112,27 +16090,31 @@
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007289</t>
+          <t>BCIO:007286</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>remove aversive consequence for outcome of behaviour BCT</t>
+          <t>remove aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove consequence for outcome of behaviour BCT&gt; in which the consequence is aversive.</t>
+          <t>A &lt;remove consequence for behaviour BCT&gt; where the consequence is aversive.</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>remove consequence for outcome of behaviour BCT</t>
+          <t>remove consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E268" s="3" t="n"/>
       <c r="F268" s="3" t="n"/>
-      <c r="G268" s="3" t="n"/>
+      <c r="G268" s="3" t="inlineStr">
+        <is>
+          <t>BCT14.10 Remove punishment</t>
+        </is>
+      </c>
       <c r="H268" s="3" t="inlineStr">
         <is>
           <t>negative reinforcement, remove punishment</t>
@@ -16174,22 +16156,22 @@
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007287</t>
+          <t>BCIO:007289</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>remove aversive material consequence for behaviour BCT</t>
+          <t>remove aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove aversive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;remove consequence for outcome of behaviour BCT&gt; in which the consequence is aversive.</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
         <is>
-          <t>remove aversive consequence for behaviour BCT</t>
+          <t>remove consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E269" s="3" t="n"/>
@@ -16197,11 +16179,15 @@
       <c r="G269" s="3" t="n"/>
       <c r="H269" s="3" t="inlineStr">
         <is>
-          <t>remove material punishment</t>
+          <t>negative reinforcement, remove punishment</t>
         </is>
       </c>
       <c r="I269" s="3" t="n"/>
-      <c r="J269" s="3" t="n"/>
+      <c r="J269" s="3" t="inlineStr">
+        <is>
+          <t>To qualify as aversive, the consequence should have been aversively valued by the person receiving it.</t>
+        </is>
+      </c>
       <c r="K269" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -16232,22 +16218,22 @@
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007288</t>
+          <t>BCIO:007287</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>remove aversive material consequence for outcome of behaviour BCT</t>
+          <t>remove aversive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove aversive consequence for outcome of behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;remove aversive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
-          <t>remove aversive consequence for outcome of behaviour BCT</t>
+          <t>remove aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E270" s="3" t="n"/>
@@ -16290,22 +16276,22 @@
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007290</t>
+          <t>BCIO:007288</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>remove aversive social consequence for behaviour BCT</t>
+          <t>remove aversive material consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove aversive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;remove aversive consequence for outcome of behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
         <is>
-          <t>remove aversive consequence for behaviour BCT</t>
+          <t>remove aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E271" s="3" t="n"/>
@@ -16313,15 +16299,11 @@
       <c r="G271" s="3" t="n"/>
       <c r="H271" s="3" t="inlineStr">
         <is>
-          <t>remove social punishment</t>
+          <t>remove material punishment</t>
         </is>
       </c>
       <c r="I271" s="3" t="n"/>
-      <c r="J271" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="J271" s="3" t="n"/>
       <c r="K271" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -16352,22 +16334,22 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007291</t>
+          <t>BCIO:007290</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>remove aversive social consequence for outcome of behaviour BCT</t>
+          <t>remove aversive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove aversive consequence for outcome of behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;remove aversive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>remove aversive consequence for outcome of behaviour BCT</t>
+          <t>remove aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E272" s="3" t="n"/>
@@ -16414,38 +16396,38 @@
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
         <is>
-          <t>BCIO:050331</t>
+          <t>BCIO:007291</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>remove aversive stimulus BCT</t>
+          <t>remove aversive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>An &lt;alter external stimulus BCT&gt; that involves removing an aversive stimulus to bring about behaviour change.</t>
+          <t>A &lt;remove aversive consequence for outcome of behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
         <is>
-          <t>alter external stimulus BCT</t>
+          <t>remove aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E273" s="3" t="n"/>
       <c r="F273" s="3" t="n"/>
-      <c r="G273" s="3" t="inlineStr">
-        <is>
-          <t>BCT7.5 Remove aversive stimulus</t>
-        </is>
-      </c>
+      <c r="G273" s="3" t="n"/>
       <c r="H273" s="3" t="inlineStr">
         <is>
-          <t>escape learning</t>
+          <t>remove social punishment</t>
         </is>
       </c>
       <c r="I273" s="3" t="n"/>
-      <c r="J273" s="3" t="n"/>
+      <c r="J273" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="K273" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -16463,7 +16445,7 @@
       <c r="Q273" s="3" t="n"/>
       <c r="R273" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S273" s="3" t="inlineStr">
@@ -16476,28 +16458,36 @@
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007285</t>
+          <t>BCIO:050331</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>remove consequence for behaviour BCT</t>
+          <t>remove aversive stimulus BCT</t>
         </is>
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>A &lt;behavioural consequence BCT&gt; that removes a previously provided consequence for performing the behaviour.</t>
+          <t>An &lt;alter external stimulus BCT&gt; that involves removing an aversive stimulus to bring about behaviour change.</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>behavioural consequence BCT</t>
+          <t>alter external stimulus BCT</t>
         </is>
       </c>
       <c r="E274" s="3" t="n"/>
       <c r="F274" s="3" t="n"/>
-      <c r="G274" s="3" t="n"/>
-      <c r="H274" s="3" t="n"/>
+      <c r="G274" s="3" t="inlineStr">
+        <is>
+          <t>BCT7.5 Remove aversive stimulus</t>
+        </is>
+      </c>
+      <c r="H274" s="3" t="inlineStr">
+        <is>
+          <t>escape learning</t>
+        </is>
+      </c>
       <c r="I274" s="3" t="n"/>
       <c r="J274" s="3" t="n"/>
       <c r="K274" s="3" t="inlineStr">
@@ -16530,22 +16520,22 @@
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007292</t>
+          <t>BCIO:007285</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>remove consequence for outcome of behaviour BCT</t>
+          <t>remove consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>An &lt;outcome consequence BCT&gt; that removes a previously provided consequence for an outcome resulting from performing or not performing the behaviour.</t>
+          <t>A &lt;behavioural consequence BCT&gt; that removes a previously provided consequence for performing the behaviour.</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
         <is>
-          <t>outcome consequence BCT</t>
+          <t>behavioural consequence BCT</t>
         </is>
       </c>
       <c r="E275" s="3" t="n"/>
@@ -16582,146 +16572,138 @@
       <c r="T275" s="3" t="n"/>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="inlineStr">
+      <c r="A276" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:007292</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="inlineStr">
+        <is>
+          <t>remove consequence for outcome of behaviour BCT</t>
+        </is>
+      </c>
+      <c r="C276" s="3" t="inlineStr">
+        <is>
+          <t>An &lt;outcome consequence BCT&gt; that removes a previously provided consequence for an outcome resulting from performing or not performing the behaviour.</t>
+        </is>
+      </c>
+      <c r="D276" s="3" t="inlineStr">
+        <is>
+          <t>outcome consequence BCT</t>
+        </is>
+      </c>
+      <c r="E276" s="3" t="n"/>
+      <c r="F276" s="3" t="n"/>
+      <c r="G276" s="3" t="n"/>
+      <c r="H276" s="3" t="n"/>
+      <c r="I276" s="3" t="n"/>
+      <c r="J276" s="3" t="n"/>
+      <c r="K276" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="L276" s="3" t="n"/>
+      <c r="M276" s="3" t="n"/>
+      <c r="N276" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O276" s="3" t="n"/>
+      <c r="P276" s="3" t="n"/>
+      <c r="Q276" s="3" t="n"/>
+      <c r="R276" s="3" t="inlineStr">
+        <is>
+          <t>LZ</t>
+        </is>
+      </c>
+      <c r="S276" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T276" s="3" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
         <is>
           <t>BCIO:050995</t>
         </is>
       </c>
-      <c r="B276" s="2" t="inlineStr">
+      <c r="B277" s="2" t="inlineStr">
         <is>
           <t>remove objects from the environment BCT</t>
         </is>
       </c>
-      <c r="C276" s="2" t="inlineStr">
+      <c r="C277" s="2" t="inlineStr">
         <is>
           <t>A &lt;restructure the physical environment BCT&gt; that removes objects from the person’s physical surroundings.</t>
         </is>
       </c>
-      <c r="D276" s="2" t="inlineStr">
+      <c r="D277" s="2" t="inlineStr">
         <is>
           <t>restructure the physical environment BCT</t>
         </is>
       </c>
-      <c r="E276" s="2" t="n"/>
-      <c r="F276" s="2" t="n"/>
-      <c r="G276" s="2" t="n"/>
-      <c r="H276" s="2" t="n"/>
-      <c r="I276" s="2" t="n"/>
-      <c r="J276" s="2" t="inlineStr">
+      <c r="E277" s="2" t="n"/>
+      <c r="F277" s="2" t="n"/>
+      <c r="G277" s="2" t="n"/>
+      <c r="H277" s="2" t="n"/>
+      <c r="I277" s="2" t="n"/>
+      <c r="J277" s="2" t="inlineStr">
         <is>
           <t>Objects include fixed structures such as fences, as well as equipment, digital devices and interactive displays. This BCT includes removing 'virtual' buttons or other interactive elements on digital devices.</t>
         </is>
       </c>
-      <c r="K276" s="2" t="n"/>
-      <c r="L276" s="2" t="n"/>
-      <c r="M276" s="2" t="n"/>
-      <c r="N276" s="2" t="inlineStr">
+      <c r="K277" s="2" t="n"/>
+      <c r="L277" s="2" t="n"/>
+      <c r="M277" s="2" t="n"/>
+      <c r="N277" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="O276" s="2" t="n"/>
-      <c r="P276" s="2" t="n"/>
-      <c r="Q276" s="2" t="n"/>
-      <c r="R276" s="2" t="n"/>
-      <c r="S276" s="2" t="n">
+      <c r="O277" s="2" t="n"/>
+      <c r="P277" s="2" t="n"/>
+      <c r="Q277" s="2" t="n"/>
+      <c r="R277" s="2" t="n"/>
+      <c r="S277" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T276" s="2" t="n"/>
-    </row>
-    <row r="277">
-      <c r="A277" s="3" t="inlineStr">
-        <is>
-          <t>BCIO:007293</t>
-        </is>
-      </c>
-      <c r="B277" s="3" t="inlineStr">
-        <is>
-          <t>remove positive consequence for behaviour BCT</t>
-        </is>
-      </c>
-      <c r="C277" s="3" t="inlineStr">
-        <is>
-          <t>A &lt;remove consequence for behaviour BCT&gt; where the consequence is positive.</t>
-        </is>
-      </c>
-      <c r="D277" s="3" t="inlineStr">
-        <is>
-          <t>remove consequence for behaviour BCT</t>
-        </is>
-      </c>
-      <c r="E277" s="3" t="n"/>
-      <c r="F277" s="3" t="n"/>
-      <c r="G277" s="3" t="inlineStr">
-        <is>
-          <t>BCT7.4 Remove access to the reward; BCT14.1 Behaviour cost; BCT14.3 Remove reward</t>
-        </is>
-      </c>
-      <c r="H277" s="3" t="inlineStr">
-        <is>
-          <t>time out, response cost, extinction, remove reward</t>
-        </is>
-      </c>
-      <c r="I277" s="3" t="n"/>
-      <c r="J277" s="3" t="inlineStr">
-        <is>
-          <t>To qualify as positive, the consequence should have been positively valued by the person receiving it.</t>
-        </is>
-      </c>
-      <c r="K277" s="3" t="inlineStr">
-        <is>
-          <t>behaviour change technique</t>
-        </is>
-      </c>
-      <c r="L277" s="3" t="n"/>
-      <c r="M277" s="3" t="n"/>
-      <c r="N277" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="O277" s="3" t="n"/>
-      <c r="P277" s="3" t="n"/>
-      <c r="Q277" s="3" t="n"/>
-      <c r="R277" s="3" t="inlineStr">
-        <is>
-          <t>LZ</t>
-        </is>
-      </c>
-      <c r="S277" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T277" s="3" t="n"/>
+      <c r="T277" s="2" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007296</t>
+          <t>BCIO:007293</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>remove positive consequence for outcome of behaviour BCT</t>
+          <t>remove positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove consequence for outcome of behaviour BCT&gt; in which the consequence is positive.</t>
+          <t>A &lt;remove consequence for behaviour BCT&gt; where the consequence is positive.</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>remove consequence for outcome of behaviour BCT</t>
+          <t>remove consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E278" s="3" t="n"/>
       <c r="F278" s="3" t="n"/>
-      <c r="G278" s="3" t="n"/>
+      <c r="G278" s="3" t="inlineStr">
+        <is>
+          <t>BCT7.4 Remove access to the reward; BCT14.1 Behaviour cost; BCT14.3 Remove reward</t>
+        </is>
+      </c>
       <c r="H278" s="3" t="inlineStr">
         <is>
-          <t>remove reward</t>
+          <t>time out, response cost, extinction, remove reward</t>
         </is>
       </c>
       <c r="I278" s="3" t="n"/>
@@ -16760,22 +16742,22 @@
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007294</t>
+          <t>BCIO:007296</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>remove positive material consequence for behaviour BCT</t>
+          <t>remove positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove positive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;remove consequence for outcome of behaviour BCT&gt; in which the consequence is positive.</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
         <is>
-          <t>remove positive consequence for behaviour BCT</t>
+          <t>remove consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E279" s="3" t="n"/>
@@ -16783,11 +16765,15 @@
       <c r="G279" s="3" t="n"/>
       <c r="H279" s="3" t="inlineStr">
         <is>
-          <t>remove material reward</t>
+          <t>remove reward</t>
         </is>
       </c>
       <c r="I279" s="3" t="n"/>
-      <c r="J279" s="3" t="n"/>
+      <c r="J279" s="3" t="inlineStr">
+        <is>
+          <t>To qualify as positive, the consequence should have been positively valued by the person receiving it.</t>
+        </is>
+      </c>
       <c r="K279" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -16818,22 +16804,22 @@
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007295</t>
+          <t>BCIO:007294</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>remove positive material consequence for outcome of behaviour BCT</t>
+          <t>remove positive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove positive consequence for outcome of behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;remove positive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>remove positive consequence for outcome of behaviour BCT</t>
+          <t>remove positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E280" s="3" t="n"/>
@@ -16876,22 +16862,22 @@
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007297</t>
+          <t>BCIO:007295</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>remove positive social consequence for behaviour BCT</t>
+          <t>remove positive material consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove positive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;remove positive consequence for outcome of behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
         <is>
-          <t>remove positive consequence for behaviour BCT</t>
+          <t>remove positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E281" s="3" t="n"/>
@@ -16899,15 +16885,11 @@
       <c r="G281" s="3" t="n"/>
       <c r="H281" s="3" t="inlineStr">
         <is>
-          <t>remove social reward</t>
+          <t>remove material reward</t>
         </is>
       </c>
       <c r="I281" s="3" t="n"/>
-      <c r="J281" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="J281" s="3" t="n"/>
       <c r="K281" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -16938,22 +16920,22 @@
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007298</t>
+          <t>BCIO:007297</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>remove positive social consequence for outcome of behaviour BCT</t>
+          <t>remove positive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove positive consequence for outcome of behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;remove positive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
         <is>
-          <t>remove positive consequence for outcome of behaviour BCT</t>
+          <t>remove positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="E282" s="3" t="n"/>
@@ -17000,30 +16982,38 @@
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007150</t>
+          <t>BCIO:007298</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>restructure the environment BCT</t>
+          <t>remove positive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>A &lt;behaviour change technique&gt; that alters the environment in which the behaviour is, or would have been, performed in a way that facilitates or impedes the behaviour.</t>
+          <t>A &lt;remove positive consequence for outcome of behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr">
         <is>
-          <t>behaviour change technique</t>
+          <t>remove positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="E283" s="3" t="n"/>
       <c r="F283" s="3" t="n"/>
       <c r="G283" s="3" t="n"/>
-      <c r="H283" s="3" t="n"/>
+      <c r="H283" s="3" t="inlineStr">
+        <is>
+          <t>remove social reward</t>
+        </is>
+      </c>
       <c r="I283" s="3" t="n"/>
-      <c r="J283" s="3" t="n"/>
+      <c r="J283" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="K283" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -17054,42 +17044,30 @@
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>BCIO:050348</t>
+          <t>BCIO:007150</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>restructure the physical environment BCT</t>
+          <t>restructure the environment BCT</t>
         </is>
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>A &lt;restructure the environment BCT&gt; that alters the physical environment in which the behaviour is, or would have been, performed in a way that facilitates or impedes the behaviour.</t>
+          <t>A &lt;behaviour change technique&gt; that alters the environment in which the behaviour is, or would have been, performed in a way that facilitates or impedes the behaviour.</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
         <is>
-          <t>restructure the environment BCT</t>
+          <t>behaviour change technique</t>
         </is>
       </c>
       <c r="E284" s="3" t="n"/>
       <c r="F284" s="3" t="n"/>
-      <c r="G284" s="3" t="inlineStr">
-        <is>
-          <t>BCT12.1 Restructuring the physical environment</t>
-        </is>
-      </c>
-      <c r="H284" s="3" t="inlineStr">
-        <is>
-          <t>physical space reorganisation, environmental modification</t>
-        </is>
-      </c>
+      <c r="G284" s="3" t="n"/>
+      <c r="H284" s="3" t="n"/>
       <c r="I284" s="3" t="n"/>
-      <c r="J284" s="3" t="inlineStr">
-        <is>
-          <t>This may also involve 'reduce exposure to cues for the behaviour BCT'</t>
-        </is>
-      </c>
+      <c r="J284" s="3" t="n"/>
       <c r="K284" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -17107,7 +17085,7 @@
       <c r="Q284" s="3" t="n"/>
       <c r="R284" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S284" s="3" t="inlineStr">
@@ -17120,17 +17098,17 @@
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>BCIO:050349</t>
+          <t>BCIO:050348</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>restructure the social environment BCT</t>
+          <t>restructure the physical environment BCT</t>
         </is>
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>A &lt;restructure the environment BCT&gt; that alters the social environment in which the behaviour is, or would have been, performed in a way that facilitates or impedes the behaviour.</t>
+          <t>A &lt;restructure the environment BCT&gt; that alters the physical environment in which the behaviour is, or would have been, performed in a way that facilitates or impedes the behaviour.</t>
         </is>
       </c>
       <c r="D285" s="3" t="inlineStr">
@@ -17142,19 +17120,15 @@
       <c r="F285" s="3" t="n"/>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>BCT12.2 Restructuring the social environment</t>
+          <t>BCT12.1 Restructuring the physical environment</t>
         </is>
       </c>
       <c r="H285" s="3" t="inlineStr">
         <is>
-          <t>interpersonal environment restructuring, social context modification</t>
-        </is>
-      </c>
-      <c r="I285" s="3" t="inlineStr">
-        <is>
-          <t>Instructing people in a smoking cessation group to sit in a circle rather than in rows; Instructing schoolchildren to form a single file queue rather than mingle in a crowd.</t>
-        </is>
-      </c>
+          <t>physical space reorganisation, environmental modification</t>
+        </is>
+      </c>
+      <c r="I285" s="3" t="n"/>
       <c r="J285" s="3" t="inlineStr">
         <is>
           <t>This may also involve 'reduce exposure to cues for the behaviour BCT'</t>
@@ -17190,36 +17164,44 @@
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007011</t>
+          <t>BCIO:050349</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">review behaviour goal BCT </t>
+          <t>restructure the social environment BCT</t>
         </is>
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>A &lt;goal directed BCT&gt; that reviews a behavioural goal and considers modifying the goal in light of progress toward the goal.</t>
+          <t>A &lt;restructure the environment BCT&gt; that alters the social environment in which the behaviour is, or would have been, performed in a way that facilitates or impedes the behaviour.</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
         <is>
-          <t>goal directed BCT</t>
+          <t>restructure the environment BCT</t>
         </is>
       </c>
       <c r="E286" s="3" t="n"/>
       <c r="F286" s="3" t="n"/>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>BCT1.5 Review behaviour goal(s)</t>
-        </is>
-      </c>
-      <c r="H286" s="3" t="n"/>
-      <c r="I286" s="3" t="n"/>
+          <t>BCT12.2 Restructuring the social environment</t>
+        </is>
+      </c>
+      <c r="H286" s="3" t="inlineStr">
+        <is>
+          <t>interpersonal environment restructuring, social context modification</t>
+        </is>
+      </c>
+      <c r="I286" s="3" t="inlineStr">
+        <is>
+          <t>Instructing people in a smoking cessation group to sit in a circle rather than in rows; Instructing schoolchildren to form a single file queue rather than mingle in a crowd.</t>
+        </is>
+      </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
-          <t>A goal is a cognitive representation of an end state towards which one is striving. If goal specified in terms of behaviour, code this class; if goal unspecified, code 'review outcome goal BCT'; if discrepancy created consider also 'attend to discrepancy between current behaviour and goal BCT'; if modifying the plan to achieve the goal consider also 'review behaviour goal plan BCT'.</t>
+          <t>This may also involve 'reduce exposure to cues for the behaviour BCT'</t>
         </is>
       </c>
       <c r="K286" s="3" t="inlineStr">
@@ -17252,17 +17234,17 @@
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007299</t>
+          <t>BCIO:007011</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">review behaviour goal plan BCT </t>
+          <t xml:space="preserve">review behaviour goal BCT </t>
         </is>
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>A &lt;goal directed BCT&gt; that reviews progress towards a behavioural goal and considers modifying the plan to achieve the goal.</t>
+          <t>A &lt;goal directed BCT&gt; that reviews a behavioural goal and considers modifying the goal in light of progress toward the goal.</t>
         </is>
       </c>
       <c r="D287" s="3" t="inlineStr">
@@ -17272,12 +17254,16 @@
       </c>
       <c r="E287" s="3" t="n"/>
       <c r="F287" s="3" t="n"/>
-      <c r="G287" s="3" t="n"/>
+      <c r="G287" s="3" t="inlineStr">
+        <is>
+          <t>BCT1.5 Review behaviour goal(s)</t>
+        </is>
+      </c>
       <c r="H287" s="3" t="n"/>
       <c r="I287" s="3" t="n"/>
       <c r="J287" s="3" t="inlineStr">
         <is>
-          <t>A goal is a cognitive representation of an end state towards which one is striving.</t>
+          <t>A goal is a cognitive representation of an end state towards which one is striving. If goal specified in terms of behaviour, code this class; if goal unspecified, code 'review outcome goal BCT'; if discrepancy created consider also 'attend to discrepancy between current behaviour and goal BCT'; if modifying the plan to achieve the goal consider also 'review behaviour goal plan BCT'.</t>
         </is>
       </c>
       <c r="K287" s="3" t="inlineStr">
@@ -17297,7 +17283,7 @@
       <c r="Q287" s="3" t="n"/>
       <c r="R287" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S287" s="3" t="inlineStr">
@@ -17310,17 +17296,17 @@
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007013</t>
+          <t>BCIO:007299</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">review outcome goal BCT </t>
+          <t xml:space="preserve">review behaviour goal plan BCT </t>
         </is>
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>A &lt;goal directed BCT&gt; that reviews an outcome goal and considers modifying the goal in light of achievement.</t>
+          <t>A &lt;goal directed BCT&gt; that reviews progress towards a behavioural goal and considers modifying the plan to achieve the goal.</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
@@ -17330,16 +17316,12 @@
       </c>
       <c r="E288" s="3" t="n"/>
       <c r="F288" s="3" t="n"/>
-      <c r="G288" s="3" t="inlineStr">
-        <is>
-          <t>BCT1.7 Review outcome goal(s)</t>
-        </is>
-      </c>
+      <c r="G288" s="3" t="n"/>
       <c r="H288" s="3" t="n"/>
       <c r="I288" s="3" t="n"/>
       <c r="J288" s="3" t="inlineStr">
         <is>
-          <t>A goal is a cognitive representation of an end state towards which one is striving. If goal specified in terms of behaviour, code 'review behaviour goal BCT'; if goal unspecified, code this class; if discrepancy created consider also 'attend to discrepancy between current behaviour and goal BCT'.</t>
+          <t>A goal is a cognitive representation of an end state towards which one is striving.</t>
         </is>
       </c>
       <c r="K288" s="3" t="inlineStr">
@@ -17359,7 +17341,7 @@
       <c r="Q288" s="3" t="n"/>
       <c r="R288" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S288" s="3" t="inlineStr">
@@ -17372,40 +17354,36 @@
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007024</t>
+          <t>BCIO:007013</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">self-monitor behaviour BCT </t>
+          <t xml:space="preserve">review outcome goal BCT </t>
         </is>
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>A &lt;monitoring BCT&gt; in which the person uses a method to monitor and record their behaviour.</t>
+          <t>A &lt;goal directed BCT&gt; that reviews an outcome goal and considers modifying the goal in light of achievement.</t>
         </is>
       </c>
       <c r="D289" s="3" t="inlineStr">
         <is>
-          <t>monitoring BCT</t>
+          <t>goal directed BCT</t>
         </is>
       </c>
       <c r="E289" s="3" t="n"/>
       <c r="F289" s="3" t="n"/>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>BCT2.3 Self-monitoring of behaviour</t>
-        </is>
-      </c>
-      <c r="H289" s="3" t="inlineStr">
-        <is>
-          <t>self-monitoring</t>
-        </is>
-      </c>
+          <t>BCT1.7 Review outcome goal(s)</t>
+        </is>
+      </c>
+      <c r="H289" s="3" t="n"/>
       <c r="I289" s="3" t="n"/>
       <c r="J289" s="3" t="inlineStr">
         <is>
-          <t>If monitoring is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if self-monitoring of outcome of behaviour, code 'self-monitor outcome of behaviour BCT'.</t>
+          <t>A goal is a cognitive representation of an end state towards which one is striving. If goal specified in terms of behaviour, code 'review behaviour goal BCT'; if goal unspecified, code this class; if discrepancy created consider also 'attend to discrepancy between current behaviour and goal BCT'.</t>
         </is>
       </c>
       <c r="K289" s="3" t="inlineStr">
@@ -17438,17 +17416,17 @@
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007025</t>
+          <t>BCIO:007024</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">self-monitor outcome of behaviour BCT </t>
+          <t xml:space="preserve">self-monitor behaviour BCT </t>
         </is>
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>A &lt;monitoring BCT&gt; in which the person uses a method to monitor and record an outcome of their behaviour.</t>
+          <t>A &lt;monitoring BCT&gt; in which the person uses a method to monitor and record their behaviour.</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
@@ -17460,14 +17438,18 @@
       <c r="F290" s="3" t="n"/>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>BCT2.4 Self-monitoring of outcome(s) of behaviour</t>
-        </is>
-      </c>
-      <c r="H290" s="3" t="n"/>
+          <t>BCT2.3 Self-monitoring of behaviour</t>
+        </is>
+      </c>
+      <c r="H290" s="3" t="inlineStr">
+        <is>
+          <t>self-monitoring</t>
+        </is>
+      </c>
       <c r="I290" s="3" t="n"/>
       <c r="J290" s="3" t="inlineStr">
         <is>
-          <t>If monitoring is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if self-monitoring behaviour, code 'self-monitor behaviour BCT'.</t>
+          <t>If monitoring is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if self-monitoring of outcome of behaviour, code 'self-monitor outcome of behaviour BCT'.</t>
         </is>
       </c>
       <c r="K290" s="3" t="inlineStr">
@@ -17500,36 +17482,36 @@
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007003</t>
+          <t>BCIO:007025</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">set behaviour goal BCT </t>
+          <t xml:space="preserve">self-monitor outcome of behaviour BCT </t>
         </is>
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>A &lt;goal setting BCT&gt; that sets a goal for the behaviour to be achieved.</t>
+          <t>A &lt;monitoring BCT&gt; in which the person uses a method to monitor and record an outcome of their behaviour.</t>
         </is>
       </c>
       <c r="D291" s="3" t="inlineStr">
         <is>
-          <t>goal setting BCT</t>
+          <t>monitoring BCT</t>
         </is>
       </c>
       <c r="E291" s="3" t="n"/>
       <c r="F291" s="3" t="n"/>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>BCT1.1 Goal setting (behaviour)</t>
+          <t>BCT2.4 Self-monitoring of outcome(s) of behaviour</t>
         </is>
       </c>
       <c r="H291" s="3" t="n"/>
       <c r="I291" s="3" t="n"/>
       <c r="J291" s="3" t="inlineStr">
         <is>
-          <t>A goal is a cognitive representation of an end state towards which one is striving. The goal could be set for the self or another person. Only code if there is sufficient evidence that the goal is set as part of intervention; if goal is a behavioural outcome, code 'set outcome goal BCT'; if goal unspecified code 'goal setting BCT'; if the goal defines a specific context, frequency, duration or intensity for the behaviour, also code 'action planning BCT'.</t>
+          <t>If monitoring is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if self-monitoring behaviour, code 'self-monitor behaviour BCT'.</t>
         </is>
       </c>
       <c r="K291" s="3" t="inlineStr">
@@ -17562,38 +17544,38 @@
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007100</t>
+          <t>BCIO:007003</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>set graded tasks BCT</t>
+          <t xml:space="preserve">set behaviour goal BCT </t>
         </is>
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>A &lt;goal directed BCT&gt; that sets easy-to-perform tasks for the person, making them increasingly difficult, but achievable, until the behaviour is performed.</t>
+          <t>A &lt;goal setting BCT&gt; that sets a goal for the behaviour to be achieved.</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
         <is>
-          <t>goal directed BCT</t>
+          <t>goal setting BCT</t>
         </is>
       </c>
       <c r="E292" s="3" t="n"/>
       <c r="F292" s="3" t="n"/>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>BCT8.7 Graded tasks</t>
-        </is>
-      </c>
-      <c r="H292" s="3" t="inlineStr">
-        <is>
-          <t>graded tasks</t>
-        </is>
-      </c>
+          <t>BCT1.1 Goal setting (behaviour)</t>
+        </is>
+      </c>
+      <c r="H292" s="3" t="n"/>
       <c r="I292" s="3" t="n"/>
-      <c r="J292" s="3" t="n"/>
+      <c r="J292" s="3" t="inlineStr">
+        <is>
+          <t>A goal is a cognitive representation of an end state towards which one is striving. The goal could be set for the self or another person. Only code if there is sufficient evidence that the goal is set as part of intervention; if goal is a behavioural outcome, code 'set outcome goal BCT'; if goal unspecified code 'goal setting BCT'; if the goal defines a specific context, frequency, duration or intensity for the behaviour, also code 'action planning BCT'.</t>
+        </is>
+      </c>
       <c r="K292" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -17624,34 +17606,38 @@
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007300</t>
+          <t>BCIO:007100</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">set measurable behaviour goal BCT </t>
+          <t>set graded tasks BCT</t>
         </is>
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>A &lt;set behaviour goal BCT&gt; that describes the behaviour to be achieved in terms of a measurable target.</t>
+          <t>A &lt;goal directed BCT&gt; that sets easy-to-perform tasks for the person, making them increasingly difficult, but achievable, until the behaviour is performed.</t>
         </is>
       </c>
       <c r="D293" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">set behaviour goal BCT </t>
+          <t>goal directed BCT</t>
         </is>
       </c>
       <c r="E293" s="3" t="n"/>
       <c r="F293" s="3" t="n"/>
-      <c r="G293" s="3" t="n"/>
-      <c r="H293" s="3" t="n"/>
+      <c r="G293" s="3" t="inlineStr">
+        <is>
+          <t>BCT8.7 Graded tasks</t>
+        </is>
+      </c>
+      <c r="H293" s="3" t="inlineStr">
+        <is>
+          <t>graded tasks</t>
+        </is>
+      </c>
       <c r="I293" s="3" t="n"/>
-      <c r="J293" s="3" t="inlineStr">
-        <is>
-          <t>A behaviour goal might be set in general terms e.g. "to do more physical activity" or in measurable terms e.g. "to do 30 minutes of physical activity five times a week" or "to walk 8000 steps a day." Use this class for measurable behaviour goals</t>
-        </is>
-      </c>
+      <c r="J293" s="3" t="n"/>
       <c r="K293" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -17669,7 +17655,7 @@
       <c r="Q293" s="3" t="n"/>
       <c r="R293" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S293" s="3" t="inlineStr">
@@ -17682,22 +17668,22 @@
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007301</t>
+          <t>BCIO:007300</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">set measurable outcome goal BCT </t>
+          <t xml:space="preserve">set measurable behaviour goal BCT </t>
         </is>
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>A &lt;set outcome goal BCT&gt; that describes the behavioural outcome to be achieved in terms of a measurable target.</t>
+          <t>A &lt;set behaviour goal BCT&gt; that describes the behaviour to be achieved in terms of a measurable target.</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
         <is>
-          <t>set outcome goal BCT</t>
+          <t xml:space="preserve">set behaviour goal BCT </t>
         </is>
       </c>
       <c r="E294" s="3" t="n"/>
@@ -17707,7 +17693,7 @@
       <c r="I294" s="3" t="n"/>
       <c r="J294" s="3" t="inlineStr">
         <is>
-          <t>An outcome goal might be set in general terms - e.g. "to lose weight" or in measurable terms - e.g. "to lose 5kg of weight" or "to lose 10% of my body weight". Use this class for measurable outcome goals</t>
+          <t>A behaviour goal might be set in general terms e.g. "to do more physical activity" or in measurable terms e.g. "to do 30 minutes of physical activity five times a week" or "to walk 8000 steps a day." Use this class for measurable behaviour goals</t>
         </is>
       </c>
       <c r="K294" s="3" t="inlineStr">
@@ -17740,36 +17726,32 @@
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007005</t>
+          <t>BCIO:007301</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">set measurable outcome goal BCT </t>
+        </is>
+      </c>
+      <c r="C295" s="3" t="inlineStr">
+        <is>
+          <t>A &lt;set outcome goal BCT&gt; that describes the behavioural outcome to be achieved in terms of a measurable target.</t>
+        </is>
+      </c>
+      <c r="D295" s="3" t="inlineStr">
+        <is>
           <t>set outcome goal BCT</t>
-        </is>
-      </c>
-      <c r="C295" s="3" t="inlineStr">
-        <is>
-          <t>A &lt;goal setting BCT&gt; in which the goal is a positive outcome of performing the behaviour.</t>
-        </is>
-      </c>
-      <c r="D295" s="3" t="inlineStr">
-        <is>
-          <t>goal setting BCT</t>
         </is>
       </c>
       <c r="E295" s="3" t="n"/>
       <c r="F295" s="3" t="n"/>
-      <c r="G295" s="3" t="inlineStr">
-        <is>
-          <t>BCT1.3 Goal setting (outcome)</t>
-        </is>
-      </c>
+      <c r="G295" s="3" t="n"/>
       <c r="H295" s="3" t="n"/>
       <c r="I295" s="3" t="n"/>
       <c r="J295" s="3" t="inlineStr">
         <is>
-          <t>A goal is a cognitive representation of an end state towards which one is striving. The goal could be set for the self or another person. Only code guidelines if set as a goal in an intervention context; if goal is a behaviour, code 'set behaviour goal BCT'; if goal unspecified code 'goal setting BCT'.</t>
+          <t>An outcome goal might be set in general terms - e.g. "to lose weight" or in measurable terms - e.g. "to lose 5kg of weight" or "to lose 10% of my body weight". Use this class for measurable outcome goals</t>
         </is>
       </c>
       <c r="K295" s="3" t="inlineStr">
@@ -17789,7 +17771,7 @@
       <c r="Q295" s="3" t="n"/>
       <c r="R295" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S295" s="3" t="inlineStr">
@@ -17802,36 +17784,36 @@
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007028</t>
+          <t>BCIO:007005</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>social support BCT</t>
+          <t>set outcome goal BCT</t>
         </is>
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>A &lt;behaviour change technique&gt; that involves taking steps to secure or deliver the support or aid of another person.</t>
+          <t>A &lt;goal setting BCT&gt; in which the goal is a positive outcome of performing the behaviour.</t>
         </is>
       </c>
       <c r="D296" s="3" t="inlineStr">
         <is>
-          <t>behaviour change technique</t>
+          <t>goal setting BCT</t>
         </is>
       </c>
       <c r="E296" s="3" t="n"/>
       <c r="F296" s="3" t="n"/>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>BCT3.1 Social support (unspecified)</t>
+          <t>BCT1.3 Goal setting (outcome)</t>
         </is>
       </c>
       <c r="H296" s="3" t="n"/>
       <c r="I296" s="3" t="n"/>
       <c r="J296" s="3" t="inlineStr">
         <is>
-          <t>Attending a group class and/or mention of ‘follow-up’ does not necessarily apply this BCT, support must be explicitly mentioned.</t>
+          <t>A goal is a cognitive representation of an end state towards which one is striving. The goal could be set for the self or another person. Only code guidelines if set as a goal in an intervention context; if goal is a behaviour, code 'set behaviour goal BCT'; if goal unspecified code 'goal setting BCT'.</t>
         </is>
       </c>
       <c r="K296" s="3" t="inlineStr">
@@ -17864,40 +17846,36 @@
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007095</t>
+          <t>BCIO:007028</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">substitute behaviour BCT </t>
+          <t>social support BCT</t>
         </is>
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>An &lt;advise specific behaviour BCT&gt; that advises the person to replace the unwanted behaviour with another behaviour.</t>
+          <t>A &lt;behaviour change technique&gt; that involves taking steps to secure or deliver the support or aid of another person.</t>
         </is>
       </c>
       <c r="D297" s="3" t="inlineStr">
         <is>
-          <t>advise specific behaviour BCT</t>
+          <t>behaviour change technique</t>
         </is>
       </c>
       <c r="E297" s="3" t="n"/>
       <c r="F297" s="3" t="n"/>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>BCT8.2 Behaviour substitution</t>
-        </is>
-      </c>
-      <c r="H297" s="3" t="inlineStr">
-        <is>
-          <t>behaviour replacement, alternative response</t>
-        </is>
-      </c>
+          <t>BCT3.1 Social support (unspecified)</t>
+        </is>
+      </c>
+      <c r="H297" s="3" t="n"/>
       <c r="I297" s="3" t="n"/>
       <c r="J297" s="3" t="inlineStr">
         <is>
-          <t>If this occurs regularly, also code 'context-specific repetition of alternative behaviour BCT'</t>
+          <t>Attending a group class and/or mention of ‘follow-up’ does not necessarily apply this BCT, support must be explicitly mentioned.</t>
         </is>
       </c>
       <c r="K297" s="3" t="inlineStr">
@@ -17930,34 +17908,42 @@
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007302</t>
+          <t>BCIO:007095</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>suggest different perspective on behaviour BCT</t>
+          <t xml:space="preserve">substitute behaviour BCT </t>
         </is>
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A &lt;behaviour change technique&gt; that suggests the deliberate adoption of a new perspective on the behaviour. </t>
+          <t>An &lt;advise specific behaviour BCT&gt; that advises the person to replace the unwanted behaviour with another behaviour.</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>behaviour change technique</t>
+          <t>advise specific behaviour BCT</t>
         </is>
       </c>
       <c r="E298" s="3" t="n"/>
       <c r="F298" s="3" t="n"/>
-      <c r="G298" s="3" t="n"/>
+      <c r="G298" s="3" t="inlineStr">
+        <is>
+          <t>BCT8.2 Behaviour substitution</t>
+        </is>
+      </c>
       <c r="H298" s="3" t="inlineStr">
         <is>
-          <t>cognitive reframing</t>
+          <t>behaviour replacement, alternative response</t>
         </is>
       </c>
       <c r="I298" s="3" t="n"/>
-      <c r="J298" s="3" t="n"/>
+      <c r="J298" s="3" t="inlineStr">
+        <is>
+          <t>If this occurs regularly, also code 'context-specific repetition of alternative behaviour BCT'</t>
+        </is>
+      </c>
       <c r="K298" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -17988,28 +17974,32 @@
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007303</t>
+          <t>BCIO:007302</t>
         </is>
       </c>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>suggest how to perform behaviour BCT</t>
+          <t>suggest different perspective on behaviour BCT</t>
         </is>
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>A &lt;guide how to perform behaviour BCT&gt; that provides a suggestion regarding how to perform the behaviour.</t>
+          <t xml:space="preserve">A &lt;behaviour change technique&gt; that suggests the deliberate adoption of a new perspective on the behaviour. </t>
         </is>
       </c>
       <c r="D299" s="3" t="inlineStr">
         <is>
-          <t>guide how to perform behaviour BCT</t>
+          <t>behaviour change technique</t>
         </is>
       </c>
       <c r="E299" s="3" t="n"/>
       <c r="F299" s="3" t="n"/>
       <c r="G299" s="3" t="n"/>
-      <c r="H299" s="3" t="n"/>
+      <c r="H299" s="3" t="inlineStr">
+        <is>
+          <t>cognitive reframing</t>
+        </is>
+      </c>
       <c r="I299" s="3" t="n"/>
       <c r="J299" s="3" t="n"/>
       <c r="K299" s="3" t="inlineStr">
@@ -18029,7 +18019,7 @@
       <c r="Q299" s="3" t="n"/>
       <c r="R299" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S299" s="3" t="inlineStr">
@@ -18042,42 +18032,30 @@
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007076</t>
+          <t>BCIO:007303</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>suggest to change behaviour BCT</t>
+          <t>suggest how to perform behaviour BCT</t>
         </is>
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>An &lt;awareness of other people's thoughts, feelings and actions BCT&gt; that involves sharing a view about what behaviour the person should do.</t>
+          <t>A &lt;guide how to perform behaviour BCT&gt; that provides a suggestion regarding how to perform the behaviour.</t>
         </is>
       </c>
       <c r="D300" s="3" t="inlineStr">
         <is>
-          <t>awareness of other peoples thoughts, feelings and actions BCT</t>
+          <t>guide how to perform behaviour BCT</t>
         </is>
       </c>
       <c r="E300" s="3" t="n"/>
       <c r="F300" s="3" t="n"/>
-      <c r="G300" s="3" t="inlineStr">
-        <is>
-          <t>BCT4.5 Advise to change behaviour</t>
-        </is>
-      </c>
-      <c r="H300" s="3" t="inlineStr">
-        <is>
-          <t>encourage to change behaviour</t>
-        </is>
-      </c>
+      <c r="G300" s="3" t="n"/>
+      <c r="H300" s="3" t="n"/>
       <c r="I300" s="3" t="n"/>
-      <c r="J300" s="3" t="inlineStr">
-        <is>
-          <t>An example of the "suggest to change behaviour BCT" would be saying to someone: "I think you should do this behaviour" whereas an example of the "Tell to change behaviour BCT" is saying "Do this behaviour". This class includes "strongly encourage".</t>
-        </is>
-      </c>
+      <c r="J300" s="3" t="n"/>
       <c r="K300" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -18108,30 +18086,42 @@
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007089</t>
+          <t>BCIO:007076</t>
         </is>
       </c>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>systematically desensitise BCT</t>
+          <t>suggest to change behaviour BCT</t>
         </is>
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>An &lt;expose to stimulus BCT&gt; that gradually exposes the person to an aversive stimulus while also engaging them in a relaxation process to reduce the response to that stimulus.</t>
+          <t>An &lt;awareness of other people's thoughts, feelings and actions BCT&gt; that involves sharing a view about what behaviour the person should do.</t>
         </is>
       </c>
       <c r="D301" s="3" t="inlineStr">
         <is>
-          <t>expose to stimulus BCT</t>
+          <t>awareness of other peoples thoughts, feelings and actions BCT</t>
         </is>
       </c>
       <c r="E301" s="3" t="n"/>
       <c r="F301" s="3" t="n"/>
-      <c r="G301" s="3" t="n"/>
-      <c r="H301" s="3" t="n"/>
+      <c r="G301" s="3" t="inlineStr">
+        <is>
+          <t>BCT4.5 Advise to change behaviour</t>
+        </is>
+      </c>
+      <c r="H301" s="3" t="inlineStr">
+        <is>
+          <t>encourage to change behaviour</t>
+        </is>
+      </c>
       <c r="I301" s="3" t="n"/>
-      <c r="J301" s="3" t="n"/>
+      <c r="J301" s="3" t="inlineStr">
+        <is>
+          <t>An example of the "suggest to change behaviour BCT" would be saying to someone: "I think you should do this behaviour" whereas an example of the "Tell to change behaviour BCT" is saying "Do this behaviour". This class includes "strongly encourage".</t>
+        </is>
+      </c>
       <c r="K301" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -18162,42 +18152,30 @@
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007077</t>
+          <t>BCIO:007089</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>tell to change behaviour BCT</t>
+          <t>systematically desensitise BCT</t>
         </is>
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>An &lt;awareness of other people's thoughts, feelings and actions BCT&gt; that involves telling the person to perform the behaviour.</t>
+          <t>An &lt;expose to stimulus BCT&gt; that gradually exposes the person to an aversive stimulus while also engaging them in a relaxation process to reduce the response to that stimulus.</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr">
         <is>
-          <t>awareness of other peoples thoughts, feelings and actions BCT</t>
+          <t>expose to stimulus BCT</t>
         </is>
       </c>
       <c r="E302" s="3" t="n"/>
       <c r="F302" s="3" t="n"/>
-      <c r="G302" s="3" t="inlineStr">
-        <is>
-          <t>BCT4.5 Advise to change behaviour</t>
-        </is>
-      </c>
-      <c r="H302" s="3" t="inlineStr">
-        <is>
-          <t>instruct, command</t>
-        </is>
-      </c>
+      <c r="G302" s="3" t="n"/>
+      <c r="H302" s="3" t="n"/>
       <c r="I302" s="3" t="n"/>
-      <c r="J302" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">An example of the "Tell to change behaviour BCT" is saying "Do this behaviour" whereas an example of the "suggest to change behaviour BCT" would be saying to someone: "I think you should do this behaviour." </t>
-        </is>
-      </c>
+      <c r="J302" s="3" t="n"/>
       <c r="K302" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -18215,7 +18193,7 @@
       <c r="Q302" s="3" t="n"/>
       <c r="R302" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S302" s="3" t="inlineStr">
@@ -18228,34 +18206,42 @@
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007121</t>
+          <t>BCIO:007077</t>
         </is>
       </c>
       <c r="B303" s="3" t="inlineStr">
         <is>
-          <t>vicarious punishment BCT</t>
+          <t>tell to change behaviour BCT</t>
         </is>
       </c>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t>An &lt;increase awareness of consequences BCT&gt; that prompts observation of another person being punished when they perform the behaviour.</t>
+          <t>An &lt;awareness of other people's thoughts, feelings and actions BCT&gt; that involves telling the person to perform the behaviour.</t>
         </is>
       </c>
       <c r="D303" s="3" t="inlineStr">
         <is>
-          <t>increase awareness of consequences BCT</t>
+          <t>awareness of other peoples thoughts, feelings and actions BCT</t>
         </is>
       </c>
       <c r="E303" s="3" t="n"/>
       <c r="F303" s="3" t="n"/>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>BCT16.3 Vicarious consequences</t>
-        </is>
-      </c>
-      <c r="H303" s="3" t="n"/>
+          <t>BCT4.5 Advise to change behaviour</t>
+        </is>
+      </c>
+      <c r="H303" s="3" t="inlineStr">
+        <is>
+          <t>instruct, command</t>
+        </is>
+      </c>
       <c r="I303" s="3" t="n"/>
-      <c r="J303" s="3" t="n"/>
+      <c r="J303" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An example of the "Tell to change behaviour BCT" is saying "Do this behaviour" whereas an example of the "suggest to change behaviour BCT" would be saying to someone: "I think you should do this behaviour." </t>
+        </is>
+      </c>
       <c r="K303" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -18273,7 +18259,7 @@
       <c r="Q303" s="3" t="n"/>
       <c r="R303" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S303" s="3" t="inlineStr">
@@ -18286,17 +18272,17 @@
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007120</t>
+          <t>BCIO:007121</t>
         </is>
       </c>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">vicarious reward BCT </t>
+          <t>vicarious punishment BCT</t>
         </is>
       </c>
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t>An &lt;increase awareness of consequences BCT&gt; that prompts observation of another person being rewarded when they perform the behaviour.</t>
+          <t>An &lt;increase awareness of consequences BCT&gt; that prompts observation of another person being punished when they perform the behaviour.</t>
         </is>
       </c>
       <c r="D304" s="3" t="inlineStr">
@@ -18311,11 +18297,7 @@
           <t>BCT16.3 Vicarious consequences</t>
         </is>
       </c>
-      <c r="H304" s="3" t="inlineStr">
-        <is>
-          <t>vicarious reinforcement</t>
-        </is>
-      </c>
+      <c r="H304" s="3" t="n"/>
       <c r="I304" s="3" t="n"/>
       <c r="J304" s="3" t="n"/>
       <c r="K304" s="3" t="inlineStr">
@@ -18335,15 +18317,77 @@
       <c r="Q304" s="3" t="n"/>
       <c r="R304" s="3" t="inlineStr">
         <is>
+          <t>LZ</t>
+        </is>
+      </c>
+      <c r="S304" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T304" s="3" t="n"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:007120</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vicarious reward BCT </t>
+        </is>
+      </c>
+      <c r="C305" s="3" t="inlineStr">
+        <is>
+          <t>An &lt;increase awareness of consequences BCT&gt; that prompts observation of another person being rewarded when they perform the behaviour.</t>
+        </is>
+      </c>
+      <c r="D305" s="3" t="inlineStr">
+        <is>
+          <t>increase awareness of consequences BCT</t>
+        </is>
+      </c>
+      <c r="E305" s="3" t="n"/>
+      <c r="F305" s="3" t="n"/>
+      <c r="G305" s="3" t="inlineStr">
+        <is>
+          <t>BCT16.3 Vicarious consequences</t>
+        </is>
+      </c>
+      <c r="H305" s="3" t="inlineStr">
+        <is>
+          <t>vicarious reinforcement</t>
+        </is>
+      </c>
+      <c r="I305" s="3" t="n"/>
+      <c r="J305" s="3" t="n"/>
+      <c r="K305" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="L305" s="3" t="n"/>
+      <c r="M305" s="3" t="n"/>
+      <c r="N305" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="O305" s="3" t="n"/>
+      <c r="P305" s="3" t="n"/>
+      <c r="Q305" s="3" t="n"/>
+      <c r="R305" s="3" t="inlineStr">
+        <is>
           <t>lz; LZ</t>
         </is>
       </c>
-      <c r="S304" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T304" s="3" t="n"/>
+      <c r="S305" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T305" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BehaviourChangeTechniques/bcto.xlsx
+++ b/BehaviourChangeTechniques/bcto.xlsx
@@ -3692,45 +3692,45 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>awareness of change of other people's thoughts, feelings and actions BCT</t>
+          <t>awareness of change of other peoples thoughts, feelings and actions BCT</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">An &lt;awareness of other people’s thoughts, feelings and actions BCT&gt; that increases awareness of changes in what other people think, do or feel. </t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr"/>
-      <c r="E57" s="2" t="inlineStr"/>
+          <t xml:space="preserve">An &lt;awareness of other peoples thoughts, feelings and actions BCT&gt; that increases awareness of changes in what other people think, do or feel. </t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n"/>
+      <c r="E57" s="2" t="n"/>
       <c r="F57" s="2" t="inlineStr">
         <is>
           <t>awareness of other peoples thoughts, feelings and actions BCT</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="n"/>
+      <c r="H57" s="2" t="n"/>
+      <c r="I57" s="2" t="n"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
           <t>dynamic norms messaging</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="2" t="inlineStr"/>
-      <c r="M57" s="2" t="inlineStr"/>
-      <c r="N57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="n"/>
+      <c r="L57" s="2" t="n"/>
+      <c r="M57" s="2" t="n"/>
+      <c r="N57" s="2" t="n"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="P57" s="2" t="inlineStr"/>
-      <c r="Q57" s="2" t="inlineStr"/>
-      <c r="R57" s="2" t="inlineStr"/>
+      <c r="P57" s="2" t="n"/>
+      <c r="Q57" s="2" t="n"/>
+      <c r="R57" s="2" t="n"/>
       <c r="S57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">

--- a/BehaviourChangeTechniques/bcto.xlsx
+++ b/BehaviourChangeTechniques/bcto.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T306"/>
+  <dimension ref="A1:T307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8780,105 +8780,83 @@
       <c r="T145" s="3" t="n"/>
     </row>
     <row r="146">
-      <c r="A146" s="3" t="inlineStr">
-        <is>
-          <t>BCIO:007075</t>
-        </is>
-      </c>
-      <c r="B146" s="3" t="inlineStr">
-        <is>
-          <t>present information from credible influence BCT</t>
-        </is>
-      </c>
-      <c r="C146" s="3" t="inlineStr">
-        <is>
-          <t>An &lt;awareness of other people's thoughts, feelings and actions BCT&gt; that presents information from a credible person or organisation to influence the behaviour.</t>
-        </is>
-      </c>
-      <c r="D146" s="3" t="n"/>
-      <c r="E146" s="3" t="n"/>
-      <c r="F146" s="3" t="inlineStr">
-        <is>
-          <t>awareness of other peoples thoughts, feelings and actions BCT</t>
-        </is>
-      </c>
-      <c r="G146" s="3" t="inlineStr">
-        <is>
-          <t>BCT9.1 Credible source</t>
-        </is>
-      </c>
-      <c r="H146" s="3" t="n"/>
-      <c r="I146" s="3" t="n"/>
-      <c r="J146" s="3" t="n"/>
-      <c r="K146" s="3" t="inlineStr">
-        <is>
-          <t>Code this BCT if influence generally agreed on as credible e.g., health professionals, celebrities or words used to indicate expertise or leader in field and if the communication has the aim of persuading</t>
-        </is>
-      </c>
-      <c r="L146" s="3" t="inlineStr">
-        <is>
-          <t>behaviour change technique</t>
-        </is>
-      </c>
-      <c r="M146" s="3" t="n"/>
-      <c r="N146" s="3" t="n"/>
-      <c r="O146" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="P146" s="3" t="n"/>
-      <c r="Q146" s="3" t="n"/>
-      <c r="R146" s="3" t="inlineStr">
-        <is>
-          <t>lz; LZ</t>
-        </is>
-      </c>
-      <c r="S146" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T146" s="3" t="n"/>
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:051020</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>present behaviour as a choice BCT</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>An &lt;increase awareness of behaviour BCT&gt; that presents the behaviour as something the person can decide to do or not, or as one of a set of options.</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr"/>
+      <c r="E146" s="2" t="inlineStr"/>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>increase awareness of behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr"/>
+      <c r="I146" s="2" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr"/>
+      <c r="K146" s="2" t="inlineStr"/>
+      <c r="L146" s="2" t="inlineStr"/>
+      <c r="M146" s="2" t="inlineStr"/>
+      <c r="N146" s="2" t="inlineStr"/>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="P146" s="2" t="inlineStr"/>
+      <c r="Q146" s="2" t="inlineStr"/>
+      <c r="R146" s="2" t="inlineStr"/>
+      <c r="S146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007189</t>
+          <t>BCIO:007075</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for behaviour BCT</t>
+          <t>present information from credible influence BCT</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise consequence for behaviour BCT&gt; where the consequence is aversive.</t>
+          <t>An &lt;awareness of other people's thoughts, feelings and actions BCT&gt; that presents information from a credible person or organisation to influence the behaviour.</t>
         </is>
       </c>
       <c r="D147" s="3" t="n"/>
       <c r="E147" s="3" t="n"/>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>promise consequence for behaviour BCT</t>
+          <t>awareness of other peoples thoughts, feelings and actions BCT</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>BCT10.11 Future punishment</t>
-        </is>
-      </c>
-      <c r="H147" s="3" t="inlineStr">
-        <is>
-          <t>threat, warning, disincentive</t>
-        </is>
-      </c>
+          <t>BCT9.1 Credible source</t>
+        </is>
+      </c>
+      <c r="H147" s="3" t="n"/>
       <c r="I147" s="3" t="n"/>
       <c r="J147" s="3" t="n"/>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>To qualify as aversive, the consequence should be aversively valued by the person receiving it.</t>
+          <t>Code this BCT if influence generally agreed on as credible e.g., health professionals, celebrities or words used to indicate expertise or leader in field and if the communication has the aim of persuading</t>
         </is>
       </c>
       <c r="L147" s="3" t="inlineStr">
@@ -8910,27 +8888,31 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007195</t>
+          <t>BCIO:007189</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for outcome of behaviour BCT</t>
+          <t>promise aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise consequence for outcome of behaviour BCT&gt; where the consequence is aversive.</t>
+          <t>A &lt;promise consequence for behaviour BCT&gt; where the consequence is aversive.</t>
         </is>
       </c>
       <c r="D148" s="3" t="n"/>
       <c r="E148" s="3" t="n"/>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>promise consequence for outcome of behaviour BCT</t>
-        </is>
-      </c>
-      <c r="G148" s="3" t="n"/>
+          <t>promise consequence for behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>BCT10.11 Future punishment</t>
+        </is>
+      </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
           <t>threat, warning, disincentive</t>
@@ -8938,7 +8920,11 @@
       </c>
       <c r="I148" s="3" t="n"/>
       <c r="J148" s="3" t="n"/>
-      <c r="K148" s="3" t="n"/>
+      <c r="K148" s="3" t="inlineStr">
+        <is>
+          <t>To qualify as aversive, the consequence should be aversively valued by the person receiving it.</t>
+        </is>
+      </c>
       <c r="L148" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -8968,30 +8954,30 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007191</t>
+          <t>BCIO:007195</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for situation specific behaviour BCT</t>
+          <t>promise aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise aversive consequence for behaviour BCT&gt; that promises the consequence will be provided for the behaviour in one situation but not in another.</t>
+          <t>A &lt;promise consequence for outcome of behaviour BCT&gt; where the consequence is aversive.</t>
         </is>
       </c>
       <c r="D149" s="3" t="n"/>
       <c r="E149" s="3" t="n"/>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for behaviour BCT</t>
+          <t>promise consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="G149" s="3" t="n"/>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>threat for situation specific behaviour</t>
+          <t>threat, warning, disincentive</t>
         </is>
       </c>
       <c r="I149" s="3" t="n"/>
@@ -9026,17 +9012,17 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007192</t>
+          <t>BCIO:007191</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>promise aversive material consequence for behaviour BCT</t>
+          <t>promise aversive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise aversive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise aversive consequence for behaviour BCT&gt; that promises the consequence will be provided for the behaviour in one situation but not in another.</t>
         </is>
       </c>
       <c r="D150" s="3" t="n"/>
@@ -9049,7 +9035,7 @@
       <c r="G150" s="3" t="n"/>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>material threat</t>
+          <t>threat for situation specific behaviour</t>
         </is>
       </c>
       <c r="I150" s="3" t="n"/>
@@ -9084,28 +9070,32 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007194</t>
+          <t>BCIO:007192</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>promise aversive material consequence for outcome of behaviour</t>
+          <t>promise aversive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise aversive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise aversive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D151" s="3" t="n"/>
       <c r="E151" s="3" t="n"/>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for outcome of behaviour BCT</t>
+          <t>promise aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="G151" s="3" t="n"/>
-      <c r="H151" s="3" t="n"/>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>material threat</t>
+        </is>
+      </c>
       <c r="I151" s="3" t="n"/>
       <c r="J151" s="3" t="n"/>
       <c r="K151" s="3" t="n"/>
@@ -9138,32 +9128,28 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007193</t>
+          <t>BCIO:007194</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>promise aversive material consequence for situation specific behaviour BCT</t>
+          <t>promise aversive material consequence for outcome of behaviour</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise aversive consequence for situation specific behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise aversive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D152" s="3" t="n"/>
       <c r="E152" s="3" t="n"/>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for situation specific behaviour BCT</t>
+          <t>promise aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="G152" s="3" t="n"/>
-      <c r="H152" s="3" t="inlineStr">
-        <is>
-          <t>material threat for situation specific behaviour</t>
-        </is>
-      </c>
+      <c r="H152" s="3" t="n"/>
       <c r="I152" s="3" t="n"/>
       <c r="J152" s="3" t="n"/>
       <c r="K152" s="3" t="n"/>
@@ -9196,39 +9182,35 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007197</t>
+          <t>BCIO:007193</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>promise aversive social consequence for behaviour BCT</t>
+          <t>promise aversive material consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise aversive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise aversive consequence for situation specific behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D153" s="3" t="n"/>
       <c r="E153" s="3" t="n"/>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for behaviour BCT</t>
+          <t>promise aversive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="G153" s="3" t="n"/>
       <c r="H153" s="3" t="inlineStr">
         <is>
-          <t>social threat</t>
+          <t>material threat for situation specific behaviour</t>
         </is>
       </c>
       <c r="I153" s="3" t="n"/>
       <c r="J153" s="3" t="n"/>
-      <c r="K153" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="K153" s="3" t="n"/>
       <c r="L153" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -9258,28 +9240,32 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007199</t>
+          <t>BCIO:007197</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>promise aversive social consequence for outcome of behaviour BCT</t>
+          <t>promise aversive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A &lt;promise aversive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process. </t>
+          <t>A &lt;promise aversive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D154" s="3" t="n"/>
       <c r="E154" s="3" t="n"/>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for outcome of behaviour BCT</t>
+          <t>promise aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="G154" s="3" t="n"/>
-      <c r="H154" s="3" t="n"/>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>social threat</t>
+        </is>
+      </c>
       <c r="I154" s="3" t="n"/>
       <c r="J154" s="3" t="n"/>
       <c r="K154" s="3" t="inlineStr">
@@ -9316,32 +9302,28 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007198</t>
+          <t>BCIO:007199</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>promise aversive social consequence for situation specific behaviour BCT</t>
+          <t>promise aversive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise aversive consequence for situation specific behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t xml:space="preserve">A &lt;promise aversive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process. </t>
         </is>
       </c>
       <c r="D155" s="3" t="n"/>
       <c r="E155" s="3" t="n"/>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for situation specific behaviour BCT</t>
+          <t>promise aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="G155" s="3" t="n"/>
-      <c r="H155" s="3" t="inlineStr">
-        <is>
-          <t>social threat for situation specific behaviour</t>
-        </is>
-      </c>
+      <c r="H155" s="3" t="n"/>
       <c r="I155" s="3" t="n"/>
       <c r="J155" s="3" t="n"/>
       <c r="K155" s="3" t="inlineStr">
@@ -9378,33 +9360,37 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007187</t>
+          <t>BCIO:007198</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>promise consequence for behaviour BCT</t>
+          <t>promise aversive social consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>A &lt;behavioural consequence BCT&gt; that promises a future consequence contingent on performing or not performing the behaviour.</t>
+          <t>A &lt;promise aversive consequence for situation specific behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D156" s="3" t="n"/>
       <c r="E156" s="3" t="n"/>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>behavioural consequence BCT</t>
+          <t>promise aversive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="G156" s="3" t="n"/>
-      <c r="H156" s="3" t="n"/>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>social threat for situation specific behaviour</t>
+        </is>
+      </c>
       <c r="I156" s="3" t="n"/>
       <c r="J156" s="3" t="n"/>
       <c r="K156" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">"promises" here means assuring someone that one will do something or that something will happen.  </t>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
         </is>
       </c>
       <c r="L156" s="3" t="inlineStr">
@@ -9423,7 +9409,7 @@
       <c r="Q156" s="3" t="n"/>
       <c r="R156" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S156" s="3" t="inlineStr">
@@ -9436,24 +9422,24 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007200</t>
+          <t>BCIO:007187</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>promise consequence for outcome of behaviour BCT</t>
+          <t>promise consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">An &lt;outcome consequence BCT&gt; that promises a future consequence contingent on an outcome of performing or not performing the behaviour. </t>
+          <t>A &lt;behavioural consequence BCT&gt; that promises a future consequence contingent on performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D157" s="3" t="n"/>
       <c r="E157" s="3" t="n"/>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>outcome consequence BCT</t>
+          <t>behavioural consequence BCT</t>
         </is>
       </c>
       <c r="G157" s="3" t="n"/>
@@ -9494,35 +9480,35 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007204</t>
+          <t>BCIO:007200</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for alternative behaviour BCT</t>
+          <t>promise consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for behaviour BCT&gt; that promises the consequence will be provided for the behaviour that is different from the unwanted behaviour.</t>
+          <t xml:space="preserve">An &lt;outcome consequence BCT&gt; that promises a future consequence contingent on an outcome of performing or not performing the behaviour. </t>
         </is>
       </c>
       <c r="D158" s="3" t="n"/>
       <c r="E158" s="3" t="n"/>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for behaviour BCT</t>
+          <t>outcome consequence BCT</t>
         </is>
       </c>
       <c r="G158" s="3" t="n"/>
-      <c r="H158" s="3" t="inlineStr">
-        <is>
-          <t>incentive for alternative behaviour</t>
-        </is>
-      </c>
+      <c r="H158" s="3" t="n"/>
       <c r="I158" s="3" t="n"/>
       <c r="J158" s="3" t="n"/>
-      <c r="K158" s="3" t="n"/>
+      <c r="K158" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"promises" here means assuring someone that one will do something or that something will happen.  </t>
+        </is>
+      </c>
       <c r="L158" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -9539,7 +9525,7 @@
       <c r="Q158" s="3" t="n"/>
       <c r="R158" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S158" s="3" t="inlineStr">
@@ -9552,17 +9538,17 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007205</t>
+          <t>BCIO:007204</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for approximating behaviour BCT</t>
+          <t>promise positive consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for behaviour BCT&gt; where the consequence is provided as the performance gradually gets closer to the behaviour.</t>
+          <t>A &lt;promise positive consequence for behaviour BCT&gt; that promises the consequence will be provided for the behaviour that is different from the unwanted behaviour.</t>
         </is>
       </c>
       <c r="D159" s="3" t="n"/>
@@ -9575,7 +9561,7 @@
       <c r="G159" s="3" t="n"/>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>incentive for approximating behaviour</t>
+          <t>incentive for alternative behaviour</t>
         </is>
       </c>
       <c r="I159" s="3" t="n"/>
@@ -9610,43 +9596,35 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007202</t>
+          <t>BCIO:007205</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for behaviour BCT</t>
+          <t>promise positive consequence for approximating behaviour BCT</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise consequence for behaviour BCT&gt; where the consequence is positive.</t>
+          <t>A &lt;promise positive consequence for behaviour BCT&gt; where the consequence is provided as the performance gradually gets closer to the behaviour.</t>
         </is>
       </c>
       <c r="D160" s="3" t="n"/>
       <c r="E160" s="3" t="n"/>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>promise consequence for behaviour BCT</t>
-        </is>
-      </c>
-      <c r="G160" s="3" t="inlineStr">
-        <is>
-          <t>BCT10.6 Non-specific incentive; BCT10.7 Self-incentive</t>
-        </is>
-      </c>
+          <t>promise positive consequence for behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="n"/>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>incentive</t>
+          <t>incentive for approximating behaviour</t>
         </is>
       </c>
       <c r="I160" s="3" t="n"/>
       <c r="J160" s="3" t="n"/>
-      <c r="K160" s="3" t="inlineStr">
-        <is>
-          <t>To qualify as positive, the consequence should be positively valued by the person receiving it. If consequence is delivered, also code 'provide positive consequence for behaviour BCT' or one of its child classes.</t>
-        </is>
-      </c>
+      <c r="K160" s="3" t="n"/>
       <c r="L160" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -9676,35 +9654,43 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007206</t>
+          <t>BCIO:007202</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for completion of behavioural sequence BCT</t>
+          <t>promise positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for behaviour BCT&gt; in which the consequence will be provided for performing the final behaviour in a sequence of behaviours, followed by adding behaviours that occur earlier in the sequence.</t>
+          <t>A &lt;promise consequence for behaviour BCT&gt; where the consequence is positive.</t>
         </is>
       </c>
       <c r="D161" s="3" t="n"/>
       <c r="E161" s="3" t="n"/>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for behaviour BCT</t>
-        </is>
-      </c>
-      <c r="G161" s="3" t="n"/>
+          <t>promise consequence for behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>BCT10.6 Non-specific incentive; BCT10.7 Self-incentive</t>
+        </is>
+      </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
-          <t>incentive for completion of behavioural sequence</t>
+          <t>incentive</t>
         </is>
       </c>
       <c r="I161" s="3" t="n"/>
       <c r="J161" s="3" t="n"/>
-      <c r="K161" s="3" t="n"/>
+      <c r="K161" s="3" t="inlineStr">
+        <is>
+          <t>To qualify as positive, the consequence should be positively valued by the person receiving it. If consequence is delivered, also code 'provide positive consequence for behaviour BCT' or one of its child classes.</t>
+        </is>
+      </c>
       <c r="L161" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -9734,17 +9720,17 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007207</t>
+          <t>BCIO:007206</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for incompatible behaviour BCT</t>
+          <t>promise positive consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for behaviour BCT&gt; that promises the consequence will be provided for the behaviour that is incompatible with the unwanted behaviour.</t>
+          <t>A &lt;promise positive consequence for behaviour BCT&gt; in which the consequence will be provided for performing the final behaviour in a sequence of behaviours, followed by adding behaviours that occur earlier in the sequence.</t>
         </is>
       </c>
       <c r="D162" s="3" t="n"/>
@@ -9757,7 +9743,7 @@
       <c r="G162" s="3" t="n"/>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>incentive for incompatible behaviour</t>
+          <t>incentive for completion of behavioural sequence</t>
         </is>
       </c>
       <c r="I162" s="3" t="n"/>
@@ -9779,7 +9765,7 @@
       <c r="Q162" s="3" t="n"/>
       <c r="R162" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S162" s="3" t="inlineStr">
@@ -9792,34 +9778,30 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007216</t>
+          <t>BCIO:007207</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for outcome of behaviour BCT</t>
+          <t>promise positive consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise consequence for outcome of behaviour BCT&gt; where the consequence is positive</t>
+          <t>A &lt;promise positive consequence for behaviour BCT&gt; that promises the consequence will be provided for the behaviour that is incompatible with the unwanted behaviour.</t>
         </is>
       </c>
       <c r="D163" s="3" t="n"/>
       <c r="E163" s="3" t="n"/>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>promise consequence for outcome of behaviour BCT</t>
-        </is>
-      </c>
-      <c r="G163" s="3" t="inlineStr">
-        <is>
-          <t>BCT10.8 Incentive (outcome)</t>
-        </is>
-      </c>
+          <t>promise positive consequence for behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="n"/>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>incentive</t>
+          <t>incentive for incompatible behaviour</t>
         </is>
       </c>
       <c r="I163" s="3" t="n"/>
@@ -9841,7 +9823,7 @@
       <c r="Q163" s="3" t="n"/>
       <c r="R163" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S163" s="3" t="inlineStr">
@@ -9854,30 +9836,34 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007208</t>
+          <t>BCIO:007216</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for situation specific behaviour BCT</t>
+          <t>promise positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for behaviour BCT&gt; that promises the consequence will be provided for the behaviour in one situation but not in another.</t>
+          <t>A &lt;promise consequence for outcome of behaviour BCT&gt; where the consequence is positive</t>
         </is>
       </c>
       <c r="D164" s="3" t="n"/>
       <c r="E164" s="3" t="n"/>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for behaviour BCT</t>
-        </is>
-      </c>
-      <c r="G164" s="3" t="n"/>
+          <t>promise consequence for outcome of behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>BCT10.8 Incentive (outcome)</t>
+        </is>
+      </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>incentive for situation specific behaviour</t>
+          <t>incentive</t>
         </is>
       </c>
       <c r="I164" s="3" t="n"/>
@@ -9899,7 +9885,7 @@
       <c r="Q164" s="3" t="n"/>
       <c r="R164" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S164" s="3" t="inlineStr">
@@ -9912,30 +9898,30 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007210</t>
+          <t>BCIO:007208</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>promise positive material consequence for alternative behaviour BCT</t>
+          <t>promise positive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for alternative behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise positive consequence for behaviour BCT&gt; that promises the consequence will be provided for the behaviour in one situation but not in another.</t>
         </is>
       </c>
       <c r="D165" s="3" t="n"/>
       <c r="E165" s="3" t="n"/>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for alternative behaviour BCT</t>
+          <t>promise positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="G165" s="3" t="n"/>
       <c r="H165" s="3" t="inlineStr">
         <is>
-          <t>material incentive for alternative behaviour</t>
+          <t>incentive for situation specific behaviour</t>
         </is>
       </c>
       <c r="I165" s="3" t="n"/>
@@ -9970,30 +9956,30 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007211</t>
+          <t>BCIO:007210</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>promise positive material consequence for approximating behaviour BCT</t>
+          <t>promise positive material consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A &lt;promise positive consequence for approximating behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects. </t>
+          <t>A &lt;promise positive consequence for alternative behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D166" s="3" t="n"/>
       <c r="E166" s="3" t="n"/>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for approximating behaviour BCT</t>
+          <t>promise positive consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="G166" s="3" t="n"/>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>material incentive for approximating behaviour</t>
+          <t>material incentive for alternative behaviour</t>
         </is>
       </c>
       <c r="I166" s="3" t="n"/>
@@ -10028,34 +10014,30 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007209</t>
+          <t>BCIO:007211</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>promise positive material consequence for behaviour BCT</t>
+          <t>promise positive material consequence for approximating behaviour BCT</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t xml:space="preserve">A &lt;promise positive consequence for approximating behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects. </t>
         </is>
       </c>
       <c r="D167" s="3" t="n"/>
       <c r="E167" s="3" t="n"/>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for behaviour BCT</t>
-        </is>
-      </c>
-      <c r="G167" s="3" t="inlineStr">
-        <is>
-          <t>BCT10.1 Material incentive (behaviour)</t>
-        </is>
-      </c>
+          <t>promise positive consequence for approximating behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="n"/>
       <c r="H167" s="3" t="inlineStr">
         <is>
-          <t>material incentive</t>
+          <t>material incentive for approximating behaviour</t>
         </is>
       </c>
       <c r="I167" s="3" t="n"/>
@@ -10077,7 +10059,7 @@
       <c r="Q167" s="3" t="n"/>
       <c r="R167" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S167" s="3" t="inlineStr">
@@ -10090,30 +10072,34 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007212</t>
+          <t>BCIO:007209</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>promise positive material consequence for completion of behavioural sequence BCT</t>
+          <t>promise positive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for completion of behavioural sequence BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise positive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D168" s="3" t="n"/>
       <c r="E168" s="3" t="n"/>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for completion of behavioural sequence BCT</t>
-        </is>
-      </c>
-      <c r="G168" s="3" t="n"/>
+          <t>promise positive consequence for behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="inlineStr">
+        <is>
+          <t>BCT10.1 Material incentive (behaviour)</t>
+        </is>
+      </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>material incentive for completion of behavioural sequence</t>
+          <t>material incentive</t>
         </is>
       </c>
       <c r="I168" s="3" t="n"/>
@@ -10135,7 +10121,7 @@
       <c r="Q168" s="3" t="n"/>
       <c r="R168" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S168" s="3" t="inlineStr">
@@ -10148,30 +10134,30 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007213</t>
+          <t>BCIO:007212</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>promise positive material consequence for incompatible behaviour BCT</t>
+          <t>promise positive material consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for incompatible behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise positive consequence for completion of behavioural sequence BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D169" s="3" t="n"/>
       <c r="E169" s="3" t="n"/>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for incompatible behaviour BCT</t>
+          <t>promise positive consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="G169" s="3" t="n"/>
       <c r="H169" s="3" t="inlineStr">
         <is>
-          <t>material incentive for incompatible behaviour</t>
+          <t>material incentive for completion of behavioural sequence</t>
         </is>
       </c>
       <c r="I169" s="3" t="n"/>
@@ -10206,28 +10192,32 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007215</t>
+          <t>BCIO:007213</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>promise positive material consequence for outcome of behaviour BCT</t>
+          <t>promise positive material consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise positive consequence for incompatible behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D170" s="3" t="n"/>
       <c r="E170" s="3" t="n"/>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for outcome of behaviour BCT</t>
+          <t>promise positive consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="G170" s="3" t="n"/>
-      <c r="H170" s="3" t="n"/>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>material incentive for incompatible behaviour</t>
+        </is>
+      </c>
       <c r="I170" s="3" t="n"/>
       <c r="J170" s="3" t="n"/>
       <c r="K170" s="3" t="n"/>
@@ -10260,32 +10250,28 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007214</t>
+          <t>BCIO:007215</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>promise positive material consequence for situation specific behaviour BCT</t>
+          <t>promise positive material consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for situation specific behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise positive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D171" s="3" t="n"/>
       <c r="E171" s="3" t="n"/>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for situation specific behaviour BCT</t>
+          <t>promise positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="G171" s="3" t="n"/>
-      <c r="H171" s="3" t="inlineStr">
-        <is>
-          <t>material incentive for situation specific behaviour</t>
-        </is>
-      </c>
+      <c r="H171" s="3" t="n"/>
       <c r="I171" s="3" t="n"/>
       <c r="J171" s="3" t="n"/>
       <c r="K171" s="3" t="n"/>
@@ -10318,39 +10304,35 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007219</t>
+          <t>BCIO:007214</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>promise positive social consequence for alternative behaviour BCT</t>
+          <t>promise positive material consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for alternative behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise positive consequence for situation specific behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D172" s="3" t="n"/>
       <c r="E172" s="3" t="n"/>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for alternative behaviour BCT</t>
+          <t>promise positive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="G172" s="3" t="n"/>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>social incentive for alternative behaviour</t>
+          <t>material incentive for situation specific behaviour</t>
         </is>
       </c>
       <c r="I172" s="3" t="n"/>
       <c r="J172" s="3" t="n"/>
-      <c r="K172" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="K172" s="3" t="n"/>
       <c r="L172" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -10380,30 +10362,30 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007220</t>
+          <t>BCIO:007219</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>promise positive social consequence for approximating behaviour BCT</t>
+          <t>promise positive social consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for approximating behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise positive consequence for alternative behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D173" s="3" t="n"/>
       <c r="E173" s="3" t="n"/>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for approximating behaviour BCT</t>
+          <t>promise positive consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="G173" s="3" t="n"/>
       <c r="H173" s="3" t="inlineStr">
         <is>
-          <t>social incentive for approximating behaviour</t>
+          <t>social incentive for alternative behaviour</t>
         </is>
       </c>
       <c r="I173" s="3" t="n"/>
@@ -10442,34 +10424,30 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007218</t>
+          <t>BCIO:007220</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>promise positive social consequence for behaviour BCT</t>
+          <t>promise positive social consequence for approximating behaviour BCT</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise positive consequence for approximating behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D174" s="3" t="n"/>
       <c r="E174" s="3" t="n"/>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for behaviour BCT</t>
-        </is>
-      </c>
-      <c r="G174" s="3" t="inlineStr">
-        <is>
-          <t>BCT10.5 Social incentive</t>
-        </is>
-      </c>
+          <t>promise positive consequence for approximating behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G174" s="3" t="n"/>
       <c r="H174" s="3" t="inlineStr">
         <is>
-          <t>social incentive</t>
+          <t>social incentive for approximating behaviour</t>
         </is>
       </c>
       <c r="I174" s="3" t="n"/>
@@ -10495,7 +10473,7 @@
       <c r="Q174" s="3" t="n"/>
       <c r="R174" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S174" s="3" t="inlineStr">
@@ -10508,30 +10486,34 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007221</t>
+          <t>BCIO:007218</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>promise positive social consequence for completion of behavioural sequence BCT</t>
+          <t>promise positive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for completion of behavioural sequence BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise positive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D175" s="3" t="n"/>
       <c r="E175" s="3" t="n"/>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for completion of behavioural sequence BCT</t>
-        </is>
-      </c>
-      <c r="G175" s="3" t="n"/>
+          <t>promise positive consequence for behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G175" s="3" t="inlineStr">
+        <is>
+          <t>BCT10.5 Social incentive</t>
+        </is>
+      </c>
       <c r="H175" s="3" t="inlineStr">
         <is>
-          <t>social incentive for completion of behavioural sequence</t>
+          <t>social incentive</t>
         </is>
       </c>
       <c r="I175" s="3" t="n"/>
@@ -10557,7 +10539,7 @@
       <c r="Q175" s="3" t="n"/>
       <c r="R175" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S175" s="3" t="inlineStr">
@@ -10570,30 +10552,30 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007222</t>
+          <t>BCIO:007221</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>promise positive social consequence for incompatible behaviour BCT</t>
+          <t>promise positive social consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for incompatible behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise positive consequence for completion of behavioural sequence BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D176" s="3" t="n"/>
       <c r="E176" s="3" t="n"/>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for incompatible behaviour BCT</t>
+          <t>promise positive consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="G176" s="3" t="n"/>
       <c r="H176" s="3" t="inlineStr">
         <is>
-          <t>social incentive for incompatible behaviour</t>
+          <t>social incentive for completion of behavioural sequence</t>
         </is>
       </c>
       <c r="I176" s="3" t="n"/>
@@ -10632,28 +10614,32 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007224</t>
+          <t>BCIO:007222</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>promise positive social consequence for outcome of behaviour BCT</t>
+          <t>promise positive social consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A &lt;promise positive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process. </t>
+          <t>A &lt;promise positive consequence for incompatible behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D177" s="3" t="n"/>
       <c r="E177" s="3" t="n"/>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for outcome of behaviour BCT</t>
+          <t>promise positive consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="G177" s="3" t="n"/>
-      <c r="H177" s="3" t="n"/>
+      <c r="H177" s="3" t="inlineStr">
+        <is>
+          <t>social incentive for incompatible behaviour</t>
+        </is>
+      </c>
       <c r="I177" s="3" t="n"/>
       <c r="J177" s="3" t="n"/>
       <c r="K177" s="3" t="inlineStr">
@@ -10690,32 +10676,28 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007223</t>
+          <t>BCIO:007224</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>promise positive social consequence for situation specific behaviour BCT</t>
+          <t>promise positive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for situation specific behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t xml:space="preserve">A &lt;promise positive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process. </t>
         </is>
       </c>
       <c r="D178" s="3" t="n"/>
       <c r="E178" s="3" t="n"/>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for situation specific behaviour BCT</t>
+          <t>promise positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="G178" s="3" t="n"/>
-      <c r="H178" s="3" t="inlineStr">
-        <is>
-          <t>social incentive for situation specific behaviour</t>
-        </is>
-      </c>
+      <c r="H178" s="3" t="n"/>
       <c r="I178" s="3" t="n"/>
       <c r="J178" s="3" t="n"/>
       <c r="K178" s="3" t="inlineStr">
@@ -10752,35 +10734,39 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007225</t>
+          <t>BCIO:007223</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>promise reduced frequency of aversive consequence for behaviour BCT</t>
+          <t>promise positive social consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise positive consequence for behaviour BCT&gt; that promises to provide the consequence at increasingly less frequent intervals.</t>
+          <t>A &lt;promise positive consequence for situation specific behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D179" s="3" t="n"/>
       <c r="E179" s="3" t="n"/>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>promise positive consequence for behaviour BCT</t>
+          <t>promise positive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="G179" s="3" t="n"/>
       <c r="H179" s="3" t="inlineStr">
         <is>
-          <t>reduce threat frequency</t>
+          <t>social incentive for situation specific behaviour</t>
         </is>
       </c>
       <c r="I179" s="3" t="n"/>
       <c r="J179" s="3" t="n"/>
-      <c r="K179" s="3" t="n"/>
+      <c r="K179" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="L179" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -10797,7 +10783,7 @@
       <c r="Q179" s="3" t="n"/>
       <c r="R179" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S179" s="3" t="inlineStr">
@@ -10810,30 +10796,30 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007226</t>
+          <t>BCIO:007225</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>promise reduced frequency of aversive material consequence for behaviour BCT</t>
+          <t>promise reduced frequency of aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise reduced frequency of aversive consequence for behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise positive consequence for behaviour BCT&gt; that promises to provide the consequence at increasingly less frequent intervals.</t>
         </is>
       </c>
       <c r="D180" s="3" t="n"/>
       <c r="E180" s="3" t="n"/>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>promise reduced frequency of aversive consequence for behaviour BCT</t>
+          <t>promise positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="G180" s="3" t="n"/>
       <c r="H180" s="3" t="inlineStr">
         <is>
-          <t>reduce material threat frequency</t>
+          <t>reduce threat frequency</t>
         </is>
       </c>
       <c r="I180" s="3" t="n"/>
@@ -10868,17 +10854,17 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007227</t>
+          <t>BCIO:007226</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>promise reduced frequency of aversive social consequence for behaviour BCT</t>
+          <t>promise reduced frequency of aversive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise reduced frequency of aversive consequence for behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise reduced frequency of aversive consequence for behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D181" s="3" t="n"/>
@@ -10891,16 +10877,12 @@
       <c r="G181" s="3" t="n"/>
       <c r="H181" s="3" t="inlineStr">
         <is>
-          <t>reduce social threat frequency</t>
+          <t>reduce material threat frequency</t>
         </is>
       </c>
       <c r="I181" s="3" t="n"/>
       <c r="J181" s="3" t="n"/>
-      <c r="K181" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="K181" s="3" t="n"/>
       <c r="L181" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -10930,35 +10912,39 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007228</t>
+          <t>BCIO:007227</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>promise reduced frequency of positive consequence for behaviour BCT</t>
+          <t>promise reduced frequency of aversive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise aversive consequence for behaviour BCT&gt; that promises to provide the consequence at increasingly less frequent intervals.</t>
+          <t>A &lt;promise reduced frequency of aversive consequence for behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D182" s="3" t="n"/>
       <c r="E182" s="3" t="n"/>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>promise aversive consequence for outcome of behaviour BCT</t>
+          <t>promise reduced frequency of aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="G182" s="3" t="n"/>
       <c r="H182" s="3" t="inlineStr">
         <is>
-          <t>reduce incentive frequency</t>
+          <t>reduce social threat frequency</t>
         </is>
       </c>
       <c r="I182" s="3" t="n"/>
       <c r="J182" s="3" t="n"/>
-      <c r="K182" s="3" t="n"/>
+      <c r="K182" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="L182" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -10975,7 +10961,7 @@
       <c r="Q182" s="3" t="n"/>
       <c r="R182" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S182" s="3" t="inlineStr">
@@ -10988,30 +10974,30 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007229</t>
+          <t>BCIO:007228</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>promise reduced frequency of positive material consequence for behaviour BCT</t>
+          <t>promise reduced frequency of positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise reduced frequency of positive consequence for behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise aversive consequence for behaviour BCT&gt; that promises to provide the consequence at increasingly less frequent intervals.</t>
         </is>
       </c>
       <c r="D183" s="3" t="n"/>
       <c r="E183" s="3" t="n"/>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>promise reduced frequency of positive consequence for behaviour BCT</t>
+          <t>promise aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="G183" s="3" t="n"/>
       <c r="H183" s="3" t="inlineStr">
         <is>
-          <t>reduce material incentive frequency</t>
+          <t>reduce incentive frequency</t>
         </is>
       </c>
       <c r="I183" s="3" t="n"/>
@@ -11046,17 +11032,17 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007230</t>
+          <t>BCIO:007229</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>promise reduced frequency of positive social consequence for behaviour BCT</t>
+          <t>promise reduced frequency of positive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise reduced frequency of positive consequence for behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise reduced frequency of positive consequence for behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D184" s="3" t="n"/>
@@ -11069,16 +11055,12 @@
       <c r="G184" s="3" t="n"/>
       <c r="H184" s="3" t="inlineStr">
         <is>
-          <t>reduce social incentive frequency</t>
+          <t>reduce material incentive frequency</t>
         </is>
       </c>
       <c r="I184" s="3" t="n"/>
       <c r="J184" s="3" t="n"/>
-      <c r="K184" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="K184" s="3" t="n"/>
       <c r="L184" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -11108,35 +11090,39 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007190</t>
+          <t>BCIO:007230</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive consequence for behaviour BCT</t>
+          <t>promise reduced frequency of positive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove consequence for behaviour BCT&gt; where the consequence is aversive.</t>
+          <t>A &lt;promise reduced frequency of positive consequence for behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D185" s="3" t="n"/>
       <c r="E185" s="3" t="n"/>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>promise to remove consequence for behaviour BCT</t>
+          <t>promise reduced frequency of positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="G185" s="3" t="n"/>
       <c r="H185" s="3" t="inlineStr">
         <is>
-          <t>incentive to remove punishment</t>
+          <t>reduce social incentive frequency</t>
         </is>
       </c>
       <c r="I185" s="3" t="n"/>
       <c r="J185" s="3" t="n"/>
-      <c r="K185" s="3" t="n"/>
+      <c r="K185" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="L185" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -11153,7 +11139,7 @@
       <c r="Q185" s="3" t="n"/>
       <c r="R185" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S185" s="3" t="inlineStr">
@@ -11166,24 +11152,24 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007196</t>
+          <t>BCIO:007190</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive consequence for outcome of behaviour BCT</t>
+          <t>promise to remove aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove consequence for outcome of behaviour BCT&gt; where the consequence is aversive.</t>
+          <t>A &lt;promise to remove consequence for behaviour BCT&gt; where the consequence is aversive.</t>
         </is>
       </c>
       <c r="D186" s="3" t="n"/>
       <c r="E186" s="3" t="n"/>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>promise to remove consequence for outcome of behaviour BCT</t>
+          <t>promise to remove consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="G186" s="3" t="n"/>
@@ -11224,30 +11210,30 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007231</t>
+          <t>BCIO:007196</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive material consequence for behaviour BCT</t>
+          <t>promise to remove aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove aversive consequence for behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise to remove consequence for outcome of behaviour BCT&gt; where the consequence is aversive.</t>
         </is>
       </c>
       <c r="D187" s="3" t="n"/>
       <c r="E187" s="3" t="n"/>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive consequence for behaviour BCT</t>
+          <t>promise to remove consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="G187" s="3" t="n"/>
       <c r="H187" s="3" t="inlineStr">
         <is>
-          <t>incentive to remove material punishment</t>
+          <t>incentive to remove punishment</t>
         </is>
       </c>
       <c r="I187" s="3" t="n"/>
@@ -11282,24 +11268,24 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007232</t>
+          <t>BCIO:007231</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive material consequence for outcome of behaviour BCT</t>
+          <t>promise to remove aversive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove aversive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise to remove aversive consequence for behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D188" s="3" t="n"/>
       <c r="E188" s="3" t="n"/>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive consequence for outcome of behaviour BCT</t>
+          <t>promise to remove aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="G188" s="3" t="n"/>
@@ -11340,39 +11326,35 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007233</t>
+          <t>BCIO:007232</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive social consequence for behaviour BCT</t>
+          <t>promise to remove aversive material consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove aversive consequence for behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process</t>
+          <t>A &lt;promise to remove aversive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D189" s="3" t="n"/>
       <c r="E189" s="3" t="n"/>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive consequence for behaviour BCT</t>
+          <t>promise to remove aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="G189" s="3" t="n"/>
       <c r="H189" s="3" t="inlineStr">
         <is>
-          <t>incentive to remove social punishment</t>
+          <t>incentive to remove material punishment</t>
         </is>
       </c>
       <c r="I189" s="3" t="n"/>
       <c r="J189" s="3" t="n"/>
-      <c r="K189" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="K189" s="3" t="n"/>
       <c r="L189" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -11402,24 +11384,24 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007234</t>
+          <t>BCIO:007233</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive social consequence for outcome of behaviour BCT</t>
+          <t>promise to remove aversive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove aversive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise to remove aversive consequence for behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process</t>
         </is>
       </c>
       <c r="D190" s="3" t="n"/>
       <c r="E190" s="3" t="n"/>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>promise to remove aversive consequence for outcome of behaviour BCT</t>
+          <t>promise to remove aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="G190" s="3" t="n"/>
@@ -11464,31 +11446,39 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007188</t>
+          <t>BCIO:007234</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>promise to remove consequence for behaviour BCT</t>
+          <t>promise to remove aversive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>A &lt;behavioural consequence BCT&gt; that promises future removal of a consequence contingent on performing or not performing the behaviour.</t>
+          <t>A &lt;promise to remove aversive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D191" s="3" t="n"/>
       <c r="E191" s="3" t="n"/>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>behavioural consequence BCT</t>
+          <t>promise to remove aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="G191" s="3" t="n"/>
-      <c r="H191" s="3" t="n"/>
+      <c r="H191" s="3" t="inlineStr">
+        <is>
+          <t>incentive to remove social punishment</t>
+        </is>
+      </c>
       <c r="I191" s="3" t="n"/>
       <c r="J191" s="3" t="n"/>
-      <c r="K191" s="3" t="n"/>
+      <c r="K191" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="L191" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -11505,7 +11495,7 @@
       <c r="Q191" s="3" t="n"/>
       <c r="R191" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S191" s="3" t="inlineStr">
@@ -11518,24 +11508,24 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007201</t>
+          <t>BCIO:007188</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>promise to remove consequence for outcome of behaviour BCT</t>
+          <t>promise to remove consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>An &lt;outcome consequence BCT&gt; that promises future removal of a consequence contingent on an outcome of performing or not performing the behaviour.</t>
+          <t>A &lt;behavioural consequence BCT&gt; that promises future removal of a consequence contingent on performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D192" s="3" t="n"/>
       <c r="E192" s="3" t="n"/>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>outcome consequence BCT</t>
+          <t>behavioural consequence BCT</t>
         </is>
       </c>
       <c r="G192" s="3" t="n"/>
@@ -11572,36 +11562,28 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007203</t>
+          <t>BCIO:007201</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive consequence for behaviour BCT</t>
+          <t>promise to remove consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove consequence for behaviour BCT&gt; where the consequence is positive.</t>
+          <t>An &lt;outcome consequence BCT&gt; that promises future removal of a consequence contingent on an outcome of performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D193" s="3" t="n"/>
       <c r="E193" s="3" t="n"/>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>promise to remove consequence for behaviour BCT</t>
-        </is>
-      </c>
-      <c r="G193" s="3" t="inlineStr">
-        <is>
-          <t>BCT10.11 Future punishment</t>
-        </is>
-      </c>
-      <c r="H193" s="3" t="inlineStr">
-        <is>
-          <t>threaten to remove reward</t>
-        </is>
-      </c>
+          <t>outcome consequence BCT</t>
+        </is>
+      </c>
+      <c r="G193" s="3" t="n"/>
+      <c r="H193" s="3" t="n"/>
       <c r="I193" s="3" t="n"/>
       <c r="J193" s="3" t="n"/>
       <c r="K193" s="3" t="n"/>
@@ -11634,27 +11616,31 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007217</t>
+          <t>BCIO:007203</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive consequence for outcome of behaviour BCT</t>
+          <t>promise to remove positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove consequence for outcome of behaviour BCT&gt; where the consequence is positive.</t>
+          <t>A &lt;promise to remove consequence for behaviour BCT&gt; where the consequence is positive.</t>
         </is>
       </c>
       <c r="D194" s="3" t="n"/>
       <c r="E194" s="3" t="n"/>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>promise to remove consequence for outcome of behaviour BCT</t>
-        </is>
-      </c>
-      <c r="G194" s="3" t="n"/>
+          <t>promise to remove consequence for behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="inlineStr">
+        <is>
+          <t>BCT10.11 Future punishment</t>
+        </is>
+      </c>
       <c r="H194" s="3" t="inlineStr">
         <is>
           <t>threaten to remove reward</t>
@@ -11692,30 +11678,30 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007235</t>
+          <t>BCIO:007217</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive material consequence for behaviour BCT</t>
+          <t>promise to remove positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove positive consequence for behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise to remove consequence for outcome of behaviour BCT&gt; where the consequence is positive.</t>
         </is>
       </c>
       <c r="D195" s="3" t="n"/>
       <c r="E195" s="3" t="n"/>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive consequence for behaviour BCT</t>
+          <t>promise to remove consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="G195" s="3" t="n"/>
       <c r="H195" s="3" t="inlineStr">
         <is>
-          <t>threaten to remove material reward</t>
+          <t>threaten to remove reward</t>
         </is>
       </c>
       <c r="I195" s="3" t="n"/>
@@ -11750,24 +11736,24 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007236</t>
+          <t>BCIO:007235</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive material consequence for outcome of behaviour BCT</t>
+          <t>promise to remove positive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove positive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;promise to remove positive consequence for behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D196" s="3" t="n"/>
       <c r="E196" s="3" t="n"/>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive consequence for outcome of behaviour BCT</t>
+          <t>promise to remove positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="G196" s="3" t="n"/>
@@ -11808,39 +11794,35 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007237</t>
+          <t>BCIO:007236</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive social consequence for behaviour BCT</t>
+          <t>promise to remove positive material consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove positive consequence for behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process</t>
+          <t>A &lt;promise to remove positive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D197" s="3" t="n"/>
       <c r="E197" s="3" t="n"/>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive consequence for behaviour BCT</t>
+          <t>promise to remove positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="G197" s="3" t="n"/>
       <c r="H197" s="3" t="inlineStr">
         <is>
-          <t>threaten to remove social reward</t>
+          <t>threaten to remove material reward</t>
         </is>
       </c>
       <c r="I197" s="3" t="n"/>
       <c r="J197" s="3" t="n"/>
-      <c r="K197" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="K197" s="3" t="n"/>
       <c r="L197" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -11870,24 +11852,24 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007238</t>
+          <t>BCIO:007237</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive social consequence for outcome of behaviour BCT</t>
+          <t>promise to remove positive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promise to remove positive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;promise to remove positive consequence for behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process</t>
         </is>
       </c>
       <c r="D198" s="3" t="n"/>
       <c r="E198" s="3" t="n"/>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>promise to remove positive consequence for outcome of behaviour BCT</t>
+          <t>promise to remove positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="G198" s="3" t="n"/>
@@ -11932,37 +11914,37 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007144</t>
+          <t>BCIO:007238</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>promote pharmacological support BCT</t>
+          <t>promise to remove positive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>A &lt;behaviour change technique&gt; promoting medicines or other drugs.</t>
+          <t>A &lt;promise to remove positive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D199" s="3" t="n"/>
       <c r="E199" s="3" t="n"/>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>behaviour change technique</t>
-        </is>
-      </c>
-      <c r="G199" s="3" t="inlineStr">
-        <is>
-          <t>BCT11.1 Pharmacological support</t>
-        </is>
-      </c>
-      <c r="H199" s="3" t="n"/>
+          <t>promise to remove positive consequence for outcome of behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G199" s="3" t="n"/>
+      <c r="H199" s="3" t="inlineStr">
+        <is>
+          <t>threaten to remove social reward</t>
+        </is>
+      </c>
       <c r="I199" s="3" t="n"/>
       <c r="J199" s="3" t="n"/>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>If pharmacological support to reduce negative emotions (i.e. anxiety) then also code 'advise how to reduce negative emotions BCT'</t>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
         </is>
       </c>
       <c r="L199" s="3" t="inlineStr">
@@ -11981,7 +11963,7 @@
       <c r="Q199" s="3" t="n"/>
       <c r="R199" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S199" s="3" t="inlineStr">
@@ -11994,39 +11976,39 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007070</t>
+          <t>BCIO:007144</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>prompt comparative imagining of future outcomes BCT</t>
+          <t>promote pharmacological support BCT</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>An &lt;increase awareness of consequences BCT&gt; that guides the person to imagine and compare the consequences of performing and not performing the behaviour.</t>
+          <t>A &lt;behaviour change technique&gt; promoting medicines or other drugs.</t>
         </is>
       </c>
       <c r="D200" s="3" t="n"/>
       <c r="E200" s="3" t="n"/>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>increase awareness of consequences BCT</t>
+          <t>behaviour change technique</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>BCT9.3 Comparative imagining of future outcomes</t>
-        </is>
-      </c>
-      <c r="H200" s="3" t="inlineStr">
-        <is>
-          <t>imagining future results</t>
-        </is>
-      </c>
+          <t>BCT11.1 Pharmacological support</t>
+        </is>
+      </c>
+      <c r="H200" s="3" t="n"/>
       <c r="I200" s="3" t="n"/>
       <c r="J200" s="3" t="n"/>
-      <c r="K200" s="3" t="n"/>
+      <c r="K200" s="3" t="inlineStr">
+        <is>
+          <t>If pharmacological support to reduce negative emotions (i.e. anxiety) then also code 'advise how to reduce negative emotions BCT'</t>
+        </is>
+      </c>
       <c r="L200" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -12056,32 +12038,36 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007139</t>
+          <t>BCIO:007070</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>prompt focus on past success BCT</t>
+          <t>prompt comparative imagining of future outcomes BCT</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>A &lt;prompt thinking related to successful performance BCT&gt; that prompts the person to think about previous successful performance of the behaviour.</t>
+          <t>An &lt;increase awareness of consequences BCT&gt; that guides the person to imagine and compare the consequences of performing and not performing the behaviour.</t>
         </is>
       </c>
       <c r="D201" s="3" t="n"/>
       <c r="E201" s="3" t="n"/>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>prompt thinking related to successful performance BCT</t>
+          <t>increase awareness of consequences BCT</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>BCT15.3 Focus on past success</t>
-        </is>
-      </c>
-      <c r="H201" s="3" t="n"/>
+          <t>BCT9.3 Comparative imagining of future outcomes</t>
+        </is>
+      </c>
+      <c r="H201" s="3" t="inlineStr">
+        <is>
+          <t>imagining future results</t>
+        </is>
+      </c>
       <c r="I201" s="3" t="n"/>
       <c r="J201" s="3" t="n"/>
       <c r="K201" s="3" t="n"/>
@@ -12101,7 +12087,7 @@
       <c r="Q201" s="3" t="n"/>
       <c r="R201" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S201" s="3" t="inlineStr">
@@ -12114,32 +12100,32 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007157</t>
+          <t>BCIO:007139</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>prompt focus on self-identity BCT</t>
+          <t>prompt focus on past success BCT</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A &lt;behaviour change technique&gt; that prompts the person to focus on their mental representation of themself. </t>
+          <t>A &lt;prompt thinking related to successful performance BCT&gt; that prompts the person to think about previous successful performance of the behaviour.</t>
         </is>
       </c>
       <c r="D202" s="3" t="n"/>
       <c r="E202" s="3" t="n"/>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>behaviour change technique</t>
-        </is>
-      </c>
-      <c r="G202" s="3" t="n"/>
-      <c r="H202" s="3" t="inlineStr">
-        <is>
-          <t>self-perception</t>
-        </is>
-      </c>
+          <t>prompt thinking related to successful performance BCT</t>
+        </is>
+      </c>
+      <c r="G202" s="3" t="inlineStr">
+        <is>
+          <t>BCT15.3 Focus on past success</t>
+        </is>
+      </c>
+      <c r="H202" s="3" t="n"/>
       <c r="I202" s="3" t="n"/>
       <c r="J202" s="3" t="n"/>
       <c r="K202" s="3" t="n"/>
@@ -12159,158 +12145,158 @@
       <c r="Q202" s="3" t="n"/>
       <c r="R202" s="3" t="inlineStr">
         <is>
+          <t>LZ</t>
+        </is>
+      </c>
+      <c r="S202" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T202" s="3" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:007157</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>prompt focus on self-identity BCT</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A &lt;behaviour change technique&gt; that prompts the person to focus on their mental representation of themself. </t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="n"/>
+      <c r="E203" s="3" t="n"/>
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="G203" s="3" t="n"/>
+      <c r="H203" s="3" t="inlineStr">
+        <is>
+          <t>self-perception</t>
+        </is>
+      </c>
+      <c r="I203" s="3" t="n"/>
+      <c r="J203" s="3" t="n"/>
+      <c r="K203" s="3" t="n"/>
+      <c r="L203" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="M203" s="3" t="n"/>
+      <c r="N203" s="3" t="n"/>
+      <c r="O203" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="P203" s="3" t="n"/>
+      <c r="Q203" s="3" t="n"/>
+      <c r="R203" s="3" t="inlineStr">
+        <is>
           <t>lz; LZ</t>
         </is>
       </c>
-      <c r="S202" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T202" s="3" t="n"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
+      <c r="S203" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T203" s="3" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>BCIO:050992</t>
         </is>
       </c>
-      <c r="B203" s="2" t="inlineStr">
+      <c r="B204" s="2" t="inlineStr">
         <is>
           <t>prompt immediate action BCT</t>
         </is>
       </c>
-      <c r="C203" s="2" t="inlineStr">
+      <c r="C204" s="2" t="inlineStr">
         <is>
           <t>An &lt;increase awareness of behaviour BCT&gt; that advises, reminds or directs the person to do the behaviour without delay.</t>
         </is>
       </c>
-      <c r="D203" s="2" t="n"/>
-      <c r="E203" s="2" t="n"/>
-      <c r="F203" s="2" t="inlineStr">
+      <c r="D204" s="2" t="n"/>
+      <c r="E204" s="2" t="n"/>
+      <c r="F204" s="2" t="inlineStr">
         <is>
           <t>increase awareness of behaviour BCT</t>
         </is>
       </c>
-      <c r="G203" s="2" t="n"/>
-      <c r="H203" s="2" t="n"/>
-      <c r="I203" s="2" t="n"/>
-      <c r="J203" s="2" t="n"/>
-      <c r="K203" s="2" t="n"/>
-      <c r="L203" s="2" t="n"/>
-      <c r="M203" s="2" t="n"/>
-      <c r="N203" s="2" t="n"/>
-      <c r="O203" s="2" t="inlineStr">
+      <c r="G204" s="2" t="n"/>
+      <c r="H204" s="2" t="n"/>
+      <c r="I204" s="2" t="n"/>
+      <c r="J204" s="2" t="n"/>
+      <c r="K204" s="2" t="n"/>
+      <c r="L204" s="2" t="n"/>
+      <c r="M204" s="2" t="n"/>
+      <c r="N204" s="2" t="n"/>
+      <c r="O204" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="P203" s="2" t="n"/>
-      <c r="Q203" s="2" t="n"/>
-      <c r="R203" s="2" t="n"/>
-      <c r="S203" s="2" t="n">
+      <c r="P204" s="2" t="n"/>
+      <c r="Q204" s="2" t="n"/>
+      <c r="R204" s="2" t="n"/>
+      <c r="S204" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T203" s="2" t="n"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="3" t="inlineStr">
-        <is>
-          <t>BCIO:007080</t>
-        </is>
-      </c>
-      <c r="B204" s="3" t="inlineStr">
-        <is>
-          <t>prompt intended action BCT</t>
-        </is>
-      </c>
-      <c r="C204" s="3" t="inlineStr">
-        <is>
-          <t>An &lt;alter external stimulus BCT&gt; that involves introducing an external stimulus to facilitate the behaviour for which an intention has previously been formed.</t>
-        </is>
-      </c>
-      <c r="D204" s="3" t="n"/>
-      <c r="E204" s="3" t="n"/>
-      <c r="F204" s="3" t="inlineStr">
-        <is>
-          <t>alter external stimulus BCT</t>
-        </is>
-      </c>
-      <c r="G204" s="3" t="inlineStr">
-        <is>
-          <t>BCT7.1 Prompts/cues</t>
-        </is>
-      </c>
-      <c r="H204" s="3" t="inlineStr">
-        <is>
-          <t>prompts</t>
-        </is>
-      </c>
-      <c r="I204" s="3" t="n"/>
-      <c r="J204" s="3" t="n"/>
-      <c r="K204" s="3" t="inlineStr">
-        <is>
-          <t>When a stimulus is linked to a specific action in an if-then plan including one or more of frequency, duration or intensity also code 'action planning BCT'</t>
-        </is>
-      </c>
-      <c r="L204" s="3" t="inlineStr">
-        <is>
-          <t>behaviour change technique</t>
-        </is>
-      </c>
-      <c r="M204" s="3" t="n"/>
-      <c r="N204" s="3" t="n"/>
-      <c r="O204" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="P204" s="3" t="n"/>
-      <c r="Q204" s="3" t="n"/>
-      <c r="R204" s="3" t="inlineStr">
-        <is>
-          <t>lz; LZ</t>
-        </is>
-      </c>
-      <c r="S204" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T204" s="3" t="n"/>
+      <c r="T204" s="2" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007138</t>
+          <t>BCIO:007080</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>prompt mental rehearsal of successful performance BCT</t>
+          <t>prompt intended action BCT</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>A &lt;prompt thinking related to successful performance BCT&gt; that prompts the person to practise imagining performing the behaviour well in a relevant context.</t>
+          <t>An &lt;alter external stimulus BCT&gt; that involves introducing an external stimulus to facilitate the behaviour for which an intention has previously been formed.</t>
         </is>
       </c>
       <c r="D205" s="3" t="n"/>
       <c r="E205" s="3" t="n"/>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>prompt thinking related to successful performance BCT</t>
+          <t>alter external stimulus BCT</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>BCT15.2 Mental rehearsal of successful performance</t>
-        </is>
-      </c>
-      <c r="H205" s="3" t="n"/>
+          <t>BCT7.1 Prompts/cues</t>
+        </is>
+      </c>
+      <c r="H205" s="3" t="inlineStr">
+        <is>
+          <t>prompts</t>
+        </is>
+      </c>
       <c r="I205" s="3" t="n"/>
       <c r="J205" s="3" t="n"/>
-      <c r="K205" s="3" t="n"/>
+      <c r="K205" s="3" t="inlineStr">
+        <is>
+          <t>When a stimulus is linked to a specific action in an if-then plan including one or more of frequency, duration or intensity also code 'action planning BCT'</t>
+        </is>
+      </c>
       <c r="L205" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -12327,7 +12313,7 @@
       <c r="Q205" s="3" t="n"/>
       <c r="R205" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S205" s="3" t="inlineStr">
@@ -12340,17 +12326,17 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007140</t>
+          <t>BCIO:007138</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>prompt self-talk BCT</t>
+          <t>prompt mental rehearsal of successful performance BCT</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A &lt;prompt thinking related to successful performance BCT&gt; that promotes the use of positive self-talk before or during the behaviour. </t>
+          <t>A &lt;prompt thinking related to successful performance BCT&gt; that prompts the person to practise imagining performing the behaviour well in a relevant context.</t>
         </is>
       </c>
       <c r="D206" s="3" t="n"/>
@@ -12362,17 +12348,13 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>BCT15.4 Self-talk</t>
+          <t>BCT15.2 Mental rehearsal of successful performance</t>
         </is>
       </c>
       <c r="H206" s="3" t="n"/>
       <c r="I206" s="3" t="n"/>
       <c r="J206" s="3" t="n"/>
-      <c r="K206" s="3" t="inlineStr">
-        <is>
-          <t>Self-talk could be about the behaviour or the context of the behaviour. Self-talk does not need to be spoken aloud</t>
-        </is>
-      </c>
+      <c r="K206" s="3" t="n"/>
       <c r="L206" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -12402,41 +12384,37 @@
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007073</t>
+          <t>BCIO:007140</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">prompt social comparison BCT </t>
+          <t>prompt self-talk BCT</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>An &lt;awareness of other people's thoughts, feelings and actions BCT&gt; that draws attention to other people's behaviour and compares it with the person's own behaviour.</t>
+          <t xml:space="preserve">A &lt;prompt thinking related to successful performance BCT&gt; that promotes the use of positive self-talk before or during the behaviour. </t>
         </is>
       </c>
       <c r="D207" s="3" t="n"/>
       <c r="E207" s="3" t="n"/>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>awareness of other peoples thoughts, feelings and actions BCT</t>
+          <t>prompt thinking related to successful performance BCT</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>BCT6.2 Social comparison</t>
-        </is>
-      </c>
-      <c r="H207" s="3" t="inlineStr">
-        <is>
-          <t>social comparison</t>
-        </is>
-      </c>
+          <t>BCT15.4 Self-talk</t>
+        </is>
+      </c>
+      <c r="H207" s="3" t="n"/>
       <c r="I207" s="3" t="n"/>
       <c r="J207" s="3" t="n"/>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Being in a group setting does not necessarily mean that social comparison is actually taking place </t>
+          <t>Self-talk could be about the behaviour or the context of the behaviour. Self-talk does not need to be spoken aloud</t>
         </is>
       </c>
       <c r="L207" s="3" t="inlineStr">
@@ -12455,7 +12433,7 @@
       <c r="Q207" s="3" t="n"/>
       <c r="R207" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S207" s="3" t="inlineStr">
@@ -12468,31 +12446,43 @@
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007239</t>
+          <t>BCIO:007073</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>prompt thinking related to successful performance BCT</t>
+          <t xml:space="preserve">prompt social comparison BCT </t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>A &lt;behaviour change technique&gt; that prompts thinking relating to successful performance of the behaviour.</t>
+          <t>An &lt;awareness of other people's thoughts, feelings and actions BCT&gt; that draws attention to other people's behaviour and compares it with the person's own behaviour.</t>
         </is>
       </c>
       <c r="D208" s="3" t="n"/>
       <c r="E208" s="3" t="n"/>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>behaviour change technique</t>
-        </is>
-      </c>
-      <c r="G208" s="3" t="n"/>
-      <c r="H208" s="3" t="n"/>
+          <t>awareness of other peoples thoughts, feelings and actions BCT</t>
+        </is>
+      </c>
+      <c r="G208" s="3" t="inlineStr">
+        <is>
+          <t>BCT6.2 Social comparison</t>
+        </is>
+      </c>
+      <c r="H208" s="3" t="inlineStr">
+        <is>
+          <t>social comparison</t>
+        </is>
+      </c>
       <c r="I208" s="3" t="n"/>
       <c r="J208" s="3" t="n"/>
-      <c r="K208" s="3" t="n"/>
+      <c r="K208" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Being in a group setting does not necessarily mean that social comparison is actually taking place </t>
+        </is>
+      </c>
       <c r="L208" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -12509,150 +12499,142 @@
       <c r="Q208" s="3" t="n"/>
       <c r="R208" s="3" t="inlineStr">
         <is>
+          <t>lz; LZ</t>
+        </is>
+      </c>
+      <c r="S208" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T208" s="3" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:007239</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>prompt thinking related to successful performance BCT</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>A &lt;behaviour change technique&gt; that prompts thinking relating to successful performance of the behaviour.</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="n"/>
+      <c r="E209" s="3" t="n"/>
+      <c r="F209" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="G209" s="3" t="n"/>
+      <c r="H209" s="3" t="n"/>
+      <c r="I209" s="3" t="n"/>
+      <c r="J209" s="3" t="n"/>
+      <c r="K209" s="3" t="n"/>
+      <c r="L209" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="M209" s="3" t="n"/>
+      <c r="N209" s="3" t="n"/>
+      <c r="O209" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="P209" s="3" t="n"/>
+      <c r="Q209" s="3" t="n"/>
+      <c r="R209" s="3" t="inlineStr">
+        <is>
           <t>LZ</t>
         </is>
       </c>
-      <c r="S208" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T208" s="3" t="n"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
+      <c r="S209" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T209" s="3" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
         <is>
           <t>BCIO:050993</t>
         </is>
       </c>
-      <c r="B209" s="2" t="inlineStr">
+      <c r="B210" s="2" t="inlineStr">
         <is>
           <t>protect time to perform behaviour BCT</t>
         </is>
       </c>
-      <c r="C209" s="2" t="inlineStr">
+      <c r="C210" s="2" t="inlineStr">
         <is>
           <t>A &lt;restructure the physical environment BCT&gt; that allocates a period of time to do the behaviour without competing with other behaviours.</t>
         </is>
       </c>
-      <c r="D209" s="2" t="n"/>
-      <c r="E209" s="2" t="n"/>
-      <c r="F209" s="2" t="inlineStr">
+      <c r="D210" s="2" t="n"/>
+      <c r="E210" s="2" t="n"/>
+      <c r="F210" s="2" t="inlineStr">
         <is>
           <t>restructure the physical environment BCT</t>
         </is>
       </c>
-      <c r="G209" s="2" t="n"/>
-      <c r="H209" s="2" t="n"/>
-      <c r="I209" s="2" t="n"/>
-      <c r="J209" s="2" t="n"/>
-      <c r="K209" s="2" t="n"/>
-      <c r="L209" s="2" t="n"/>
-      <c r="M209" s="2" t="n"/>
-      <c r="N209" s="2" t="n"/>
-      <c r="O209" s="2" t="inlineStr">
+      <c r="G210" s="2" t="n"/>
+      <c r="H210" s="2" t="n"/>
+      <c r="I210" s="2" t="n"/>
+      <c r="J210" s="2" t="n"/>
+      <c r="K210" s="2" t="n"/>
+      <c r="L210" s="2" t="n"/>
+      <c r="M210" s="2" t="n"/>
+      <c r="N210" s="2" t="n"/>
+      <c r="O210" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="P209" s="2" t="n"/>
-      <c r="Q209" s="2" t="n"/>
-      <c r="R209" s="2" t="n"/>
-      <c r="S209" s="2" t="n">
+      <c r="P210" s="2" t="n"/>
+      <c r="Q210" s="2" t="n"/>
+      <c r="R210" s="2" t="n"/>
+      <c r="S210" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T209" s="2" t="n"/>
-    </row>
-    <row r="210">
-      <c r="A210" s="3" t="inlineStr">
-        <is>
-          <t>BCIO:007241</t>
-        </is>
-      </c>
-      <c r="B210" s="3" t="inlineStr">
-        <is>
-          <t>provide aversive consequence for behaviour BCT</t>
-        </is>
-      </c>
-      <c r="C210" s="3" t="inlineStr">
-        <is>
-          <t>A &lt;provide consequence for behaviour BCT&gt; where the consequence is aversive.</t>
-        </is>
-      </c>
-      <c r="D210" s="3" t="n"/>
-      <c r="E210" s="3" t="n"/>
-      <c r="F210" s="3" t="inlineStr">
-        <is>
-          <t>provide consequence for behaviour BCT</t>
-        </is>
-      </c>
-      <c r="G210" s="3" t="inlineStr">
-        <is>
-          <t>BCT14.2 Punishment</t>
-        </is>
-      </c>
-      <c r="H210" s="3" t="inlineStr">
-        <is>
-          <t>punishment</t>
-        </is>
-      </c>
-      <c r="I210" s="3" t="n"/>
-      <c r="J210" s="3" t="n"/>
-      <c r="K210" s="3" t="inlineStr">
-        <is>
-          <t>To qualify as aversive, the consequence should be aversively valued by the person receiving it.</t>
-        </is>
-      </c>
-      <c r="L210" s="3" t="inlineStr">
-        <is>
-          <t>behaviour change technique</t>
-        </is>
-      </c>
-      <c r="M210" s="3" t="n"/>
-      <c r="N210" s="3" t="n"/>
-      <c r="O210" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="P210" s="3" t="n"/>
-      <c r="Q210" s="3" t="n"/>
-      <c r="R210" s="3" t="inlineStr">
-        <is>
-          <t>lz; LZ</t>
-        </is>
-      </c>
-      <c r="S210" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T210" s="3" t="n"/>
+      <c r="T210" s="2" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007246</t>
+          <t>BCIO:007241</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for outcome of behaviour BCT</t>
+          <t>provide aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide consequence for outcome of behaviour BCT&gt; where the consequence is aversive.</t>
+          <t>A &lt;provide consequence for behaviour BCT&gt; where the consequence is aversive.</t>
         </is>
       </c>
       <c r="D211" s="3" t="n"/>
       <c r="E211" s="3" t="n"/>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>provide consequence for outcome of behaviour BCT</t>
-        </is>
-      </c>
-      <c r="G211" s="3" t="n"/>
+          <t>provide consequence for behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G211" s="3" t="inlineStr">
+        <is>
+          <t>BCT14.2 Punishment</t>
+        </is>
+      </c>
       <c r="H211" s="3" t="inlineStr">
         <is>
           <t>punishment</t>
@@ -12694,35 +12676,39 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007242</t>
+          <t>BCIO:007246</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for situation specific behaviour BCT</t>
+          <t>provide aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide aversive consequence for behaviour BCT&gt; that provides the consequence for the behaviour in one situation but not in another.</t>
+          <t>A &lt;provide consequence for outcome of behaviour BCT&gt; where the consequence is aversive.</t>
         </is>
       </c>
       <c r="D212" s="3" t="n"/>
       <c r="E212" s="3" t="n"/>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for behaviour BCT</t>
+          <t>provide consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="G212" s="3" t="n"/>
       <c r="H212" s="3" t="inlineStr">
         <is>
-          <t>punishment for situation specific behaviour</t>
+          <t>punishment</t>
         </is>
       </c>
       <c r="I212" s="3" t="n"/>
       <c r="J212" s="3" t="n"/>
-      <c r="K212" s="3" t="n"/>
+      <c r="K212" s="3" t="inlineStr">
+        <is>
+          <t>To qualify as aversive, the consequence should be aversively valued by the person receiving it.</t>
+        </is>
+      </c>
       <c r="L212" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -12752,17 +12738,17 @@
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007243</t>
+          <t>BCIO:007242</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>provide aversive material consequence for behaviour BCT</t>
+          <t>provide aversive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide aversive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide aversive consequence for behaviour BCT&gt; that provides the consequence for the behaviour in one situation but not in another.</t>
         </is>
       </c>
       <c r="D213" s="3" t="n"/>
@@ -12775,7 +12761,7 @@
       <c r="G213" s="3" t="n"/>
       <c r="H213" s="3" t="inlineStr">
         <is>
-          <t>material punishment</t>
+          <t>punishment for situation specific behaviour</t>
         </is>
       </c>
       <c r="I213" s="3" t="n"/>
@@ -12810,24 +12796,24 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007245</t>
+          <t>BCIO:007243</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>provide aversive material consequence for outcome of behaviour BCT</t>
+          <t>provide aversive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide aversive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide aversive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D214" s="3" t="n"/>
       <c r="E214" s="3" t="n"/>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for outcome of behaviour BCT</t>
+          <t>provide aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="G214" s="3" t="n"/>
@@ -12868,30 +12854,30 @@
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007244</t>
+          <t>BCIO:007245</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>provide aversive material consequence for situation specific behaviour BCT</t>
+          <t>provide aversive material consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide aversive consequence for situation specific behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide aversive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D215" s="3" t="n"/>
       <c r="E215" s="3" t="n"/>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for situation specific behaviour BCT</t>
+          <t>provide aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="G215" s="3" t="n"/>
       <c r="H215" s="3" t="inlineStr">
         <is>
-          <t>material punishment for situation specific behaviour</t>
+          <t>material punishment</t>
         </is>
       </c>
       <c r="I215" s="3" t="n"/>
@@ -12926,39 +12912,35 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007247</t>
+          <t>BCIO:007244</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>provide aversive social consequence for behaviour BCT</t>
+          <t>provide aversive material consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide aversive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide aversive consequence for situation specific behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D216" s="3" t="n"/>
       <c r="E216" s="3" t="n"/>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for behaviour BCT</t>
+          <t>provide aversive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="G216" s="3" t="n"/>
       <c r="H216" s="3" t="inlineStr">
         <is>
-          <t>social punishment</t>
+          <t>material punishment for situation specific behaviour</t>
         </is>
       </c>
       <c r="I216" s="3" t="n"/>
       <c r="J216" s="3" t="n"/>
-      <c r="K216" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="K216" s="3" t="n"/>
       <c r="L216" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -12988,24 +12970,24 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007249</t>
+          <t>BCIO:007247</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>provide aversive social consequence for outcome of behaviour BCT</t>
+          <t>provide aversive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide aversive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide aversive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D217" s="3" t="n"/>
       <c r="E217" s="3" t="n"/>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for outcome of behaviour BCT</t>
+          <t>provide aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="G217" s="3" t="n"/>
@@ -13050,30 +13032,30 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007248</t>
+          <t>BCIO:007249</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>provide aversive social consequence for situation specific behaviour BCT</t>
+          <t>provide aversive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide aversive consequence for situation specific behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide aversive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D218" s="3" t="n"/>
       <c r="E218" s="3" t="n"/>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for situation specific behaviour BCT</t>
+          <t>provide aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="G218" s="3" t="n"/>
       <c r="H218" s="3" t="inlineStr">
         <is>
-          <t>social punishment for situation specific behaviour</t>
+          <t>social punishment</t>
         </is>
       </c>
       <c r="I218" s="3" t="n"/>
@@ -13112,43 +13094,39 @@
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007026</t>
+          <t>BCIO:007248</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">provide biofeedback BCT </t>
+          <t>provide aversive social consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide feedback BCT&gt; that provides information about the functioning or state of the person's body, based on information collected by an external monitoring device.</t>
+          <t>A &lt;provide aversive consequence for situation specific behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D219" s="3" t="n"/>
       <c r="E219" s="3" t="n"/>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>provide feedback BCT</t>
-        </is>
-      </c>
-      <c r="G219" s="3" t="inlineStr">
-        <is>
-          <t>BCT2.6 Biofeedback</t>
-        </is>
-      </c>
+          <t>provide aversive consequence for situation specific behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G219" s="3" t="n"/>
       <c r="H219" s="3" t="inlineStr">
         <is>
-          <t>biofeedback</t>
+          <t>social punishment for situation specific behaviour</t>
         </is>
       </c>
       <c r="I219" s="3" t="n"/>
-      <c r="J219" s="3" t="inlineStr">
-        <is>
-          <t>Using a pedometer to keep track of number of steps taken in a day.</t>
-        </is>
-      </c>
-      <c r="K219" s="3" t="n"/>
+      <c r="J219" s="3" t="n"/>
+      <c r="K219" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="L219" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -13178,30 +13156,42 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007240</t>
+          <t>BCIO:007026</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>provide consequence for behaviour BCT</t>
+          <t xml:space="preserve">provide biofeedback BCT </t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>A &lt;behavioural consequence BCT&gt; that provides a consequence for the behaviour.</t>
+          <t>A &lt;provide feedback BCT&gt; that provides information about the functioning or state of the person's body, based on information collected by an external monitoring device.</t>
         </is>
       </c>
       <c r="D220" s="3" t="n"/>
       <c r="E220" s="3" t="n"/>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>behavioural consequence BCT</t>
-        </is>
-      </c>
-      <c r="G220" s="3" t="n"/>
-      <c r="H220" s="3" t="n"/>
+          <t>provide feedback BCT</t>
+        </is>
+      </c>
+      <c r="G220" s="3" t="inlineStr">
+        <is>
+          <t>BCT2.6 Biofeedback</t>
+        </is>
+      </c>
+      <c r="H220" s="3" t="inlineStr">
+        <is>
+          <t>biofeedback</t>
+        </is>
+      </c>
       <c r="I220" s="3" t="n"/>
-      <c r="J220" s="3" t="n"/>
+      <c r="J220" s="3" t="inlineStr">
+        <is>
+          <t>Using a pedometer to keep track of number of steps taken in a day.</t>
+        </is>
+      </c>
       <c r="K220" s="3" t="n"/>
       <c r="L220" s="3" t="inlineStr">
         <is>
@@ -13219,7 +13209,7 @@
       <c r="Q220" s="3" t="n"/>
       <c r="R220" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S220" s="3" t="inlineStr">
@@ -13232,24 +13222,24 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007250</t>
+          <t>BCIO:007240</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>provide consequence for outcome of behaviour BCT</t>
+          <t>provide consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>An &lt;outcome consequence BCT&gt; that provides a consequence for an outcome resulting from performing or not performing the behaviour.</t>
+          <t>A &lt;behavioural consequence BCT&gt; that provides a consequence for the behaviour.</t>
         </is>
       </c>
       <c r="D221" s="3" t="n"/>
       <c r="E221" s="3" t="n"/>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>outcome consequence BCT</t>
+          <t>behavioural consequence BCT</t>
         </is>
       </c>
       <c r="G221" s="3" t="n"/>
@@ -13286,36 +13276,28 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007155</t>
+          <t>BCIO:007250</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">provide distraction BCT </t>
+          <t>provide consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>A &lt;restructure the physical environment BCT&gt; that organises an alternative focus for attention for the person to avoid internal or external states or events associated with an unwanted behaviour.</t>
+          <t>An &lt;outcome consequence BCT&gt; that provides a consequence for an outcome resulting from performing or not performing the behaviour.</t>
         </is>
       </c>
       <c r="D222" s="3" t="n"/>
       <c r="E222" s="3" t="n"/>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>restructure the physical environment BCT</t>
-        </is>
-      </c>
-      <c r="G222" s="3" t="inlineStr">
-        <is>
-          <t>BCT12.4 Distraction</t>
-        </is>
-      </c>
-      <c r="H222" s="3" t="inlineStr">
-        <is>
-          <t>attention shift</t>
-        </is>
-      </c>
+          <t>outcome consequence BCT</t>
+        </is>
+      </c>
+      <c r="G222" s="3" t="n"/>
+      <c r="H222" s="3" t="n"/>
       <c r="I222" s="3" t="n"/>
       <c r="J222" s="3" t="n"/>
       <c r="K222" s="3" t="n"/>
@@ -13335,7 +13317,7 @@
       <c r="Q222" s="3" t="n"/>
       <c r="R222" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S222" s="3" t="inlineStr">
@@ -13348,39 +13330,39 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007022</t>
+          <t>BCIO:007155</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>provide feedback BCT</t>
+          <t xml:space="preserve">provide distraction BCT </t>
         </is>
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>A &lt;monitoring BCT&gt; in which feedback about the behaviour is provided.</t>
+          <t>A &lt;restructure the physical environment BCT&gt; that organises an alternative focus for attention for the person to avoid internal or external states or events associated with an unwanted behaviour.</t>
         </is>
       </c>
       <c r="D223" s="3" t="n"/>
       <c r="E223" s="3" t="n"/>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>monitoring BCT</t>
-        </is>
-      </c>
-      <c r="G223" s="3" t="n"/>
+          <t>restructure the physical environment BCT</t>
+        </is>
+      </c>
+      <c r="G223" s="3" t="inlineStr">
+        <is>
+          <t>BCT12.4 Distraction</t>
+        </is>
+      </c>
       <c r="H223" s="3" t="inlineStr">
         <is>
-          <t>feedback, behavioural feedback</t>
+          <t>attention shift</t>
         </is>
       </c>
       <c r="I223" s="3" t="n"/>
       <c r="J223" s="3" t="n"/>
-      <c r="K223" s="3" t="inlineStr">
-        <is>
-          <t>Feedback is provision of data about some aspect of behaviour without an evaluation (positive or negative). Where feedback includes reward or punishment, see behavioural consequence BCT, outcome consequence BCT and their child classes. If there is no clear evidence that feedback was given, code 'observe behaviour without feedback BCT' or 'record behaviour without feedback BCT'.</t>
-        </is>
-      </c>
+      <c r="K223" s="3" t="n"/>
       <c r="L223" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -13410,35 +13392,39 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007023</t>
+          <t>BCIO:007022</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">provide feedback on behaviour BCT </t>
+          <t>provide feedback BCT</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide feedback BCT&gt; that provides information about the person's previous performance of the behaviour.</t>
+          <t>A &lt;monitoring BCT&gt; in which feedback about the behaviour is provided.</t>
         </is>
       </c>
       <c r="D224" s="3" t="n"/>
       <c r="E224" s="3" t="n"/>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>provide feedback BCT</t>
-        </is>
-      </c>
-      <c r="G224" s="3" t="inlineStr">
-        <is>
-          <t>BCT2.2 Feedback on behaviour</t>
-        </is>
-      </c>
-      <c r="H224" s="3" t="n"/>
+          <t>monitoring BCT</t>
+        </is>
+      </c>
+      <c r="G224" s="3" t="n"/>
+      <c r="H224" s="3" t="inlineStr">
+        <is>
+          <t>feedback, behavioural feedback</t>
+        </is>
+      </c>
       <c r="I224" s="3" t="n"/>
       <c r="J224" s="3" t="n"/>
-      <c r="K224" s="3" t="n"/>
+      <c r="K224" s="3" t="inlineStr">
+        <is>
+          <t>Feedback is provision of data about some aspect of behaviour without an evaluation (positive or negative). Where feedback includes reward or punishment, see behavioural consequence BCT, outcome consequence BCT and their child classes. If there is no clear evidence that feedback was given, code 'observe behaviour without feedback BCT' or 'record behaviour without feedback BCT'.</t>
+        </is>
+      </c>
       <c r="L224" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -13455,7 +13441,7 @@
       <c r="Q224" s="3" t="n"/>
       <c r="R224" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S224" s="3" t="inlineStr">
@@ -13468,17 +13454,17 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007027</t>
+          <t>BCIO:007023</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">provide feedback on outcome of behaviour BCT </t>
+          <t xml:space="preserve">provide feedback on behaviour BCT </t>
         </is>
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide feedback BCT&gt; that provides information about an outcome of the person's previous performance of the behaviour.</t>
+          <t>A &lt;provide feedback BCT&gt; that provides information about the person's previous performance of the behaviour.</t>
         </is>
       </c>
       <c r="D225" s="3" t="n"/>
@@ -13490,7 +13476,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>BCT2.7 Feedback on outcome(s) of behaviour</t>
+          <t>BCT2.2 Feedback on behaviour</t>
         </is>
       </c>
       <c r="H225" s="3" t="n"/>
@@ -13526,29 +13512,29 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007145</t>
+          <t>BCIO:007027</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">provide pharmacological support BCT </t>
+          <t xml:space="preserve">provide feedback on outcome of behaviour BCT </t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>A &lt;promote pharmacological support BCT&gt; that provides the person with medicines or other drugs.</t>
+          <t>A &lt;provide feedback BCT&gt; that provides information about an outcome of the person's previous performance of the behaviour.</t>
         </is>
       </c>
       <c r="D226" s="3" t="n"/>
       <c r="E226" s="3" t="n"/>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>promote pharmacological support BCT</t>
+          <t>provide feedback BCT</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>BCT11.1 Pharmacological support</t>
+          <t>BCT2.7 Feedback on outcome(s) of behaviour</t>
         </is>
       </c>
       <c r="H226" s="3" t="n"/>
@@ -13584,42 +13570,34 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007251</t>
+          <t>BCIO:007145</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for alternative behaviour BCT</t>
+          <t xml:space="preserve">provide pharmacological support BCT </t>
         </is>
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A &lt;provide positive consequence for behaviour BCT&gt; that provides the consequence for a behaviour that is different from the unwanted behaviour. </t>
+          <t>A &lt;promote pharmacological support BCT&gt; that provides the person with medicines or other drugs.</t>
         </is>
       </c>
       <c r="D227" s="3" t="n"/>
       <c r="E227" s="3" t="n"/>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for behaviour BCT</t>
+          <t>promote pharmacological support BCT</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>BCT14.8 Reward alternative behaviour</t>
-        </is>
-      </c>
-      <c r="H227" s="3" t="inlineStr">
-        <is>
-          <t>differential reinforcement, reward for alternative behaviour</t>
-        </is>
-      </c>
+          <t>BCT11.1 Pharmacological support</t>
+        </is>
+      </c>
+      <c r="H227" s="3" t="n"/>
       <c r="I227" s="3" t="n"/>
-      <c r="J227" s="3" t="inlineStr">
-        <is>
-          <t>Provide a reward for consuming low sugar food instead of high sugar food</t>
-        </is>
-      </c>
+      <c r="J227" s="3" t="n"/>
       <c r="K227" s="3" t="n"/>
       <c r="L227" s="3" t="inlineStr">
         <is>
@@ -13637,7 +13615,7 @@
       <c r="Q227" s="3" t="n"/>
       <c r="R227" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S227" s="3" t="inlineStr">
@@ -13650,17 +13628,17 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007253</t>
+          <t>BCIO:007251</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for approximating behaviour BCT</t>
+          <t>provide positive consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for behaviour BCT&gt; where the consequence is provided as the performance gradually gets closer to the behaviour.</t>
+          <t xml:space="preserve">A &lt;provide positive consequence for behaviour BCT&gt; that provides the consequence for a behaviour that is different from the unwanted behaviour. </t>
         </is>
       </c>
       <c r="D228" s="3" t="n"/>
@@ -13672,18 +13650,18 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>BCT14.4 Reward approximation</t>
+          <t>BCT14.8 Reward alternative behaviour</t>
         </is>
       </c>
       <c r="H228" s="3" t="inlineStr">
         <is>
-          <t>shaping, reward for approximating behaviour</t>
+          <t>differential reinforcement, reward for alternative behaviour</t>
         </is>
       </c>
       <c r="I228" s="3" t="n"/>
       <c r="J228" s="3" t="inlineStr">
         <is>
-          <t>Reward a person who has recently had a stroke who is learning to use cutlery again</t>
+          <t>Provide a reward for consuming low sugar food instead of high sugar food</t>
         </is>
       </c>
       <c r="K228" s="3" t="n"/>
@@ -13716,43 +13694,43 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007252</t>
+          <t>BCIO:007253</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for behaviour BCT</t>
+          <t>provide positive consequence for approximating behaviour BCT</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide consequence for behaviour BCT&gt; where the consequence is positive.</t>
+          <t>A &lt;provide positive consequence for behaviour BCT&gt; where the consequence is provided as the performance gradually gets closer to the behaviour.</t>
         </is>
       </c>
       <c r="D229" s="3" t="n"/>
       <c r="E229" s="3" t="n"/>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>provide consequence for behaviour BCT</t>
+          <t>provide positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>BCT10.3 Non-specific reward; BCT10.9 Self-reward</t>
+          <t>BCT14.4 Reward approximation</t>
         </is>
       </c>
       <c r="H229" s="3" t="inlineStr">
         <is>
-          <t>positive reinforcement, reward</t>
+          <t>shaping, reward for approximating behaviour</t>
         </is>
       </c>
       <c r="I229" s="3" t="n"/>
-      <c r="J229" s="3" t="n"/>
-      <c r="K229" s="3" t="inlineStr">
-        <is>
-          <t>To qualify as positive, the consequence should be positively valued by the person receiving it. If informed of consequence in advance of rewarded behaviour, also code 'promise positive consequence for behaviour BCT' or one of its child classses.</t>
-        </is>
-      </c>
+      <c r="J229" s="3" t="inlineStr">
+        <is>
+          <t>Reward a person who has recently had a stroke who is learning to use cutlery again</t>
+        </is>
+      </c>
+      <c r="K229" s="3" t="n"/>
       <c r="L229" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -13782,39 +13760,43 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007254</t>
+          <t>BCIO:007252</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for completion of behavioural sequence BCT</t>
+          <t>provide positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for behaviour BCT&gt; where the consequence is provided for performing the final behaviour in a sequence of behaviours, followed by adding behaviours that occur earlier in the sequence.</t>
+          <t>A &lt;provide consequence for behaviour BCT&gt; where the consequence is positive.</t>
         </is>
       </c>
       <c r="D230" s="3" t="n"/>
       <c r="E230" s="3" t="n"/>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for behaviour BCT</t>
+          <t>provide consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>BCT14.5 Rewarding completion</t>
+          <t>BCT10.3 Non-specific reward; BCT10.9 Self-reward</t>
         </is>
       </c>
       <c r="H230" s="3" t="inlineStr">
         <is>
-          <t>backward chaining, reward for completion of behavoural sequence</t>
+          <t>positive reinforcement, reward</t>
         </is>
       </c>
       <c r="I230" s="3" t="n"/>
       <c r="J230" s="3" t="n"/>
-      <c r="K230" s="3" t="n"/>
+      <c r="K230" s="3" t="inlineStr">
+        <is>
+          <t>To qualify as positive, the consequence should be positively valued by the person receiving it. If informed of consequence in advance of rewarded behaviour, also code 'promise positive consequence for behaviour BCT' or one of its child classses.</t>
+        </is>
+      </c>
       <c r="L230" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -13844,17 +13826,17 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007255</t>
+          <t>BCIO:007254</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for incompatible behaviour BCT</t>
+          <t>provide positive consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for behaviour BCT&gt; that provides the consequence for a behaviour that is incompatible with the unwanted behaviour.</t>
+          <t>A &lt;provide positive consequence for behaviour BCT&gt; where the consequence is provided for performing the final behaviour in a sequence of behaviours, followed by adding behaviours that occur earlier in the sequence.</t>
         </is>
       </c>
       <c r="D231" s="3" t="n"/>
@@ -13866,20 +13848,16 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>BCT14.7 Reward incompatible behaviour</t>
+          <t>BCT14.5 Rewarding completion</t>
         </is>
       </c>
       <c r="H231" s="3" t="inlineStr">
         <is>
-          <t>counter-conditioning, reward for incompatible behaviour</t>
+          <t>backward chaining, reward for completion of behavoural sequence</t>
         </is>
       </c>
       <c r="I231" s="3" t="n"/>
-      <c r="J231" s="3" t="inlineStr">
-        <is>
-          <t>Provide a reward when a person folds their arms or sits on their hands instead of touching their face.</t>
-        </is>
-      </c>
+      <c r="J231" s="3" t="n"/>
       <c r="K231" s="3" t="n"/>
       <c r="L231" s="3" t="inlineStr">
         <is>
@@ -13910,43 +13888,43 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007264</t>
+          <t>BCIO:007255</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for outcome of behaviour BCT</t>
+          <t>provide positive consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide consequence for outcome of behaviour BCT&gt; where the consequence is positive.</t>
+          <t>A &lt;provide positive consequence for behaviour BCT&gt; that provides the consequence for a behaviour that is incompatible with the unwanted behaviour.</t>
         </is>
       </c>
       <c r="D232" s="3" t="n"/>
       <c r="E232" s="3" t="n"/>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>provide consequence for outcome of behaviour BCT</t>
+          <t>provide positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>BCT10.10 Reward (outcome)</t>
+          <t>BCT14.7 Reward incompatible behaviour</t>
         </is>
       </c>
       <c r="H232" s="3" t="inlineStr">
         <is>
-          <t>positive reinforcement, reward</t>
+          <t>counter-conditioning, reward for incompatible behaviour</t>
         </is>
       </c>
       <c r="I232" s="3" t="n"/>
-      <c r="J232" s="3" t="n"/>
-      <c r="K232" s="3" t="inlineStr">
-        <is>
-          <t>To qualify as positive, the consequence should be positively valued by the person receiving it.</t>
-        </is>
-      </c>
+      <c r="J232" s="3" t="inlineStr">
+        <is>
+          <t>Provide a reward when a person folds their arms or sits on their hands instead of touching their face.</t>
+        </is>
+      </c>
+      <c r="K232" s="3" t="n"/>
       <c r="L232" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -13963,7 +13941,7 @@
       <c r="Q232" s="3" t="n"/>
       <c r="R232" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S232" s="3" t="inlineStr">
@@ -13976,39 +13954,43 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007256</t>
+          <t>BCIO:007264</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for situation specific behaviour BCT</t>
+          <t>provide positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for behaviour BCT&gt; that provides the consequence for the behaviour in one situation but not in another.</t>
+          <t>A &lt;provide consequence for outcome of behaviour BCT&gt; where the consequence is positive.</t>
         </is>
       </c>
       <c r="D233" s="3" t="n"/>
       <c r="E233" s="3" t="n"/>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for behaviour BCT</t>
+          <t>provide consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>BCT14.6 Situation-specific reward</t>
+          <t>BCT10.10 Reward (outcome)</t>
         </is>
       </c>
       <c r="H233" s="3" t="inlineStr">
         <is>
-          <t>discrimination training, reward for situation specific behaviour</t>
+          <t>positive reinforcement, reward</t>
         </is>
       </c>
       <c r="I233" s="3" t="n"/>
       <c r="J233" s="3" t="n"/>
-      <c r="K233" s="3" t="n"/>
+      <c r="K233" s="3" t="inlineStr">
+        <is>
+          <t>To qualify as positive, the consequence should be positively valued by the person receiving it.</t>
+        </is>
+      </c>
       <c r="L233" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -14038,30 +14020,34 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007258</t>
+          <t>BCIO:007256</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>provide positive material consequence for alternative behaviour BCT</t>
+          <t>provide positive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for alternative behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide positive consequence for behaviour BCT&gt; that provides the consequence for the behaviour in one situation but not in another.</t>
         </is>
       </c>
       <c r="D234" s="3" t="n"/>
       <c r="E234" s="3" t="n"/>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for alternative behaviour BCT</t>
-        </is>
-      </c>
-      <c r="G234" s="3" t="n"/>
+          <t>provide positive consequence for behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G234" s="3" t="inlineStr">
+        <is>
+          <t>BCT14.6 Situation-specific reward</t>
+        </is>
+      </c>
       <c r="H234" s="3" t="inlineStr">
         <is>
-          <t>material reward for alternative behaviour</t>
+          <t>discrimination training, reward for situation specific behaviour</t>
         </is>
       </c>
       <c r="I234" s="3" t="n"/>
@@ -14096,30 +14082,30 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007259</t>
+          <t>BCIO:007258</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>provide positive material consequence for approximating behaviour BCT</t>
+          <t>provide positive material consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for approximating behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide positive consequence for alternative behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D235" s="3" t="n"/>
       <c r="E235" s="3" t="n"/>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for approximating behaviour BCT</t>
+          <t>provide positive consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="G235" s="3" t="n"/>
       <c r="H235" s="3" t="inlineStr">
         <is>
-          <t>material reward for approximating behaviour</t>
+          <t>material reward for alternative behaviour</t>
         </is>
       </c>
       <c r="I235" s="3" t="n"/>
@@ -14154,34 +14140,30 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007257</t>
+          <t>BCIO:007259</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>provide positive material consequence for behaviour BCT</t>
+          <t>provide positive material consequence for approximating behaviour BCT</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide positive consequence for approximating behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D236" s="3" t="n"/>
       <c r="E236" s="3" t="n"/>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for behaviour BCT</t>
-        </is>
-      </c>
-      <c r="G236" s="3" t="inlineStr">
-        <is>
-          <t>BCT10.2 Material reward (behaviour)</t>
-        </is>
-      </c>
+          <t>provide positive consequence for approximating behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G236" s="3" t="n"/>
       <c r="H236" s="3" t="inlineStr">
         <is>
-          <t>material reward, tangible reinforcement</t>
+          <t>material reward for approximating behaviour</t>
         </is>
       </c>
       <c r="I236" s="3" t="n"/>
@@ -14203,7 +14185,7 @@
       <c r="Q236" s="3" t="n"/>
       <c r="R236" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S236" s="3" t="inlineStr">
@@ -14216,30 +14198,34 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007260</t>
+          <t>BCIO:007257</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>provide positive material consequence for completion of behavioural sequence BCT</t>
+          <t>provide positive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for completion of behavioural sequence BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide positive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D237" s="3" t="n"/>
       <c r="E237" s="3" t="n"/>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for completion of behavioural sequence BCT</t>
-        </is>
-      </c>
-      <c r="G237" s="3" t="n"/>
+          <t>provide positive consequence for behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G237" s="3" t="inlineStr">
+        <is>
+          <t>BCT10.2 Material reward (behaviour)</t>
+        </is>
+      </c>
       <c r="H237" s="3" t="inlineStr">
         <is>
-          <t>material reward for completion of behavoural sequence</t>
+          <t>material reward, tangible reinforcement</t>
         </is>
       </c>
       <c r="I237" s="3" t="n"/>
@@ -14261,7 +14247,7 @@
       <c r="Q237" s="3" t="n"/>
       <c r="R237" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S237" s="3" t="inlineStr">
@@ -14274,30 +14260,30 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007261</t>
+          <t>BCIO:007260</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>provide positive material consequence for incompatible behaviour BCT</t>
+          <t>provide positive material consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for incompatible behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide positive consequence for completion of behavioural sequence BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D238" s="3" t="n"/>
       <c r="E238" s="3" t="n"/>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for incompatible behaviour BCT</t>
+          <t>provide positive consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="G238" s="3" t="n"/>
       <c r="H238" s="3" t="inlineStr">
         <is>
-          <t>material reward for incompatible behaviour</t>
+          <t>material reward for completion of behavoural sequence</t>
         </is>
       </c>
       <c r="I238" s="3" t="n"/>
@@ -14332,30 +14318,30 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007263</t>
+          <t>BCIO:007261</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>provide positive material consequence for outcome of behaviour BCT</t>
+          <t>provide positive material consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide positive consequence for incompatible behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D239" s="3" t="n"/>
       <c r="E239" s="3" t="n"/>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for outcome of behaviour BCT</t>
+          <t>provide positive consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="G239" s="3" t="n"/>
       <c r="H239" s="3" t="inlineStr">
         <is>
-          <t>material reward, tangible reinforcement</t>
+          <t>material reward for incompatible behaviour</t>
         </is>
       </c>
       <c r="I239" s="3" t="n"/>
@@ -14377,7 +14363,7 @@
       <c r="Q239" s="3" t="n"/>
       <c r="R239" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S239" s="3" t="inlineStr">
@@ -14390,30 +14376,30 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007262</t>
+          <t>BCIO:007263</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>provide positive material consequence for situation specific behaviour BCT</t>
+          <t>provide positive material consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for situation specific behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide positive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D240" s="3" t="n"/>
       <c r="E240" s="3" t="n"/>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for situation specific behaviour BCT</t>
+          <t>provide positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="G240" s="3" t="n"/>
       <c r="H240" s="3" t="inlineStr">
         <is>
-          <t>material reward for situation specific behaviour</t>
+          <t>material reward, tangible reinforcement</t>
         </is>
       </c>
       <c r="I240" s="3" t="n"/>
@@ -14435,7 +14421,7 @@
       <c r="Q240" s="3" t="n"/>
       <c r="R240" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S240" s="3" t="inlineStr">
@@ -14448,39 +14434,35 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007266</t>
+          <t>BCIO:007262</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>provide positive social consequence for alternative behaviour BCT</t>
+          <t>provide positive material consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for alternative behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide positive consequence for situation specific behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D241" s="3" t="n"/>
       <c r="E241" s="3" t="n"/>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for alternative behaviour BCT</t>
+          <t>provide positive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="G241" s="3" t="n"/>
       <c r="H241" s="3" t="inlineStr">
         <is>
-          <t>social reward for alternative behaviour</t>
+          <t>material reward for situation specific behaviour</t>
         </is>
       </c>
       <c r="I241" s="3" t="n"/>
       <c r="J241" s="3" t="n"/>
-      <c r="K241" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="K241" s="3" t="n"/>
       <c r="L241" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -14510,30 +14492,30 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007267</t>
+          <t>BCIO:007266</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>provide positive social consequence for approximating behaviour BCT</t>
+          <t>provide positive social consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for approximating behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide positive consequence for alternative behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D242" s="3" t="n"/>
       <c r="E242" s="3" t="n"/>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for approximating behaviour BCT</t>
+          <t>provide positive consequence for alternative behaviour BCT</t>
         </is>
       </c>
       <c r="G242" s="3" t="n"/>
       <c r="H242" s="3" t="inlineStr">
         <is>
-          <t>social reward for approximating behaviour</t>
+          <t>social reward for alternative behaviour</t>
         </is>
       </c>
       <c r="I242" s="3" t="n"/>
@@ -14572,34 +14554,30 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007265</t>
+          <t>BCIO:007267</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>provide positive social consequence for behaviour BCT</t>
+          <t>provide positive social consequence for approximating behaviour BCT</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide positive consequence for approximating behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D243" s="3" t="n"/>
       <c r="E243" s="3" t="n"/>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for behaviour BCT</t>
-        </is>
-      </c>
-      <c r="G243" s="3" t="inlineStr">
-        <is>
-          <t>BCT10.4 Social reward</t>
-        </is>
-      </c>
+          <t>provide positive consequence for approximating behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G243" s="3" t="n"/>
       <c r="H243" s="3" t="inlineStr">
         <is>
-          <t>social reward</t>
+          <t>social reward for approximating behaviour</t>
         </is>
       </c>
       <c r="I243" s="3" t="n"/>
@@ -14625,7 +14603,7 @@
       <c r="Q243" s="3" t="n"/>
       <c r="R243" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S243" s="3" t="inlineStr">
@@ -14638,30 +14616,34 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007268</t>
+          <t>BCIO:007265</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>provide positive social consequence for completion of behavioural sequence BCT</t>
+          <t>provide positive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for completion of behavioural sequence BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide positive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D244" s="3" t="n"/>
       <c r="E244" s="3" t="n"/>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for completion of behavioural sequence BCT</t>
-        </is>
-      </c>
-      <c r="G244" s="3" t="n"/>
+          <t>provide positive consequence for behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G244" s="3" t="inlineStr">
+        <is>
+          <t>BCT10.4 Social reward</t>
+        </is>
+      </c>
       <c r="H244" s="3" t="inlineStr">
         <is>
-          <t>social reward for completion of behavoural sequence</t>
+          <t>social reward</t>
         </is>
       </c>
       <c r="I244" s="3" t="n"/>
@@ -14687,7 +14669,7 @@
       <c r="Q244" s="3" t="n"/>
       <c r="R244" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S244" s="3" t="inlineStr">
@@ -14700,30 +14682,30 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007269</t>
+          <t>BCIO:007268</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>provide positive social consequence for incompatible behaviour BCT</t>
+          <t>provide positive social consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for incompatible behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide positive consequence for completion of behavioural sequence BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D245" s="3" t="n"/>
       <c r="E245" s="3" t="n"/>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for incompatible behaviour BCT</t>
+          <t>provide positive consequence for completion of behavioural sequence BCT</t>
         </is>
       </c>
       <c r="G245" s="3" t="n"/>
       <c r="H245" s="3" t="inlineStr">
         <is>
-          <t>social reward for incompatible behaviour</t>
+          <t>social reward for completion of behavoural sequence</t>
         </is>
       </c>
       <c r="I245" s="3" t="n"/>
@@ -14762,30 +14744,30 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007271</t>
+          <t>BCIO:007269</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>provide positive social consequence for outcome of behaviour BCT</t>
+          <t>provide positive social consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide positive consequence for incompatible behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D246" s="3" t="n"/>
       <c r="E246" s="3" t="n"/>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for outcome of behaviour BCT</t>
+          <t>provide positive consequence for incompatible behaviour BCT</t>
         </is>
       </c>
       <c r="G246" s="3" t="n"/>
       <c r="H246" s="3" t="inlineStr">
         <is>
-          <t>social reward</t>
+          <t>social reward for incompatible behaviour</t>
         </is>
       </c>
       <c r="I246" s="3" t="n"/>
@@ -14824,30 +14806,30 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007270</t>
+          <t>BCIO:007271</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>provide positive social consequence for situation specific behaviour BCT</t>
+          <t>provide positive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for  situation specific behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide positive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D247" s="3" t="n"/>
       <c r="E247" s="3" t="n"/>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for situation specific behaviour BCT</t>
+          <t>provide positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="G247" s="3" t="n"/>
       <c r="H247" s="3" t="inlineStr">
         <is>
-          <t>social reward for situation specific behaviour</t>
+          <t>social reward</t>
         </is>
       </c>
       <c r="I247" s="3" t="n"/>
@@ -14886,35 +14868,39 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007273</t>
+          <t>BCIO:007270</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive consequence for behaviour BCT</t>
+          <t>provide positive social consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide aversive consequence for behaviour BCT&gt; that provides the consequence at increasingly less frequent intervals.</t>
+          <t>A &lt;provide positive consequence for  situation specific behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D248" s="3" t="n"/>
       <c r="E248" s="3" t="n"/>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for behaviour BCT</t>
+          <t>provide positive consequence for situation specific behaviour BCT</t>
         </is>
       </c>
       <c r="G248" s="3" t="n"/>
       <c r="H248" s="3" t="inlineStr">
         <is>
-          <t>reduce punishment frequency</t>
+          <t>social reward for situation specific behaviour</t>
         </is>
       </c>
       <c r="I248" s="3" t="n"/>
       <c r="J248" s="3" t="n"/>
-      <c r="K248" s="3" t="n"/>
+      <c r="K248" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="L248" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -14931,7 +14917,7 @@
       <c r="Q248" s="3" t="n"/>
       <c r="R248" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S248" s="3" t="inlineStr">
@@ -14944,24 +14930,24 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007276</t>
+          <t>BCIO:007273</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide aversive consequence for outcome of behaviour BCT&gt; that provides the consequence at increasingly less frequent intervals.</t>
+          <t>A &lt;provide aversive consequence for behaviour BCT&gt; that provides the consequence at increasingly less frequent intervals.</t>
         </is>
       </c>
       <c r="D249" s="3" t="n"/>
       <c r="E249" s="3" t="n"/>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>provide aversive consequence for outcome of behaviour BCT</t>
+          <t>provide aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="G249" s="3" t="n"/>
@@ -15002,30 +14988,30 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007274</t>
+          <t>BCIO:007276</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive material consequence for behaviour BCT</t>
+          <t>provide reduced frequency of aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide reduced frequency of aversive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide aversive consequence for outcome of behaviour BCT&gt; that provides the consequence at increasingly less frequent intervals.</t>
         </is>
       </c>
       <c r="D250" s="3" t="n"/>
       <c r="E250" s="3" t="n"/>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive consequence for behaviour BCT</t>
+          <t>provide aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="G250" s="3" t="n"/>
       <c r="H250" s="3" t="inlineStr">
         <is>
-          <t>reduce material punishment frequency</t>
+          <t>reduce punishment frequency</t>
         </is>
       </c>
       <c r="I250" s="3" t="n"/>
@@ -15060,24 +15046,24 @@
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007275</t>
+          <t>BCIO:007274</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive material consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of aversive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide reduced frequency of aversive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide reduced frequency of aversive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D251" s="3" t="n"/>
       <c r="E251" s="3" t="n"/>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="G251" s="3" t="n"/>
@@ -15118,39 +15104,35 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007277</t>
+          <t>BCIO:007275</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive social consequence for behaviour BCT</t>
+          <t>provide reduced frequency of aversive material consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide reduced frequency of aversive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide reduced frequency of aversive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D252" s="3" t="n"/>
       <c r="E252" s="3" t="n"/>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive consequence for behaviour BCT</t>
+          <t>provide reduced frequency of aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="G252" s="3" t="n"/>
       <c r="H252" s="3" t="inlineStr">
         <is>
-          <t>reduce social punishment frequency</t>
+          <t>reduce material punishment frequency</t>
         </is>
       </c>
       <c r="I252" s="3" t="n"/>
       <c r="J252" s="3" t="n"/>
-      <c r="K252" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="K252" s="3" t="n"/>
       <c r="L252" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -15180,24 +15162,24 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007278</t>
+          <t>BCIO:007277</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive social consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of aversive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide reduced frequency of aversive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide reduced frequency of aversive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D253" s="3" t="n"/>
       <c r="E253" s="3" t="n"/>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of aversive consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="G253" s="3" t="n"/>
@@ -15242,39 +15224,39 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007279</t>
+          <t>BCIO:007278</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive consequence for behaviour BCT</t>
+          <t>provide reduced frequency of aversive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for behaviour BCT&gt; that provides the consequence at increasingly less frequent intervals.</t>
+          <t>A &lt;provide reduced frequency of aversive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D254" s="3" t="n"/>
       <c r="E254" s="3" t="n"/>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for behaviour BCT</t>
-        </is>
-      </c>
-      <c r="G254" s="3" t="inlineStr">
-        <is>
-          <t>BCT14.9 Reduce reward frequency</t>
-        </is>
-      </c>
+          <t>provide reduced frequency of aversive consequence for outcome of behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G254" s="3" t="n"/>
       <c r="H254" s="3" t="inlineStr">
         <is>
-          <t>thinning, reduce reward frequency</t>
+          <t>reduce social punishment frequency</t>
         </is>
       </c>
       <c r="I254" s="3" t="n"/>
       <c r="J254" s="3" t="n"/>
-      <c r="K254" s="3" t="n"/>
+      <c r="K254" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="L254" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -15291,7 +15273,7 @@
       <c r="Q254" s="3" t="n"/>
       <c r="R254" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S254" s="3" t="inlineStr">
@@ -15304,27 +15286,31 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007281</t>
+          <t>BCIO:007279</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide positive consequence for outcome of behaviour BCT&gt; that provides the consequence at increasingly less frequent intervals.</t>
+          <t>A &lt;provide positive consequence for behaviour BCT&gt; that provides the consequence at increasingly less frequent intervals.</t>
         </is>
       </c>
       <c r="D255" s="3" t="n"/>
       <c r="E255" s="3" t="n"/>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>provide positive consequence for outcome of behaviour BCT</t>
-        </is>
-      </c>
-      <c r="G255" s="3" t="n"/>
+          <t>provide positive consequence for behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G255" s="3" t="inlineStr">
+        <is>
+          <t>BCT14.9 Reduce reward frequency</t>
+        </is>
+      </c>
       <c r="H255" s="3" t="inlineStr">
         <is>
           <t>thinning, reduce reward frequency</t>
@@ -15362,30 +15348,30 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007280</t>
+          <t>BCIO:007281</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive material consequence for behaviour BCT</t>
+          <t>provide reduced frequency of positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide reduced frequency of positive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide positive consequence for outcome of behaviour BCT&gt; that provides the consequence at increasingly less frequent intervals.</t>
         </is>
       </c>
       <c r="D256" s="3" t="n"/>
       <c r="E256" s="3" t="n"/>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive consequence for behaviour BCT</t>
+          <t>provide positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="G256" s="3" t="n"/>
       <c r="H256" s="3" t="inlineStr">
         <is>
-          <t>reduce material reward frequency</t>
+          <t>thinning, reduce reward frequency</t>
         </is>
       </c>
       <c r="I256" s="3" t="n"/>
@@ -15420,24 +15406,24 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007272</t>
+          <t>BCIO:007280</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive material consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of positive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide reduced frequency of positive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;provide reduced frequency of positive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D257" s="3" t="n"/>
       <c r="E257" s="3" t="n"/>
       <c r="F257" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="G257" s="3" t="n"/>
@@ -15478,39 +15464,35 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007282</t>
+          <t>BCIO:007272</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive social consequence for behaviour BCT</t>
+          <t>provide reduced frequency of positive material consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide reduced frequency of positive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide reduced frequency of positive consequence for outcome of behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D258" s="3" t="n"/>
       <c r="E258" s="3" t="n"/>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive consequence for behaviour BCT</t>
+          <t>provide reduced frequency of positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="G258" s="3" t="n"/>
       <c r="H258" s="3" t="inlineStr">
         <is>
-          <t>reduce social reward frequency</t>
+          <t>reduce material reward frequency</t>
         </is>
       </c>
       <c r="I258" s="3" t="n"/>
       <c r="J258" s="3" t="n"/>
-      <c r="K258" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="K258" s="3" t="n"/>
       <c r="L258" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -15540,24 +15522,24 @@
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007283</t>
+          <t>BCIO:007282</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive social consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of positive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>A &lt;provide reduced frequency of positive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;provide reduced frequency of positive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D259" s="3" t="n"/>
       <c r="E259" s="3" t="n"/>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>provide reduced frequency of positive consequence for outcome of behaviour BCT</t>
+          <t>provide reduced frequency of positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="G259" s="3" t="n"/>
@@ -15602,39 +15584,39 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007053</t>
+          <t>BCIO:007283</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">re-attribute cause BCT </t>
+          <t>provide reduced frequency of positive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>A &lt;suggest different perspective on behaviour BCT&gt; that involves eliciting the person's beliefs about, and suggesting alternative beliefs about, the causes of the behaviour.</t>
+          <t>A &lt;provide reduced frequency of positive consequence for outcome of behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D260" s="3" t="n"/>
       <c r="E260" s="3" t="n"/>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>suggest different perspective on behaviour BCT</t>
-        </is>
-      </c>
-      <c r="G260" s="3" t="inlineStr">
-        <is>
-          <t>BCT4.3 Re-attribution</t>
-        </is>
-      </c>
+          <t>provide reduced frequency of positive consequence for outcome of behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G260" s="3" t="n"/>
       <c r="H260" s="3" t="inlineStr">
         <is>
-          <t>re-attribution</t>
+          <t>reduce social reward frequency</t>
         </is>
       </c>
       <c r="I260" s="3" t="n"/>
       <c r="J260" s="3" t="n"/>
-      <c r="K260" s="3" t="n"/>
+      <c r="K260" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="L260" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -15651,7 +15633,7 @@
       <c r="Q260" s="3" t="n"/>
       <c r="R260" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S260" s="3" t="inlineStr">
@@ -15664,43 +15646,39 @@
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007019</t>
+          <t>BCIO:007053</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">record behaviour without feedback BCT </t>
+          <t xml:space="preserve">re-attribute cause BCT </t>
         </is>
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>A &lt;monitoring BCT&gt; that records current performance of the behaviour with the person’s knowledge but without providing feedback about their behaviour.</t>
+          <t>A &lt;suggest different perspective on behaviour BCT&gt; that involves eliciting the person's beliefs about, and suggesting alternative beliefs about, the causes of the behaviour.</t>
         </is>
       </c>
       <c r="D261" s="3" t="n"/>
       <c r="E261" s="3" t="n"/>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>monitoring BCT</t>
+          <t>suggest different perspective on behaviour BCT</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>BCT2.1 Monitoring of behaviour by others without feedback</t>
+          <t>BCT4.3 Re-attribution</t>
         </is>
       </c>
       <c r="H261" s="3" t="inlineStr">
         <is>
-          <t>monitoring</t>
+          <t>re-attribution</t>
         </is>
       </c>
       <c r="I261" s="3" t="n"/>
       <c r="J261" s="3" t="n"/>
-      <c r="K261" s="3" t="inlineStr">
-        <is>
-          <t>The monitoring agent can be a human or a technical device. If recording is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if feedback given, code only 'provide feedback on behaviour BCT' and not this class; if recording outcomes code 'record outcome of behaviour without feedback BCT'.</t>
-        </is>
-      </c>
+      <c r="K261" s="3" t="n"/>
       <c r="L261" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -15730,17 +15708,17 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007021</t>
+          <t>BCIO:007019</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">record outcome of behaviour without feedback BCT </t>
+          <t xml:space="preserve">record behaviour without feedback BCT </t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>A &lt;monitoring BCT&gt; that records an outcome of performing the behaviour with the person's knowledge but without providing feedback about the outcome.</t>
+          <t>A &lt;monitoring BCT&gt; that records current performance of the behaviour with the person’s knowledge but without providing feedback about their behaviour.</t>
         </is>
       </c>
       <c r="D262" s="3" t="n"/>
@@ -15752,15 +15730,19 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>BCT2.5 Monitoring outcome(s) of behaviour by others without feedback</t>
-        </is>
-      </c>
-      <c r="H262" s="3" t="n"/>
+          <t>BCT2.1 Monitoring of behaviour by others without feedback</t>
+        </is>
+      </c>
+      <c r="H262" s="3" t="inlineStr">
+        <is>
+          <t>monitoring</t>
+        </is>
+      </c>
       <c r="I262" s="3" t="n"/>
       <c r="J262" s="3" t="n"/>
       <c r="K262" s="3" t="inlineStr">
         <is>
-          <t>The monitoring agent can be a human or a technical device. If recording is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if feedback given, code only 'provide feedback on outcome of behaviour BCT' and not this class; if recording behaviour code 'record behaviour without feedback BCT'.</t>
+          <t>The monitoring agent can be a human or a technical device. If recording is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if feedback given, code only 'provide feedback on behaviour BCT' and not this class; if recording outcomes code 'record outcome of behaviour without feedback BCT'.</t>
         </is>
       </c>
       <c r="L262" s="3" t="inlineStr">
@@ -15792,41 +15774,37 @@
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007084</t>
+          <t>BCIO:007021</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>reduce cue frequency BCTs</t>
+          <t xml:space="preserve">record outcome of behaviour without feedback BCT </t>
         </is>
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>An &lt;alter external stimulus BCT&gt; in which cues for the behaviour are presented less frequently.</t>
+          <t>A &lt;monitoring BCT&gt; that records an outcome of performing the behaviour with the person's knowledge but without providing feedback about the outcome.</t>
         </is>
       </c>
       <c r="D263" s="3" t="n"/>
       <c r="E263" s="3" t="n"/>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>alter external stimulus BCT</t>
+          <t>monitoring BCT</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>BCT7.3 Reduce prompts/cues</t>
-        </is>
-      </c>
-      <c r="H263" s="3" t="inlineStr">
-        <is>
-          <t>fading</t>
-        </is>
-      </c>
+          <t>BCT2.5 Monitoring outcome(s) of behaviour by others without feedback</t>
+        </is>
+      </c>
+      <c r="H263" s="3" t="n"/>
       <c r="I263" s="3" t="n"/>
       <c r="J263" s="3" t="n"/>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>The reduction in frequency of cue presentation can be gradual or rapid. This BCT is concerned with reducing the frequency of cue presentation. In contrast, in "reduce exposure to cues for the behaviour BCT", the cue frequency may remain unchanged but the person's exposure to the presentation of the cue is reduced.</t>
+          <t>The monitoring agent can be a human or a technical device. If recording is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if feedback given, code only 'provide feedback on outcome of behaviour BCT' and not this class; if recording behaviour code 'record behaviour without feedback BCT'.</t>
         </is>
       </c>
       <c r="L263" s="3" t="inlineStr">
@@ -15845,7 +15823,7 @@
       <c r="Q263" s="3" t="n"/>
       <c r="R263" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S263" s="3" t="inlineStr">
@@ -15858,33 +15836,41 @@
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007284</t>
+          <t>BCIO:007084</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>reduce distraction BCT</t>
+          <t>reduce cue frequency BCTs</t>
         </is>
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>A &lt;restructure the physical environment BCT&gt; that reduces an alternative focus for attention for the person to concentrate on internal or external states or events associated with the behaviour.</t>
+          <t>An &lt;alter external stimulus BCT&gt; in which cues for the behaviour are presented less frequently.</t>
         </is>
       </c>
       <c r="D264" s="3" t="n"/>
       <c r="E264" s="3" t="n"/>
       <c r="F264" s="3" t="inlineStr">
         <is>
-          <t>restructure the physical environment BCT</t>
-        </is>
-      </c>
-      <c r="G264" s="3" t="n"/>
-      <c r="H264" s="3" t="n"/>
+          <t>alter external stimulus BCT</t>
+        </is>
+      </c>
+      <c r="G264" s="3" t="inlineStr">
+        <is>
+          <t>BCT7.3 Reduce prompts/cues</t>
+        </is>
+      </c>
+      <c r="H264" s="3" t="inlineStr">
+        <is>
+          <t>fading</t>
+        </is>
+      </c>
       <c r="I264" s="3" t="n"/>
       <c r="J264" s="3" t="n"/>
       <c r="K264" s="3" t="inlineStr">
         <is>
-          <t>Reducing a distraction to zero is equivalent to removing a distraction</t>
+          <t>The reduction in frequency of cue presentation can be gradual or rapid. This BCT is concerned with reducing the frequency of cue presentation. In contrast, in "reduce exposure to cues for the behaviour BCT", the cue frequency may remain unchanged but the person's exposure to the presentation of the cue is reduced.</t>
         </is>
       </c>
       <c r="L264" s="3" t="inlineStr">
@@ -15916,37 +15902,33 @@
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007153</t>
+          <t>BCIO:007284</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">reduce exposure to cues for the behaviour BCT </t>
+          <t>reduce distraction BCT</t>
         </is>
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">An &lt;alter external stimulus BCT&gt; that reduces an external stimulus that signals the behaviour. </t>
+          <t>A &lt;restructure the physical environment BCT&gt; that reduces an alternative focus for attention for the person to concentrate on internal or external states or events associated with the behaviour.</t>
         </is>
       </c>
       <c r="D265" s="3" t="n"/>
       <c r="E265" s="3" t="n"/>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>alter external stimulus BCT</t>
-        </is>
-      </c>
-      <c r="G265" s="3" t="inlineStr">
-        <is>
-          <t>BCT12.3 Avoidance/reducing exposure to cues for the behaviour</t>
-        </is>
-      </c>
+          <t>restructure the physical environment BCT</t>
+        </is>
+      </c>
+      <c r="G265" s="3" t="n"/>
       <c r="H265" s="3" t="n"/>
       <c r="I265" s="3" t="n"/>
       <c r="J265" s="3" t="n"/>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>The reduction in exposure can be gradual, as in the technique of "fading" or not so gradual. This BCT is concerned with reducing the person's exposure to the cue, while the cue frequency may remain unchanged. In contrast, "reduce cue frequency BCT" is concerned with a reduction in the number of times with which the cue is presented. This BCT may also involve 'restructure the physical environment BCT' and/or 'restructure the social environment BCT'.</t>
+          <t>Reducing a distraction to zero is equivalent to removing a distraction</t>
         </is>
       </c>
       <c r="L265" s="3" t="inlineStr">
@@ -15965,147 +15947,155 @@
       <c r="Q265" s="3" t="n"/>
       <c r="R265" s="3" t="inlineStr">
         <is>
+          <t>LZ</t>
+        </is>
+      </c>
+      <c r="S265" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T265" s="3" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:007153</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reduce exposure to cues for the behaviour BCT </t>
+        </is>
+      </c>
+      <c r="C266" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An &lt;alter external stimulus BCT&gt; that reduces an external stimulus that signals the behaviour. </t>
+        </is>
+      </c>
+      <c r="D266" s="3" t="n"/>
+      <c r="E266" s="3" t="n"/>
+      <c r="F266" s="3" t="inlineStr">
+        <is>
+          <t>alter external stimulus BCT</t>
+        </is>
+      </c>
+      <c r="G266" s="3" t="inlineStr">
+        <is>
+          <t>BCT12.3 Avoidance/reducing exposure to cues for the behaviour</t>
+        </is>
+      </c>
+      <c r="H266" s="3" t="n"/>
+      <c r="I266" s="3" t="n"/>
+      <c r="J266" s="3" t="n"/>
+      <c r="K266" s="3" t="inlineStr">
+        <is>
+          <t>The reduction in exposure can be gradual, as in the technique of "fading" or not so gradual. This BCT is concerned with reducing the person's exposure to the cue, while the cue frequency may remain unchanged. In contrast, "reduce cue frequency BCT" is concerned with a reduction in the number of times with which the cue is presented. This BCT may also involve 'restructure the physical environment BCT' and/or 'restructure the social environment BCT'.</t>
+        </is>
+      </c>
+      <c r="L266" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="M266" s="3" t="n"/>
+      <c r="N266" s="3" t="n"/>
+      <c r="O266" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="P266" s="3" t="n"/>
+      <c r="Q266" s="3" t="n"/>
+      <c r="R266" s="3" t="inlineStr">
+        <is>
           <t>lz; LZ</t>
         </is>
       </c>
-      <c r="S265" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T265" s="3" t="n"/>
-    </row>
-    <row r="266">
-      <c r="A266" s="2" t="inlineStr">
+      <c r="S266" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T266" s="3" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
         <is>
           <t>BCIO:050994</t>
         </is>
       </c>
-      <c r="B266" s="2" t="inlineStr">
+      <c r="B267" s="2" t="inlineStr">
         <is>
           <t>reduce time needed to perform behaviour BCT</t>
         </is>
       </c>
-      <c r="C266" s="2" t="inlineStr">
+      <c r="C267" s="2" t="inlineStr">
         <is>
           <t>A &lt;restructure the physical environment BCT&gt; that reduces the amount of time required for the behaviour to be undertaken.</t>
         </is>
       </c>
-      <c r="D266" s="2" t="n"/>
-      <c r="E266" s="2" t="n"/>
-      <c r="F266" s="2" t="inlineStr">
+      <c r="D267" s="2" t="n"/>
+      <c r="E267" s="2" t="n"/>
+      <c r="F267" s="2" t="inlineStr">
         <is>
           <t>restructure the physical environment BCT</t>
         </is>
       </c>
-      <c r="G266" s="2" t="n"/>
-      <c r="H266" s="2" t="n"/>
-      <c r="I266" s="2" t="n"/>
-      <c r="J266" s="2" t="n"/>
-      <c r="K266" s="2" t="n"/>
-      <c r="L266" s="2" t="n"/>
-      <c r="M266" s="2" t="n"/>
-      <c r="N266" s="2" t="n"/>
-      <c r="O266" s="2" t="inlineStr">
+      <c r="G267" s="2" t="n"/>
+      <c r="H267" s="2" t="n"/>
+      <c r="I267" s="2" t="n"/>
+      <c r="J267" s="2" t="n"/>
+      <c r="K267" s="2" t="n"/>
+      <c r="L267" s="2" t="n"/>
+      <c r="M267" s="2" t="n"/>
+      <c r="N267" s="2" t="n"/>
+      <c r="O267" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="P266" s="2" t="n"/>
-      <c r="Q266" s="2" t="n"/>
-      <c r="R266" s="2" t="n"/>
-      <c r="S266" s="2" t="n">
+      <c r="P267" s="2" t="n"/>
+      <c r="Q267" s="2" t="n"/>
+      <c r="R267" s="2" t="n"/>
+      <c r="S267" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T266" s="2" t="n"/>
-    </row>
-    <row r="267">
-      <c r="A267" s="3" t="inlineStr">
-        <is>
-          <t>BCIO:007056</t>
-        </is>
-      </c>
-      <c r="B267" s="3" t="inlineStr">
-        <is>
-          <t>reframe past behaviour BCT</t>
-        </is>
-      </c>
-      <c r="C267" s="3" t="inlineStr">
-        <is>
-          <t>A &lt;suggest different perspective on behaviour BCT&gt; that involves reattributing a person's successes to internal, stable or global factors or failures to external, unstable or specific factors.</t>
-        </is>
-      </c>
-      <c r="D267" s="3" t="n"/>
-      <c r="E267" s="3" t="n"/>
-      <c r="F267" s="3" t="inlineStr">
-        <is>
-          <t>suggest different perspective on behaviour BCT</t>
-        </is>
-      </c>
-      <c r="G267" s="3" t="inlineStr">
-        <is>
-          <t>BCT13.2 Framing/reframing</t>
-        </is>
-      </c>
-      <c r="H267" s="3" t="inlineStr">
-        <is>
-          <t>cognitive re-structuring, re-attribution</t>
-        </is>
-      </c>
-      <c r="I267" s="3" t="n"/>
-      <c r="J267" s="3" t="n"/>
-      <c r="K267" s="3" t="n"/>
-      <c r="L267" s="3" t="inlineStr">
-        <is>
-          <t>behaviour change technique</t>
-        </is>
-      </c>
-      <c r="M267" s="3" t="n"/>
-      <c r="N267" s="3" t="n"/>
-      <c r="O267" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="P267" s="3" t="n"/>
-      <c r="Q267" s="3" t="n"/>
-      <c r="R267" s="3" t="inlineStr">
-        <is>
-          <t>lz; LZ</t>
-        </is>
-      </c>
-      <c r="S267" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T267" s="3" t="n"/>
+      <c r="T267" s="2" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007060</t>
+          <t>BCIO:007056</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>remind about personal capability BCT</t>
+          <t>reframe past behaviour BCT</t>
         </is>
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>A &lt;prompt thinking related to successful performance BCT&gt; that reminds the person of their skills and abilities that are relevant to the performance of the behaviour.</t>
+          <t>A &lt;suggest different perspective on behaviour BCT&gt; that involves reattributing a person's successes to internal, stable or global factors or failures to external, unstable or specific factors.</t>
         </is>
       </c>
       <c r="D268" s="3" t="n"/>
       <c r="E268" s="3" t="n"/>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>prompt thinking related to successful performance BCT</t>
-        </is>
-      </c>
-      <c r="G268" s="3" t="n"/>
-      <c r="H268" s="3" t="n"/>
+          <t>suggest different perspective on behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G268" s="3" t="inlineStr">
+        <is>
+          <t>BCT13.2 Framing/reframing</t>
+        </is>
+      </c>
+      <c r="H268" s="3" t="inlineStr">
+        <is>
+          <t>cognitive re-structuring, re-attribution</t>
+        </is>
+      </c>
       <c r="I268" s="3" t="n"/>
       <c r="J268" s="3" t="n"/>
       <c r="K268" s="3" t="n"/>
@@ -16125,7 +16115,7 @@
       <c r="Q268" s="3" t="n"/>
       <c r="R268" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S268" s="3" t="inlineStr">
@@ -16138,43 +16128,31 @@
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007286</t>
+          <t>BCIO:007060</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>remove aversive consequence for behaviour BCT</t>
+          <t>remind about personal capability BCT</t>
         </is>
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove consequence for behaviour BCT&gt; where the consequence is aversive.</t>
+          <t>A &lt;prompt thinking related to successful performance BCT&gt; that reminds the person of their skills and abilities that are relevant to the performance of the behaviour.</t>
         </is>
       </c>
       <c r="D269" s="3" t="n"/>
       <c r="E269" s="3" t="n"/>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>remove consequence for behaviour BCT</t>
-        </is>
-      </c>
-      <c r="G269" s="3" t="inlineStr">
-        <is>
-          <t>BCT14.10 Remove punishment</t>
-        </is>
-      </c>
-      <c r="H269" s="3" t="inlineStr">
-        <is>
-          <t>negative reinforcement, remove punishment</t>
-        </is>
-      </c>
+          <t>prompt thinking related to successful performance BCT</t>
+        </is>
+      </c>
+      <c r="G269" s="3" t="n"/>
+      <c r="H269" s="3" t="n"/>
       <c r="I269" s="3" t="n"/>
       <c r="J269" s="3" t="n"/>
-      <c r="K269" s="3" t="inlineStr">
-        <is>
-          <t>To qualify as aversive, the consequence should have been aversively valued by the person receiving it.</t>
-        </is>
-      </c>
+      <c r="K269" s="3" t="n"/>
       <c r="L269" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -16191,7 +16169,7 @@
       <c r="Q269" s="3" t="n"/>
       <c r="R269" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S269" s="3" t="inlineStr">
@@ -16204,27 +16182,31 @@
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007289</t>
+          <t>BCIO:007286</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>remove aversive consequence for outcome of behaviour BCT</t>
+          <t>remove aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove consequence for outcome of behaviour BCT&gt; in which the consequence is aversive.</t>
+          <t>A &lt;remove consequence for behaviour BCT&gt; where the consequence is aversive.</t>
         </is>
       </c>
       <c r="D270" s="3" t="n"/>
       <c r="E270" s="3" t="n"/>
       <c r="F270" s="3" t="inlineStr">
         <is>
-          <t>remove consequence for outcome of behaviour BCT</t>
-        </is>
-      </c>
-      <c r="G270" s="3" t="n"/>
+          <t>remove consequence for behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G270" s="3" t="inlineStr">
+        <is>
+          <t>BCT14.10 Remove punishment</t>
+        </is>
+      </c>
       <c r="H270" s="3" t="inlineStr">
         <is>
           <t>negative reinforcement, remove punishment</t>
@@ -16266,35 +16248,39 @@
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007287</t>
+          <t>BCIO:007289</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>remove aversive material consequence for behaviour BCT</t>
+          <t>remove aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove aversive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;remove consequence for outcome of behaviour BCT&gt; in which the consequence is aversive.</t>
         </is>
       </c>
       <c r="D271" s="3" t="n"/>
       <c r="E271" s="3" t="n"/>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>remove aversive consequence for behaviour BCT</t>
+          <t>remove consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="G271" s="3" t="n"/>
       <c r="H271" s="3" t="inlineStr">
         <is>
-          <t>remove material punishment</t>
+          <t>negative reinforcement, remove punishment</t>
         </is>
       </c>
       <c r="I271" s="3" t="n"/>
       <c r="J271" s="3" t="n"/>
-      <c r="K271" s="3" t="n"/>
+      <c r="K271" s="3" t="inlineStr">
+        <is>
+          <t>To qualify as aversive, the consequence should have been aversively valued by the person receiving it.</t>
+        </is>
+      </c>
       <c r="L271" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -16324,24 +16310,24 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007288</t>
+          <t>BCIO:007287</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>remove aversive material consequence for outcome of behaviour BCT</t>
+          <t>remove aversive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove aversive consequence for outcome of behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;remove aversive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D272" s="3" t="n"/>
       <c r="E272" s="3" t="n"/>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>remove aversive consequence for outcome of behaviour BCT</t>
+          <t>remove aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="G272" s="3" t="n"/>
@@ -16382,39 +16368,35 @@
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007290</t>
+          <t>BCIO:007288</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>remove aversive social consequence for behaviour BCT</t>
+          <t>remove aversive material consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove aversive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;remove aversive consequence for outcome of behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D273" s="3" t="n"/>
       <c r="E273" s="3" t="n"/>
       <c r="F273" s="3" t="inlineStr">
         <is>
-          <t>remove aversive consequence for behaviour BCT</t>
+          <t>remove aversive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="G273" s="3" t="n"/>
       <c r="H273" s="3" t="inlineStr">
         <is>
-          <t>remove social punishment</t>
+          <t>remove material punishment</t>
         </is>
       </c>
       <c r="I273" s="3" t="n"/>
       <c r="J273" s="3" t="n"/>
-      <c r="K273" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="K273" s="3" t="n"/>
       <c r="L273" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -16444,24 +16426,24 @@
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007291</t>
+          <t>BCIO:007290</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>remove aversive social consequence for outcome of behaviour BCT</t>
+          <t>remove aversive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove aversive consequence for outcome of behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;remove aversive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D274" s="3" t="n"/>
       <c r="E274" s="3" t="n"/>
       <c r="F274" s="3" t="inlineStr">
         <is>
-          <t>remove aversive consequence for outcome of behaviour BCT</t>
+          <t>remove aversive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="G274" s="3" t="n"/>
@@ -16506,39 +16488,39 @@
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
         <is>
-          <t>BCIO:050331</t>
+          <t>BCIO:007291</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>remove aversive stimulus BCT</t>
+          <t>remove aversive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>An &lt;alter external stimulus BCT&gt; that involves removing an aversive stimulus to bring about behaviour change.</t>
+          <t>A &lt;remove aversive consequence for outcome of behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D275" s="3" t="n"/>
       <c r="E275" s="3" t="n"/>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>alter external stimulus BCT</t>
-        </is>
-      </c>
-      <c r="G275" s="3" t="inlineStr">
-        <is>
-          <t>BCT7.5 Remove aversive stimulus</t>
-        </is>
-      </c>
+          <t>remove aversive consequence for outcome of behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G275" s="3" t="n"/>
       <c r="H275" s="3" t="inlineStr">
         <is>
-          <t>escape learning</t>
+          <t>remove social punishment</t>
         </is>
       </c>
       <c r="I275" s="3" t="n"/>
       <c r="J275" s="3" t="n"/>
-      <c r="K275" s="3" t="n"/>
+      <c r="K275" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="L275" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -16555,7 +16537,7 @@
       <c r="Q275" s="3" t="n"/>
       <c r="R275" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S275" s="3" t="inlineStr">
@@ -16568,28 +16550,36 @@
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007285</t>
+          <t>BCIO:050331</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>remove consequence for behaviour BCT</t>
+          <t>remove aversive stimulus BCT</t>
         </is>
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>A &lt;behavioural consequence BCT&gt; that removes a previously provided consequence for performing the behaviour.</t>
+          <t>An &lt;alter external stimulus BCT&gt; that involves removing an aversive stimulus to bring about behaviour change.</t>
         </is>
       </c>
       <c r="D276" s="3" t="n"/>
       <c r="E276" s="3" t="n"/>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>behavioural consequence BCT</t>
-        </is>
-      </c>
-      <c r="G276" s="3" t="n"/>
-      <c r="H276" s="3" t="n"/>
+          <t>alter external stimulus BCT</t>
+        </is>
+      </c>
+      <c r="G276" s="3" t="inlineStr">
+        <is>
+          <t>BCT7.5 Remove aversive stimulus</t>
+        </is>
+      </c>
+      <c r="H276" s="3" t="inlineStr">
+        <is>
+          <t>escape learning</t>
+        </is>
+      </c>
       <c r="I276" s="3" t="n"/>
       <c r="J276" s="3" t="n"/>
       <c r="K276" s="3" t="n"/>
@@ -16622,24 +16612,24 @@
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007292</t>
+          <t>BCIO:007285</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>remove consequence for outcome of behaviour BCT</t>
+          <t>remove consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>An &lt;outcome consequence BCT&gt; that removes a previously provided consequence for an outcome resulting from performing or not performing the behaviour.</t>
+          <t>A &lt;behavioural consequence BCT&gt; that removes a previously provided consequence for performing the behaviour.</t>
         </is>
       </c>
       <c r="D277" s="3" t="n"/>
       <c r="E277" s="3" t="n"/>
       <c r="F277" s="3" t="inlineStr">
         <is>
-          <t>outcome consequence BCT</t>
+          <t>behavioural consequence BCT</t>
         </is>
       </c>
       <c r="G277" s="3" t="n"/>
@@ -16674,146 +16664,138 @@
       <c r="T277" s="3" t="n"/>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="inlineStr">
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:007292</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>remove consequence for outcome of behaviour BCT</t>
+        </is>
+      </c>
+      <c r="C278" s="3" t="inlineStr">
+        <is>
+          <t>An &lt;outcome consequence BCT&gt; that removes a previously provided consequence for an outcome resulting from performing or not performing the behaviour.</t>
+        </is>
+      </c>
+      <c r="D278" s="3" t="n"/>
+      <c r="E278" s="3" t="n"/>
+      <c r="F278" s="3" t="inlineStr">
+        <is>
+          <t>outcome consequence BCT</t>
+        </is>
+      </c>
+      <c r="G278" s="3" t="n"/>
+      <c r="H278" s="3" t="n"/>
+      <c r="I278" s="3" t="n"/>
+      <c r="J278" s="3" t="n"/>
+      <c r="K278" s="3" t="n"/>
+      <c r="L278" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="M278" s="3" t="n"/>
+      <c r="N278" s="3" t="n"/>
+      <c r="O278" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="P278" s="3" t="n"/>
+      <c r="Q278" s="3" t="n"/>
+      <c r="R278" s="3" t="inlineStr">
+        <is>
+          <t>LZ</t>
+        </is>
+      </c>
+      <c r="S278" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T278" s="3" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
         <is>
           <t>BCIO:050995</t>
         </is>
       </c>
-      <c r="B278" s="2" t="inlineStr">
+      <c r="B279" s="2" t="inlineStr">
         <is>
           <t>remove objects from the environment BCT</t>
         </is>
       </c>
-      <c r="C278" s="2" t="inlineStr">
+      <c r="C279" s="2" t="inlineStr">
         <is>
           <t>A &lt;restructure the physical environment BCT&gt; that removes objects from the person’s physical surroundings.</t>
         </is>
       </c>
-      <c r="D278" s="2" t="n"/>
-      <c r="E278" s="2" t="n"/>
-      <c r="F278" s="2" t="inlineStr">
+      <c r="D279" s="2" t="n"/>
+      <c r="E279" s="2" t="n"/>
+      <c r="F279" s="2" t="inlineStr">
         <is>
           <t>restructure the physical environment BCT</t>
         </is>
       </c>
-      <c r="G278" s="2" t="n"/>
-      <c r="H278" s="2" t="n"/>
-      <c r="I278" s="2" t="n"/>
-      <c r="J278" s="2" t="n"/>
-      <c r="K278" s="2" t="inlineStr">
+      <c r="G279" s="2" t="n"/>
+      <c r="H279" s="2" t="n"/>
+      <c r="I279" s="2" t="n"/>
+      <c r="J279" s="2" t="n"/>
+      <c r="K279" s="2" t="inlineStr">
         <is>
           <t>Objects include fixed structures such as fences, as well as equipment, digital devices and interactive displays. This BCT includes removing 'virtual' buttons or other interactive elements on digital devices.</t>
         </is>
       </c>
-      <c r="L278" s="2" t="n"/>
-      <c r="M278" s="2" t="n"/>
-      <c r="N278" s="2" t="n"/>
-      <c r="O278" s="2" t="inlineStr">
+      <c r="L279" s="2" t="n"/>
+      <c r="M279" s="2" t="n"/>
+      <c r="N279" s="2" t="n"/>
+      <c r="O279" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="P278" s="2" t="n"/>
-      <c r="Q278" s="2" t="n"/>
-      <c r="R278" s="2" t="n"/>
-      <c r="S278" s="2" t="n">
+      <c r="P279" s="2" t="n"/>
+      <c r="Q279" s="2" t="n"/>
+      <c r="R279" s="2" t="n"/>
+      <c r="S279" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T278" s="2" t="n"/>
-    </row>
-    <row r="279">
-      <c r="A279" s="3" t="inlineStr">
-        <is>
-          <t>BCIO:007293</t>
-        </is>
-      </c>
-      <c r="B279" s="3" t="inlineStr">
-        <is>
-          <t>remove positive consequence for behaviour BCT</t>
-        </is>
-      </c>
-      <c r="C279" s="3" t="inlineStr">
-        <is>
-          <t>A &lt;remove consequence for behaviour BCT&gt; where the consequence is positive.</t>
-        </is>
-      </c>
-      <c r="D279" s="3" t="n"/>
-      <c r="E279" s="3" t="n"/>
-      <c r="F279" s="3" t="inlineStr">
-        <is>
-          <t>remove consequence for behaviour BCT</t>
-        </is>
-      </c>
-      <c r="G279" s="3" t="inlineStr">
-        <is>
-          <t>BCT7.4 Remove access to the reward; BCT14.1 Behaviour cost; BCT14.3 Remove reward</t>
-        </is>
-      </c>
-      <c r="H279" s="3" t="inlineStr">
-        <is>
-          <t>time out, response cost, extinction, remove reward</t>
-        </is>
-      </c>
-      <c r="I279" s="3" t="n"/>
-      <c r="J279" s="3" t="n"/>
-      <c r="K279" s="3" t="inlineStr">
-        <is>
-          <t>To qualify as positive, the consequence should have been positively valued by the person receiving it.</t>
-        </is>
-      </c>
-      <c r="L279" s="3" t="inlineStr">
-        <is>
-          <t>behaviour change technique</t>
-        </is>
-      </c>
-      <c r="M279" s="3" t="n"/>
-      <c r="N279" s="3" t="n"/>
-      <c r="O279" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="P279" s="3" t="n"/>
-      <c r="Q279" s="3" t="n"/>
-      <c r="R279" s="3" t="inlineStr">
-        <is>
-          <t>LZ</t>
-        </is>
-      </c>
-      <c r="S279" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T279" s="3" t="n"/>
+      <c r="T279" s="2" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007296</t>
+          <t>BCIO:007293</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>remove positive consequence for outcome of behaviour BCT</t>
+          <t>remove positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove consequence for outcome of behaviour BCT&gt; in which the consequence is positive.</t>
+          <t>A &lt;remove consequence for behaviour BCT&gt; where the consequence is positive.</t>
         </is>
       </c>
       <c r="D280" s="3" t="n"/>
       <c r="E280" s="3" t="n"/>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>remove consequence for outcome of behaviour BCT</t>
-        </is>
-      </c>
-      <c r="G280" s="3" t="n"/>
+          <t>remove consequence for behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G280" s="3" t="inlineStr">
+        <is>
+          <t>BCT7.4 Remove access to the reward; BCT14.1 Behaviour cost; BCT14.3 Remove reward</t>
+        </is>
+      </c>
       <c r="H280" s="3" t="inlineStr">
         <is>
-          <t>remove reward</t>
+          <t>time out, response cost, extinction, remove reward</t>
         </is>
       </c>
       <c r="I280" s="3" t="n"/>
@@ -16852,35 +16834,39 @@
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007294</t>
+          <t>BCIO:007296</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>remove positive material consequence for behaviour BCT</t>
+          <t>remove positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove positive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;remove consequence for outcome of behaviour BCT&gt; in which the consequence is positive.</t>
         </is>
       </c>
       <c r="D281" s="3" t="n"/>
       <c r="E281" s="3" t="n"/>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>remove positive consequence for behaviour BCT</t>
+          <t>remove consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="G281" s="3" t="n"/>
       <c r="H281" s="3" t="inlineStr">
         <is>
-          <t>remove material reward</t>
+          <t>remove reward</t>
         </is>
       </c>
       <c r="I281" s="3" t="n"/>
       <c r="J281" s="3" t="n"/>
-      <c r="K281" s="3" t="n"/>
+      <c r="K281" s="3" t="inlineStr">
+        <is>
+          <t>To qualify as positive, the consequence should have been positively valued by the person receiving it.</t>
+        </is>
+      </c>
       <c r="L281" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -16910,24 +16896,24 @@
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007295</t>
+          <t>BCIO:007294</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>remove positive material consequence for outcome of behaviour BCT</t>
+          <t>remove positive material consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove positive consequence for outcome of behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
+          <t>A &lt;remove positive consequence for behaviour BCT&gt; where the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D282" s="3" t="n"/>
       <c r="E282" s="3" t="n"/>
       <c r="F282" s="3" t="inlineStr">
         <is>
-          <t>remove positive consequence for outcome of behaviour BCT</t>
+          <t>remove positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="G282" s="3" t="n"/>
@@ -16968,39 +16954,35 @@
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007297</t>
+          <t>BCIO:007295</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>remove positive social consequence for behaviour BCT</t>
+          <t>remove positive material consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove positive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;remove positive consequence for outcome of behaviour BCT&gt; in which the consequence is money, vouchers or other valued objects.</t>
         </is>
       </c>
       <c r="D283" s="3" t="n"/>
       <c r="E283" s="3" t="n"/>
       <c r="F283" s="3" t="inlineStr">
         <is>
-          <t>remove positive consequence for behaviour BCT</t>
+          <t>remove positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="G283" s="3" t="n"/>
       <c r="H283" s="3" t="inlineStr">
         <is>
-          <t>remove social reward</t>
+          <t>remove material reward</t>
         </is>
       </c>
       <c r="I283" s="3" t="n"/>
       <c r="J283" s="3" t="n"/>
-      <c r="K283" s="3" t="inlineStr">
-        <is>
-          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
-        </is>
-      </c>
+      <c r="K283" s="3" t="n"/>
       <c r="L283" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -17030,24 +17012,24 @@
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007298</t>
+          <t>BCIO:007297</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>remove positive social consequence for outcome of behaviour BCT</t>
+          <t>remove positive social consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>A &lt;remove positive consequence for outcome of behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
+          <t>A &lt;remove positive consequence for behaviour BCT&gt; where the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D284" s="3" t="n"/>
       <c r="E284" s="3" t="n"/>
       <c r="F284" s="3" t="inlineStr">
         <is>
-          <t>remove positive consequence for outcome of behaviour BCT</t>
+          <t>remove positive consequence for behaviour BCT</t>
         </is>
       </c>
       <c r="G284" s="3" t="n"/>
@@ -17092,31 +17074,39 @@
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007150</t>
+          <t>BCIO:007298</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>restructure the environment BCT</t>
+          <t>remove positive social consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>A &lt;behaviour change technique&gt; that alters the environment in which the behaviour is, or would have been, performed in a way that facilitates or impedes the behaviour.</t>
+          <t>A &lt;remove positive consequence for outcome of behaviour BCT&gt; in which the consequence is an interpersonal process or a proxy interpersonal process.</t>
         </is>
       </c>
       <c r="D285" s="3" t="n"/>
       <c r="E285" s="3" t="n"/>
       <c r="F285" s="3" t="inlineStr">
         <is>
-          <t>behaviour change technique</t>
+          <t>remove positive consequence for outcome of behaviour BCT</t>
         </is>
       </c>
       <c r="G285" s="3" t="n"/>
-      <c r="H285" s="3" t="n"/>
+      <c r="H285" s="3" t="inlineStr">
+        <is>
+          <t>remove social reward</t>
+        </is>
+      </c>
       <c r="I285" s="3" t="n"/>
       <c r="J285" s="3" t="n"/>
-      <c r="K285" s="3" t="n"/>
+      <c r="K285" s="3" t="inlineStr">
+        <is>
+          <t>A proxy interpersonal process is where the person interacts with a chatbot, digital assistant, or similar computer program designed to simulate and process human communication</t>
+        </is>
+      </c>
       <c r="L285" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -17146,43 +17136,31 @@
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>BCIO:050348</t>
+          <t>BCIO:007150</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>restructure the physical environment BCT</t>
+          <t>restructure the environment BCT</t>
         </is>
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>A &lt;restructure the environment BCT&gt; that alters the physical environment in which the behaviour is, or would have been, performed in a way that facilitates or impedes the behaviour.</t>
+          <t>A &lt;behaviour change technique&gt; that alters the environment in which the behaviour is, or would have been, performed in a way that facilitates or impedes the behaviour.</t>
         </is>
       </c>
       <c r="D286" s="3" t="n"/>
       <c r="E286" s="3" t="n"/>
       <c r="F286" s="3" t="inlineStr">
         <is>
-          <t>restructure the environment BCT</t>
-        </is>
-      </c>
-      <c r="G286" s="3" t="inlineStr">
-        <is>
-          <t>BCT12.1 Restructuring the physical environment</t>
-        </is>
-      </c>
-      <c r="H286" s="3" t="inlineStr">
-        <is>
-          <t>physical space reorganisation, environmental modification</t>
-        </is>
-      </c>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="G286" s="3" t="n"/>
+      <c r="H286" s="3" t="n"/>
       <c r="I286" s="3" t="n"/>
       <c r="J286" s="3" t="n"/>
-      <c r="K286" s="3" t="inlineStr">
-        <is>
-          <t>This may also involve 'reduce exposure to cues for the behaviour BCT'</t>
-        </is>
-      </c>
+      <c r="K286" s="3" t="n"/>
       <c r="L286" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -17199,7 +17177,7 @@
       <c r="Q286" s="3" t="n"/>
       <c r="R286" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S286" s="3" t="inlineStr">
@@ -17212,17 +17190,17 @@
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>BCIO:050349</t>
+          <t>BCIO:050348</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>restructure the social environment BCT</t>
+          <t>restructure the physical environment BCT</t>
         </is>
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>A &lt;restructure the environment BCT&gt; that alters the social environment in which the behaviour is, or would have been, performed in a way that facilitates or impedes the behaviour.</t>
+          <t>A &lt;restructure the environment BCT&gt; that alters the physical environment in which the behaviour is, or would have been, performed in a way that facilitates or impedes the behaviour.</t>
         </is>
       </c>
       <c r="D287" s="3" t="n"/>
@@ -17234,20 +17212,16 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>BCT12.2 Restructuring the social environment</t>
+          <t>BCT12.1 Restructuring the physical environment</t>
         </is>
       </c>
       <c r="H287" s="3" t="inlineStr">
         <is>
-          <t>interpersonal environment restructuring, social context modification</t>
+          <t>physical space reorganisation, environmental modification</t>
         </is>
       </c>
       <c r="I287" s="3" t="n"/>
-      <c r="J287" s="3" t="inlineStr">
-        <is>
-          <t>Instructing people in a smoking cessation group to sit in a circle rather than in rows; Instructing schoolchildren to form a single file queue rather than mingle in a crowd.</t>
-        </is>
-      </c>
+      <c r="J287" s="3" t="n"/>
       <c r="K287" s="3" t="inlineStr">
         <is>
           <t>This may also involve 'reduce exposure to cues for the behaviour BCT'</t>
@@ -17282,37 +17256,45 @@
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007011</t>
+          <t>BCIO:050349</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">review behaviour goal BCT </t>
+          <t>restructure the social environment BCT</t>
         </is>
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>A &lt;goal directed BCT&gt; that reviews a behavioural goal and considers modifying the goal in light of progress toward the goal.</t>
+          <t>A &lt;restructure the environment BCT&gt; that alters the social environment in which the behaviour is, or would have been, performed in a way that facilitates or impedes the behaviour.</t>
         </is>
       </c>
       <c r="D288" s="3" t="n"/>
       <c r="E288" s="3" t="n"/>
       <c r="F288" s="3" t="inlineStr">
         <is>
-          <t>goal directed BCT</t>
+          <t>restructure the environment BCT</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>BCT1.5 Review behaviour goal(s)</t>
-        </is>
-      </c>
-      <c r="H288" s="3" t="n"/>
+          <t>BCT12.2 Restructuring the social environment</t>
+        </is>
+      </c>
+      <c r="H288" s="3" t="inlineStr">
+        <is>
+          <t>interpersonal environment restructuring, social context modification</t>
+        </is>
+      </c>
       <c r="I288" s="3" t="n"/>
-      <c r="J288" s="3" t="n"/>
+      <c r="J288" s="3" t="inlineStr">
+        <is>
+          <t>Instructing people in a smoking cessation group to sit in a circle rather than in rows; Instructing schoolchildren to form a single file queue rather than mingle in a crowd.</t>
+        </is>
+      </c>
       <c r="K288" s="3" t="inlineStr">
         <is>
-          <t>A goal is a cognitive representation of an end state towards which one is striving. If goal specified in terms of behaviour, code this class; if goal unspecified, code 'review outcome goal BCT'; if discrepancy created consider also 'attend to discrepancy between current behaviour and goal BCT'; if modifying the plan to achieve the goal consider also 'review behaviour goal plan BCT'.</t>
+          <t>This may also involve 'reduce exposure to cues for the behaviour BCT'</t>
         </is>
       </c>
       <c r="L288" s="3" t="inlineStr">
@@ -17344,17 +17326,17 @@
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007299</t>
+          <t>BCIO:007011</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">review behaviour goal plan BCT </t>
+          <t xml:space="preserve">review behaviour goal BCT </t>
         </is>
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>A &lt;goal directed BCT&gt; that reviews progress towards a behavioural goal and considers modifying the plan to achieve the goal.</t>
+          <t>A &lt;goal directed BCT&gt; that reviews a behavioural goal and considers modifying the goal in light of progress toward the goal.</t>
         </is>
       </c>
       <c r="D289" s="3" t="n"/>
@@ -17364,13 +17346,17 @@
           <t>goal directed BCT</t>
         </is>
       </c>
-      <c r="G289" s="3" t="n"/>
+      <c r="G289" s="3" t="inlineStr">
+        <is>
+          <t>BCT1.5 Review behaviour goal(s)</t>
+        </is>
+      </c>
       <c r="H289" s="3" t="n"/>
       <c r="I289" s="3" t="n"/>
       <c r="J289" s="3" t="n"/>
       <c r="K289" s="3" t="inlineStr">
         <is>
-          <t>A goal is a cognitive representation of an end state towards which one is striving.</t>
+          <t>A goal is a cognitive representation of an end state towards which one is striving. If goal specified in terms of behaviour, code this class; if goal unspecified, code 'review outcome goal BCT'; if discrepancy created consider also 'attend to discrepancy between current behaviour and goal BCT'; if modifying the plan to achieve the goal consider also 'review behaviour goal plan BCT'.</t>
         </is>
       </c>
       <c r="L289" s="3" t="inlineStr">
@@ -17389,7 +17375,7 @@
       <c r="Q289" s="3" t="n"/>
       <c r="R289" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S289" s="3" t="inlineStr">
@@ -17402,17 +17388,17 @@
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007013</t>
+          <t>BCIO:007299</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">review outcome goal BCT </t>
+          <t xml:space="preserve">review behaviour goal plan BCT </t>
         </is>
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>A &lt;goal directed BCT&gt; that reviews an outcome goal and considers modifying the goal in light of achievement.</t>
+          <t>A &lt;goal directed BCT&gt; that reviews progress towards a behavioural goal and considers modifying the plan to achieve the goal.</t>
         </is>
       </c>
       <c r="D290" s="3" t="n"/>
@@ -17422,17 +17408,13 @@
           <t>goal directed BCT</t>
         </is>
       </c>
-      <c r="G290" s="3" t="inlineStr">
-        <is>
-          <t>BCT1.7 Review outcome goal(s)</t>
-        </is>
-      </c>
+      <c r="G290" s="3" t="n"/>
       <c r="H290" s="3" t="n"/>
       <c r="I290" s="3" t="n"/>
       <c r="J290" s="3" t="n"/>
       <c r="K290" s="3" t="inlineStr">
         <is>
-          <t>A goal is a cognitive representation of an end state towards which one is striving. If goal specified in terms of behaviour, code 'review behaviour goal BCT'; if goal unspecified, code this class; if discrepancy created consider also 'attend to discrepancy between current behaviour and goal BCT'.</t>
+          <t>A goal is a cognitive representation of an end state towards which one is striving.</t>
         </is>
       </c>
       <c r="L290" s="3" t="inlineStr">
@@ -17451,7 +17433,7 @@
       <c r="Q290" s="3" t="n"/>
       <c r="R290" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S290" s="3" t="inlineStr">
@@ -17464,41 +17446,37 @@
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007024</t>
+          <t>BCIO:007013</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">self-monitor behaviour BCT </t>
+          <t xml:space="preserve">review outcome goal BCT </t>
         </is>
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>A &lt;monitoring BCT&gt; in which the person uses a method to monitor and record their behaviour.</t>
+          <t>A &lt;goal directed BCT&gt; that reviews an outcome goal and considers modifying the goal in light of achievement.</t>
         </is>
       </c>
       <c r="D291" s="3" t="n"/>
       <c r="E291" s="3" t="n"/>
       <c r="F291" s="3" t="inlineStr">
         <is>
-          <t>monitoring BCT</t>
+          <t>goal directed BCT</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>BCT2.3 Self-monitoring of behaviour</t>
-        </is>
-      </c>
-      <c r="H291" s="3" t="inlineStr">
-        <is>
-          <t>self-monitoring</t>
-        </is>
-      </c>
+          <t>BCT1.7 Review outcome goal(s)</t>
+        </is>
+      </c>
+      <c r="H291" s="3" t="n"/>
       <c r="I291" s="3" t="n"/>
       <c r="J291" s="3" t="n"/>
       <c r="K291" s="3" t="inlineStr">
         <is>
-          <t>If monitoring is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if self-monitoring of outcome of behaviour, code 'self-monitor outcome of behaviour BCT'.</t>
+          <t>A goal is a cognitive representation of an end state towards which one is striving. If goal specified in terms of behaviour, code 'review behaviour goal BCT'; if goal unspecified, code this class; if discrepancy created consider also 'attend to discrepancy between current behaviour and goal BCT'.</t>
         </is>
       </c>
       <c r="L291" s="3" t="inlineStr">
@@ -17530,17 +17508,17 @@
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007025</t>
+          <t>BCIO:007024</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">self-monitor outcome of behaviour BCT </t>
+          <t xml:space="preserve">self-monitor behaviour BCT </t>
         </is>
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>A &lt;monitoring BCT&gt; in which the person uses a method to monitor and record an outcome of their behaviour.</t>
+          <t>A &lt;monitoring BCT&gt; in which the person uses a method to monitor and record their behaviour.</t>
         </is>
       </c>
       <c r="D292" s="3" t="n"/>
@@ -17552,15 +17530,19 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>BCT2.4 Self-monitoring of outcome(s) of behaviour</t>
-        </is>
-      </c>
-      <c r="H292" s="3" t="n"/>
+          <t>BCT2.3 Self-monitoring of behaviour</t>
+        </is>
+      </c>
+      <c r="H292" s="3" t="inlineStr">
+        <is>
+          <t>self-monitoring</t>
+        </is>
+      </c>
       <c r="I292" s="3" t="n"/>
       <c r="J292" s="3" t="n"/>
       <c r="K292" s="3" t="inlineStr">
         <is>
-          <t>If monitoring is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if self-monitoring behaviour, code 'self-monitor behaviour BCT'.</t>
+          <t>If monitoring is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if self-monitoring of outcome of behaviour, code 'self-monitor outcome of behaviour BCT'.</t>
         </is>
       </c>
       <c r="L292" s="3" t="inlineStr">
@@ -17592,29 +17574,29 @@
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007003</t>
+          <t>BCIO:007025</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">set behaviour goal BCT </t>
+          <t xml:space="preserve">self-monitor outcome of behaviour BCT </t>
         </is>
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>A &lt;goal setting BCT&gt; that sets a goal for the behaviour to be achieved.</t>
+          <t>A &lt;monitoring BCT&gt; in which the person uses a method to monitor and record an outcome of their behaviour.</t>
         </is>
       </c>
       <c r="D293" s="3" t="n"/>
       <c r="E293" s="3" t="n"/>
       <c r="F293" s="3" t="inlineStr">
         <is>
-          <t>goal setting BCT</t>
+          <t>monitoring BCT</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>BCT1.1 Goal setting (behaviour)</t>
+          <t>BCT2.4 Self-monitoring of outcome(s) of behaviour</t>
         </is>
       </c>
       <c r="H293" s="3" t="n"/>
@@ -17622,7 +17604,7 @@
       <c r="J293" s="3" t="n"/>
       <c r="K293" s="3" t="inlineStr">
         <is>
-          <t>A goal is a cognitive representation of an end state towards which one is striving. The goal could be set for the self or another person. Only code if there is sufficient evidence that the goal is set as part of intervention; if goal is a behavioural outcome, code 'set outcome goal BCT'; if goal unspecified code 'goal setting BCT'; if the goal defines a specific context, frequency, duration or intensity for the behaviour, also code 'action planning BCT'.</t>
+          <t>If monitoring is part of a data collection procedure rather than a strategy aimed at changing behaviour, do not code; if self-monitoring behaviour, code 'self-monitor behaviour BCT'.</t>
         </is>
       </c>
       <c r="L293" s="3" t="inlineStr">
@@ -17654,39 +17636,39 @@
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007100</t>
+          <t>BCIO:007003</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>set graded tasks BCT</t>
+          <t xml:space="preserve">set behaviour goal BCT </t>
         </is>
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>A &lt;goal directed BCT&gt; that sets easy-to-perform tasks for the person, making them increasingly difficult, but achievable, until the behaviour is performed.</t>
+          <t>A &lt;goal setting BCT&gt; that sets a goal for the behaviour to be achieved.</t>
         </is>
       </c>
       <c r="D294" s="3" t="n"/>
       <c r="E294" s="3" t="n"/>
       <c r="F294" s="3" t="inlineStr">
         <is>
-          <t>goal directed BCT</t>
+          <t>goal setting BCT</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>BCT8.7 Graded tasks</t>
-        </is>
-      </c>
-      <c r="H294" s="3" t="inlineStr">
-        <is>
-          <t>graded tasks</t>
-        </is>
-      </c>
+          <t>BCT1.1 Goal setting (behaviour)</t>
+        </is>
+      </c>
+      <c r="H294" s="3" t="n"/>
       <c r="I294" s="3" t="n"/>
       <c r="J294" s="3" t="n"/>
-      <c r="K294" s="3" t="n"/>
+      <c r="K294" s="3" t="inlineStr">
+        <is>
+          <t>A goal is a cognitive representation of an end state towards which one is striving. The goal could be set for the self or another person. Only code if there is sufficient evidence that the goal is set as part of intervention; if goal is a behavioural outcome, code 'set outcome goal BCT'; if goal unspecified code 'goal setting BCT'; if the goal defines a specific context, frequency, duration or intensity for the behaviour, also code 'action planning BCT'.</t>
+        </is>
+      </c>
       <c r="L294" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -17716,35 +17698,39 @@
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007300</t>
+          <t>BCIO:007100</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">set measurable behaviour goal BCT </t>
+          <t>set graded tasks BCT</t>
         </is>
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>A &lt;set behaviour goal BCT&gt; that describes the behaviour to be achieved in terms of a measurable target.</t>
+          <t>A &lt;goal directed BCT&gt; that sets easy-to-perform tasks for the person, making them increasingly difficult, but achievable, until the behaviour is performed.</t>
         </is>
       </c>
       <c r="D295" s="3" t="n"/>
       <c r="E295" s="3" t="n"/>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">set behaviour goal BCT </t>
-        </is>
-      </c>
-      <c r="G295" s="3" t="n"/>
-      <c r="H295" s="3" t="n"/>
+          <t>goal directed BCT</t>
+        </is>
+      </c>
+      <c r="G295" s="3" t="inlineStr">
+        <is>
+          <t>BCT8.7 Graded tasks</t>
+        </is>
+      </c>
+      <c r="H295" s="3" t="inlineStr">
+        <is>
+          <t>graded tasks</t>
+        </is>
+      </c>
       <c r="I295" s="3" t="n"/>
       <c r="J295" s="3" t="n"/>
-      <c r="K295" s="3" t="inlineStr">
-        <is>
-          <t>A behaviour goal might be set in general terms e.g. "to do more physical activity" or in measurable terms e.g. "to do 30 minutes of physical activity five times a week" or "to walk 8000 steps a day." Use this class for measurable behaviour goals</t>
-        </is>
-      </c>
+      <c r="K295" s="3" t="n"/>
       <c r="L295" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -17761,7 +17747,7 @@
       <c r="Q295" s="3" t="n"/>
       <c r="R295" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S295" s="3" t="inlineStr">
@@ -17774,24 +17760,24 @@
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007301</t>
+          <t>BCIO:007300</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">set measurable outcome goal BCT </t>
+          <t xml:space="preserve">set measurable behaviour goal BCT </t>
         </is>
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>A &lt;set outcome goal BCT&gt; that describes the behavioural outcome to be achieved in terms of a measurable target.</t>
+          <t>A &lt;set behaviour goal BCT&gt; that describes the behaviour to be achieved in terms of a measurable target.</t>
         </is>
       </c>
       <c r="D296" s="3" t="n"/>
       <c r="E296" s="3" t="n"/>
       <c r="F296" s="3" t="inlineStr">
         <is>
-          <t>set outcome goal BCT</t>
+          <t xml:space="preserve">set behaviour goal BCT </t>
         </is>
       </c>
       <c r="G296" s="3" t="n"/>
@@ -17800,7 +17786,7 @@
       <c r="J296" s="3" t="n"/>
       <c r="K296" s="3" t="inlineStr">
         <is>
-          <t>An outcome goal might be set in general terms - e.g. "to lose weight" or in measurable terms - e.g. "to lose 5kg of weight" or "to lose 10% of my body weight". Use this class for measurable outcome goals</t>
+          <t>A behaviour goal might be set in general terms e.g. "to do more physical activity" or in measurable terms e.g. "to do 30 minutes of physical activity five times a week" or "to walk 8000 steps a day." Use this class for measurable behaviour goals</t>
         </is>
       </c>
       <c r="L296" s="3" t="inlineStr">
@@ -17832,37 +17818,33 @@
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007005</t>
+          <t>BCIO:007301</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>set outcome goal BCT</t>
+          <t xml:space="preserve">set measurable outcome goal BCT </t>
         </is>
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>A &lt;goal setting BCT&gt; in which the goal is a positive outcome of performing the behaviour.</t>
+          <t>A &lt;set outcome goal BCT&gt; that describes the behavioural outcome to be achieved in terms of a measurable target.</t>
         </is>
       </c>
       <c r="D297" s="3" t="n"/>
       <c r="E297" s="3" t="n"/>
       <c r="F297" s="3" t="inlineStr">
         <is>
-          <t>goal setting BCT</t>
-        </is>
-      </c>
-      <c r="G297" s="3" t="inlineStr">
-        <is>
-          <t>BCT1.3 Goal setting (outcome)</t>
-        </is>
-      </c>
+          <t>set outcome goal BCT</t>
+        </is>
+      </c>
+      <c r="G297" s="3" t="n"/>
       <c r="H297" s="3" t="n"/>
       <c r="I297" s="3" t="n"/>
       <c r="J297" s="3" t="n"/>
       <c r="K297" s="3" t="inlineStr">
         <is>
-          <t>A goal is a cognitive representation of an end state towards which one is striving. The goal could be set for the self or another person. Only code guidelines if set as a goal in an intervention context; if goal is a behaviour, code 'set behaviour goal BCT'; if goal unspecified code 'goal setting BCT'.</t>
+          <t>An outcome goal might be set in general terms - e.g. "to lose weight" or in measurable terms - e.g. "to lose 5kg of weight" or "to lose 10% of my body weight". Use this class for measurable outcome goals</t>
         </is>
       </c>
       <c r="L297" s="3" t="inlineStr">
@@ -17881,7 +17863,7 @@
       <c r="Q297" s="3" t="n"/>
       <c r="R297" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S297" s="3" t="inlineStr">
@@ -17894,29 +17876,29 @@
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007028</t>
+          <t>BCIO:007005</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>social support BCT</t>
+          <t>set outcome goal BCT</t>
         </is>
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>A &lt;behaviour change technique&gt; that involves taking steps to secure or deliver the support or aid of another person.</t>
+          <t>A &lt;goal setting BCT&gt; in which the goal is a positive outcome of performing the behaviour.</t>
         </is>
       </c>
       <c r="D298" s="3" t="n"/>
       <c r="E298" s="3" t="n"/>
       <c r="F298" s="3" t="inlineStr">
         <is>
-          <t>behaviour change technique</t>
+          <t>goal setting BCT</t>
         </is>
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>BCT3.1 Social support (unspecified)</t>
+          <t>BCT1.3 Goal setting (outcome)</t>
         </is>
       </c>
       <c r="H298" s="3" t="n"/>
@@ -17924,7 +17906,7 @@
       <c r="J298" s="3" t="n"/>
       <c r="K298" s="3" t="inlineStr">
         <is>
-          <t>Attending a group class and/or mention of ‘follow-up’ does not necessarily apply this BCT, support must be explicitly mentioned.</t>
+          <t>A goal is a cognitive representation of an end state towards which one is striving. The goal could be set for the self or another person. Only code guidelines if set as a goal in an intervention context; if goal is a behaviour, code 'set behaviour goal BCT'; if goal unspecified code 'goal setting BCT'.</t>
         </is>
       </c>
       <c r="L298" s="3" t="inlineStr">
@@ -17956,41 +17938,37 @@
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007095</t>
+          <t>BCIO:007028</t>
         </is>
       </c>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">substitute behaviour BCT </t>
+          <t>social support BCT</t>
         </is>
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>An &lt;advise specific behaviour BCT&gt; that advises the person to replace the unwanted behaviour with another behaviour.</t>
+          <t>A &lt;behaviour change technique&gt; that involves taking steps to secure or deliver the support or aid of another person.</t>
         </is>
       </c>
       <c r="D299" s="3" t="n"/>
       <c r="E299" s="3" t="n"/>
       <c r="F299" s="3" t="inlineStr">
         <is>
-          <t>advise specific behaviour BCT</t>
+          <t>behaviour change technique</t>
         </is>
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>BCT8.2 Behaviour substitution</t>
-        </is>
-      </c>
-      <c r="H299" s="3" t="inlineStr">
-        <is>
-          <t>behaviour replacement, alternative response</t>
-        </is>
-      </c>
+          <t>BCT3.1 Social support (unspecified)</t>
+        </is>
+      </c>
+      <c r="H299" s="3" t="n"/>
       <c r="I299" s="3" t="n"/>
       <c r="J299" s="3" t="n"/>
       <c r="K299" s="3" t="inlineStr">
         <is>
-          <t>If this occurs regularly, also code 'context-specific repetition of alternative behaviour BCT'</t>
+          <t>Attending a group class and/or mention of ‘follow-up’ does not necessarily apply this BCT, support must be explicitly mentioned.</t>
         </is>
       </c>
       <c r="L299" s="3" t="inlineStr">
@@ -18022,35 +18000,43 @@
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007302</t>
+          <t>BCIO:007095</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>suggest different perspective on behaviour BCT</t>
+          <t xml:space="preserve">substitute behaviour BCT </t>
         </is>
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A &lt;behaviour change technique&gt; that suggests the deliberate adoption of a new perspective on the behaviour. </t>
+          <t>An &lt;advise specific behaviour BCT&gt; that advises the person to replace the unwanted behaviour with another behaviour.</t>
         </is>
       </c>
       <c r="D300" s="3" t="n"/>
       <c r="E300" s="3" t="n"/>
       <c r="F300" s="3" t="inlineStr">
         <is>
-          <t>behaviour change technique</t>
-        </is>
-      </c>
-      <c r="G300" s="3" t="n"/>
+          <t>advise specific behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G300" s="3" t="inlineStr">
+        <is>
+          <t>BCT8.2 Behaviour substitution</t>
+        </is>
+      </c>
       <c r="H300" s="3" t="inlineStr">
         <is>
-          <t>cognitive reframing</t>
+          <t>behaviour replacement, alternative response</t>
         </is>
       </c>
       <c r="I300" s="3" t="n"/>
       <c r="J300" s="3" t="n"/>
-      <c r="K300" s="3" t="n"/>
+      <c r="K300" s="3" t="inlineStr">
+        <is>
+          <t>If this occurs regularly, also code 'context-specific repetition of alternative behaviour BCT'</t>
+        </is>
+      </c>
       <c r="L300" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -18080,28 +18066,32 @@
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007303</t>
+          <t>BCIO:007302</t>
         </is>
       </c>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>suggest how to perform behaviour BCT</t>
+          <t>suggest different perspective on behaviour BCT</t>
         </is>
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>A &lt;guide how to perform behaviour BCT&gt; that provides a suggestion regarding how to perform the behaviour.</t>
+          <t xml:space="preserve">A &lt;behaviour change technique&gt; that suggests the deliberate adoption of a new perspective on the behaviour. </t>
         </is>
       </c>
       <c r="D301" s="3" t="n"/>
       <c r="E301" s="3" t="n"/>
       <c r="F301" s="3" t="inlineStr">
         <is>
-          <t>guide how to perform behaviour BCT</t>
+          <t>behaviour change technique</t>
         </is>
       </c>
       <c r="G301" s="3" t="n"/>
-      <c r="H301" s="3" t="n"/>
+      <c r="H301" s="3" t="inlineStr">
+        <is>
+          <t>cognitive reframing</t>
+        </is>
+      </c>
       <c r="I301" s="3" t="n"/>
       <c r="J301" s="3" t="n"/>
       <c r="K301" s="3" t="n"/>
@@ -18121,7 +18111,7 @@
       <c r="Q301" s="3" t="n"/>
       <c r="R301" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S301" s="3" t="inlineStr">
@@ -18134,43 +18124,31 @@
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007076</t>
+          <t>BCIO:007303</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>suggest to change behaviour BCT</t>
+          <t>suggest how to perform behaviour BCT</t>
         </is>
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>An &lt;awareness of other people's thoughts, feelings and actions BCT&gt; that involves sharing a view about what behaviour the person should do.</t>
+          <t>A &lt;guide how to perform behaviour BCT&gt; that provides a suggestion regarding how to perform the behaviour.</t>
         </is>
       </c>
       <c r="D302" s="3" t="n"/>
       <c r="E302" s="3" t="n"/>
       <c r="F302" s="3" t="inlineStr">
         <is>
-          <t>awareness of other peoples thoughts, feelings and actions BCT</t>
-        </is>
-      </c>
-      <c r="G302" s="3" t="inlineStr">
-        <is>
-          <t>BCT4.5 Advise to change behaviour</t>
-        </is>
-      </c>
-      <c r="H302" s="3" t="inlineStr">
-        <is>
-          <t>encourage to change behaviour</t>
-        </is>
-      </c>
+          <t>guide how to perform behaviour BCT</t>
+        </is>
+      </c>
+      <c r="G302" s="3" t="n"/>
+      <c r="H302" s="3" t="n"/>
       <c r="I302" s="3" t="n"/>
       <c r="J302" s="3" t="n"/>
-      <c r="K302" s="3" t="inlineStr">
-        <is>
-          <t>An example of the "suggest to change behaviour BCT" would be saying to someone: "I think you should do this behaviour" whereas an example of the "Tell to change behaviour BCT" is saying "Do this behaviour". This class includes "strongly encourage".</t>
-        </is>
-      </c>
+      <c r="K302" s="3" t="n"/>
       <c r="L302" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -18200,31 +18178,43 @@
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007089</t>
+          <t>BCIO:007076</t>
         </is>
       </c>
       <c r="B303" s="3" t="inlineStr">
         <is>
-          <t>systematically desensitise BCT</t>
+          <t>suggest to change behaviour BCT</t>
         </is>
       </c>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t>An &lt;expose to stimulus BCT&gt; that gradually exposes the person to an aversive stimulus while also engaging them in a relaxation process to reduce the response to that stimulus.</t>
+          <t>An &lt;awareness of other people's thoughts, feelings and actions BCT&gt; that involves sharing a view about what behaviour the person should do.</t>
         </is>
       </c>
       <c r="D303" s="3" t="n"/>
       <c r="E303" s="3" t="n"/>
       <c r="F303" s="3" t="inlineStr">
         <is>
-          <t>expose to stimulus BCT</t>
-        </is>
-      </c>
-      <c r="G303" s="3" t="n"/>
-      <c r="H303" s="3" t="n"/>
+          <t>awareness of other peoples thoughts, feelings and actions BCT</t>
+        </is>
+      </c>
+      <c r="G303" s="3" t="inlineStr">
+        <is>
+          <t>BCT4.5 Advise to change behaviour</t>
+        </is>
+      </c>
+      <c r="H303" s="3" t="inlineStr">
+        <is>
+          <t>encourage to change behaviour</t>
+        </is>
+      </c>
       <c r="I303" s="3" t="n"/>
       <c r="J303" s="3" t="n"/>
-      <c r="K303" s="3" t="n"/>
+      <c r="K303" s="3" t="inlineStr">
+        <is>
+          <t>An example of the "suggest to change behaviour BCT" would be saying to someone: "I think you should do this behaviour" whereas an example of the "Tell to change behaviour BCT" is saying "Do this behaviour". This class includes "strongly encourage".</t>
+        </is>
+      </c>
       <c r="L303" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -18254,43 +18244,31 @@
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007077</t>
+          <t>BCIO:007089</t>
         </is>
       </c>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>tell to change behaviour BCT</t>
+          <t>systematically desensitise BCT</t>
         </is>
       </c>
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t>An &lt;awareness of other people's thoughts, feelings and actions BCT&gt; that involves telling the person to perform the behaviour.</t>
+          <t>An &lt;expose to stimulus BCT&gt; that gradually exposes the person to an aversive stimulus while also engaging them in a relaxation process to reduce the response to that stimulus.</t>
         </is>
       </c>
       <c r="D304" s="3" t="n"/>
       <c r="E304" s="3" t="n"/>
       <c r="F304" s="3" t="inlineStr">
         <is>
-          <t>awareness of other peoples thoughts, feelings and actions BCT</t>
-        </is>
-      </c>
-      <c r="G304" s="3" t="inlineStr">
-        <is>
-          <t>BCT4.5 Advise to change behaviour</t>
-        </is>
-      </c>
-      <c r="H304" s="3" t="inlineStr">
-        <is>
-          <t>instruct, command</t>
-        </is>
-      </c>
+          <t>expose to stimulus BCT</t>
+        </is>
+      </c>
+      <c r="G304" s="3" t="n"/>
+      <c r="H304" s="3" t="n"/>
       <c r="I304" s="3" t="n"/>
       <c r="J304" s="3" t="n"/>
-      <c r="K304" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">An example of the "Tell to change behaviour BCT" is saying "Do this behaviour" whereas an example of the "suggest to change behaviour BCT" would be saying to someone: "I think you should do this behaviour." </t>
-        </is>
-      </c>
+      <c r="K304" s="3" t="n"/>
       <c r="L304" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -18307,7 +18285,7 @@
       <c r="Q304" s="3" t="n"/>
       <c r="R304" s="3" t="inlineStr">
         <is>
-          <t>lz; LZ</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="S304" s="3" t="inlineStr">
@@ -18320,35 +18298,43 @@
     <row r="305">
       <c r="A305" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007121</t>
+          <t>BCIO:007077</t>
         </is>
       </c>
       <c r="B305" s="3" t="inlineStr">
         <is>
-          <t>vicarious punishment BCT</t>
+          <t>tell to change behaviour BCT</t>
         </is>
       </c>
       <c r="C305" s="3" t="inlineStr">
         <is>
-          <t>An &lt;increase awareness of consequences BCT&gt; that prompts observation of another person being punished when they perform the behaviour.</t>
+          <t>An &lt;awareness of other people's thoughts, feelings and actions BCT&gt; that involves telling the person to perform the behaviour.</t>
         </is>
       </c>
       <c r="D305" s="3" t="n"/>
       <c r="E305" s="3" t="n"/>
       <c r="F305" s="3" t="inlineStr">
         <is>
-          <t>increase awareness of consequences BCT</t>
+          <t>awareness of other peoples thoughts, feelings and actions BCT</t>
         </is>
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>BCT16.3 Vicarious consequences</t>
-        </is>
-      </c>
-      <c r="H305" s="3" t="n"/>
+          <t>BCT4.5 Advise to change behaviour</t>
+        </is>
+      </c>
+      <c r="H305" s="3" t="inlineStr">
+        <is>
+          <t>instruct, command</t>
+        </is>
+      </c>
       <c r="I305" s="3" t="n"/>
       <c r="J305" s="3" t="n"/>
-      <c r="K305" s="3" t="n"/>
+      <c r="K305" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An example of the "Tell to change behaviour BCT" is saying "Do this behaviour" whereas an example of the "suggest to change behaviour BCT" would be saying to someone: "I think you should do this behaviour." </t>
+        </is>
+      </c>
       <c r="L305" s="3" t="inlineStr">
         <is>
           <t>behaviour change technique</t>
@@ -18365,7 +18351,7 @@
       <c r="Q305" s="3" t="n"/>
       <c r="R305" s="3" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>lz; LZ</t>
         </is>
       </c>
       <c r="S305" s="3" t="inlineStr">
@@ -18378,17 +18364,17 @@
     <row r="306">
       <c r="A306" s="3" t="inlineStr">
         <is>
-          <t>BCIO:007120</t>
+          <t>BCIO:007121</t>
         </is>
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">vicarious reward BCT </t>
+          <t>vicarious punishment BCT</t>
         </is>
       </c>
       <c r="C306" s="3" t="inlineStr">
         <is>
-          <t>An &lt;increase awareness of consequences BCT&gt; that prompts observation of another person being rewarded when they perform the behaviour.</t>
+          <t>An &lt;increase awareness of consequences BCT&gt; that prompts observation of another person being punished when they perform the behaviour.</t>
         </is>
       </c>
       <c r="D306" s="3" t="n"/>
@@ -18403,11 +18389,7 @@
           <t>BCT16.3 Vicarious consequences</t>
         </is>
       </c>
-      <c r="H306" s="3" t="inlineStr">
-        <is>
-          <t>vicarious reinforcement</t>
-        </is>
-      </c>
+      <c r="H306" s="3" t="n"/>
       <c r="I306" s="3" t="n"/>
       <c r="J306" s="3" t="n"/>
       <c r="K306" s="3" t="n"/>
@@ -18427,15 +18409,77 @@
       <c r="Q306" s="3" t="n"/>
       <c r="R306" s="3" t="inlineStr">
         <is>
+          <t>LZ</t>
+        </is>
+      </c>
+      <c r="S306" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T306" s="3" t="n"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:007120</t>
+        </is>
+      </c>
+      <c r="B307" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vicarious reward BCT </t>
+        </is>
+      </c>
+      <c r="C307" s="3" t="inlineStr">
+        <is>
+          <t>An &lt;increase awareness of consequences BCT&gt; that prompts observation of another person being rewarded when they perform the behaviour.</t>
+        </is>
+      </c>
+      <c r="D307" s="3" t="n"/>
+      <c r="E307" s="3" t="n"/>
+      <c r="F307" s="3" t="inlineStr">
+        <is>
+          <t>increase awareness of consequences BCT</t>
+        </is>
+      </c>
+      <c r="G307" s="3" t="inlineStr">
+        <is>
+          <t>BCT16.3 Vicarious consequences</t>
+        </is>
+      </c>
+      <c r="H307" s="3" t="inlineStr">
+        <is>
+          <t>vicarious reinforcement</t>
+        </is>
+      </c>
+      <c r="I307" s="3" t="n"/>
+      <c r="J307" s="3" t="n"/>
+      <c r="K307" s="3" t="n"/>
+      <c r="L307" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change technique</t>
+        </is>
+      </c>
+      <c r="M307" s="3" t="n"/>
+      <c r="N307" s="3" t="n"/>
+      <c r="O307" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="P307" s="3" t="n"/>
+      <c r="Q307" s="3" t="n"/>
+      <c r="R307" s="3" t="inlineStr">
+        <is>
           <t>lz; LZ</t>
         </is>
       </c>
-      <c r="S306" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T306" s="3" t="n"/>
+      <c r="S307" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T307" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
